--- a/jo.xlsx
+++ b/jo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\production_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9185BDB-8E51-448C-916A-E225539A50BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4F5433C-7247-42DA-B299-53B9E62F6A4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -383,7 +383,7 @@
     <t>YBE-Y</t>
   </si>
   <si>
-    <t>MMA H248 ENGINE</t>
+    <t>MMA H248 MAIN L/R HD</t>
   </si>
 </sst>
 </file>
@@ -2226,28 +2226,333 @@
     <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="61" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="34" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="35" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="40" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="57" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="36" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="37" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="50" fillId="0" borderId="34" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="50" fillId="0" borderId="35" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="50" fillId="0" borderId="40" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="50" fillId="0" borderId="57" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="50" fillId="0" borderId="36" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="50" fillId="0" borderId="37" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="44" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="45" fillId="0" borderId="31" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="41" fillId="0" borderId="34" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="41" fillId="0" borderId="42" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="40" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="36" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="44" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="51" xfId="0" applyBorder="1"/>
+    <xf numFmtId="49" fontId="42" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="55" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="24" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="55" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="60" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="24" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="62" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="58" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="60" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
+    <xf numFmtId="49" fontId="27" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="59" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="52" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="53" xfId="0" applyBorder="1"/>
+    <xf numFmtId="3" fontId="48" fillId="0" borderId="54" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="64" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="64" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="41" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="17" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="38" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="57" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1"/>
+    <xf numFmtId="43" fontId="60" fillId="0" borderId="5" xfId="26" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="44" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="20" xfId="26" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="33" fillId="0" borderId="65" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="72" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="73" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="68" fillId="0" borderId="20" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="41" fillId="0" borderId="43" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="40" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="41" fillId="0" borderId="41" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="36" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="44" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="41" fillId="0" borderId="45" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2261,19 +2566,6 @@
     <xf numFmtId="0" fontId="56" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="56" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="56" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="48" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2291,12 +2583,6 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="63" fillId="7" borderId="65" xfId="26" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2309,12 +2595,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="34" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2323,12 +2603,9 @@
     <xf numFmtId="0" fontId="62" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2353,285 +2630,8 @@
     <xf numFmtId="0" fontId="41" fillId="0" borderId="68" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="55" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="44" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="20" xfId="26" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="52" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="53" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="33" fillId="0" borderId="65" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="72" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="73" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="68" fillId="0" borderId="20" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="64" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="64" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" applyBorder="1"/>
-    <xf numFmtId="3" fontId="41" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="17" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="38" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="57" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="60" fillId="0" borderId="5" xfId="26" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="48" fillId="0" borderId="54" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" xfId="0" applyBorder="1"/>
-    <xf numFmtId="3" fontId="60" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="24" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="62" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="58" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="60" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="27" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="59" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="45" fillId="0" borderId="31" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="51" xfId="0" applyBorder="1"/>
-    <xf numFmtId="49" fontId="42" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="24" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="55" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="61" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="34" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="35" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="40" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="57" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="36" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="37" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="50" fillId="0" borderId="34" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="50" fillId="0" borderId="35" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="50" fillId="0" borderId="40" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="50" fillId="0" borderId="57" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="50" fillId="0" borderId="36" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="50" fillId="0" borderId="37" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="59" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="59" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="44" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="29">
@@ -2976,70 +2976,70 @@
       <c r="A1" s="1">
         <v>24</v>
       </c>
-      <c r="B1" s="296"/>
-      <c r="C1" s="297"/>
-      <c r="D1" s="234" t="s">
+      <c r="B1" s="138"/>
+      <c r="C1" s="139"/>
+      <c r="D1" s="243" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="147" t="s">
+      <c r="E1" s="278" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="148"/>
-      <c r="G1" s="148"/>
-      <c r="H1" s="148"/>
-      <c r="I1" s="148"/>
-      <c r="J1" s="148"/>
-      <c r="K1" s="148"/>
-      <c r="L1" s="148"/>
-      <c r="M1" s="148"/>
-      <c r="N1" s="149"/>
-      <c r="O1" s="164" t="s">
+      <c r="F1" s="279"/>
+      <c r="G1" s="279"/>
+      <c r="H1" s="279"/>
+      <c r="I1" s="279"/>
+      <c r="J1" s="279"/>
+      <c r="K1" s="279"/>
+      <c r="L1" s="279"/>
+      <c r="M1" s="279"/>
+      <c r="N1" s="280"/>
+      <c r="O1" s="288" t="s">
         <v>2</v>
       </c>
-      <c r="P1" s="165"/>
-      <c r="Q1" s="165"/>
-      <c r="R1" s="165"/>
-      <c r="S1" s="165"/>
-      <c r="T1" s="165"/>
-      <c r="U1" s="166"/>
+      <c r="P1" s="289"/>
+      <c r="Q1" s="289"/>
+      <c r="R1" s="289"/>
+      <c r="S1" s="289"/>
+      <c r="T1" s="289"/>
+      <c r="U1" s="290"/>
     </row>
     <row r="2" spans="1:22" s="1" customFormat="1" ht="18.75" customHeight="1">
-      <c r="B2" s="236"/>
-      <c r="C2" s="188"/>
-      <c r="D2" s="232"/>
-      <c r="E2" s="150"/>
-      <c r="F2" s="151"/>
-      <c r="G2" s="151"/>
-      <c r="H2" s="151"/>
-      <c r="I2" s="151"/>
-      <c r="J2" s="151"/>
-      <c r="K2" s="151"/>
-      <c r="L2" s="151"/>
-      <c r="M2" s="151"/>
-      <c r="N2" s="152"/>
-      <c r="O2" s="167"/>
-      <c r="P2" s="168"/>
-      <c r="Q2" s="168"/>
-      <c r="R2" s="168"/>
-      <c r="S2" s="168"/>
-      <c r="T2" s="168"/>
-      <c r="U2" s="169"/>
+      <c r="B2" s="140"/>
+      <c r="C2" s="141"/>
+      <c r="D2" s="244"/>
+      <c r="E2" s="281"/>
+      <c r="F2" s="282"/>
+      <c r="G2" s="282"/>
+      <c r="H2" s="282"/>
+      <c r="I2" s="282"/>
+      <c r="J2" s="282"/>
+      <c r="K2" s="282"/>
+      <c r="L2" s="282"/>
+      <c r="M2" s="282"/>
+      <c r="N2" s="283"/>
+      <c r="O2" s="291"/>
+      <c r="P2" s="292"/>
+      <c r="Q2" s="292"/>
+      <c r="R2" s="292"/>
+      <c r="S2" s="292"/>
+      <c r="T2" s="292"/>
+      <c r="U2" s="293"/>
     </row>
     <row r="3" spans="1:22" ht="12.45" customHeight="1">
-      <c r="B3" s="236"/>
-      <c r="C3" s="188"/>
-      <c r="D3" s="259" t="s">
+      <c r="B3" s="140"/>
+      <c r="C3" s="141"/>
+      <c r="D3" s="157" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="170" t="s">
+      <c r="E3" s="294" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="171"/>
-      <c r="G3" s="171"/>
-      <c r="H3" s="171"/>
-      <c r="I3" s="171"/>
-      <c r="J3" s="171"/>
-      <c r="K3" s="171"/>
+      <c r="F3" s="186"/>
+      <c r="G3" s="186"/>
+      <c r="H3" s="186"/>
+      <c r="I3" s="186"/>
+      <c r="J3" s="186"/>
+      <c r="K3" s="186"/>
       <c r="L3" s="128"/>
       <c r="M3" s="5"/>
       <c r="N3" s="5"/>
@@ -3052,49 +3052,49 @@
       <c r="U3" s="129"/>
     </row>
     <row r="4" spans="1:22" ht="14.85" customHeight="1">
-      <c r="B4" s="236"/>
-      <c r="C4" s="188"/>
-      <c r="D4" s="154"/>
-      <c r="E4" s="172"/>
-      <c r="F4" s="173"/>
-      <c r="G4" s="173"/>
-      <c r="H4" s="173"/>
-      <c r="I4" s="173"/>
-      <c r="J4" s="173"/>
-      <c r="K4" s="174"/>
+      <c r="B4" s="140"/>
+      <c r="C4" s="141"/>
+      <c r="D4" s="153"/>
+      <c r="E4" s="159"/>
+      <c r="F4" s="187"/>
+      <c r="G4" s="187"/>
+      <c r="H4" s="187"/>
+      <c r="I4" s="187"/>
+      <c r="J4" s="187"/>
+      <c r="K4" s="265"/>
       <c r="L4" s="130"/>
       <c r="U4" s="131"/>
     </row>
     <row r="5" spans="1:22" ht="14.85" customHeight="1">
-      <c r="B5" s="217"/>
-      <c r="C5" s="186"/>
-      <c r="D5" s="155"/>
-      <c r="E5" s="175"/>
-      <c r="F5" s="176"/>
-      <c r="G5" s="176"/>
-      <c r="H5" s="176"/>
-      <c r="I5" s="176"/>
-      <c r="J5" s="176"/>
-      <c r="K5" s="176"/>
+      <c r="B5" s="142"/>
+      <c r="C5" s="143"/>
+      <c r="D5" s="154"/>
+      <c r="E5" s="151"/>
+      <c r="F5" s="188"/>
+      <c r="G5" s="188"/>
+      <c r="H5" s="188"/>
+      <c r="I5" s="188"/>
+      <c r="J5" s="188"/>
+      <c r="K5" s="188"/>
       <c r="L5" s="130"/>
       <c r="U5" s="131"/>
     </row>
     <row r="6" spans="1:22" s="2" customFormat="1" ht="27.75" customHeight="1">
-      <c r="B6" s="247" t="s">
+      <c r="B6" s="149" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="185"/>
-      <c r="D6" s="317"/>
-      <c r="E6" s="215" t="s">
+      <c r="C6" s="145"/>
+      <c r="D6" s="177"/>
+      <c r="E6" s="264" t="s">
         <v>6</v>
       </c>
-      <c r="F6" s="171"/>
-      <c r="G6" s="171"/>
-      <c r="H6" s="185"/>
-      <c r="I6" s="213" t="s">
+      <c r="F6" s="186"/>
+      <c r="G6" s="186"/>
+      <c r="H6" s="145"/>
+      <c r="I6" s="262" t="s">
         <v>7</v>
       </c>
-      <c r="J6" s="157"/>
+      <c r="J6" s="148"/>
       <c r="K6" s="102" t="s">
         <v>8</v>
       </c>
@@ -3102,55 +3102,55 @@
       <c r="U6" s="131"/>
     </row>
     <row r="7" spans="1:22" s="2" customFormat="1" ht="28.5" customHeight="1">
-      <c r="B7" s="217"/>
-      <c r="C7" s="186"/>
-      <c r="D7" s="155"/>
-      <c r="E7" s="172"/>
-      <c r="F7" s="174"/>
-      <c r="G7" s="174"/>
-      <c r="H7" s="188"/>
-      <c r="I7" s="214"/>
-      <c r="J7" s="157"/>
+      <c r="B7" s="142"/>
+      <c r="C7" s="143"/>
+      <c r="D7" s="154"/>
+      <c r="E7" s="159"/>
+      <c r="F7" s="265"/>
+      <c r="G7" s="265"/>
+      <c r="H7" s="141"/>
+      <c r="I7" s="263"/>
+      <c r="J7" s="148"/>
       <c r="K7" s="103"/>
       <c r="L7" s="130"/>
       <c r="P7" s="135"/>
       <c r="U7" s="131"/>
     </row>
     <row r="8" spans="1:22" s="2" customFormat="1" ht="31.95" customHeight="1">
-      <c r="B8" s="247" t="s">
+      <c r="B8" s="149" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="185"/>
-      <c r="D8" s="242"/>
-      <c r="E8" s="301" t="s">
+      <c r="C8" s="145"/>
+      <c r="D8" s="250"/>
+      <c r="E8" s="161" t="s">
         <v>102</v>
       </c>
-      <c r="F8" s="302"/>
-      <c r="G8" s="307" t="s">
+      <c r="F8" s="162"/>
+      <c r="G8" s="167" t="s">
         <v>101</v>
       </c>
-      <c r="H8" s="308"/>
-      <c r="I8" s="263" t="s">
+      <c r="H8" s="168"/>
+      <c r="I8" s="215" t="s">
         <v>104</v>
       </c>
-      <c r="J8" s="264"/>
-      <c r="K8" s="228"/>
+      <c r="J8" s="216"/>
+      <c r="K8" s="271"/>
       <c r="L8" s="130"/>
       <c r="P8" s="135"/>
       <c r="U8" s="131"/>
       <c r="V8" s="101"/>
     </row>
     <row r="9" spans="1:22" s="2" customFormat="1" ht="3.75" hidden="1" customHeight="1">
-      <c r="B9" s="217"/>
-      <c r="C9" s="186"/>
-      <c r="D9" s="175"/>
-      <c r="E9" s="303"/>
-      <c r="F9" s="304"/>
-      <c r="G9" s="309"/>
-      <c r="H9" s="310"/>
-      <c r="I9" s="265"/>
-      <c r="J9" s="266"/>
-      <c r="K9" s="229"/>
+      <c r="B9" s="142"/>
+      <c r="C9" s="143"/>
+      <c r="D9" s="151"/>
+      <c r="E9" s="163"/>
+      <c r="F9" s="164"/>
+      <c r="G9" s="169"/>
+      <c r="H9" s="170"/>
+      <c r="I9" s="217"/>
+      <c r="J9" s="218"/>
+      <c r="K9" s="272"/>
       <c r="L9" s="130"/>
       <c r="P9" s="135" t="str">
         <f t="shared" ref="P9" si="0">"*"&amp;J18&amp;"*"</f>
@@ -3160,34 +3160,34 @@
       <c r="V9" s="101"/>
     </row>
     <row r="10" spans="1:22" s="2" customFormat="1" ht="15" customHeight="1">
-      <c r="B10" s="254" t="s">
+      <c r="B10" s="259" t="s">
         <v>11</v>
       </c>
-      <c r="C10" s="185"/>
-      <c r="D10" s="231"/>
-      <c r="E10" s="305"/>
-      <c r="F10" s="306"/>
-      <c r="G10" s="311"/>
-      <c r="H10" s="312"/>
-      <c r="I10" s="265"/>
-      <c r="J10" s="266"/>
-      <c r="K10" s="229"/>
+      <c r="C10" s="145"/>
+      <c r="D10" s="274"/>
+      <c r="E10" s="165"/>
+      <c r="F10" s="166"/>
+      <c r="G10" s="171"/>
+      <c r="H10" s="172"/>
+      <c r="I10" s="217"/>
+      <c r="J10" s="218"/>
+      <c r="K10" s="272"/>
       <c r="L10" s="130"/>
       <c r="P10" s="135"/>
       <c r="U10" s="131"/>
       <c r="V10" s="101"/>
     </row>
     <row r="11" spans="1:22" s="2" customFormat="1" ht="78.599999999999994" customHeight="1">
-      <c r="B11" s="217"/>
-      <c r="C11" s="186"/>
-      <c r="D11" s="232"/>
-      <c r="E11" s="313"/>
-      <c r="F11" s="314"/>
-      <c r="G11" s="315"/>
-      <c r="H11" s="316"/>
-      <c r="I11" s="267"/>
-      <c r="J11" s="268"/>
-      <c r="K11" s="230"/>
+      <c r="B11" s="142"/>
+      <c r="C11" s="143"/>
+      <c r="D11" s="244"/>
+      <c r="E11" s="173"/>
+      <c r="F11" s="174"/>
+      <c r="G11" s="175"/>
+      <c r="H11" s="176"/>
+      <c r="I11" s="219"/>
+      <c r="J11" s="220"/>
+      <c r="K11" s="273"/>
       <c r="L11" s="130"/>
       <c r="M11" s="136" t="str">
         <f>"*"&amp;J16&amp;"*"</f>
@@ -3202,68 +3202,68 @@
       <c r="V11" s="101"/>
     </row>
     <row r="12" spans="1:22" s="2" customFormat="1" ht="28.5" customHeight="1">
-      <c r="B12" s="318" t="s">
+      <c r="B12" s="179" t="s">
         <v>12</v>
       </c>
-      <c r="C12" s="185"/>
-      <c r="D12" s="249" t="s">
+      <c r="C12" s="145"/>
+      <c r="D12" s="256" t="s">
         <v>103</v>
       </c>
-      <c r="E12" s="284"/>
-      <c r="F12" s="171"/>
-      <c r="G12" s="171"/>
-      <c r="H12" s="185"/>
-      <c r="I12" s="189" t="s">
+      <c r="E12" s="185"/>
+      <c r="F12" s="186"/>
+      <c r="G12" s="186"/>
+      <c r="H12" s="145"/>
+      <c r="I12" s="303" t="s">
         <v>13</v>
       </c>
-      <c r="J12" s="190"/>
-      <c r="K12" s="291"/>
+      <c r="J12" s="304"/>
+      <c r="K12" s="204"/>
       <c r="L12" s="130"/>
       <c r="U12" s="131"/>
     </row>
     <row r="13" spans="1:22" s="2" customFormat="1" ht="13.5" customHeight="1">
-      <c r="B13" s="217"/>
-      <c r="C13" s="186"/>
-      <c r="D13" s="250"/>
-      <c r="E13" s="172"/>
-      <c r="F13" s="173"/>
-      <c r="G13" s="173"/>
-      <c r="H13" s="188"/>
-      <c r="I13" s="191"/>
-      <c r="J13" s="192"/>
-      <c r="K13" s="172"/>
+      <c r="B13" s="142"/>
+      <c r="C13" s="143"/>
+      <c r="D13" s="214"/>
+      <c r="E13" s="159"/>
+      <c r="F13" s="187"/>
+      <c r="G13" s="187"/>
+      <c r="H13" s="141"/>
+      <c r="I13" s="305"/>
+      <c r="J13" s="306"/>
+      <c r="K13" s="159"/>
       <c r="L13" s="130"/>
       <c r="U13" s="131"/>
     </row>
     <row r="14" spans="1:22" s="2" customFormat="1" ht="15" customHeight="1">
-      <c r="B14" s="285" t="s">
+      <c r="B14" s="189" t="s">
         <v>14</v>
       </c>
-      <c r="C14" s="185"/>
-      <c r="D14" s="262" t="s">
+      <c r="C14" s="145"/>
+      <c r="D14" s="213" t="s">
         <v>108</v>
       </c>
-      <c r="E14" s="172"/>
-      <c r="F14" s="173"/>
-      <c r="G14" s="173"/>
-      <c r="H14" s="188"/>
-      <c r="I14" s="191"/>
-      <c r="J14" s="192"/>
-      <c r="K14" s="172"/>
+      <c r="E14" s="159"/>
+      <c r="F14" s="187"/>
+      <c r="G14" s="187"/>
+      <c r="H14" s="141"/>
+      <c r="I14" s="305"/>
+      <c r="J14" s="306"/>
+      <c r="K14" s="159"/>
       <c r="L14" s="130"/>
       <c r="U14" s="131"/>
     </row>
     <row r="15" spans="1:22" s="2" customFormat="1" ht="48" customHeight="1">
-      <c r="B15" s="217"/>
-      <c r="C15" s="186"/>
-      <c r="D15" s="250"/>
-      <c r="E15" s="175"/>
-      <c r="F15" s="176"/>
-      <c r="G15" s="176"/>
-      <c r="H15" s="186"/>
-      <c r="I15" s="193"/>
-      <c r="J15" s="194"/>
-      <c r="K15" s="175"/>
+      <c r="B15" s="142"/>
+      <c r="C15" s="143"/>
+      <c r="D15" s="214"/>
+      <c r="E15" s="151"/>
+      <c r="F15" s="188"/>
+      <c r="G15" s="188"/>
+      <c r="H15" s="143"/>
+      <c r="I15" s="307"/>
+      <c r="J15" s="308"/>
+      <c r="K15" s="151"/>
       <c r="L15" s="132"/>
       <c r="M15" s="133"/>
       <c r="N15" s="133"/>
@@ -3276,145 +3276,145 @@
       <c r="U15" s="134"/>
     </row>
     <row r="16" spans="1:22" s="2" customFormat="1" ht="15" customHeight="1">
-      <c r="B16" s="247" t="s">
+      <c r="B16" s="149" t="s">
         <v>15</v>
       </c>
-      <c r="C16" s="185"/>
-      <c r="D16" s="269"/>
-      <c r="E16" s="248" t="s">
+      <c r="C16" s="145"/>
+      <c r="D16" s="221"/>
+      <c r="E16" s="200" t="s">
         <v>16</v>
       </c>
-      <c r="F16" s="171"/>
-      <c r="G16" s="171"/>
-      <c r="H16" s="171"/>
-      <c r="I16" s="185"/>
-      <c r="J16" s="218">
+      <c r="F16" s="186"/>
+      <c r="G16" s="186"/>
+      <c r="H16" s="186"/>
+      <c r="I16" s="145"/>
+      <c r="J16" s="267">
         <v>232323</v>
       </c>
-      <c r="K16" s="219"/>
-      <c r="L16" s="138" t="s">
+      <c r="K16" s="253"/>
+      <c r="L16" s="192" t="s">
         <v>105</v>
       </c>
-      <c r="M16" s="139"/>
-      <c r="N16" s="139"/>
-      <c r="O16" s="139"/>
-      <c r="P16" s="139"/>
-      <c r="Q16" s="139"/>
-      <c r="R16" s="139"/>
-      <c r="S16" s="138" t="s">
+      <c r="M16" s="193"/>
+      <c r="N16" s="193"/>
+      <c r="O16" s="193"/>
+      <c r="P16" s="193"/>
+      <c r="Q16" s="193"/>
+      <c r="R16" s="193"/>
+      <c r="S16" s="192" t="s">
         <v>106</v>
       </c>
-      <c r="T16" s="139"/>
-      <c r="U16" s="140"/>
+      <c r="T16" s="193"/>
+      <c r="U16" s="275"/>
     </row>
     <row r="17" spans="2:22" s="2" customFormat="1" ht="15" customHeight="1">
-      <c r="B17" s="217"/>
-      <c r="C17" s="186"/>
-      <c r="D17" s="250"/>
-      <c r="E17" s="172"/>
-      <c r="F17" s="173"/>
-      <c r="G17" s="173"/>
-      <c r="H17" s="173"/>
-      <c r="I17" s="188"/>
-      <c r="J17" s="172"/>
-      <c r="K17" s="220"/>
-      <c r="L17" s="141"/>
-      <c r="M17" s="142"/>
-      <c r="N17" s="142"/>
-      <c r="O17" s="142"/>
-      <c r="P17" s="142"/>
-      <c r="Q17" s="142"/>
-      <c r="R17" s="142"/>
-      <c r="S17" s="141"/>
-      <c r="T17" s="142"/>
-      <c r="U17" s="143"/>
+      <c r="B17" s="142"/>
+      <c r="C17" s="143"/>
+      <c r="D17" s="214"/>
+      <c r="E17" s="159"/>
+      <c r="F17" s="187"/>
+      <c r="G17" s="187"/>
+      <c r="H17" s="187"/>
+      <c r="I17" s="141"/>
+      <c r="J17" s="159"/>
+      <c r="K17" s="268"/>
+      <c r="L17" s="194"/>
+      <c r="M17" s="195"/>
+      <c r="N17" s="195"/>
+      <c r="O17" s="195"/>
+      <c r="P17" s="195"/>
+      <c r="Q17" s="195"/>
+      <c r="R17" s="195"/>
+      <c r="S17" s="194"/>
+      <c r="T17" s="195"/>
+      <c r="U17" s="276"/>
     </row>
     <row r="18" spans="2:22" s="2" customFormat="1" ht="15" customHeight="1">
-      <c r="B18" s="298" t="s">
+      <c r="B18" s="146" t="s">
         <v>17</v>
       </c>
-      <c r="C18" s="185"/>
-      <c r="D18" s="240" t="s">
+      <c r="C18" s="145"/>
+      <c r="D18" s="248" t="s">
         <v>109</v>
       </c>
-      <c r="E18" s="172"/>
-      <c r="F18" s="173"/>
-      <c r="G18" s="173"/>
-      <c r="H18" s="173"/>
-      <c r="I18" s="188"/>
-      <c r="J18" s="172"/>
-      <c r="K18" s="220"/>
-      <c r="L18" s="141"/>
-      <c r="M18" s="142"/>
-      <c r="N18" s="142"/>
-      <c r="O18" s="142"/>
-      <c r="P18" s="142"/>
-      <c r="Q18" s="142"/>
-      <c r="R18" s="142"/>
-      <c r="S18" s="141"/>
-      <c r="T18" s="142"/>
-      <c r="U18" s="143"/>
+      <c r="E18" s="159"/>
+      <c r="F18" s="187"/>
+      <c r="G18" s="187"/>
+      <c r="H18" s="187"/>
+      <c r="I18" s="141"/>
+      <c r="J18" s="159"/>
+      <c r="K18" s="268"/>
+      <c r="L18" s="194"/>
+      <c r="M18" s="195"/>
+      <c r="N18" s="195"/>
+      <c r="O18" s="195"/>
+      <c r="P18" s="195"/>
+      <c r="Q18" s="195"/>
+      <c r="R18" s="195"/>
+      <c r="S18" s="194"/>
+      <c r="T18" s="195"/>
+      <c r="U18" s="276"/>
     </row>
     <row r="19" spans="2:22" s="2" customFormat="1" ht="15" customHeight="1">
-      <c r="B19" s="217"/>
-      <c r="C19" s="186"/>
-      <c r="D19" s="241"/>
-      <c r="E19" s="175"/>
-      <c r="F19" s="176"/>
-      <c r="G19" s="176"/>
-      <c r="H19" s="176"/>
-      <c r="I19" s="186"/>
-      <c r="J19" s="175"/>
-      <c r="K19" s="221"/>
-      <c r="L19" s="144"/>
-      <c r="M19" s="145"/>
-      <c r="N19" s="145"/>
-      <c r="O19" s="145"/>
-      <c r="P19" s="145"/>
-      <c r="Q19" s="145"/>
-      <c r="R19" s="145"/>
-      <c r="S19" s="144"/>
-      <c r="T19" s="145"/>
-      <c r="U19" s="146"/>
+      <c r="B19" s="142"/>
+      <c r="C19" s="143"/>
+      <c r="D19" s="249"/>
+      <c r="E19" s="151"/>
+      <c r="F19" s="188"/>
+      <c r="G19" s="188"/>
+      <c r="H19" s="188"/>
+      <c r="I19" s="143"/>
+      <c r="J19" s="151"/>
+      <c r="K19" s="255"/>
+      <c r="L19" s="196"/>
+      <c r="M19" s="197"/>
+      <c r="N19" s="197"/>
+      <c r="O19" s="197"/>
+      <c r="P19" s="197"/>
+      <c r="Q19" s="197"/>
+      <c r="R19" s="197"/>
+      <c r="S19" s="196"/>
+      <c r="T19" s="197"/>
+      <c r="U19" s="277"/>
     </row>
     <row r="20" spans="2:22" s="2" customFormat="1" ht="15" customHeight="1">
-      <c r="B20" s="247" t="s">
+      <c r="B20" s="149" t="s">
         <v>18</v>
       </c>
-      <c r="C20" s="185"/>
-      <c r="D20" s="255"/>
-      <c r="E20" s="248" t="s">
+      <c r="C20" s="145"/>
+      <c r="D20" s="260"/>
+      <c r="E20" s="200" t="s">
         <v>107</v>
       </c>
-      <c r="F20" s="171"/>
-      <c r="G20" s="171"/>
-      <c r="H20" s="171"/>
-      <c r="I20" s="185"/>
-      <c r="J20" s="244"/>
-      <c r="K20" s="219"/>
-      <c r="L20" s="205"/>
-      <c r="M20" s="206"/>
-      <c r="N20" s="206"/>
-      <c r="O20" s="206"/>
-      <c r="P20" s="206"/>
-      <c r="Q20" s="206"/>
-      <c r="R20" s="206"/>
-      <c r="S20" s="206"/>
-      <c r="T20" s="206"/>
-      <c r="U20" s="206"/>
+      <c r="F20" s="186"/>
+      <c r="G20" s="186"/>
+      <c r="H20" s="186"/>
+      <c r="I20" s="145"/>
+      <c r="J20" s="252"/>
+      <c r="K20" s="253"/>
+      <c r="L20" s="316"/>
+      <c r="M20" s="317"/>
+      <c r="N20" s="317"/>
+      <c r="O20" s="317"/>
+      <c r="P20" s="317"/>
+      <c r="Q20" s="317"/>
+      <c r="R20" s="317"/>
+      <c r="S20" s="317"/>
+      <c r="T20" s="317"/>
+      <c r="U20" s="317"/>
       <c r="V20" s="122"/>
     </row>
     <row r="21" spans="2:22" s="2" customFormat="1" ht="62.4" customHeight="1">
-      <c r="B21" s="217"/>
-      <c r="C21" s="186"/>
-      <c r="D21" s="155"/>
-      <c r="E21" s="172"/>
-      <c r="F21" s="173"/>
-      <c r="G21" s="173"/>
-      <c r="H21" s="173"/>
-      <c r="I21" s="188"/>
-      <c r="J21" s="172"/>
-      <c r="K21" s="245"/>
+      <c r="B21" s="142"/>
+      <c r="C21" s="143"/>
+      <c r="D21" s="154"/>
+      <c r="E21" s="159"/>
+      <c r="F21" s="187"/>
+      <c r="G21" s="187"/>
+      <c r="H21" s="187"/>
+      <c r="I21" s="141"/>
+      <c r="J21" s="159"/>
+      <c r="K21" s="254"/>
       <c r="L21" s="123"/>
       <c r="M21" s="124"/>
       <c r="N21" s="124"/>
@@ -3428,79 +3428,79 @@
       <c r="V21" s="122"/>
     </row>
     <row r="22" spans="2:22" s="2" customFormat="1" ht="15" customHeight="1">
-      <c r="B22" s="247" t="s">
+      <c r="B22" s="149" t="s">
         <v>19</v>
       </c>
-      <c r="C22" s="185"/>
-      <c r="D22" s="212"/>
-      <c r="E22" s="172"/>
-      <c r="F22" s="173"/>
-      <c r="G22" s="173"/>
-      <c r="H22" s="173"/>
-      <c r="I22" s="188"/>
-      <c r="J22" s="172"/>
-      <c r="K22" s="245"/>
-      <c r="L22" s="199"/>
-      <c r="M22" s="199"/>
-      <c r="N22" s="199"/>
-      <c r="O22" s="199"/>
-      <c r="P22" s="199"/>
-      <c r="Q22" s="199"/>
-      <c r="R22" s="199"/>
-      <c r="S22" s="199"/>
-      <c r="T22" s="199"/>
-      <c r="U22" s="200"/>
+      <c r="C22" s="145"/>
+      <c r="D22" s="261"/>
+      <c r="E22" s="159"/>
+      <c r="F22" s="187"/>
+      <c r="G22" s="187"/>
+      <c r="H22" s="187"/>
+      <c r="I22" s="141"/>
+      <c r="J22" s="159"/>
+      <c r="K22" s="254"/>
+      <c r="L22" s="310"/>
+      <c r="M22" s="310"/>
+      <c r="N22" s="310"/>
+      <c r="O22" s="310"/>
+      <c r="P22" s="310"/>
+      <c r="Q22" s="310"/>
+      <c r="R22" s="310"/>
+      <c r="S22" s="310"/>
+      <c r="T22" s="310"/>
+      <c r="U22" s="311"/>
     </row>
     <row r="23" spans="2:22" s="2" customFormat="1" ht="15" customHeight="1">
-      <c r="B23" s="236"/>
-      <c r="C23" s="188"/>
-      <c r="D23" s="154"/>
-      <c r="E23" s="172"/>
-      <c r="F23" s="173"/>
-      <c r="G23" s="173"/>
-      <c r="H23" s="173"/>
-      <c r="I23" s="188"/>
-      <c r="J23" s="172"/>
-      <c r="K23" s="245"/>
-      <c r="L23" s="201"/>
-      <c r="M23" s="201"/>
-      <c r="N23" s="201"/>
-      <c r="O23" s="201"/>
-      <c r="P23" s="201"/>
-      <c r="Q23" s="201"/>
-      <c r="R23" s="201"/>
-      <c r="S23" s="201"/>
-      <c r="T23" s="201"/>
-      <c r="U23" s="202"/>
+      <c r="B23" s="140"/>
+      <c r="C23" s="141"/>
+      <c r="D23" s="153"/>
+      <c r="E23" s="159"/>
+      <c r="F23" s="187"/>
+      <c r="G23" s="187"/>
+      <c r="H23" s="187"/>
+      <c r="I23" s="141"/>
+      <c r="J23" s="159"/>
+      <c r="K23" s="254"/>
+      <c r="L23" s="312"/>
+      <c r="M23" s="312"/>
+      <c r="N23" s="312"/>
+      <c r="O23" s="312"/>
+      <c r="P23" s="312"/>
+      <c r="Q23" s="312"/>
+      <c r="R23" s="312"/>
+      <c r="S23" s="312"/>
+      <c r="T23" s="312"/>
+      <c r="U23" s="313"/>
     </row>
     <row r="24" spans="2:22" s="2" customFormat="1" ht="7.5" customHeight="1">
-      <c r="B24" s="217"/>
-      <c r="C24" s="186"/>
-      <c r="D24" s="155"/>
-      <c r="E24" s="175"/>
-      <c r="F24" s="176"/>
-      <c r="G24" s="176"/>
-      <c r="H24" s="176"/>
-      <c r="I24" s="186"/>
-      <c r="J24" s="175"/>
-      <c r="K24" s="221"/>
-      <c r="L24" s="203"/>
-      <c r="M24" s="203"/>
-      <c r="N24" s="203"/>
-      <c r="O24" s="203"/>
-      <c r="P24" s="203"/>
-      <c r="Q24" s="203"/>
-      <c r="R24" s="203"/>
-      <c r="S24" s="203"/>
-      <c r="T24" s="203"/>
-      <c r="U24" s="204"/>
+      <c r="B24" s="142"/>
+      <c r="C24" s="143"/>
+      <c r="D24" s="154"/>
+      <c r="E24" s="151"/>
+      <c r="F24" s="188"/>
+      <c r="G24" s="188"/>
+      <c r="H24" s="188"/>
+      <c r="I24" s="143"/>
+      <c r="J24" s="151"/>
+      <c r="K24" s="255"/>
+      <c r="L24" s="314"/>
+      <c r="M24" s="314"/>
+      <c r="N24" s="314"/>
+      <c r="O24" s="314"/>
+      <c r="P24" s="314"/>
+      <c r="Q24" s="314"/>
+      <c r="R24" s="314"/>
+      <c r="S24" s="314"/>
+      <c r="T24" s="314"/>
+      <c r="U24" s="315"/>
     </row>
     <row r="25" spans="2:22" s="2" customFormat="1" ht="30" customHeight="1">
-      <c r="B25" s="216" t="s">
+      <c r="B25" s="266" t="s">
         <v>20</v>
       </c>
-      <c r="C25" s="171"/>
-      <c r="D25" s="185"/>
+      <c r="C25" s="186"/>
+      <c r="D25" s="145"/>
       <c r="E25" s="3" t="s">
         <v>21</v>
       </c>
@@ -3516,21 +3516,21 @@
       <c r="K25" s="104" t="s">
         <v>24</v>
       </c>
-      <c r="L25" s="207" t="s">
+      <c r="L25" s="212" t="s">
         <v>25</v>
       </c>
-      <c r="M25" s="188"/>
-      <c r="N25" s="187" t="s">
+      <c r="M25" s="141"/>
+      <c r="N25" s="211" t="s">
         <v>26</v>
       </c>
-      <c r="O25" s="188"/>
+      <c r="O25" s="141"/>
       <c r="P25" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="Q25" s="187" t="s">
+      <c r="Q25" s="211" t="s">
         <v>28</v>
       </c>
-      <c r="R25" s="188"/>
+      <c r="R25" s="141"/>
       <c r="S25" s="7" t="s">
         <v>29</v>
       </c>
@@ -3542,9 +3542,9 @@
       </c>
     </row>
     <row r="26" spans="2:22" s="2" customFormat="1" ht="39" customHeight="1">
-      <c r="B26" s="217"/>
-      <c r="C26" s="176"/>
-      <c r="D26" s="186"/>
+      <c r="B26" s="142"/>
+      <c r="C26" s="188"/>
+      <c r="D26" s="143"/>
       <c r="E26" s="10"/>
       <c r="F26" s="11"/>
       <c r="G26" s="12"/>
@@ -3552,19 +3552,19 @@
       <c r="I26" s="12"/>
       <c r="J26" s="11"/>
       <c r="K26" s="13"/>
-      <c r="L26" s="175"/>
-      <c r="M26" s="186"/>
-      <c r="N26" s="207" t="s">
+      <c r="L26" s="151"/>
+      <c r="M26" s="143"/>
+      <c r="N26" s="212" t="s">
         <v>31</v>
       </c>
-      <c r="O26" s="186"/>
+      <c r="O26" s="143"/>
       <c r="P26" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="Q26" s="207" t="s">
+      <c r="Q26" s="212" t="s">
         <v>33</v>
       </c>
-      <c r="R26" s="186"/>
+      <c r="R26" s="143"/>
       <c r="S26" s="14" t="s">
         <v>34</v>
       </c>
@@ -3576,11 +3576,11 @@
       </c>
     </row>
     <row r="27" spans="2:22" s="2" customFormat="1" ht="46.05" customHeight="1">
-      <c r="B27" s="216" t="s">
+      <c r="B27" s="266" t="s">
         <v>36</v>
       </c>
-      <c r="C27" s="171"/>
-      <c r="D27" s="185"/>
+      <c r="C27" s="186"/>
+      <c r="D27" s="145"/>
       <c r="E27" s="3" t="s">
         <v>21</v>
       </c>
@@ -3594,25 +3594,25 @@
       </c>
       <c r="J27" s="5"/>
       <c r="K27" s="6"/>
-      <c r="L27" s="292" t="s">
+      <c r="L27" s="205" t="s">
         <v>39</v>
       </c>
       <c r="M27" s="120" t="s">
         <v>9</v>
       </c>
-      <c r="N27" s="299"/>
-      <c r="O27" s="300"/>
+      <c r="N27" s="155"/>
+      <c r="O27" s="156"/>
       <c r="P27" s="93"/>
-      <c r="Q27" s="222"/>
-      <c r="R27" s="157"/>
+      <c r="Q27" s="231"/>
+      <c r="R27" s="148"/>
       <c r="S27" s="17"/>
       <c r="T27" s="18"/>
       <c r="U27" s="19"/>
     </row>
     <row r="28" spans="2:22" s="2" customFormat="1" ht="46.05" customHeight="1">
-      <c r="B28" s="217"/>
-      <c r="C28" s="176"/>
-      <c r="D28" s="186"/>
+      <c r="B28" s="142"/>
+      <c r="C28" s="188"/>
+      <c r="D28" s="143"/>
       <c r="E28" s="20"/>
       <c r="F28" s="21"/>
       <c r="G28" s="21"/>
@@ -3620,62 +3620,62 @@
       <c r="I28" s="22"/>
       <c r="J28" s="22"/>
       <c r="K28" s="23"/>
-      <c r="L28" s="210"/>
+      <c r="L28" s="206"/>
       <c r="M28" s="120" t="s">
         <v>40</v>
       </c>
-      <c r="N28" s="223"/>
-      <c r="O28" s="224"/>
+      <c r="N28" s="269"/>
+      <c r="O28" s="270"/>
       <c r="P28" s="93"/>
-      <c r="Q28" s="222"/>
-      <c r="R28" s="157"/>
+      <c r="Q28" s="231"/>
+      <c r="R28" s="148"/>
       <c r="S28" s="17"/>
       <c r="T28" s="18"/>
       <c r="U28" s="19"/>
     </row>
     <row r="29" spans="2:22" s="2" customFormat="1" ht="46.5" customHeight="1">
-      <c r="B29" s="235" t="s">
+      <c r="B29" s="245" t="s">
         <v>41</v>
       </c>
-      <c r="C29" s="171"/>
-      <c r="D29" s="185"/>
-      <c r="E29" s="246" t="s">
+      <c r="C29" s="186"/>
+      <c r="D29" s="145"/>
+      <c r="E29" s="198" t="s">
         <v>42</v>
       </c>
-      <c r="F29" s="171"/>
-      <c r="G29" s="171"/>
-      <c r="H29" s="171"/>
-      <c r="I29" s="171"/>
-      <c r="J29" s="171"/>
-      <c r="K29" s="185"/>
-      <c r="L29" s="211"/>
+      <c r="F29" s="186"/>
+      <c r="G29" s="186"/>
+      <c r="H29" s="186"/>
+      <c r="I29" s="186"/>
+      <c r="J29" s="186"/>
+      <c r="K29" s="145"/>
+      <c r="L29" s="207"/>
       <c r="M29" s="121" t="s">
         <v>43</v>
       </c>
-      <c r="N29" s="223"/>
-      <c r="O29" s="224"/>
+      <c r="N29" s="269"/>
+      <c r="O29" s="270"/>
       <c r="P29" s="94"/>
-      <c r="Q29" s="222"/>
-      <c r="R29" s="157"/>
+      <c r="Q29" s="231"/>
+      <c r="R29" s="148"/>
       <c r="S29" s="25"/>
       <c r="T29" s="5"/>
       <c r="U29" s="26"/>
     </row>
     <row r="30" spans="2:22" s="2" customFormat="1" ht="15" customHeight="1">
-      <c r="B30" s="236"/>
-      <c r="C30" s="173"/>
-      <c r="D30" s="188"/>
-      <c r="E30" s="175"/>
-      <c r="F30" s="176"/>
-      <c r="G30" s="176"/>
-      <c r="H30" s="176"/>
-      <c r="I30" s="176"/>
-      <c r="J30" s="176"/>
-      <c r="K30" s="186"/>
-      <c r="L30" s="209" t="s">
+      <c r="B30" s="140"/>
+      <c r="C30" s="187"/>
+      <c r="D30" s="141"/>
+      <c r="E30" s="151"/>
+      <c r="F30" s="188"/>
+      <c r="G30" s="188"/>
+      <c r="H30" s="188"/>
+      <c r="I30" s="188"/>
+      <c r="J30" s="188"/>
+      <c r="K30" s="143"/>
+      <c r="L30" s="318" t="s">
         <v>44</v>
       </c>
-      <c r="M30" s="251" t="s">
+      <c r="M30" s="182" t="s">
         <v>45</v>
       </c>
       <c r="N30" s="27"/>
@@ -3688,121 +3688,121 @@
       <c r="U30" s="26"/>
     </row>
     <row r="31" spans="2:22" s="2" customFormat="1" ht="42" customHeight="1">
-      <c r="B31" s="217"/>
-      <c r="C31" s="176"/>
-      <c r="D31" s="186"/>
-      <c r="E31" s="246" t="s">
+      <c r="B31" s="142"/>
+      <c r="C31" s="188"/>
+      <c r="D31" s="143"/>
+      <c r="E31" s="198" t="s">
         <v>46</v>
       </c>
-      <c r="F31" s="159"/>
-      <c r="G31" s="159"/>
-      <c r="H31" s="159"/>
-      <c r="I31" s="159"/>
-      <c r="J31" s="159"/>
-      <c r="K31" s="157"/>
-      <c r="L31" s="210"/>
-      <c r="M31" s="155"/>
-      <c r="N31" s="243"/>
-      <c r="O31" s="186"/>
+      <c r="F31" s="181"/>
+      <c r="G31" s="181"/>
+      <c r="H31" s="181"/>
+      <c r="I31" s="181"/>
+      <c r="J31" s="181"/>
+      <c r="K31" s="148"/>
+      <c r="L31" s="206"/>
+      <c r="M31" s="154"/>
+      <c r="N31" s="251"/>
+      <c r="O31" s="143"/>
       <c r="P31" s="98"/>
-      <c r="Q31" s="155"/>
-      <c r="R31" s="186"/>
+      <c r="Q31" s="154"/>
+      <c r="R31" s="143"/>
       <c r="S31" s="31"/>
       <c r="T31" s="31"/>
       <c r="U31" s="32"/>
     </row>
     <row r="32" spans="2:22" s="2" customFormat="1" ht="21" customHeight="1">
-      <c r="B32" s="256" t="s">
+      <c r="B32" s="235" t="s">
         <v>47</v>
       </c>
-      <c r="C32" s="171"/>
-      <c r="D32" s="171"/>
-      <c r="E32" s="171"/>
-      <c r="F32" s="171"/>
-      <c r="G32" s="171"/>
-      <c r="H32" s="171"/>
-      <c r="I32" s="171"/>
-      <c r="J32" s="171"/>
-      <c r="K32" s="185"/>
-      <c r="L32" s="210"/>
-      <c r="M32" s="251" t="s">
+      <c r="C32" s="186"/>
+      <c r="D32" s="186"/>
+      <c r="E32" s="186"/>
+      <c r="F32" s="186"/>
+      <c r="G32" s="186"/>
+      <c r="H32" s="186"/>
+      <c r="I32" s="186"/>
+      <c r="J32" s="186"/>
+      <c r="K32" s="145"/>
+      <c r="L32" s="206"/>
+      <c r="M32" s="182" t="s">
         <v>48</v>
       </c>
-      <c r="N32" s="184"/>
-      <c r="O32" s="185"/>
+      <c r="N32" s="302"/>
+      <c r="O32" s="145"/>
       <c r="P32" s="97"/>
-      <c r="Q32" s="208"/>
-      <c r="R32" s="185"/>
+      <c r="Q32" s="144"/>
+      <c r="R32" s="145"/>
       <c r="S32" s="33"/>
       <c r="T32" s="33"/>
       <c r="U32" s="34"/>
     </row>
     <row r="33" spans="1:22" s="2" customFormat="1" ht="21" customHeight="1">
-      <c r="B33" s="217"/>
-      <c r="C33" s="176"/>
-      <c r="D33" s="176"/>
-      <c r="E33" s="176"/>
-      <c r="F33" s="176"/>
-      <c r="G33" s="176"/>
-      <c r="H33" s="176"/>
-      <c r="I33" s="176"/>
-      <c r="J33" s="176"/>
-      <c r="K33" s="186"/>
-      <c r="L33" s="210"/>
-      <c r="M33" s="155"/>
-      <c r="N33" s="288"/>
-      <c r="O33" s="186"/>
+      <c r="B33" s="142"/>
+      <c r="C33" s="188"/>
+      <c r="D33" s="188"/>
+      <c r="E33" s="188"/>
+      <c r="F33" s="188"/>
+      <c r="G33" s="188"/>
+      <c r="H33" s="188"/>
+      <c r="I33" s="188"/>
+      <c r="J33" s="188"/>
+      <c r="K33" s="143"/>
+      <c r="L33" s="206"/>
+      <c r="M33" s="154"/>
+      <c r="N33" s="201"/>
+      <c r="O33" s="143"/>
       <c r="P33" s="100"/>
-      <c r="Q33" s="287"/>
-      <c r="R33" s="186"/>
+      <c r="Q33" s="199"/>
+      <c r="R33" s="143"/>
       <c r="S33" s="36"/>
       <c r="T33" s="36"/>
       <c r="U33" s="32"/>
     </row>
     <row r="34" spans="1:22" s="2" customFormat="1" ht="21" customHeight="1">
-      <c r="B34" s="293" t="s">
+      <c r="B34" s="208" t="s">
         <v>49</v>
       </c>
-      <c r="C34" s="171"/>
-      <c r="D34" s="171"/>
-      <c r="E34" s="171"/>
-      <c r="F34" s="171"/>
-      <c r="G34" s="171"/>
-      <c r="H34" s="171"/>
-      <c r="I34" s="171"/>
-      <c r="J34" s="171"/>
-      <c r="K34" s="185"/>
-      <c r="L34" s="210"/>
-      <c r="M34" s="251" t="s">
+      <c r="C34" s="186"/>
+      <c r="D34" s="186"/>
+      <c r="E34" s="186"/>
+      <c r="F34" s="186"/>
+      <c r="G34" s="186"/>
+      <c r="H34" s="186"/>
+      <c r="I34" s="186"/>
+      <c r="J34" s="186"/>
+      <c r="K34" s="145"/>
+      <c r="L34" s="206"/>
+      <c r="M34" s="182" t="s">
         <v>50</v>
       </c>
-      <c r="N34" s="208"/>
-      <c r="O34" s="185"/>
+      <c r="N34" s="144"/>
+      <c r="O34" s="145"/>
       <c r="P34" s="24"/>
-      <c r="Q34" s="208"/>
-      <c r="R34" s="185"/>
+      <c r="Q34" s="144"/>
+      <c r="R34" s="145"/>
       <c r="S34" s="25"/>
       <c r="T34" s="25"/>
       <c r="U34" s="26"/>
     </row>
     <row r="35" spans="1:22" s="2" customFormat="1" ht="21" customHeight="1">
-      <c r="B35" s="217"/>
-      <c r="C35" s="176"/>
-      <c r="D35" s="176"/>
-      <c r="E35" s="176"/>
-      <c r="F35" s="176"/>
-      <c r="G35" s="176"/>
-      <c r="H35" s="176"/>
-      <c r="I35" s="176"/>
-      <c r="J35" s="176"/>
-      <c r="K35" s="186"/>
-      <c r="L35" s="210"/>
-      <c r="M35" s="155"/>
-      <c r="N35" s="155"/>
-      <c r="O35" s="186"/>
+      <c r="B35" s="142"/>
+      <c r="C35" s="188"/>
+      <c r="D35" s="188"/>
+      <c r="E35" s="188"/>
+      <c r="F35" s="188"/>
+      <c r="G35" s="188"/>
+      <c r="H35" s="188"/>
+      <c r="I35" s="188"/>
+      <c r="J35" s="188"/>
+      <c r="K35" s="143"/>
+      <c r="L35" s="206"/>
+      <c r="M35" s="154"/>
+      <c r="N35" s="154"/>
+      <c r="O35" s="143"/>
       <c r="P35" s="35"/>
-      <c r="Q35" s="155"/>
-      <c r="R35" s="186"/>
+      <c r="Q35" s="154"/>
+      <c r="R35" s="143"/>
       <c r="S35" s="36"/>
       <c r="T35" s="36"/>
       <c r="U35" s="32"/>
@@ -3812,103 +3812,103 @@
         <v>51</v>
       </c>
       <c r="C36" s="38"/>
-      <c r="D36" s="237"/>
-      <c r="E36" s="171"/>
-      <c r="F36" s="171"/>
-      <c r="G36" s="171"/>
-      <c r="H36" s="171"/>
-      <c r="I36" s="171"/>
-      <c r="J36" s="171"/>
-      <c r="K36" s="185"/>
-      <c r="L36" s="210"/>
-      <c r="M36" s="251" t="s">
+      <c r="D36" s="246"/>
+      <c r="E36" s="186"/>
+      <c r="F36" s="186"/>
+      <c r="G36" s="186"/>
+      <c r="H36" s="186"/>
+      <c r="I36" s="186"/>
+      <c r="J36" s="186"/>
+      <c r="K36" s="145"/>
+      <c r="L36" s="206"/>
+      <c r="M36" s="182" t="s">
         <v>52</v>
       </c>
-      <c r="N36" s="208"/>
-      <c r="O36" s="185"/>
+      <c r="N36" s="144"/>
+      <c r="O36" s="145"/>
       <c r="P36" s="24"/>
-      <c r="Q36" s="208"/>
-      <c r="R36" s="185"/>
+      <c r="Q36" s="144"/>
+      <c r="R36" s="145"/>
       <c r="S36" s="25"/>
       <c r="T36" s="25"/>
       <c r="U36" s="26"/>
     </row>
     <row r="37" spans="1:22" s="2" customFormat="1" ht="49.2" customHeight="1">
-      <c r="B37" s="294" t="s">
+      <c r="B37" s="209" t="s">
         <v>53</v>
       </c>
-      <c r="C37" s="159"/>
+      <c r="C37" s="181"/>
       <c r="D37" s="127" t="s">
         <v>54</v>
       </c>
-      <c r="E37" s="286" t="s">
+      <c r="E37" s="190" t="s">
         <v>55</v>
       </c>
-      <c r="F37" s="159"/>
-      <c r="G37" s="239"/>
+      <c r="F37" s="181"/>
+      <c r="G37" s="191"/>
       <c r="H37" s="115" t="s">
         <v>56</v>
       </c>
-      <c r="I37" s="289" t="s">
+      <c r="I37" s="202" t="s">
         <v>57</v>
       </c>
-      <c r="J37" s="290"/>
+      <c r="J37" s="203"/>
       <c r="K37" s="116" t="s">
         <v>58</v>
       </c>
-      <c r="L37" s="210"/>
-      <c r="M37" s="155"/>
-      <c r="N37" s="155"/>
-      <c r="O37" s="186"/>
+      <c r="L37" s="206"/>
+      <c r="M37" s="154"/>
+      <c r="N37" s="154"/>
+      <c r="O37" s="143"/>
       <c r="P37" s="35"/>
-      <c r="Q37" s="155"/>
-      <c r="R37" s="186"/>
+      <c r="Q37" s="154"/>
+      <c r="R37" s="143"/>
       <c r="S37" s="36"/>
       <c r="T37" s="36"/>
       <c r="U37" s="32"/>
     </row>
     <row r="38" spans="1:22" s="2" customFormat="1" ht="24.6" customHeight="1">
-      <c r="B38" s="238"/>
-      <c r="C38" s="239"/>
-      <c r="D38" s="260"/>
-      <c r="E38" s="177"/>
-      <c r="F38" s="178"/>
-      <c r="G38" s="179"/>
-      <c r="H38" s="257"/>
-      <c r="I38" s="160"/>
-      <c r="J38" s="161"/>
-      <c r="K38" s="282"/>
-      <c r="L38" s="210"/>
-      <c r="M38" s="251" t="s">
+      <c r="B38" s="247"/>
+      <c r="C38" s="191"/>
+      <c r="D38" s="241"/>
+      <c r="E38" s="295"/>
+      <c r="F38" s="296"/>
+      <c r="G38" s="297"/>
+      <c r="H38" s="236"/>
+      <c r="I38" s="284"/>
+      <c r="J38" s="285"/>
+      <c r="K38" s="183"/>
+      <c r="L38" s="206"/>
+      <c r="M38" s="182" t="s">
         <v>59</v>
       </c>
-      <c r="N38" s="208"/>
-      <c r="O38" s="185"/>
+      <c r="N38" s="144"/>
+      <c r="O38" s="145"/>
       <c r="P38" s="24"/>
-      <c r="Q38" s="208"/>
-      <c r="R38" s="185"/>
+      <c r="Q38" s="144"/>
+      <c r="R38" s="145"/>
       <c r="S38" s="25"/>
       <c r="T38" s="25"/>
       <c r="U38" s="26"/>
     </row>
     <row r="39" spans="1:22" s="2" customFormat="1" ht="22.95" customHeight="1">
-      <c r="B39" s="295"/>
-      <c r="C39" s="239"/>
-      <c r="D39" s="261"/>
-      <c r="E39" s="180"/>
-      <c r="F39" s="181"/>
-      <c r="G39" s="182"/>
-      <c r="H39" s="258"/>
-      <c r="I39" s="162"/>
-      <c r="J39" s="163"/>
-      <c r="K39" s="283"/>
-      <c r="L39" s="210"/>
-      <c r="M39" s="155"/>
-      <c r="N39" s="155"/>
-      <c r="O39" s="186"/>
+      <c r="B39" s="210"/>
+      <c r="C39" s="191"/>
+      <c r="D39" s="242"/>
+      <c r="E39" s="298"/>
+      <c r="F39" s="299"/>
+      <c r="G39" s="300"/>
+      <c r="H39" s="237"/>
+      <c r="I39" s="286"/>
+      <c r="J39" s="287"/>
+      <c r="K39" s="184"/>
+      <c r="L39" s="206"/>
+      <c r="M39" s="154"/>
+      <c r="N39" s="154"/>
+      <c r="O39" s="143"/>
       <c r="P39" s="35"/>
-      <c r="Q39" s="155"/>
-      <c r="R39" s="186"/>
+      <c r="Q39" s="154"/>
+      <c r="R39" s="143"/>
       <c r="S39" s="36"/>
       <c r="T39" s="36"/>
       <c r="U39" s="32"/>
@@ -3917,24 +3917,24 @@
       <c r="A40" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="B40" s="281"/>
-      <c r="C40" s="159"/>
-      <c r="D40" s="157"/>
-      <c r="E40" s="253"/>
-      <c r="F40" s="159"/>
-      <c r="G40" s="157"/>
-      <c r="H40" s="252"/>
-      <c r="I40" s="186"/>
+      <c r="B40" s="180"/>
+      <c r="C40" s="181"/>
+      <c r="D40" s="148"/>
+      <c r="E40" s="258"/>
+      <c r="F40" s="181"/>
+      <c r="G40" s="148"/>
+      <c r="H40" s="257"/>
+      <c r="I40" s="143"/>
       <c r="K40" s="99"/>
-      <c r="L40" s="210"/>
-      <c r="M40" s="251" t="s">
+      <c r="L40" s="206"/>
+      <c r="M40" s="182" t="s">
         <v>61</v>
       </c>
-      <c r="N40" s="208"/>
-      <c r="O40" s="185"/>
+      <c r="N40" s="144"/>
+      <c r="O40" s="145"/>
       <c r="P40" s="24"/>
-      <c r="Q40" s="208"/>
-      <c r="R40" s="185"/>
+      <c r="Q40" s="144"/>
+      <c r="R40" s="145"/>
       <c r="S40" s="25"/>
       <c r="T40" s="25"/>
       <c r="U40" s="26"/>
@@ -3952,142 +3952,142 @@
       <c r="I41" s="40"/>
       <c r="J41" s="91"/>
       <c r="K41" s="96"/>
-      <c r="L41" s="211"/>
-      <c r="M41" s="155"/>
-      <c r="N41" s="155"/>
-      <c r="O41" s="186"/>
+      <c r="L41" s="207"/>
+      <c r="M41" s="154"/>
+      <c r="N41" s="154"/>
+      <c r="O41" s="143"/>
       <c r="P41" s="35"/>
-      <c r="Q41" s="155"/>
-      <c r="R41" s="186"/>
+      <c r="Q41" s="154"/>
+      <c r="R41" s="143"/>
       <c r="S41" s="36"/>
       <c r="T41" s="36"/>
       <c r="U41" s="32"/>
     </row>
     <row r="42" spans="1:22" ht="18" customHeight="1">
-      <c r="B42" s="225" t="s">
+      <c r="B42" s="238" t="s">
         <v>63</v>
       </c>
       <c r="C42" s="41"/>
       <c r="D42" s="41"/>
-      <c r="E42" s="278" t="s">
+      <c r="E42" s="158" t="s">
         <v>64</v>
       </c>
-      <c r="F42" s="185"/>
-      <c r="G42" s="259" t="s">
+      <c r="F42" s="145"/>
+      <c r="G42" s="157" t="s">
         <v>65</v>
       </c>
-      <c r="H42" s="185"/>
-      <c r="I42" s="153" t="s">
+      <c r="H42" s="145"/>
+      <c r="I42" s="152" t="s">
         <v>66</v>
       </c>
       <c r="J42" s="95" t="s">
         <v>67</v>
       </c>
-      <c r="K42" s="259" t="s">
+      <c r="K42" s="157" t="s">
         <v>68</v>
       </c>
-      <c r="L42" s="171"/>
-      <c r="M42" s="185"/>
-      <c r="N42" s="153" t="s">
+      <c r="L42" s="186"/>
+      <c r="M42" s="145"/>
+      <c r="N42" s="152" t="s">
         <v>69</v>
       </c>
       <c r="O42" s="42" t="s">
         <v>67</v>
       </c>
-      <c r="P42" s="153" t="s">
+      <c r="P42" s="152" t="s">
         <v>70</v>
       </c>
       <c r="Q42" s="41"/>
-      <c r="R42" s="153" t="s">
+      <c r="R42" s="152" t="s">
         <v>71</v>
       </c>
-      <c r="S42" s="171"/>
-      <c r="T42" s="185"/>
-      <c r="U42" s="196" t="s">
+      <c r="S42" s="186"/>
+      <c r="T42" s="145"/>
+      <c r="U42" s="309" t="s">
         <v>72</v>
       </c>
       <c r="V42" s="43"/>
     </row>
     <row r="43" spans="1:22" ht="50.4" customHeight="1">
-      <c r="B43" s="226"/>
+      <c r="B43" s="239"/>
       <c r="C43" s="95" t="s">
         <v>73</v>
       </c>
       <c r="D43" s="118" t="s">
         <v>74</v>
       </c>
-      <c r="E43" s="172"/>
-      <c r="F43" s="188"/>
-      <c r="G43" s="175"/>
-      <c r="H43" s="186"/>
-      <c r="I43" s="154"/>
-      <c r="J43" s="280" t="s">
+      <c r="E43" s="159"/>
+      <c r="F43" s="141"/>
+      <c r="G43" s="151"/>
+      <c r="H43" s="143"/>
+      <c r="I43" s="153"/>
+      <c r="J43" s="234" t="s">
         <v>75</v>
       </c>
-      <c r="K43" s="175"/>
-      <c r="L43" s="176"/>
-      <c r="M43" s="186"/>
-      <c r="N43" s="154"/>
-      <c r="O43" s="233" t="s">
+      <c r="K43" s="151"/>
+      <c r="L43" s="188"/>
+      <c r="M43" s="143"/>
+      <c r="N43" s="153"/>
+      <c r="O43" s="178" t="s">
         <v>75</v>
       </c>
-      <c r="P43" s="154"/>
+      <c r="P43" s="153"/>
       <c r="Q43" s="44" t="s">
         <v>76</v>
       </c>
-      <c r="R43" s="172"/>
-      <c r="S43" s="173"/>
-      <c r="T43" s="188"/>
-      <c r="U43" s="197"/>
+      <c r="R43" s="159"/>
+      <c r="S43" s="187"/>
+      <c r="T43" s="141"/>
+      <c r="U43" s="227"/>
       <c r="V43" s="43"/>
     </row>
     <row r="44" spans="1:22" ht="55.5" customHeight="1">
-      <c r="B44" s="226"/>
+      <c r="B44" s="239"/>
       <c r="C44" s="112" t="s">
         <v>77</v>
       </c>
       <c r="D44" s="111" t="s">
         <v>78</v>
       </c>
-      <c r="E44" s="175"/>
-      <c r="F44" s="186"/>
+      <c r="E44" s="151"/>
+      <c r="F44" s="143"/>
       <c r="G44" s="46" t="s">
         <v>79</v>
       </c>
       <c r="H44" s="73" t="s">
         <v>80</v>
       </c>
-      <c r="I44" s="155"/>
-      <c r="J44" s="155"/>
+      <c r="I44" s="154"/>
+      <c r="J44" s="154"/>
       <c r="K44" s="117" t="s">
         <v>81</v>
       </c>
-      <c r="L44" s="183" t="s">
+      <c r="L44" s="301" t="s">
         <v>80</v>
       </c>
-      <c r="M44" s="157"/>
-      <c r="N44" s="155"/>
-      <c r="O44" s="155"/>
-      <c r="P44" s="155"/>
+      <c r="M44" s="148"/>
+      <c r="N44" s="154"/>
+      <c r="O44" s="154"/>
+      <c r="P44" s="154"/>
       <c r="Q44" s="47" t="s">
         <v>82</v>
       </c>
-      <c r="R44" s="175"/>
-      <c r="S44" s="176"/>
-      <c r="T44" s="186"/>
-      <c r="U44" s="198"/>
+      <c r="R44" s="151"/>
+      <c r="S44" s="188"/>
+      <c r="T44" s="143"/>
+      <c r="U44" s="228"/>
       <c r="V44" s="43"/>
     </row>
     <row r="45" spans="1:22" ht="50.1" customHeight="1">
-      <c r="B45" s="226"/>
+      <c r="B45" s="239"/>
       <c r="C45" s="113">
         <v>1</v>
       </c>
       <c r="D45" s="107" t="s">
         <v>83</v>
       </c>
-      <c r="E45" s="156"/>
-      <c r="F45" s="157"/>
+      <c r="E45" s="160"/>
+      <c r="F45" s="148"/>
       <c r="G45" s="50" t="s">
         <v>84</v>
       </c>
@@ -4097,28 +4097,28 @@
       <c r="K45" s="50" t="s">
         <v>84</v>
       </c>
-      <c r="L45" s="195"/>
-      <c r="M45" s="157"/>
+      <c r="L45" s="147"/>
+      <c r="M45" s="148"/>
       <c r="N45" s="53"/>
       <c r="O45" s="53"/>
       <c r="P45" s="54"/>
       <c r="Q45" s="55"/>
-      <c r="R45" s="158"/>
-      <c r="S45" s="159"/>
-      <c r="T45" s="157"/>
+      <c r="R45" s="233"/>
+      <c r="S45" s="181"/>
+      <c r="T45" s="148"/>
       <c r="U45" s="58"/>
       <c r="V45" s="59"/>
     </row>
     <row r="46" spans="1:22" ht="50.1" customHeight="1">
-      <c r="B46" s="226"/>
+      <c r="B46" s="239"/>
       <c r="C46" s="114">
         <v>2</v>
       </c>
       <c r="D46" s="108" t="s">
         <v>85</v>
       </c>
-      <c r="E46" s="156"/>
-      <c r="F46" s="157"/>
+      <c r="E46" s="160"/>
+      <c r="F46" s="148"/>
       <c r="G46" s="50" t="s">
         <v>84</v>
       </c>
@@ -4128,28 +4128,28 @@
       <c r="K46" s="50" t="s">
         <v>84</v>
       </c>
-      <c r="L46" s="195"/>
-      <c r="M46" s="157"/>
+      <c r="L46" s="147"/>
+      <c r="M46" s="148"/>
       <c r="N46" s="51"/>
       <c r="O46" s="51"/>
       <c r="P46" s="61"/>
       <c r="Q46" s="62"/>
-      <c r="R46" s="158"/>
-      <c r="S46" s="159"/>
-      <c r="T46" s="157"/>
+      <c r="R46" s="233"/>
+      <c r="S46" s="181"/>
+      <c r="T46" s="148"/>
       <c r="U46" s="58"/>
       <c r="V46" s="59"/>
     </row>
     <row r="47" spans="1:22" ht="50.1" customHeight="1">
-      <c r="B47" s="226"/>
+      <c r="B47" s="239"/>
       <c r="C47" s="114">
         <v>3</v>
       </c>
       <c r="D47" s="108" t="s">
         <v>86</v>
       </c>
-      <c r="E47" s="156"/>
-      <c r="F47" s="157"/>
+      <c r="E47" s="160"/>
+      <c r="F47" s="148"/>
       <c r="G47" s="50" t="s">
         <v>84</v>
       </c>
@@ -4159,28 +4159,28 @@
       <c r="K47" s="50" t="s">
         <v>84</v>
       </c>
-      <c r="L47" s="195"/>
-      <c r="M47" s="157"/>
+      <c r="L47" s="147"/>
+      <c r="M47" s="148"/>
       <c r="N47" s="51"/>
       <c r="O47" s="51"/>
       <c r="P47" s="54"/>
       <c r="Q47" s="62"/>
-      <c r="R47" s="158"/>
-      <c r="S47" s="159"/>
-      <c r="T47" s="157"/>
+      <c r="R47" s="233"/>
+      <c r="S47" s="181"/>
+      <c r="T47" s="148"/>
       <c r="U47" s="58"/>
       <c r="V47" s="59"/>
     </row>
     <row r="48" spans="1:22" ht="50.1" customHeight="1">
-      <c r="B48" s="226"/>
+      <c r="B48" s="239"/>
       <c r="C48" s="114">
         <v>4</v>
       </c>
       <c r="D48" s="108" t="s">
         <v>87</v>
       </c>
-      <c r="E48" s="156"/>
-      <c r="F48" s="157"/>
+      <c r="E48" s="160"/>
+      <c r="F48" s="148"/>
       <c r="G48" s="50" t="s">
         <v>84</v>
       </c>
@@ -4190,28 +4190,28 @@
       <c r="K48" s="50" t="s">
         <v>84</v>
       </c>
-      <c r="L48" s="195"/>
-      <c r="M48" s="157"/>
+      <c r="L48" s="147"/>
+      <c r="M48" s="148"/>
       <c r="N48" s="51"/>
       <c r="O48" s="51"/>
       <c r="P48" s="54"/>
       <c r="Q48" s="62"/>
-      <c r="R48" s="158"/>
-      <c r="S48" s="159"/>
-      <c r="T48" s="157"/>
+      <c r="R48" s="233"/>
+      <c r="S48" s="181"/>
+      <c r="T48" s="148"/>
       <c r="U48" s="58"/>
       <c r="V48" s="59"/>
     </row>
     <row r="49" spans="2:23" ht="50.1" customHeight="1">
-      <c r="B49" s="226"/>
+      <c r="B49" s="239"/>
       <c r="C49" s="114">
         <v>5</v>
       </c>
       <c r="D49" s="109" t="s">
         <v>88</v>
       </c>
-      <c r="E49" s="156"/>
-      <c r="F49" s="157"/>
+      <c r="E49" s="160"/>
+      <c r="F49" s="148"/>
       <c r="G49" s="50" t="s">
         <v>84</v>
       </c>
@@ -4221,28 +4221,28 @@
       <c r="K49" s="50" t="s">
         <v>84</v>
       </c>
-      <c r="L49" s="195"/>
-      <c r="M49" s="157"/>
+      <c r="L49" s="147"/>
+      <c r="M49" s="148"/>
       <c r="N49" s="51"/>
       <c r="O49" s="51"/>
       <c r="P49" s="54"/>
       <c r="Q49" s="62"/>
-      <c r="R49" s="158"/>
-      <c r="S49" s="159"/>
-      <c r="T49" s="157"/>
+      <c r="R49" s="233"/>
+      <c r="S49" s="181"/>
+      <c r="T49" s="148"/>
       <c r="U49" s="58"/>
       <c r="V49" s="59"/>
     </row>
     <row r="50" spans="2:23" ht="53.4" customHeight="1">
-      <c r="B50" s="226"/>
+      <c r="B50" s="239"/>
       <c r="C50" s="114">
         <v>6</v>
       </c>
       <c r="D50" s="110" t="s">
         <v>89</v>
       </c>
-      <c r="E50" s="156"/>
-      <c r="F50" s="157"/>
+      <c r="E50" s="160"/>
+      <c r="F50" s="148"/>
       <c r="G50" s="50" t="s">
         <v>84</v>
       </c>
@@ -4252,28 +4252,28 @@
       <c r="K50" s="50" t="s">
         <v>84</v>
       </c>
-      <c r="L50" s="195"/>
-      <c r="M50" s="157"/>
+      <c r="L50" s="147"/>
+      <c r="M50" s="148"/>
       <c r="N50" s="51"/>
       <c r="O50" s="51"/>
       <c r="P50" s="54"/>
       <c r="Q50" s="62"/>
-      <c r="R50" s="158"/>
-      <c r="S50" s="159"/>
-      <c r="T50" s="157"/>
+      <c r="R50" s="233"/>
+      <c r="S50" s="181"/>
+      <c r="T50" s="148"/>
       <c r="U50" s="58"/>
       <c r="V50" s="59"/>
     </row>
     <row r="51" spans="2:23" ht="50.1" customHeight="1">
-      <c r="B51" s="227"/>
+      <c r="B51" s="240"/>
       <c r="C51" s="113">
         <v>7</v>
       </c>
       <c r="D51" s="110" t="s">
         <v>90</v>
       </c>
-      <c r="E51" s="156"/>
-      <c r="F51" s="157"/>
+      <c r="E51" s="160"/>
+      <c r="F51" s="148"/>
       <c r="G51" s="50" t="s">
         <v>84</v>
       </c>
@@ -4283,15 +4283,15 @@
       <c r="K51" s="50" t="s">
         <v>84</v>
       </c>
-      <c r="L51" s="195"/>
-      <c r="M51" s="157"/>
+      <c r="L51" s="147"/>
+      <c r="M51" s="148"/>
       <c r="N51" s="53"/>
       <c r="O51" s="53"/>
       <c r="P51" s="61"/>
       <c r="Q51" s="55"/>
-      <c r="R51" s="158"/>
-      <c r="S51" s="159"/>
-      <c r="T51" s="157"/>
+      <c r="R51" s="233"/>
+      <c r="S51" s="181"/>
+      <c r="T51" s="148"/>
       <c r="U51" s="58"/>
       <c r="V51" s="59"/>
     </row>
@@ -4319,128 +4319,128 @@
       <c r="V52" s="59"/>
     </row>
     <row r="53" spans="2:23" ht="18" customHeight="1">
-      <c r="B53" s="225" t="s">
+      <c r="B53" s="238" t="s">
         <v>91</v>
       </c>
       <c r="C53" s="72"/>
       <c r="D53" s="72"/>
-      <c r="E53" s="278" t="s">
+      <c r="E53" s="158" t="s">
         <v>64</v>
       </c>
-      <c r="F53" s="185"/>
-      <c r="G53" s="279" t="s">
+      <c r="F53" s="145"/>
+      <c r="G53" s="150" t="s">
         <v>92</v>
       </c>
-      <c r="H53" s="185"/>
-      <c r="I53" s="153" t="s">
+      <c r="H53" s="145"/>
+      <c r="I53" s="152" t="s">
         <v>93</v>
       </c>
-      <c r="J53" s="273" t="s">
+      <c r="J53" s="225" t="s">
         <v>94</v>
       </c>
-      <c r="K53" s="279" t="s">
+      <c r="K53" s="150" t="s">
         <v>68</v>
       </c>
-      <c r="L53" s="171"/>
-      <c r="M53" s="185"/>
-      <c r="N53" s="153" t="s">
+      <c r="L53" s="186"/>
+      <c r="M53" s="145"/>
+      <c r="N53" s="152" t="s">
         <v>69</v>
       </c>
       <c r="O53" s="42" t="s">
         <v>67</v>
       </c>
-      <c r="P53" s="153" t="s">
+      <c r="P53" s="152" t="s">
         <v>70</v>
       </c>
       <c r="Q53" s="41"/>
-      <c r="R53" s="153" t="s">
+      <c r="R53" s="152" t="s">
         <v>71</v>
       </c>
-      <c r="S53" s="171"/>
-      <c r="T53" s="185"/>
-      <c r="U53" s="274" t="s">
+      <c r="S53" s="186"/>
+      <c r="T53" s="145"/>
+      <c r="U53" s="226" t="s">
         <v>72</v>
       </c>
       <c r="V53" s="43"/>
     </row>
     <row r="54" spans="2:23" ht="50.4" customHeight="1">
-      <c r="B54" s="226"/>
+      <c r="B54" s="239"/>
       <c r="C54" s="41" t="s">
         <v>73</v>
       </c>
       <c r="D54" s="41" t="s">
         <v>74</v>
       </c>
-      <c r="E54" s="172"/>
-      <c r="F54" s="188"/>
-      <c r="G54" s="175"/>
-      <c r="H54" s="186"/>
-      <c r="I54" s="154"/>
-      <c r="J54" s="154"/>
-      <c r="K54" s="175"/>
-      <c r="L54" s="176"/>
-      <c r="M54" s="186"/>
-      <c r="N54" s="154"/>
-      <c r="O54" s="233" t="s">
+      <c r="E54" s="159"/>
+      <c r="F54" s="141"/>
+      <c r="G54" s="151"/>
+      <c r="H54" s="143"/>
+      <c r="I54" s="153"/>
+      <c r="J54" s="153"/>
+      <c r="K54" s="151"/>
+      <c r="L54" s="188"/>
+      <c r="M54" s="143"/>
+      <c r="N54" s="153"/>
+      <c r="O54" s="178" t="s">
         <v>75</v>
       </c>
-      <c r="P54" s="154"/>
+      <c r="P54" s="153"/>
       <c r="Q54" s="44" t="s">
         <v>76</v>
       </c>
-      <c r="R54" s="172"/>
-      <c r="S54" s="173"/>
-      <c r="T54" s="188"/>
-      <c r="U54" s="197"/>
+      <c r="R54" s="159"/>
+      <c r="S54" s="187"/>
+      <c r="T54" s="141"/>
+      <c r="U54" s="227"/>
       <c r="V54" s="43"/>
     </row>
     <row r="55" spans="2:23" ht="50.4" customHeight="1">
-      <c r="B55" s="226"/>
+      <c r="B55" s="239"/>
       <c r="C55" s="45" t="s">
         <v>77</v>
       </c>
       <c r="D55" s="45" t="s">
         <v>78</v>
       </c>
-      <c r="E55" s="175"/>
-      <c r="F55" s="186"/>
+      <c r="E55" s="151"/>
+      <c r="F55" s="143"/>
       <c r="G55" s="46" t="s">
         <v>81</v>
       </c>
       <c r="H55" s="73" t="s">
         <v>80</v>
       </c>
-      <c r="I55" s="155"/>
-      <c r="J55" s="155"/>
+      <c r="I55" s="154"/>
+      <c r="J55" s="154"/>
       <c r="K55" s="46" t="s">
         <v>81</v>
       </c>
-      <c r="L55" s="279" t="s">
+      <c r="L55" s="150" t="s">
         <v>80</v>
       </c>
-      <c r="M55" s="157"/>
-      <c r="N55" s="155"/>
-      <c r="O55" s="155"/>
-      <c r="P55" s="155"/>
+      <c r="M55" s="148"/>
+      <c r="N55" s="154"/>
+      <c r="O55" s="154"/>
+      <c r="P55" s="154"/>
       <c r="Q55" s="47" t="s">
         <v>82</v>
       </c>
-      <c r="R55" s="175"/>
-      <c r="S55" s="176"/>
-      <c r="T55" s="186"/>
-      <c r="U55" s="198"/>
+      <c r="R55" s="151"/>
+      <c r="S55" s="188"/>
+      <c r="T55" s="143"/>
+      <c r="U55" s="228"/>
       <c r="V55" s="43"/>
     </row>
     <row r="56" spans="2:23" ht="30" customHeight="1">
-      <c r="B56" s="226"/>
+      <c r="B56" s="239"/>
       <c r="C56" s="48">
         <v>1</v>
       </c>
       <c r="D56" s="49" t="s">
         <v>83</v>
       </c>
-      <c r="E56" s="156"/>
-      <c r="F56" s="157"/>
+      <c r="E56" s="160"/>
+      <c r="F56" s="148"/>
       <c r="G56" s="50" t="s">
         <v>84</v>
       </c>
@@ -4450,8 +4450,8 @@
       <c r="K56" s="50" t="s">
         <v>84</v>
       </c>
-      <c r="L56" s="195"/>
-      <c r="M56" s="157"/>
+      <c r="L56" s="147"/>
+      <c r="M56" s="148"/>
       <c r="N56" s="53"/>
       <c r="O56" s="53"/>
       <c r="P56" s="61"/>
@@ -4463,15 +4463,15 @@
       <c r="V56" s="59"/>
     </row>
     <row r="57" spans="2:23" ht="30" customHeight="1">
-      <c r="B57" s="226"/>
+      <c r="B57" s="239"/>
       <c r="C57" s="56">
         <v>2</v>
       </c>
       <c r="D57" s="75" t="s">
         <v>95</v>
       </c>
-      <c r="E57" s="156"/>
-      <c r="F57" s="157"/>
+      <c r="E57" s="160"/>
+      <c r="F57" s="148"/>
       <c r="G57" s="50" t="s">
         <v>84</v>
       </c>
@@ -4481,8 +4481,8 @@
       <c r="K57" s="50" t="s">
         <v>84</v>
       </c>
-      <c r="L57" s="195"/>
-      <c r="M57" s="157"/>
+      <c r="L57" s="147"/>
+      <c r="M57" s="148"/>
       <c r="N57" s="51"/>
       <c r="O57" s="51"/>
       <c r="P57" s="54"/>
@@ -4494,15 +4494,15 @@
       <c r="V57" s="59"/>
     </row>
     <row r="58" spans="2:23" ht="30" customHeight="1">
-      <c r="B58" s="226"/>
+      <c r="B58" s="239"/>
       <c r="C58" s="56">
         <v>3</v>
       </c>
       <c r="D58" s="77" t="s">
         <v>96</v>
       </c>
-      <c r="E58" s="156"/>
-      <c r="F58" s="157"/>
+      <c r="E58" s="160"/>
+      <c r="F58" s="148"/>
       <c r="G58" s="50" t="s">
         <v>84</v>
       </c>
@@ -4512,8 +4512,8 @@
       <c r="K58" s="50" t="s">
         <v>84</v>
       </c>
-      <c r="L58" s="195"/>
-      <c r="M58" s="157"/>
+      <c r="L58" s="147"/>
+      <c r="M58" s="148"/>
       <c r="N58" s="51"/>
       <c r="O58" s="51"/>
       <c r="P58" s="54"/>
@@ -4525,15 +4525,15 @@
       <c r="V58" s="59"/>
     </row>
     <row r="59" spans="2:23" ht="30" customHeight="1">
-      <c r="B59" s="226"/>
+      <c r="B59" s="239"/>
       <c r="C59" s="78">
         <v>4</v>
       </c>
       <c r="D59" s="79" t="s">
         <v>97</v>
       </c>
-      <c r="E59" s="156"/>
-      <c r="F59" s="157"/>
+      <c r="E59" s="160"/>
+      <c r="F59" s="148"/>
       <c r="G59" s="50" t="s">
         <v>84</v>
       </c>
@@ -4543,8 +4543,8 @@
       <c r="K59" s="59" t="s">
         <v>84</v>
       </c>
-      <c r="L59" s="195"/>
-      <c r="M59" s="157"/>
+      <c r="L59" s="147"/>
+      <c r="M59" s="148"/>
       <c r="N59" s="51"/>
       <c r="O59" s="51"/>
       <c r="P59" s="54"/>
@@ -4556,15 +4556,15 @@
       <c r="V59" s="59"/>
     </row>
     <row r="60" spans="2:23" ht="30" customHeight="1">
-      <c r="B60" s="226"/>
+      <c r="B60" s="239"/>
       <c r="C60" s="78">
         <v>5</v>
       </c>
       <c r="D60" s="79" t="s">
         <v>87</v>
       </c>
-      <c r="E60" s="156"/>
-      <c r="F60" s="157"/>
+      <c r="E60" s="160"/>
+      <c r="F60" s="148"/>
       <c r="G60" s="50" t="s">
         <v>84</v>
       </c>
@@ -4574,8 +4574,8 @@
       <c r="K60" s="59" t="s">
         <v>84</v>
       </c>
-      <c r="L60" s="195"/>
-      <c r="M60" s="157"/>
+      <c r="L60" s="147"/>
+      <c r="M60" s="148"/>
       <c r="N60" s="51"/>
       <c r="O60" s="51"/>
       <c r="P60" s="54"/>
@@ -4587,15 +4587,15 @@
       <c r="V60" s="59"/>
     </row>
     <row r="61" spans="2:23" ht="30" customHeight="1">
-      <c r="B61" s="227"/>
+      <c r="B61" s="240"/>
       <c r="C61" s="84">
         <v>6</v>
       </c>
       <c r="D61" s="85" t="s">
         <v>90</v>
       </c>
-      <c r="E61" s="156"/>
-      <c r="F61" s="157"/>
+      <c r="E61" s="160"/>
+      <c r="F61" s="148"/>
       <c r="G61" s="59" t="s">
         <v>84</v>
       </c>
@@ -4605,8 +4605,8 @@
       <c r="K61" s="84" t="s">
         <v>84</v>
       </c>
-      <c r="L61" s="195"/>
-      <c r="M61" s="157"/>
+      <c r="L61" s="147"/>
+      <c r="M61" s="148"/>
       <c r="N61" s="87"/>
       <c r="O61" s="87"/>
       <c r="P61" s="84"/>
@@ -4618,32 +4618,32 @@
       <c r="V61" s="59"/>
     </row>
     <row r="62" spans="2:23" s="88" customFormat="1" ht="23.25" customHeight="1" thickBot="1">
-      <c r="B62" s="275" t="s">
+      <c r="B62" s="229" t="s">
         <v>98</v>
       </c>
-      <c r="C62" s="271"/>
-      <c r="D62" s="271"/>
-      <c r="E62" s="271"/>
-      <c r="F62" s="276"/>
-      <c r="G62" s="277" t="s">
+      <c r="C62" s="223"/>
+      <c r="D62" s="223"/>
+      <c r="E62" s="223"/>
+      <c r="F62" s="230"/>
+      <c r="G62" s="232" t="s">
         <v>99</v>
       </c>
-      <c r="H62" s="271"/>
-      <c r="I62" s="271"/>
-      <c r="J62" s="271"/>
-      <c r="K62" s="271"/>
-      <c r="L62" s="271"/>
-      <c r="M62" s="276"/>
-      <c r="N62" s="270" t="s">
+      <c r="H62" s="223"/>
+      <c r="I62" s="223"/>
+      <c r="J62" s="223"/>
+      <c r="K62" s="223"/>
+      <c r="L62" s="223"/>
+      <c r="M62" s="230"/>
+      <c r="N62" s="222" t="s">
         <v>100</v>
       </c>
-      <c r="O62" s="271"/>
-      <c r="P62" s="271"/>
-      <c r="Q62" s="271"/>
-      <c r="R62" s="271"/>
-      <c r="S62" s="271"/>
-      <c r="T62" s="271"/>
-      <c r="U62" s="272"/>
+      <c r="O62" s="223"/>
+      <c r="P62" s="223"/>
+      <c r="Q62" s="223"/>
+      <c r="R62" s="223"/>
+      <c r="S62" s="223"/>
+      <c r="T62" s="223"/>
+      <c r="U62" s="224"/>
       <c r="W62" s="89"/>
     </row>
     <row r="63" spans="2:23" ht="14.4" customHeight="1"/>
@@ -4668,6 +4668,148 @@
     </row>
   </sheetData>
   <mergeCells count="166">
+    <mergeCell ref="S16:U19"/>
+    <mergeCell ref="E1:N2"/>
+    <mergeCell ref="P42:P44"/>
+    <mergeCell ref="E51:F51"/>
+    <mergeCell ref="R47:T47"/>
+    <mergeCell ref="I38:J39"/>
+    <mergeCell ref="O1:U2"/>
+    <mergeCell ref="E3:K5"/>
+    <mergeCell ref="E38:G39"/>
+    <mergeCell ref="L44:M44"/>
+    <mergeCell ref="N32:O32"/>
+    <mergeCell ref="Q41:R41"/>
+    <mergeCell ref="Q25:R25"/>
+    <mergeCell ref="R50:T50"/>
+    <mergeCell ref="N35:O35"/>
+    <mergeCell ref="I12:J15"/>
+    <mergeCell ref="L50:M50"/>
+    <mergeCell ref="U42:U44"/>
+    <mergeCell ref="R42:T44"/>
+    <mergeCell ref="L22:U24"/>
+    <mergeCell ref="L20:U20"/>
+    <mergeCell ref="Q26:R26"/>
+    <mergeCell ref="Q34:R34"/>
+    <mergeCell ref="L30:L41"/>
+    <mergeCell ref="R53:T55"/>
+    <mergeCell ref="Q35:R35"/>
+    <mergeCell ref="N39:O39"/>
+    <mergeCell ref="R46:T46"/>
+    <mergeCell ref="D22:D24"/>
+    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="I7:J7"/>
+    <mergeCell ref="E6:H7"/>
+    <mergeCell ref="Q39:R39"/>
+    <mergeCell ref="B25:D26"/>
+    <mergeCell ref="J16:K19"/>
+    <mergeCell ref="Q29:R29"/>
+    <mergeCell ref="B27:D28"/>
+    <mergeCell ref="Q32:R32"/>
+    <mergeCell ref="N29:O29"/>
+    <mergeCell ref="N38:O38"/>
+    <mergeCell ref="E49:F49"/>
+    <mergeCell ref="B42:B51"/>
+    <mergeCell ref="R51:T51"/>
+    <mergeCell ref="K8:K11"/>
+    <mergeCell ref="N28:O28"/>
+    <mergeCell ref="D10:D11"/>
+    <mergeCell ref="N26:O26"/>
+    <mergeCell ref="O54:O55"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="B29:D31"/>
+    <mergeCell ref="D36:K36"/>
+    <mergeCell ref="Q38:R38"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="D18:D19"/>
+    <mergeCell ref="D8:D9"/>
+    <mergeCell ref="R48:T48"/>
+    <mergeCell ref="Q27:R27"/>
+    <mergeCell ref="N31:O31"/>
+    <mergeCell ref="N40:O40"/>
+    <mergeCell ref="J20:K24"/>
+    <mergeCell ref="E31:K31"/>
+    <mergeCell ref="B20:C21"/>
+    <mergeCell ref="E20:I24"/>
+    <mergeCell ref="D12:D13"/>
+    <mergeCell ref="M40:M41"/>
+    <mergeCell ref="N41:O41"/>
+    <mergeCell ref="H40:I40"/>
+    <mergeCell ref="L47:M47"/>
+    <mergeCell ref="E40:G40"/>
+    <mergeCell ref="R45:T45"/>
+    <mergeCell ref="B10:C11"/>
+    <mergeCell ref="D20:D21"/>
+    <mergeCell ref="E60:F60"/>
+    <mergeCell ref="L59:M59"/>
+    <mergeCell ref="B32:K33"/>
+    <mergeCell ref="L46:M46"/>
+    <mergeCell ref="L61:M61"/>
+    <mergeCell ref="E58:F58"/>
+    <mergeCell ref="I42:I44"/>
+    <mergeCell ref="L48:M48"/>
+    <mergeCell ref="E50:F50"/>
+    <mergeCell ref="H38:H39"/>
+    <mergeCell ref="E61:F61"/>
+    <mergeCell ref="E59:F59"/>
+    <mergeCell ref="L58:M58"/>
+    <mergeCell ref="E56:F56"/>
+    <mergeCell ref="B53:B61"/>
+    <mergeCell ref="L60:M60"/>
+    <mergeCell ref="L45:M45"/>
+    <mergeCell ref="G42:H43"/>
+    <mergeCell ref="I53:I55"/>
+    <mergeCell ref="D38:D39"/>
+    <mergeCell ref="K42:M43"/>
+    <mergeCell ref="M34:M35"/>
+    <mergeCell ref="M32:M33"/>
+    <mergeCell ref="E46:F46"/>
+    <mergeCell ref="P53:P55"/>
+    <mergeCell ref="N25:O25"/>
+    <mergeCell ref="L25:M26"/>
+    <mergeCell ref="D14:D15"/>
+    <mergeCell ref="I8:J11"/>
+    <mergeCell ref="E45:F45"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="N62:U62"/>
+    <mergeCell ref="Q31:R31"/>
+    <mergeCell ref="Q40:R40"/>
+    <mergeCell ref="J53:J55"/>
+    <mergeCell ref="N53:N55"/>
+    <mergeCell ref="U53:U55"/>
+    <mergeCell ref="B62:F62"/>
+    <mergeCell ref="Q28:R28"/>
+    <mergeCell ref="G62:M62"/>
+    <mergeCell ref="R49:T49"/>
+    <mergeCell ref="Q37:R37"/>
+    <mergeCell ref="E42:F44"/>
+    <mergeCell ref="K53:M54"/>
+    <mergeCell ref="L57:M57"/>
+    <mergeCell ref="J43:J44"/>
+    <mergeCell ref="E57:F57"/>
+    <mergeCell ref="E48:F48"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="M36:M37"/>
+    <mergeCell ref="M30:M31"/>
+    <mergeCell ref="B16:C17"/>
+    <mergeCell ref="K38:K39"/>
+    <mergeCell ref="E12:H15"/>
+    <mergeCell ref="B14:C15"/>
+    <mergeCell ref="N37:O37"/>
+    <mergeCell ref="E37:G37"/>
+    <mergeCell ref="L16:R19"/>
+    <mergeCell ref="E29:K30"/>
+    <mergeCell ref="Q33:R33"/>
+    <mergeCell ref="B22:C24"/>
+    <mergeCell ref="M38:M39"/>
+    <mergeCell ref="E16:I19"/>
+    <mergeCell ref="N33:O33"/>
+    <mergeCell ref="I37:J37"/>
+    <mergeCell ref="K12:K15"/>
+    <mergeCell ref="L27:L29"/>
+    <mergeCell ref="B34:K35"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B39:C39"/>
     <mergeCell ref="B1:C5"/>
     <mergeCell ref="Q36:R36"/>
     <mergeCell ref="B18:C19"/>
@@ -4692,148 +4834,6 @@
     <mergeCell ref="O43:O44"/>
     <mergeCell ref="L51:M51"/>
     <mergeCell ref="B12:C13"/>
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="M36:M37"/>
-    <mergeCell ref="M30:M31"/>
-    <mergeCell ref="B16:C17"/>
-    <mergeCell ref="K38:K39"/>
-    <mergeCell ref="E12:H15"/>
-    <mergeCell ref="B14:C15"/>
-    <mergeCell ref="N37:O37"/>
-    <mergeCell ref="E37:G37"/>
-    <mergeCell ref="L16:R19"/>
-    <mergeCell ref="E29:K30"/>
-    <mergeCell ref="Q33:R33"/>
-    <mergeCell ref="B22:C24"/>
-    <mergeCell ref="M38:M39"/>
-    <mergeCell ref="E16:I19"/>
-    <mergeCell ref="N33:O33"/>
-    <mergeCell ref="I37:J37"/>
-    <mergeCell ref="K12:K15"/>
-    <mergeCell ref="L27:L29"/>
-    <mergeCell ref="B34:K35"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="P53:P55"/>
-    <mergeCell ref="N25:O25"/>
-    <mergeCell ref="L25:M26"/>
-    <mergeCell ref="D14:D15"/>
-    <mergeCell ref="I8:J11"/>
-    <mergeCell ref="E45:F45"/>
-    <mergeCell ref="D16:D17"/>
-    <mergeCell ref="N62:U62"/>
-    <mergeCell ref="Q31:R31"/>
-    <mergeCell ref="Q40:R40"/>
-    <mergeCell ref="J53:J55"/>
-    <mergeCell ref="N53:N55"/>
-    <mergeCell ref="U53:U55"/>
-    <mergeCell ref="B62:F62"/>
-    <mergeCell ref="Q28:R28"/>
-    <mergeCell ref="G62:M62"/>
-    <mergeCell ref="R49:T49"/>
-    <mergeCell ref="Q37:R37"/>
-    <mergeCell ref="E42:F44"/>
-    <mergeCell ref="K53:M54"/>
-    <mergeCell ref="L57:M57"/>
-    <mergeCell ref="J43:J44"/>
-    <mergeCell ref="E57:F57"/>
-    <mergeCell ref="E48:F48"/>
-    <mergeCell ref="E60:F60"/>
-    <mergeCell ref="L59:M59"/>
-    <mergeCell ref="B32:K33"/>
-    <mergeCell ref="L46:M46"/>
-    <mergeCell ref="L61:M61"/>
-    <mergeCell ref="E58:F58"/>
-    <mergeCell ref="I42:I44"/>
-    <mergeCell ref="L48:M48"/>
-    <mergeCell ref="E50:F50"/>
-    <mergeCell ref="H38:H39"/>
-    <mergeCell ref="E61:F61"/>
-    <mergeCell ref="E59:F59"/>
-    <mergeCell ref="L58:M58"/>
-    <mergeCell ref="E56:F56"/>
-    <mergeCell ref="B53:B61"/>
-    <mergeCell ref="L60:M60"/>
-    <mergeCell ref="L45:M45"/>
-    <mergeCell ref="G42:H43"/>
-    <mergeCell ref="I53:I55"/>
-    <mergeCell ref="D38:D39"/>
-    <mergeCell ref="K42:M43"/>
-    <mergeCell ref="M34:M35"/>
-    <mergeCell ref="M32:M33"/>
-    <mergeCell ref="E46:F46"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="B29:D31"/>
-    <mergeCell ref="D36:K36"/>
-    <mergeCell ref="Q38:R38"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="D18:D19"/>
-    <mergeCell ref="D8:D9"/>
-    <mergeCell ref="R48:T48"/>
-    <mergeCell ref="Q27:R27"/>
-    <mergeCell ref="N31:O31"/>
-    <mergeCell ref="N40:O40"/>
-    <mergeCell ref="J20:K24"/>
-    <mergeCell ref="E31:K31"/>
-    <mergeCell ref="B20:C21"/>
-    <mergeCell ref="E20:I24"/>
-    <mergeCell ref="D12:D13"/>
-    <mergeCell ref="M40:M41"/>
-    <mergeCell ref="N41:O41"/>
-    <mergeCell ref="H40:I40"/>
-    <mergeCell ref="L47:M47"/>
-    <mergeCell ref="E40:G40"/>
-    <mergeCell ref="R45:T45"/>
-    <mergeCell ref="B10:C11"/>
-    <mergeCell ref="D20:D21"/>
-    <mergeCell ref="R53:T55"/>
-    <mergeCell ref="Q35:R35"/>
-    <mergeCell ref="N39:O39"/>
-    <mergeCell ref="R46:T46"/>
-    <mergeCell ref="D22:D24"/>
-    <mergeCell ref="I6:J6"/>
-    <mergeCell ref="I7:J7"/>
-    <mergeCell ref="E6:H7"/>
-    <mergeCell ref="Q39:R39"/>
-    <mergeCell ref="B25:D26"/>
-    <mergeCell ref="J16:K19"/>
-    <mergeCell ref="Q29:R29"/>
-    <mergeCell ref="B27:D28"/>
-    <mergeCell ref="Q32:R32"/>
-    <mergeCell ref="N29:O29"/>
-    <mergeCell ref="N38:O38"/>
-    <mergeCell ref="E49:F49"/>
-    <mergeCell ref="B42:B51"/>
-    <mergeCell ref="R51:T51"/>
-    <mergeCell ref="K8:K11"/>
-    <mergeCell ref="N28:O28"/>
-    <mergeCell ref="D10:D11"/>
-    <mergeCell ref="N26:O26"/>
-    <mergeCell ref="O54:O55"/>
-    <mergeCell ref="S16:U19"/>
-    <mergeCell ref="E1:N2"/>
-    <mergeCell ref="P42:P44"/>
-    <mergeCell ref="E51:F51"/>
-    <mergeCell ref="R47:T47"/>
-    <mergeCell ref="I38:J39"/>
-    <mergeCell ref="O1:U2"/>
-    <mergeCell ref="E3:K5"/>
-    <mergeCell ref="E38:G39"/>
-    <mergeCell ref="L44:M44"/>
-    <mergeCell ref="N32:O32"/>
-    <mergeCell ref="Q41:R41"/>
-    <mergeCell ref="Q25:R25"/>
-    <mergeCell ref="R50:T50"/>
-    <mergeCell ref="N35:O35"/>
-    <mergeCell ref="I12:J15"/>
-    <mergeCell ref="L50:M50"/>
-    <mergeCell ref="U42:U44"/>
-    <mergeCell ref="R42:T44"/>
-    <mergeCell ref="L22:U24"/>
-    <mergeCell ref="L20:U20"/>
-    <mergeCell ref="Q26:R26"/>
-    <mergeCell ref="Q34:R34"/>
-    <mergeCell ref="L30:L41"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1" gridLines="1"/>
   <pageMargins left="3.9370078740157501E-2" right="3.9370078740157501E-2" top="0.35433070866141703" bottom="0.35433070866141703" header="0.118110236220472" footer="0.118110236220472"/>

--- a/jo.xlsx
+++ b/jo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\production_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4F5433C-7247-42DA-B299-53B9E62F6A4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5098E19-ECD3-4DCB-940A-634C11017550}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -175,9 +175,6 @@
     <t>A</t>
   </si>
   <si>
-    <t>ОДОБРЕНО / APPROVAL:</t>
-  </si>
-  <si>
     <t>ЗАБЕЛЕЖКА РАЗМЕРИ ПО ( X,Y,Z )  + 5 мм / + 2мм при рязане преди процеса за оразмеряване на заготовка:
 Note:  Measurement of (X,Y,Z) can not be bigger than +5 mm and smaller than 2mm at cutting before trimming process.</t>
   </si>
@@ -383,7 +380,21 @@
     <t>YBE-Y</t>
   </si>
   <si>
-    <t>MMA H248 MAIN L/R HD</t>
+    <r>
+      <t xml:space="preserve">ОДОБРЕНО / APPROVAL: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="22"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Пламен Димитров</t>
+    </r>
+  </si>
+  <si>
+    <t>H248</t>
   </si>
 </sst>
 </file>
@@ -3123,15 +3134,15 @@
       <c r="C8" s="145"/>
       <c r="D8" s="250"/>
       <c r="E8" s="161" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F8" s="162"/>
       <c r="G8" s="167" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H8" s="168"/>
       <c r="I8" s="215" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="J8" s="216"/>
       <c r="K8" s="271"/>
@@ -3207,7 +3218,7 @@
       </c>
       <c r="C12" s="145"/>
       <c r="D12" s="256" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E12" s="185"/>
       <c r="F12" s="186"/>
@@ -3241,7 +3252,7 @@
       </c>
       <c r="C14" s="145"/>
       <c r="D14" s="213" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E14" s="159"/>
       <c r="F14" s="187"/>
@@ -3293,7 +3304,7 @@
       </c>
       <c r="K16" s="253"/>
       <c r="L16" s="192" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="M16" s="193"/>
       <c r="N16" s="193"/>
@@ -3302,7 +3313,7 @@
       <c r="Q16" s="193"/>
       <c r="R16" s="193"/>
       <c r="S16" s="192" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="T16" s="193"/>
       <c r="U16" s="275"/>
@@ -3384,7 +3395,7 @@
       <c r="C20" s="145"/>
       <c r="D20" s="260"/>
       <c r="E20" s="200" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F20" s="186"/>
       <c r="G20" s="186"/>
@@ -3692,7 +3703,7 @@
       <c r="C31" s="188"/>
       <c r="D31" s="143"/>
       <c r="E31" s="198" t="s">
-        <v>46</v>
+        <v>108</v>
       </c>
       <c r="F31" s="181"/>
       <c r="G31" s="181"/>
@@ -3713,7 +3724,7 @@
     </row>
     <row r="32" spans="2:22" s="2" customFormat="1" ht="21" customHeight="1">
       <c r="B32" s="235" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C32" s="186"/>
       <c r="D32" s="186"/>
@@ -3726,7 +3737,7 @@
       <c r="K32" s="145"/>
       <c r="L32" s="206"/>
       <c r="M32" s="182" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N32" s="302"/>
       <c r="O32" s="145"/>
@@ -3761,7 +3772,7 @@
     </row>
     <row r="34" spans="1:22" s="2" customFormat="1" ht="21" customHeight="1">
       <c r="B34" s="208" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C34" s="186"/>
       <c r="D34" s="186"/>
@@ -3774,7 +3785,7 @@
       <c r="K34" s="145"/>
       <c r="L34" s="206"/>
       <c r="M34" s="182" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="N34" s="144"/>
       <c r="O34" s="145"/>
@@ -3809,7 +3820,7 @@
     </row>
     <row r="36" spans="1:22" s="2" customFormat="1" ht="21" customHeight="1">
       <c r="B36" s="37" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C36" s="38"/>
       <c r="D36" s="246"/>
@@ -3822,7 +3833,7 @@
       <c r="K36" s="145"/>
       <c r="L36" s="206"/>
       <c r="M36" s="182" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="N36" s="144"/>
       <c r="O36" s="145"/>
@@ -3835,26 +3846,26 @@
     </row>
     <row r="37" spans="1:22" s="2" customFormat="1" ht="49.2" customHeight="1">
       <c r="B37" s="209" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C37" s="181"/>
       <c r="D37" s="127" t="s">
+        <v>53</v>
+      </c>
+      <c r="E37" s="190" t="s">
         <v>54</v>
-      </c>
-      <c r="E37" s="190" t="s">
-        <v>55</v>
       </c>
       <c r="F37" s="181"/>
       <c r="G37" s="191"/>
       <c r="H37" s="115" t="s">
+        <v>55</v>
+      </c>
+      <c r="I37" s="202" t="s">
         <v>56</v>
-      </c>
-      <c r="I37" s="202" t="s">
-        <v>57</v>
       </c>
       <c r="J37" s="203"/>
       <c r="K37" s="116" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="L37" s="206"/>
       <c r="M37" s="154"/>
@@ -3880,7 +3891,7 @@
       <c r="K38" s="183"/>
       <c r="L38" s="206"/>
       <c r="M38" s="182" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="N38" s="144"/>
       <c r="O38" s="145"/>
@@ -3915,7 +3926,7 @@
     </row>
     <row r="40" spans="1:22" s="2" customFormat="1" ht="29.25" customHeight="1">
       <c r="A40" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B40" s="180"/>
       <c r="C40" s="181"/>
@@ -3928,7 +3939,7 @@
       <c r="K40" s="99"/>
       <c r="L40" s="206"/>
       <c r="M40" s="182" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="N40" s="144"/>
       <c r="O40" s="145"/>
@@ -3947,7 +3958,7 @@
       <c r="F41" s="40"/>
       <c r="G41" s="40"/>
       <c r="H41" s="92" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="I41" s="40"/>
       <c r="J41" s="91"/>
@@ -3965,56 +3976,56 @@
     </row>
     <row r="42" spans="1:22" ht="18" customHeight="1">
       <c r="B42" s="238" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C42" s="41"/>
       <c r="D42" s="41"/>
       <c r="E42" s="158" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F42" s="145"/>
       <c r="G42" s="157" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="H42" s="145"/>
       <c r="I42" s="152" t="s">
+        <v>65</v>
+      </c>
+      <c r="J42" s="95" t="s">
         <v>66</v>
       </c>
-      <c r="J42" s="95" t="s">
+      <c r="K42" s="157" t="s">
         <v>67</v>
-      </c>
-      <c r="K42" s="157" t="s">
-        <v>68</v>
       </c>
       <c r="L42" s="186"/>
       <c r="M42" s="145"/>
       <c r="N42" s="152" t="s">
+        <v>68</v>
+      </c>
+      <c r="O42" s="42" t="s">
+        <v>66</v>
+      </c>
+      <c r="P42" s="152" t="s">
         <v>69</v>
-      </c>
-      <c r="O42" s="42" t="s">
-        <v>67</v>
-      </c>
-      <c r="P42" s="152" t="s">
-        <v>70</v>
       </c>
       <c r="Q42" s="41"/>
       <c r="R42" s="152" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="S42" s="186"/>
       <c r="T42" s="145"/>
       <c r="U42" s="309" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="V42" s="43"/>
     </row>
     <row r="43" spans="1:22" ht="50.4" customHeight="1">
       <c r="B43" s="239"/>
       <c r="C43" s="95" t="s">
+        <v>72</v>
+      </c>
+      <c r="D43" s="118" t="s">
         <v>73</v>
-      </c>
-      <c r="D43" s="118" t="s">
-        <v>74</v>
       </c>
       <c r="E43" s="159"/>
       <c r="F43" s="141"/>
@@ -4022,18 +4033,18 @@
       <c r="H43" s="143"/>
       <c r="I43" s="153"/>
       <c r="J43" s="234" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="K43" s="151"/>
       <c r="L43" s="188"/>
       <c r="M43" s="143"/>
       <c r="N43" s="153"/>
       <c r="O43" s="178" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="P43" s="153"/>
       <c r="Q43" s="44" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="R43" s="159"/>
       <c r="S43" s="187"/>
@@ -4044,33 +4055,33 @@
     <row r="44" spans="1:22" ht="55.5" customHeight="1">
       <c r="B44" s="239"/>
       <c r="C44" s="112" t="s">
+        <v>76</v>
+      </c>
+      <c r="D44" s="111" t="s">
         <v>77</v>
-      </c>
-      <c r="D44" s="111" t="s">
-        <v>78</v>
       </c>
       <c r="E44" s="151"/>
       <c r="F44" s="143"/>
       <c r="G44" s="46" t="s">
+        <v>78</v>
+      </c>
+      <c r="H44" s="73" t="s">
         <v>79</v>
-      </c>
-      <c r="H44" s="73" t="s">
-        <v>80</v>
       </c>
       <c r="I44" s="154"/>
       <c r="J44" s="154"/>
       <c r="K44" s="117" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="L44" s="301" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="M44" s="148"/>
       <c r="N44" s="154"/>
       <c r="O44" s="154"/>
       <c r="P44" s="154"/>
       <c r="Q44" s="47" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="R44" s="151"/>
       <c r="S44" s="188"/>
@@ -4084,18 +4095,18 @@
         <v>1</v>
       </c>
       <c r="D45" s="107" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E45" s="160"/>
       <c r="F45" s="148"/>
       <c r="G45" s="50" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H45" s="51"/>
       <c r="I45" s="52"/>
       <c r="J45" s="53"/>
       <c r="K45" s="50" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="L45" s="147"/>
       <c r="M45" s="148"/>
@@ -4115,18 +4126,18 @@
         <v>2</v>
       </c>
       <c r="D46" s="108" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E46" s="160"/>
       <c r="F46" s="148"/>
       <c r="G46" s="50" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H46" s="51"/>
       <c r="I46" s="60"/>
       <c r="J46" s="51"/>
       <c r="K46" s="50" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="L46" s="147"/>
       <c r="M46" s="148"/>
@@ -4146,18 +4157,18 @@
         <v>3</v>
       </c>
       <c r="D47" s="108" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E47" s="160"/>
       <c r="F47" s="148"/>
       <c r="G47" s="50" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H47" s="51"/>
       <c r="I47" s="60"/>
       <c r="J47" s="51"/>
       <c r="K47" s="50" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="L47" s="147"/>
       <c r="M47" s="148"/>
@@ -4177,18 +4188,18 @@
         <v>4</v>
       </c>
       <c r="D48" s="108" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E48" s="160"/>
       <c r="F48" s="148"/>
       <c r="G48" s="50" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H48" s="51"/>
       <c r="I48" s="60"/>
       <c r="J48" s="51"/>
       <c r="K48" s="50" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="L48" s="147"/>
       <c r="M48" s="148"/>
@@ -4208,18 +4219,18 @@
         <v>5</v>
       </c>
       <c r="D49" s="109" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E49" s="160"/>
       <c r="F49" s="148"/>
       <c r="G49" s="50" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H49" s="51"/>
       <c r="I49" s="60"/>
       <c r="J49" s="51"/>
       <c r="K49" s="50" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="L49" s="147"/>
       <c r="M49" s="148"/>
@@ -4239,18 +4250,18 @@
         <v>6</v>
       </c>
       <c r="D50" s="110" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E50" s="160"/>
       <c r="F50" s="148"/>
       <c r="G50" s="50" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H50" s="51"/>
       <c r="I50" s="60"/>
       <c r="J50" s="51"/>
       <c r="K50" s="50" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="L50" s="147"/>
       <c r="M50" s="148"/>
@@ -4270,18 +4281,18 @@
         <v>7</v>
       </c>
       <c r="D51" s="110" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E51" s="160"/>
       <c r="F51" s="148"/>
       <c r="G51" s="50" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H51" s="51"/>
       <c r="I51" s="52"/>
       <c r="J51" s="53"/>
       <c r="K51" s="50" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="L51" s="147"/>
       <c r="M51" s="148"/>
@@ -4320,56 +4331,56 @@
     </row>
     <row r="53" spans="2:23" ht="18" customHeight="1">
       <c r="B53" s="238" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C53" s="72"/>
       <c r="D53" s="72"/>
       <c r="E53" s="158" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F53" s="145"/>
       <c r="G53" s="150" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H53" s="145"/>
       <c r="I53" s="152" t="s">
+        <v>92</v>
+      </c>
+      <c r="J53" s="225" t="s">
         <v>93</v>
       </c>
-      <c r="J53" s="225" t="s">
-        <v>94</v>
-      </c>
       <c r="K53" s="150" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="L53" s="186"/>
       <c r="M53" s="145"/>
       <c r="N53" s="152" t="s">
+        <v>68</v>
+      </c>
+      <c r="O53" s="42" t="s">
+        <v>66</v>
+      </c>
+      <c r="P53" s="152" t="s">
         <v>69</v>
-      </c>
-      <c r="O53" s="42" t="s">
-        <v>67</v>
-      </c>
-      <c r="P53" s="152" t="s">
-        <v>70</v>
       </c>
       <c r="Q53" s="41"/>
       <c r="R53" s="152" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="S53" s="186"/>
       <c r="T53" s="145"/>
       <c r="U53" s="226" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="V53" s="43"/>
     </row>
     <row r="54" spans="2:23" ht="50.4" customHeight="1">
       <c r="B54" s="239"/>
       <c r="C54" s="41" t="s">
+        <v>72</v>
+      </c>
+      <c r="D54" s="41" t="s">
         <v>73</v>
-      </c>
-      <c r="D54" s="41" t="s">
-        <v>74</v>
       </c>
       <c r="E54" s="159"/>
       <c r="F54" s="141"/>
@@ -4382,11 +4393,11 @@
       <c r="M54" s="143"/>
       <c r="N54" s="153"/>
       <c r="O54" s="178" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="P54" s="153"/>
       <c r="Q54" s="44" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="R54" s="159"/>
       <c r="S54" s="187"/>
@@ -4397,33 +4408,33 @@
     <row r="55" spans="2:23" ht="50.4" customHeight="1">
       <c r="B55" s="239"/>
       <c r="C55" s="45" t="s">
+        <v>76</v>
+      </c>
+      <c r="D55" s="45" t="s">
         <v>77</v>
-      </c>
-      <c r="D55" s="45" t="s">
-        <v>78</v>
       </c>
       <c r="E55" s="151"/>
       <c r="F55" s="143"/>
       <c r="G55" s="46" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H55" s="73" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I55" s="154"/>
       <c r="J55" s="154"/>
       <c r="K55" s="46" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="L55" s="150" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="M55" s="148"/>
       <c r="N55" s="154"/>
       <c r="O55" s="154"/>
       <c r="P55" s="154"/>
       <c r="Q55" s="47" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="R55" s="151"/>
       <c r="S55" s="188"/>
@@ -4437,18 +4448,18 @@
         <v>1</v>
       </c>
       <c r="D56" s="49" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E56" s="160"/>
       <c r="F56" s="148"/>
       <c r="G56" s="50" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H56" s="51"/>
       <c r="I56" s="74"/>
       <c r="J56" s="51"/>
       <c r="K56" s="50" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="L56" s="147"/>
       <c r="M56" s="148"/>
@@ -4468,18 +4479,18 @@
         <v>2</v>
       </c>
       <c r="D57" s="75" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E57" s="160"/>
       <c r="F57" s="148"/>
       <c r="G57" s="50" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H57" s="51"/>
       <c r="I57" s="76"/>
       <c r="J57" s="53"/>
       <c r="K57" s="50" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="L57" s="147"/>
       <c r="M57" s="148"/>
@@ -4499,18 +4510,18 @@
         <v>3</v>
       </c>
       <c r="D58" s="77" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E58" s="160"/>
       <c r="F58" s="148"/>
       <c r="G58" s="50" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H58" s="51"/>
       <c r="I58" s="76"/>
       <c r="J58" s="51"/>
       <c r="K58" s="50" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="L58" s="147"/>
       <c r="M58" s="148"/>
@@ -4530,18 +4541,18 @@
         <v>4</v>
       </c>
       <c r="D59" s="79" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E59" s="160"/>
       <c r="F59" s="148"/>
       <c r="G59" s="50" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H59" s="51"/>
       <c r="I59" s="80"/>
       <c r="J59" s="81"/>
       <c r="K59" s="59" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="L59" s="147"/>
       <c r="M59" s="148"/>
@@ -4561,18 +4572,18 @@
         <v>5</v>
       </c>
       <c r="D60" s="79" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E60" s="160"/>
       <c r="F60" s="148"/>
       <c r="G60" s="50" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H60" s="51"/>
       <c r="I60" s="80"/>
       <c r="J60" s="81"/>
       <c r="K60" s="59" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="L60" s="147"/>
       <c r="M60" s="148"/>
@@ -4592,18 +4603,18 @@
         <v>6</v>
       </c>
       <c r="D61" s="85" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E61" s="160"/>
       <c r="F61" s="148"/>
       <c r="G61" s="59" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H61" s="86"/>
       <c r="I61" s="81"/>
       <c r="J61" s="86"/>
       <c r="K61" s="84" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="L61" s="147"/>
       <c r="M61" s="148"/>
@@ -4619,14 +4630,14 @@
     </row>
     <row r="62" spans="2:23" s="88" customFormat="1" ht="23.25" customHeight="1" thickBot="1">
       <c r="B62" s="229" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C62" s="223"/>
       <c r="D62" s="223"/>
       <c r="E62" s="223"/>
       <c r="F62" s="230"/>
       <c r="G62" s="232" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H62" s="223"/>
       <c r="I62" s="223"/>
@@ -4635,7 +4646,7 @@
       <c r="L62" s="223"/>
       <c r="M62" s="230"/>
       <c r="N62" s="222" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="O62" s="223"/>
       <c r="P62" s="223"/>

--- a/jo.xlsx
+++ b/jo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\production_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5098E19-ECD3-4DCB-940A-634C11017550}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F90296E-414C-44DF-BBC5-A2555E5355EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -409,7 +409,7 @@
     <numFmt numFmtId="167" formatCode="&quot; &quot;#,##0&quot; &quot;;&quot; (&quot;#,##0&quot;)&quot;;&quot; - &quot;;@&quot; &quot;"/>
     <numFmt numFmtId="168" formatCode="[$-402]0%"/>
   </numFmts>
-  <fonts count="69">
+  <fonts count="70">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -905,6 +905,13 @@
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="40"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="204"/>
     </font>
   </fonts>
   <fills count="16">
@@ -1926,7 +1933,7 @@
     <xf numFmtId="0" fontId="49" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="319">
+  <cellXfs count="320">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2237,333 +2244,28 @@
     <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="61" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="34" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="35" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="40" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="57" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="36" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="37" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="50" fillId="0" borderId="34" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="50" fillId="0" borderId="35" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="50" fillId="0" borderId="40" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="50" fillId="0" borderId="57" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="50" fillId="0" borderId="36" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="50" fillId="0" borderId="37" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="59" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="59" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="44" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="45" fillId="0" borderId="31" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="41" fillId="0" borderId="34" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="41" fillId="0" borderId="42" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="43" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="41" fillId="0" borderId="40" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="41" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="41" fillId="0" borderId="36" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="41" fillId="0" borderId="44" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="51" xfId="0" applyBorder="1"/>
-    <xf numFmtId="49" fontId="42" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="55" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="24" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="55" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="60" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="24" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="62" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="58" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="60" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
-    <xf numFmtId="49" fontId="27" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="59" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="52" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="53" xfId="0" applyBorder="1"/>
-    <xf numFmtId="3" fontId="48" fillId="0" borderId="54" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="64" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="64" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="41" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="17" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="38" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="57" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1"/>
-    <xf numFmtId="43" fontId="60" fillId="0" borderId="5" xfId="26" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="44" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="20" xfId="26" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="33" fillId="0" borderId="65" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="72" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="73" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="68" fillId="0" borderId="20" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="43" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="41" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="41" fillId="0" borderId="45" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2577,6 +2279,19 @@
     <xf numFmtId="0" fontId="56" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="56" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="56" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="48" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2594,6 +2309,12 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="63" fillId="7" borderId="65" xfId="26" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2606,6 +2327,12 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="34" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2614,9 +2341,12 @@
     <xf numFmtId="0" fontId="62" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2641,8 +2371,288 @@
     <xf numFmtId="0" fontId="41" fillId="0" borderId="68" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="55" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="44" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="20" xfId="26" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="52" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="53" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="33" fillId="0" borderId="65" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="72" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="73" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="68" fillId="0" borderId="20" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="64" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="64" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" applyBorder="1"/>
+    <xf numFmtId="3" fontId="41" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="17" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="38" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="57" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="60" fillId="0" borderId="5" xfId="26" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="48" fillId="0" borderId="54" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" xfId="0" applyBorder="1"/>
+    <xf numFmtId="3" fontId="60" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="24" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="62" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="58" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="60" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="27" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="59" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="45" fillId="0" borderId="31" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="51" xfId="0" applyBorder="1"/>
+    <xf numFmtId="49" fontId="42" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="24" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="55" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="61" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="34" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="35" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="40" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="57" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="36" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="37" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="50" fillId="0" borderId="34" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="50" fillId="0" borderId="35" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="50" fillId="0" borderId="40" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="50" fillId="0" borderId="57" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="50" fillId="0" borderId="36" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="50" fillId="0" borderId="37" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="44" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="69" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="29">
@@ -2987,70 +2997,70 @@
       <c r="A1" s="1">
         <v>24</v>
       </c>
-      <c r="B1" s="138"/>
-      <c r="C1" s="139"/>
-      <c r="D1" s="243" t="s">
+      <c r="B1" s="296"/>
+      <c r="C1" s="297"/>
+      <c r="D1" s="234" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="278" t="s">
+      <c r="E1" s="147" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="279"/>
-      <c r="G1" s="279"/>
-      <c r="H1" s="279"/>
-      <c r="I1" s="279"/>
-      <c r="J1" s="279"/>
-      <c r="K1" s="279"/>
-      <c r="L1" s="279"/>
-      <c r="M1" s="279"/>
-      <c r="N1" s="280"/>
-      <c r="O1" s="288" t="s">
+      <c r="F1" s="148"/>
+      <c r="G1" s="148"/>
+      <c r="H1" s="148"/>
+      <c r="I1" s="148"/>
+      <c r="J1" s="148"/>
+      <c r="K1" s="148"/>
+      <c r="L1" s="148"/>
+      <c r="M1" s="148"/>
+      <c r="N1" s="149"/>
+      <c r="O1" s="164" t="s">
         <v>2</v>
       </c>
-      <c r="P1" s="289"/>
-      <c r="Q1" s="289"/>
-      <c r="R1" s="289"/>
-      <c r="S1" s="289"/>
-      <c r="T1" s="289"/>
-      <c r="U1" s="290"/>
+      <c r="P1" s="165"/>
+      <c r="Q1" s="165"/>
+      <c r="R1" s="165"/>
+      <c r="S1" s="165"/>
+      <c r="T1" s="165"/>
+      <c r="U1" s="166"/>
     </row>
     <row r="2" spans="1:22" s="1" customFormat="1" ht="18.75" customHeight="1">
-      <c r="B2" s="140"/>
-      <c r="C2" s="141"/>
-      <c r="D2" s="244"/>
-      <c r="E2" s="281"/>
-      <c r="F2" s="282"/>
-      <c r="G2" s="282"/>
-      <c r="H2" s="282"/>
-      <c r="I2" s="282"/>
-      <c r="J2" s="282"/>
-      <c r="K2" s="282"/>
-      <c r="L2" s="282"/>
-      <c r="M2" s="282"/>
-      <c r="N2" s="283"/>
-      <c r="O2" s="291"/>
-      <c r="P2" s="292"/>
-      <c r="Q2" s="292"/>
-      <c r="R2" s="292"/>
-      <c r="S2" s="292"/>
-      <c r="T2" s="292"/>
-      <c r="U2" s="293"/>
+      <c r="B2" s="236"/>
+      <c r="C2" s="188"/>
+      <c r="D2" s="232"/>
+      <c r="E2" s="150"/>
+      <c r="F2" s="151"/>
+      <c r="G2" s="151"/>
+      <c r="H2" s="151"/>
+      <c r="I2" s="151"/>
+      <c r="J2" s="151"/>
+      <c r="K2" s="151"/>
+      <c r="L2" s="151"/>
+      <c r="M2" s="151"/>
+      <c r="N2" s="152"/>
+      <c r="O2" s="167"/>
+      <c r="P2" s="168"/>
+      <c r="Q2" s="168"/>
+      <c r="R2" s="168"/>
+      <c r="S2" s="168"/>
+      <c r="T2" s="168"/>
+      <c r="U2" s="169"/>
     </row>
     <row r="3" spans="1:22" ht="12.45" customHeight="1">
-      <c r="B3" s="140"/>
-      <c r="C3" s="141"/>
-      <c r="D3" s="157" t="s">
+      <c r="B3" s="236"/>
+      <c r="C3" s="188"/>
+      <c r="D3" s="259" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="294" t="s">
+      <c r="E3" s="170" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="186"/>
-      <c r="G3" s="186"/>
-      <c r="H3" s="186"/>
-      <c r="I3" s="186"/>
-      <c r="J3" s="186"/>
-      <c r="K3" s="186"/>
+      <c r="F3" s="171"/>
+      <c r="G3" s="171"/>
+      <c r="H3" s="171"/>
+      <c r="I3" s="171"/>
+      <c r="J3" s="171"/>
+      <c r="K3" s="171"/>
       <c r="L3" s="128"/>
       <c r="M3" s="5"/>
       <c r="N3" s="5"/>
@@ -3063,49 +3073,49 @@
       <c r="U3" s="129"/>
     </row>
     <row r="4" spans="1:22" ht="14.85" customHeight="1">
-      <c r="B4" s="140"/>
-      <c r="C4" s="141"/>
-      <c r="D4" s="153"/>
-      <c r="E4" s="159"/>
-      <c r="F4" s="187"/>
-      <c r="G4" s="187"/>
-      <c r="H4" s="187"/>
-      <c r="I4" s="187"/>
-      <c r="J4" s="187"/>
-      <c r="K4" s="265"/>
+      <c r="B4" s="236"/>
+      <c r="C4" s="188"/>
+      <c r="D4" s="154"/>
+      <c r="E4" s="172"/>
+      <c r="F4" s="173"/>
+      <c r="G4" s="173"/>
+      <c r="H4" s="173"/>
+      <c r="I4" s="173"/>
+      <c r="J4" s="173"/>
+      <c r="K4" s="174"/>
       <c r="L4" s="130"/>
       <c r="U4" s="131"/>
     </row>
     <row r="5" spans="1:22" ht="14.85" customHeight="1">
-      <c r="B5" s="142"/>
-      <c r="C5" s="143"/>
-      <c r="D5" s="154"/>
-      <c r="E5" s="151"/>
-      <c r="F5" s="188"/>
-      <c r="G5" s="188"/>
-      <c r="H5" s="188"/>
-      <c r="I5" s="188"/>
-      <c r="J5" s="188"/>
-      <c r="K5" s="188"/>
+      <c r="B5" s="217"/>
+      <c r="C5" s="186"/>
+      <c r="D5" s="155"/>
+      <c r="E5" s="175"/>
+      <c r="F5" s="176"/>
+      <c r="G5" s="176"/>
+      <c r="H5" s="176"/>
+      <c r="I5" s="176"/>
+      <c r="J5" s="176"/>
+      <c r="K5" s="176"/>
       <c r="L5" s="130"/>
       <c r="U5" s="131"/>
     </row>
     <row r="6" spans="1:22" s="2" customFormat="1" ht="27.75" customHeight="1">
-      <c r="B6" s="149" t="s">
+      <c r="B6" s="247" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="145"/>
-      <c r="D6" s="177"/>
-      <c r="E6" s="264" t="s">
+      <c r="C6" s="185"/>
+      <c r="D6" s="317"/>
+      <c r="E6" s="215" t="s">
         <v>6</v>
       </c>
-      <c r="F6" s="186"/>
-      <c r="G6" s="186"/>
-      <c r="H6" s="145"/>
-      <c r="I6" s="262" t="s">
+      <c r="F6" s="171"/>
+      <c r="G6" s="171"/>
+      <c r="H6" s="185"/>
+      <c r="I6" s="213" t="s">
         <v>7</v>
       </c>
-      <c r="J6" s="148"/>
+      <c r="J6" s="157"/>
       <c r="K6" s="102" t="s">
         <v>8</v>
       </c>
@@ -3113,55 +3123,55 @@
       <c r="U6" s="131"/>
     </row>
     <row r="7" spans="1:22" s="2" customFormat="1" ht="28.5" customHeight="1">
-      <c r="B7" s="142"/>
-      <c r="C7" s="143"/>
-      <c r="D7" s="154"/>
-      <c r="E7" s="159"/>
-      <c r="F7" s="265"/>
-      <c r="G7" s="265"/>
-      <c r="H7" s="141"/>
-      <c r="I7" s="263"/>
-      <c r="J7" s="148"/>
+      <c r="B7" s="217"/>
+      <c r="C7" s="186"/>
+      <c r="D7" s="155"/>
+      <c r="E7" s="172"/>
+      <c r="F7" s="174"/>
+      <c r="G7" s="174"/>
+      <c r="H7" s="188"/>
+      <c r="I7" s="214"/>
+      <c r="J7" s="157"/>
       <c r="K7" s="103"/>
       <c r="L7" s="130"/>
       <c r="P7" s="135"/>
       <c r="U7" s="131"/>
     </row>
     <row r="8" spans="1:22" s="2" customFormat="1" ht="31.95" customHeight="1">
-      <c r="B8" s="149" t="s">
+      <c r="B8" s="247" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="145"/>
-      <c r="D8" s="250"/>
-      <c r="E8" s="161" t="s">
+      <c r="C8" s="185"/>
+      <c r="D8" s="242"/>
+      <c r="E8" s="301" t="s">
         <v>101</v>
       </c>
-      <c r="F8" s="162"/>
-      <c r="G8" s="167" t="s">
+      <c r="F8" s="302"/>
+      <c r="G8" s="307" t="s">
         <v>100</v>
       </c>
-      <c r="H8" s="168"/>
-      <c r="I8" s="215" t="s">
+      <c r="H8" s="308"/>
+      <c r="I8" s="263" t="s">
         <v>103</v>
       </c>
-      <c r="J8" s="216"/>
-      <c r="K8" s="271"/>
+      <c r="J8" s="264"/>
+      <c r="K8" s="228"/>
       <c r="L8" s="130"/>
       <c r="P8" s="135"/>
       <c r="U8" s="131"/>
       <c r="V8" s="101"/>
     </row>
     <row r="9" spans="1:22" s="2" customFormat="1" ht="3.75" hidden="1" customHeight="1">
-      <c r="B9" s="142"/>
-      <c r="C9" s="143"/>
-      <c r="D9" s="151"/>
-      <c r="E9" s="163"/>
-      <c r="F9" s="164"/>
-      <c r="G9" s="169"/>
-      <c r="H9" s="170"/>
-      <c r="I9" s="217"/>
-      <c r="J9" s="218"/>
-      <c r="K9" s="272"/>
+      <c r="B9" s="217"/>
+      <c r="C9" s="186"/>
+      <c r="D9" s="175"/>
+      <c r="E9" s="303"/>
+      <c r="F9" s="304"/>
+      <c r="G9" s="309"/>
+      <c r="H9" s="310"/>
+      <c r="I9" s="265"/>
+      <c r="J9" s="266"/>
+      <c r="K9" s="229"/>
       <c r="L9" s="130"/>
       <c r="P9" s="135" t="str">
         <f t="shared" ref="P9" si="0">"*"&amp;J18&amp;"*"</f>
@@ -3171,34 +3181,34 @@
       <c r="V9" s="101"/>
     </row>
     <row r="10" spans="1:22" s="2" customFormat="1" ht="15" customHeight="1">
-      <c r="B10" s="259" t="s">
+      <c r="B10" s="254" t="s">
         <v>11</v>
       </c>
-      <c r="C10" s="145"/>
-      <c r="D10" s="274"/>
-      <c r="E10" s="165"/>
-      <c r="F10" s="166"/>
-      <c r="G10" s="171"/>
-      <c r="H10" s="172"/>
-      <c r="I10" s="217"/>
-      <c r="J10" s="218"/>
-      <c r="K10" s="272"/>
+      <c r="C10" s="185"/>
+      <c r="D10" s="231"/>
+      <c r="E10" s="305"/>
+      <c r="F10" s="306"/>
+      <c r="G10" s="311"/>
+      <c r="H10" s="312"/>
+      <c r="I10" s="265"/>
+      <c r="J10" s="266"/>
+      <c r="K10" s="229"/>
       <c r="L10" s="130"/>
       <c r="P10" s="135"/>
       <c r="U10" s="131"/>
       <c r="V10" s="101"/>
     </row>
     <row r="11" spans="1:22" s="2" customFormat="1" ht="78.599999999999994" customHeight="1">
-      <c r="B11" s="142"/>
-      <c r="C11" s="143"/>
-      <c r="D11" s="244"/>
-      <c r="E11" s="173"/>
-      <c r="F11" s="174"/>
-      <c r="G11" s="175"/>
-      <c r="H11" s="176"/>
-      <c r="I11" s="219"/>
-      <c r="J11" s="220"/>
-      <c r="K11" s="273"/>
+      <c r="B11" s="217"/>
+      <c r="C11" s="186"/>
+      <c r="D11" s="232"/>
+      <c r="E11" s="313"/>
+      <c r="F11" s="314"/>
+      <c r="G11" s="315"/>
+      <c r="H11" s="316"/>
+      <c r="I11" s="267"/>
+      <c r="J11" s="268"/>
+      <c r="K11" s="230"/>
       <c r="L11" s="130"/>
       <c r="M11" s="136" t="str">
         <f>"*"&amp;J16&amp;"*"</f>
@@ -3213,71 +3223,71 @@
       <c r="V11" s="101"/>
     </row>
     <row r="12" spans="1:22" s="2" customFormat="1" ht="28.5" customHeight="1">
-      <c r="B12" s="179" t="s">
+      <c r="B12" s="318" t="s">
         <v>12</v>
       </c>
-      <c r="C12" s="145"/>
-      <c r="D12" s="256" t="s">
+      <c r="C12" s="185"/>
+      <c r="D12" s="249" t="s">
         <v>102</v>
       </c>
-      <c r="E12" s="185"/>
-      <c r="F12" s="186"/>
-      <c r="G12" s="186"/>
-      <c r="H12" s="145"/>
-      <c r="I12" s="303" t="s">
+      <c r="E12" s="284"/>
+      <c r="F12" s="171"/>
+      <c r="G12" s="171"/>
+      <c r="H12" s="185"/>
+      <c r="I12" s="189" t="s">
         <v>13</v>
       </c>
-      <c r="J12" s="304"/>
-      <c r="K12" s="204"/>
+      <c r="J12" s="190"/>
+      <c r="K12" s="291"/>
       <c r="L12" s="130"/>
       <c r="U12" s="131"/>
     </row>
     <row r="13" spans="1:22" s="2" customFormat="1" ht="13.5" customHeight="1">
-      <c r="B13" s="142"/>
-      <c r="C13" s="143"/>
-      <c r="D13" s="214"/>
-      <c r="E13" s="159"/>
-      <c r="F13" s="187"/>
-      <c r="G13" s="187"/>
-      <c r="H13" s="141"/>
-      <c r="I13" s="305"/>
-      <c r="J13" s="306"/>
-      <c r="K13" s="159"/>
+      <c r="B13" s="217"/>
+      <c r="C13" s="186"/>
+      <c r="D13" s="250"/>
+      <c r="E13" s="172"/>
+      <c r="F13" s="173"/>
+      <c r="G13" s="173"/>
+      <c r="H13" s="188"/>
+      <c r="I13" s="191"/>
+      <c r="J13" s="192"/>
+      <c r="K13" s="172"/>
       <c r="L13" s="130"/>
       <c r="U13" s="131"/>
     </row>
     <row r="14" spans="1:22" s="2" customFormat="1" ht="15" customHeight="1">
-      <c r="B14" s="189" t="s">
+      <c r="B14" s="285" t="s">
         <v>14</v>
       </c>
-      <c r="C14" s="145"/>
-      <c r="D14" s="213" t="s">
+      <c r="C14" s="185"/>
+      <c r="D14" s="262" t="s">
         <v>107</v>
       </c>
-      <c r="E14" s="159"/>
-      <c r="F14" s="187"/>
-      <c r="G14" s="187"/>
-      <c r="H14" s="141"/>
-      <c r="I14" s="305"/>
-      <c r="J14" s="306"/>
-      <c r="K14" s="159"/>
+      <c r="E14" s="172"/>
+      <c r="F14" s="173"/>
+      <c r="G14" s="173"/>
+      <c r="H14" s="188"/>
+      <c r="I14" s="191"/>
+      <c r="J14" s="192"/>
+      <c r="K14" s="172"/>
       <c r="L14" s="130"/>
       <c r="U14" s="131"/>
     </row>
     <row r="15" spans="1:22" s="2" customFormat="1" ht="48" customHeight="1">
-      <c r="B15" s="142"/>
-      <c r="C15" s="143"/>
-      <c r="D15" s="214"/>
-      <c r="E15" s="151"/>
-      <c r="F15" s="188"/>
-      <c r="G15" s="188"/>
-      <c r="H15" s="143"/>
-      <c r="I15" s="307"/>
-      <c r="J15" s="308"/>
-      <c r="K15" s="151"/>
+      <c r="B15" s="217"/>
+      <c r="C15" s="186"/>
+      <c r="D15" s="250"/>
+      <c r="E15" s="175"/>
+      <c r="F15" s="176"/>
+      <c r="G15" s="176"/>
+      <c r="H15" s="186"/>
+      <c r="I15" s="193"/>
+      <c r="J15" s="194"/>
+      <c r="K15" s="175"/>
       <c r="L15" s="132"/>
       <c r="M15" s="133"/>
-      <c r="N15" s="133"/>
+      <c r="N15" s="319"/>
       <c r="O15" s="133"/>
       <c r="P15" s="133"/>
       <c r="Q15" s="133"/>
@@ -3287,145 +3297,145 @@
       <c r="U15" s="134"/>
     </row>
     <row r="16" spans="1:22" s="2" customFormat="1" ht="15" customHeight="1">
-      <c r="B16" s="149" t="s">
+      <c r="B16" s="247" t="s">
         <v>15</v>
       </c>
-      <c r="C16" s="145"/>
-      <c r="D16" s="221"/>
-      <c r="E16" s="200" t="s">
+      <c r="C16" s="185"/>
+      <c r="D16" s="269"/>
+      <c r="E16" s="248" t="s">
         <v>16</v>
       </c>
-      <c r="F16" s="186"/>
-      <c r="G16" s="186"/>
-      <c r="H16" s="186"/>
-      <c r="I16" s="145"/>
-      <c r="J16" s="267">
+      <c r="F16" s="171"/>
+      <c r="G16" s="171"/>
+      <c r="H16" s="171"/>
+      <c r="I16" s="185"/>
+      <c r="J16" s="218">
         <v>232323</v>
       </c>
-      <c r="K16" s="253"/>
-      <c r="L16" s="192" t="s">
+      <c r="K16" s="219"/>
+      <c r="L16" s="138" t="s">
         <v>104</v>
       </c>
-      <c r="M16" s="193"/>
-      <c r="N16" s="193"/>
-      <c r="O16" s="193"/>
-      <c r="P16" s="193"/>
-      <c r="Q16" s="193"/>
-      <c r="R16" s="193"/>
-      <c r="S16" s="192" t="s">
+      <c r="M16" s="139"/>
+      <c r="N16" s="139"/>
+      <c r="O16" s="139"/>
+      <c r="P16" s="139"/>
+      <c r="Q16" s="139"/>
+      <c r="R16" s="139"/>
+      <c r="S16" s="138" t="s">
         <v>105</v>
       </c>
-      <c r="T16" s="193"/>
-      <c r="U16" s="275"/>
+      <c r="T16" s="139"/>
+      <c r="U16" s="140"/>
     </row>
     <row r="17" spans="2:22" s="2" customFormat="1" ht="15" customHeight="1">
-      <c r="B17" s="142"/>
-      <c r="C17" s="143"/>
-      <c r="D17" s="214"/>
-      <c r="E17" s="159"/>
-      <c r="F17" s="187"/>
-      <c r="G17" s="187"/>
-      <c r="H17" s="187"/>
-      <c r="I17" s="141"/>
-      <c r="J17" s="159"/>
-      <c r="K17" s="268"/>
-      <c r="L17" s="194"/>
-      <c r="M17" s="195"/>
-      <c r="N17" s="195"/>
-      <c r="O17" s="195"/>
-      <c r="P17" s="195"/>
-      <c r="Q17" s="195"/>
-      <c r="R17" s="195"/>
-      <c r="S17" s="194"/>
-      <c r="T17" s="195"/>
-      <c r="U17" s="276"/>
+      <c r="B17" s="217"/>
+      <c r="C17" s="186"/>
+      <c r="D17" s="250"/>
+      <c r="E17" s="172"/>
+      <c r="F17" s="173"/>
+      <c r="G17" s="173"/>
+      <c r="H17" s="173"/>
+      <c r="I17" s="188"/>
+      <c r="J17" s="172"/>
+      <c r="K17" s="220"/>
+      <c r="L17" s="141"/>
+      <c r="M17" s="142"/>
+      <c r="N17" s="142"/>
+      <c r="O17" s="142"/>
+      <c r="P17" s="142"/>
+      <c r="Q17" s="142"/>
+      <c r="R17" s="142"/>
+      <c r="S17" s="141"/>
+      <c r="T17" s="142"/>
+      <c r="U17" s="143"/>
     </row>
     <row r="18" spans="2:22" s="2" customFormat="1" ht="15" customHeight="1">
-      <c r="B18" s="146" t="s">
+      <c r="B18" s="298" t="s">
         <v>17</v>
       </c>
-      <c r="C18" s="145"/>
-      <c r="D18" s="248" t="s">
+      <c r="C18" s="185"/>
+      <c r="D18" s="240" t="s">
         <v>109</v>
       </c>
-      <c r="E18" s="159"/>
-      <c r="F18" s="187"/>
-      <c r="G18" s="187"/>
-      <c r="H18" s="187"/>
-      <c r="I18" s="141"/>
-      <c r="J18" s="159"/>
-      <c r="K18" s="268"/>
-      <c r="L18" s="194"/>
-      <c r="M18" s="195"/>
-      <c r="N18" s="195"/>
-      <c r="O18" s="195"/>
-      <c r="P18" s="195"/>
-      <c r="Q18" s="195"/>
-      <c r="R18" s="195"/>
-      <c r="S18" s="194"/>
-      <c r="T18" s="195"/>
-      <c r="U18" s="276"/>
+      <c r="E18" s="172"/>
+      <c r="F18" s="173"/>
+      <c r="G18" s="173"/>
+      <c r="H18" s="173"/>
+      <c r="I18" s="188"/>
+      <c r="J18" s="172"/>
+      <c r="K18" s="220"/>
+      <c r="L18" s="141"/>
+      <c r="M18" s="142"/>
+      <c r="N18" s="142"/>
+      <c r="O18" s="142"/>
+      <c r="P18" s="142"/>
+      <c r="Q18" s="142"/>
+      <c r="R18" s="142"/>
+      <c r="S18" s="141"/>
+      <c r="T18" s="142"/>
+      <c r="U18" s="143"/>
     </row>
     <row r="19" spans="2:22" s="2" customFormat="1" ht="15" customHeight="1">
-      <c r="B19" s="142"/>
-      <c r="C19" s="143"/>
-      <c r="D19" s="249"/>
-      <c r="E19" s="151"/>
-      <c r="F19" s="188"/>
-      <c r="G19" s="188"/>
-      <c r="H19" s="188"/>
-      <c r="I19" s="143"/>
-      <c r="J19" s="151"/>
-      <c r="K19" s="255"/>
-      <c r="L19" s="196"/>
-      <c r="M19" s="197"/>
-      <c r="N19" s="197"/>
-      <c r="O19" s="197"/>
-      <c r="P19" s="197"/>
-      <c r="Q19" s="197"/>
-      <c r="R19" s="197"/>
-      <c r="S19" s="196"/>
-      <c r="T19" s="197"/>
-      <c r="U19" s="277"/>
+      <c r="B19" s="217"/>
+      <c r="C19" s="186"/>
+      <c r="D19" s="241"/>
+      <c r="E19" s="175"/>
+      <c r="F19" s="176"/>
+      <c r="G19" s="176"/>
+      <c r="H19" s="176"/>
+      <c r="I19" s="186"/>
+      <c r="J19" s="175"/>
+      <c r="K19" s="221"/>
+      <c r="L19" s="144"/>
+      <c r="M19" s="145"/>
+      <c r="N19" s="145"/>
+      <c r="O19" s="145"/>
+      <c r="P19" s="145"/>
+      <c r="Q19" s="145"/>
+      <c r="R19" s="145"/>
+      <c r="S19" s="144"/>
+      <c r="T19" s="145"/>
+      <c r="U19" s="146"/>
     </row>
     <row r="20" spans="2:22" s="2" customFormat="1" ht="15" customHeight="1">
-      <c r="B20" s="149" t="s">
+      <c r="B20" s="247" t="s">
         <v>18</v>
       </c>
-      <c r="C20" s="145"/>
-      <c r="D20" s="260"/>
-      <c r="E20" s="200" t="s">
+      <c r="C20" s="185"/>
+      <c r="D20" s="255"/>
+      <c r="E20" s="248" t="s">
         <v>106</v>
       </c>
-      <c r="F20" s="186"/>
-      <c r="G20" s="186"/>
-      <c r="H20" s="186"/>
-      <c r="I20" s="145"/>
-      <c r="J20" s="252"/>
-      <c r="K20" s="253"/>
-      <c r="L20" s="316"/>
-      <c r="M20" s="317"/>
-      <c r="N20" s="317"/>
-      <c r="O20" s="317"/>
-      <c r="P20" s="317"/>
-      <c r="Q20" s="317"/>
-      <c r="R20" s="317"/>
-      <c r="S20" s="317"/>
-      <c r="T20" s="317"/>
-      <c r="U20" s="317"/>
+      <c r="F20" s="171"/>
+      <c r="G20" s="171"/>
+      <c r="H20" s="171"/>
+      <c r="I20" s="185"/>
+      <c r="J20" s="244"/>
+      <c r="K20" s="219"/>
+      <c r="L20" s="205"/>
+      <c r="M20" s="206"/>
+      <c r="N20" s="206"/>
+      <c r="O20" s="206"/>
+      <c r="P20" s="206"/>
+      <c r="Q20" s="206"/>
+      <c r="R20" s="206"/>
+      <c r="S20" s="206"/>
+      <c r="T20" s="206"/>
+      <c r="U20" s="206"/>
       <c r="V20" s="122"/>
     </row>
     <row r="21" spans="2:22" s="2" customFormat="1" ht="62.4" customHeight="1">
-      <c r="B21" s="142"/>
-      <c r="C21" s="143"/>
-      <c r="D21" s="154"/>
-      <c r="E21" s="159"/>
-      <c r="F21" s="187"/>
-      <c r="G21" s="187"/>
-      <c r="H21" s="187"/>
-      <c r="I21" s="141"/>
-      <c r="J21" s="159"/>
-      <c r="K21" s="254"/>
+      <c r="B21" s="217"/>
+      <c r="C21" s="186"/>
+      <c r="D21" s="155"/>
+      <c r="E21" s="172"/>
+      <c r="F21" s="173"/>
+      <c r="G21" s="173"/>
+      <c r="H21" s="173"/>
+      <c r="I21" s="188"/>
+      <c r="J21" s="172"/>
+      <c r="K21" s="245"/>
       <c r="L21" s="123"/>
       <c r="M21" s="124"/>
       <c r="N21" s="124"/>
@@ -3439,79 +3449,79 @@
       <c r="V21" s="122"/>
     </row>
     <row r="22" spans="2:22" s="2" customFormat="1" ht="15" customHeight="1">
-      <c r="B22" s="149" t="s">
+      <c r="B22" s="247" t="s">
         <v>19</v>
       </c>
-      <c r="C22" s="145"/>
-      <c r="D22" s="261"/>
-      <c r="E22" s="159"/>
-      <c r="F22" s="187"/>
-      <c r="G22" s="187"/>
-      <c r="H22" s="187"/>
-      <c r="I22" s="141"/>
-      <c r="J22" s="159"/>
-      <c r="K22" s="254"/>
-      <c r="L22" s="310"/>
-      <c r="M22" s="310"/>
-      <c r="N22" s="310"/>
-      <c r="O22" s="310"/>
-      <c r="P22" s="310"/>
-      <c r="Q22" s="310"/>
-      <c r="R22" s="310"/>
-      <c r="S22" s="310"/>
-      <c r="T22" s="310"/>
-      <c r="U22" s="311"/>
+      <c r="C22" s="185"/>
+      <c r="D22" s="212"/>
+      <c r="E22" s="172"/>
+      <c r="F22" s="173"/>
+      <c r="G22" s="173"/>
+      <c r="H22" s="173"/>
+      <c r="I22" s="188"/>
+      <c r="J22" s="172"/>
+      <c r="K22" s="245"/>
+      <c r="L22" s="199"/>
+      <c r="M22" s="199"/>
+      <c r="N22" s="199"/>
+      <c r="O22" s="199"/>
+      <c r="P22" s="199"/>
+      <c r="Q22" s="199"/>
+      <c r="R22" s="199"/>
+      <c r="S22" s="199"/>
+      <c r="T22" s="199"/>
+      <c r="U22" s="200"/>
     </row>
     <row r="23" spans="2:22" s="2" customFormat="1" ht="15" customHeight="1">
-      <c r="B23" s="140"/>
-      <c r="C23" s="141"/>
-      <c r="D23" s="153"/>
-      <c r="E23" s="159"/>
-      <c r="F23" s="187"/>
-      <c r="G23" s="187"/>
-      <c r="H23" s="187"/>
-      <c r="I23" s="141"/>
-      <c r="J23" s="159"/>
-      <c r="K23" s="254"/>
-      <c r="L23" s="312"/>
-      <c r="M23" s="312"/>
-      <c r="N23" s="312"/>
-      <c r="O23" s="312"/>
-      <c r="P23" s="312"/>
-      <c r="Q23" s="312"/>
-      <c r="R23" s="312"/>
-      <c r="S23" s="312"/>
-      <c r="T23" s="312"/>
-      <c r="U23" s="313"/>
+      <c r="B23" s="236"/>
+      <c r="C23" s="188"/>
+      <c r="D23" s="154"/>
+      <c r="E23" s="172"/>
+      <c r="F23" s="173"/>
+      <c r="G23" s="173"/>
+      <c r="H23" s="173"/>
+      <c r="I23" s="188"/>
+      <c r="J23" s="172"/>
+      <c r="K23" s="245"/>
+      <c r="L23" s="201"/>
+      <c r="M23" s="201"/>
+      <c r="N23" s="201"/>
+      <c r="O23" s="201"/>
+      <c r="P23" s="201"/>
+      <c r="Q23" s="201"/>
+      <c r="R23" s="201"/>
+      <c r="S23" s="201"/>
+      <c r="T23" s="201"/>
+      <c r="U23" s="202"/>
     </row>
     <row r="24" spans="2:22" s="2" customFormat="1" ht="7.5" customHeight="1">
-      <c r="B24" s="142"/>
-      <c r="C24" s="143"/>
-      <c r="D24" s="154"/>
-      <c r="E24" s="151"/>
-      <c r="F24" s="188"/>
-      <c r="G24" s="188"/>
-      <c r="H24" s="188"/>
-      <c r="I24" s="143"/>
-      <c r="J24" s="151"/>
-      <c r="K24" s="255"/>
-      <c r="L24" s="314"/>
-      <c r="M24" s="314"/>
-      <c r="N24" s="314"/>
-      <c r="O24" s="314"/>
-      <c r="P24" s="314"/>
-      <c r="Q24" s="314"/>
-      <c r="R24" s="314"/>
-      <c r="S24" s="314"/>
-      <c r="T24" s="314"/>
-      <c r="U24" s="315"/>
+      <c r="B24" s="217"/>
+      <c r="C24" s="186"/>
+      <c r="D24" s="155"/>
+      <c r="E24" s="175"/>
+      <c r="F24" s="176"/>
+      <c r="G24" s="176"/>
+      <c r="H24" s="176"/>
+      <c r="I24" s="186"/>
+      <c r="J24" s="175"/>
+      <c r="K24" s="221"/>
+      <c r="L24" s="203"/>
+      <c r="M24" s="203"/>
+      <c r="N24" s="203"/>
+      <c r="O24" s="203"/>
+      <c r="P24" s="203"/>
+      <c r="Q24" s="203"/>
+      <c r="R24" s="203"/>
+      <c r="S24" s="203"/>
+      <c r="T24" s="203"/>
+      <c r="U24" s="204"/>
     </row>
     <row r="25" spans="2:22" s="2" customFormat="1" ht="30" customHeight="1">
-      <c r="B25" s="266" t="s">
+      <c r="B25" s="216" t="s">
         <v>20</v>
       </c>
-      <c r="C25" s="186"/>
-      <c r="D25" s="145"/>
+      <c r="C25" s="171"/>
+      <c r="D25" s="185"/>
       <c r="E25" s="3" t="s">
         <v>21</v>
       </c>
@@ -3527,21 +3537,21 @@
       <c r="K25" s="104" t="s">
         <v>24</v>
       </c>
-      <c r="L25" s="212" t="s">
+      <c r="L25" s="207" t="s">
         <v>25</v>
       </c>
-      <c r="M25" s="141"/>
-      <c r="N25" s="211" t="s">
+      <c r="M25" s="188"/>
+      <c r="N25" s="187" t="s">
         <v>26</v>
       </c>
-      <c r="O25" s="141"/>
+      <c r="O25" s="188"/>
       <c r="P25" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="Q25" s="211" t="s">
+      <c r="Q25" s="187" t="s">
         <v>28</v>
       </c>
-      <c r="R25" s="141"/>
+      <c r="R25" s="188"/>
       <c r="S25" s="7" t="s">
         <v>29</v>
       </c>
@@ -3553,9 +3563,9 @@
       </c>
     </row>
     <row r="26" spans="2:22" s="2" customFormat="1" ht="39" customHeight="1">
-      <c r="B26" s="142"/>
-      <c r="C26" s="188"/>
-      <c r="D26" s="143"/>
+      <c r="B26" s="217"/>
+      <c r="C26" s="176"/>
+      <c r="D26" s="186"/>
       <c r="E26" s="10"/>
       <c r="F26" s="11"/>
       <c r="G26" s="12"/>
@@ -3563,19 +3573,19 @@
       <c r="I26" s="12"/>
       <c r="J26" s="11"/>
       <c r="K26" s="13"/>
-      <c r="L26" s="151"/>
-      <c r="M26" s="143"/>
-      <c r="N26" s="212" t="s">
+      <c r="L26" s="175"/>
+      <c r="M26" s="186"/>
+      <c r="N26" s="207" t="s">
         <v>31</v>
       </c>
-      <c r="O26" s="143"/>
+      <c r="O26" s="186"/>
       <c r="P26" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="Q26" s="212" t="s">
+      <c r="Q26" s="207" t="s">
         <v>33</v>
       </c>
-      <c r="R26" s="143"/>
+      <c r="R26" s="186"/>
       <c r="S26" s="14" t="s">
         <v>34</v>
       </c>
@@ -3587,11 +3597,11 @@
       </c>
     </row>
     <row r="27" spans="2:22" s="2" customFormat="1" ht="46.05" customHeight="1">
-      <c r="B27" s="266" t="s">
+      <c r="B27" s="216" t="s">
         <v>36</v>
       </c>
-      <c r="C27" s="186"/>
-      <c r="D27" s="145"/>
+      <c r="C27" s="171"/>
+      <c r="D27" s="185"/>
       <c r="E27" s="3" t="s">
         <v>21</v>
       </c>
@@ -3605,25 +3615,25 @@
       </c>
       <c r="J27" s="5"/>
       <c r="K27" s="6"/>
-      <c r="L27" s="205" t="s">
+      <c r="L27" s="292" t="s">
         <v>39</v>
       </c>
       <c r="M27" s="120" t="s">
         <v>9</v>
       </c>
-      <c r="N27" s="155"/>
-      <c r="O27" s="156"/>
+      <c r="N27" s="299"/>
+      <c r="O27" s="300"/>
       <c r="P27" s="93"/>
-      <c r="Q27" s="231"/>
-      <c r="R27" s="148"/>
+      <c r="Q27" s="222"/>
+      <c r="R27" s="157"/>
       <c r="S27" s="17"/>
       <c r="T27" s="18"/>
       <c r="U27" s="19"/>
     </row>
     <row r="28" spans="2:22" s="2" customFormat="1" ht="46.05" customHeight="1">
-      <c r="B28" s="142"/>
-      <c r="C28" s="188"/>
-      <c r="D28" s="143"/>
+      <c r="B28" s="217"/>
+      <c r="C28" s="176"/>
+      <c r="D28" s="186"/>
       <c r="E28" s="20"/>
       <c r="F28" s="21"/>
       <c r="G28" s="21"/>
@@ -3631,62 +3641,62 @@
       <c r="I28" s="22"/>
       <c r="J28" s="22"/>
       <c r="K28" s="23"/>
-      <c r="L28" s="206"/>
+      <c r="L28" s="210"/>
       <c r="M28" s="120" t="s">
         <v>40</v>
       </c>
-      <c r="N28" s="269"/>
-      <c r="O28" s="270"/>
+      <c r="N28" s="223"/>
+      <c r="O28" s="224"/>
       <c r="P28" s="93"/>
-      <c r="Q28" s="231"/>
-      <c r="R28" s="148"/>
+      <c r="Q28" s="222"/>
+      <c r="R28" s="157"/>
       <c r="S28" s="17"/>
       <c r="T28" s="18"/>
       <c r="U28" s="19"/>
     </row>
     <row r="29" spans="2:22" s="2" customFormat="1" ht="46.5" customHeight="1">
-      <c r="B29" s="245" t="s">
+      <c r="B29" s="235" t="s">
         <v>41</v>
       </c>
-      <c r="C29" s="186"/>
-      <c r="D29" s="145"/>
-      <c r="E29" s="198" t="s">
+      <c r="C29" s="171"/>
+      <c r="D29" s="185"/>
+      <c r="E29" s="246" t="s">
         <v>42</v>
       </c>
-      <c r="F29" s="186"/>
-      <c r="G29" s="186"/>
-      <c r="H29" s="186"/>
-      <c r="I29" s="186"/>
-      <c r="J29" s="186"/>
-      <c r="K29" s="145"/>
-      <c r="L29" s="207"/>
+      <c r="F29" s="171"/>
+      <c r="G29" s="171"/>
+      <c r="H29" s="171"/>
+      <c r="I29" s="171"/>
+      <c r="J29" s="171"/>
+      <c r="K29" s="185"/>
+      <c r="L29" s="211"/>
       <c r="M29" s="121" t="s">
         <v>43</v>
       </c>
-      <c r="N29" s="269"/>
-      <c r="O29" s="270"/>
+      <c r="N29" s="223"/>
+      <c r="O29" s="224"/>
       <c r="P29" s="94"/>
-      <c r="Q29" s="231"/>
-      <c r="R29" s="148"/>
+      <c r="Q29" s="222"/>
+      <c r="R29" s="157"/>
       <c r="S29" s="25"/>
       <c r="T29" s="5"/>
       <c r="U29" s="26"/>
     </row>
     <row r="30" spans="2:22" s="2" customFormat="1" ht="15" customHeight="1">
-      <c r="B30" s="140"/>
-      <c r="C30" s="187"/>
-      <c r="D30" s="141"/>
-      <c r="E30" s="151"/>
-      <c r="F30" s="188"/>
-      <c r="G30" s="188"/>
-      <c r="H30" s="188"/>
-      <c r="I30" s="188"/>
-      <c r="J30" s="188"/>
-      <c r="K30" s="143"/>
-      <c r="L30" s="318" t="s">
+      <c r="B30" s="236"/>
+      <c r="C30" s="173"/>
+      <c r="D30" s="188"/>
+      <c r="E30" s="175"/>
+      <c r="F30" s="176"/>
+      <c r="G30" s="176"/>
+      <c r="H30" s="176"/>
+      <c r="I30" s="176"/>
+      <c r="J30" s="176"/>
+      <c r="K30" s="186"/>
+      <c r="L30" s="209" t="s">
         <v>44</v>
       </c>
-      <c r="M30" s="182" t="s">
+      <c r="M30" s="251" t="s">
         <v>45</v>
       </c>
       <c r="N30" s="27"/>
@@ -3699,121 +3709,121 @@
       <c r="U30" s="26"/>
     </row>
     <row r="31" spans="2:22" s="2" customFormat="1" ht="42" customHeight="1">
-      <c r="B31" s="142"/>
-      <c r="C31" s="188"/>
-      <c r="D31" s="143"/>
-      <c r="E31" s="198" t="s">
+      <c r="B31" s="217"/>
+      <c r="C31" s="176"/>
+      <c r="D31" s="186"/>
+      <c r="E31" s="246" t="s">
         <v>108</v>
       </c>
-      <c r="F31" s="181"/>
-      <c r="G31" s="181"/>
-      <c r="H31" s="181"/>
-      <c r="I31" s="181"/>
-      <c r="J31" s="181"/>
-      <c r="K31" s="148"/>
-      <c r="L31" s="206"/>
-      <c r="M31" s="154"/>
-      <c r="N31" s="251"/>
-      <c r="O31" s="143"/>
+      <c r="F31" s="159"/>
+      <c r="G31" s="159"/>
+      <c r="H31" s="159"/>
+      <c r="I31" s="159"/>
+      <c r="J31" s="159"/>
+      <c r="K31" s="157"/>
+      <c r="L31" s="210"/>
+      <c r="M31" s="155"/>
+      <c r="N31" s="243"/>
+      <c r="O31" s="186"/>
       <c r="P31" s="98"/>
-      <c r="Q31" s="154"/>
-      <c r="R31" s="143"/>
+      <c r="Q31" s="155"/>
+      <c r="R31" s="186"/>
       <c r="S31" s="31"/>
       <c r="T31" s="31"/>
       <c r="U31" s="32"/>
     </row>
     <row r="32" spans="2:22" s="2" customFormat="1" ht="21" customHeight="1">
-      <c r="B32" s="235" t="s">
+      <c r="B32" s="256" t="s">
         <v>46</v>
       </c>
-      <c r="C32" s="186"/>
-      <c r="D32" s="186"/>
-      <c r="E32" s="186"/>
-      <c r="F32" s="186"/>
-      <c r="G32" s="186"/>
-      <c r="H32" s="186"/>
-      <c r="I32" s="186"/>
-      <c r="J32" s="186"/>
-      <c r="K32" s="145"/>
-      <c r="L32" s="206"/>
-      <c r="M32" s="182" t="s">
+      <c r="C32" s="171"/>
+      <c r="D32" s="171"/>
+      <c r="E32" s="171"/>
+      <c r="F32" s="171"/>
+      <c r="G32" s="171"/>
+      <c r="H32" s="171"/>
+      <c r="I32" s="171"/>
+      <c r="J32" s="171"/>
+      <c r="K32" s="185"/>
+      <c r="L32" s="210"/>
+      <c r="M32" s="251" t="s">
         <v>47</v>
       </c>
-      <c r="N32" s="302"/>
-      <c r="O32" s="145"/>
+      <c r="N32" s="184"/>
+      <c r="O32" s="185"/>
       <c r="P32" s="97"/>
-      <c r="Q32" s="144"/>
-      <c r="R32" s="145"/>
+      <c r="Q32" s="208"/>
+      <c r="R32" s="185"/>
       <c r="S32" s="33"/>
       <c r="T32" s="33"/>
       <c r="U32" s="34"/>
     </row>
     <row r="33" spans="1:22" s="2" customFormat="1" ht="21" customHeight="1">
-      <c r="B33" s="142"/>
-      <c r="C33" s="188"/>
-      <c r="D33" s="188"/>
-      <c r="E33" s="188"/>
-      <c r="F33" s="188"/>
-      <c r="G33" s="188"/>
-      <c r="H33" s="188"/>
-      <c r="I33" s="188"/>
-      <c r="J33" s="188"/>
-      <c r="K33" s="143"/>
-      <c r="L33" s="206"/>
-      <c r="M33" s="154"/>
-      <c r="N33" s="201"/>
-      <c r="O33" s="143"/>
+      <c r="B33" s="217"/>
+      <c r="C33" s="176"/>
+      <c r="D33" s="176"/>
+      <c r="E33" s="176"/>
+      <c r="F33" s="176"/>
+      <c r="G33" s="176"/>
+      <c r="H33" s="176"/>
+      <c r="I33" s="176"/>
+      <c r="J33" s="176"/>
+      <c r="K33" s="186"/>
+      <c r="L33" s="210"/>
+      <c r="M33" s="155"/>
+      <c r="N33" s="288"/>
+      <c r="O33" s="186"/>
       <c r="P33" s="100"/>
-      <c r="Q33" s="199"/>
-      <c r="R33" s="143"/>
+      <c r="Q33" s="287"/>
+      <c r="R33" s="186"/>
       <c r="S33" s="36"/>
       <c r="T33" s="36"/>
       <c r="U33" s="32"/>
     </row>
     <row r="34" spans="1:22" s="2" customFormat="1" ht="21" customHeight="1">
-      <c r="B34" s="208" t="s">
+      <c r="B34" s="293" t="s">
         <v>48</v>
       </c>
-      <c r="C34" s="186"/>
-      <c r="D34" s="186"/>
-      <c r="E34" s="186"/>
-      <c r="F34" s="186"/>
-      <c r="G34" s="186"/>
-      <c r="H34" s="186"/>
-      <c r="I34" s="186"/>
-      <c r="J34" s="186"/>
-      <c r="K34" s="145"/>
-      <c r="L34" s="206"/>
-      <c r="M34" s="182" t="s">
+      <c r="C34" s="171"/>
+      <c r="D34" s="171"/>
+      <c r="E34" s="171"/>
+      <c r="F34" s="171"/>
+      <c r="G34" s="171"/>
+      <c r="H34" s="171"/>
+      <c r="I34" s="171"/>
+      <c r="J34" s="171"/>
+      <c r="K34" s="185"/>
+      <c r="L34" s="210"/>
+      <c r="M34" s="251" t="s">
         <v>49</v>
       </c>
-      <c r="N34" s="144"/>
-      <c r="O34" s="145"/>
+      <c r="N34" s="208"/>
+      <c r="O34" s="185"/>
       <c r="P34" s="24"/>
-      <c r="Q34" s="144"/>
-      <c r="R34" s="145"/>
+      <c r="Q34" s="208"/>
+      <c r="R34" s="185"/>
       <c r="S34" s="25"/>
       <c r="T34" s="25"/>
       <c r="U34" s="26"/>
     </row>
     <row r="35" spans="1:22" s="2" customFormat="1" ht="21" customHeight="1">
-      <c r="B35" s="142"/>
-      <c r="C35" s="188"/>
-      <c r="D35" s="188"/>
-      <c r="E35" s="188"/>
-      <c r="F35" s="188"/>
-      <c r="G35" s="188"/>
-      <c r="H35" s="188"/>
-      <c r="I35" s="188"/>
-      <c r="J35" s="188"/>
-      <c r="K35" s="143"/>
-      <c r="L35" s="206"/>
-      <c r="M35" s="154"/>
-      <c r="N35" s="154"/>
-      <c r="O35" s="143"/>
+      <c r="B35" s="217"/>
+      <c r="C35" s="176"/>
+      <c r="D35" s="176"/>
+      <c r="E35" s="176"/>
+      <c r="F35" s="176"/>
+      <c r="G35" s="176"/>
+      <c r="H35" s="176"/>
+      <c r="I35" s="176"/>
+      <c r="J35" s="176"/>
+      <c r="K35" s="186"/>
+      <c r="L35" s="210"/>
+      <c r="M35" s="155"/>
+      <c r="N35" s="155"/>
+      <c r="O35" s="186"/>
       <c r="P35" s="35"/>
-      <c r="Q35" s="154"/>
-      <c r="R35" s="143"/>
+      <c r="Q35" s="155"/>
+      <c r="R35" s="186"/>
       <c r="S35" s="36"/>
       <c r="T35" s="36"/>
       <c r="U35" s="32"/>
@@ -3823,103 +3833,103 @@
         <v>50</v>
       </c>
       <c r="C36" s="38"/>
-      <c r="D36" s="246"/>
-      <c r="E36" s="186"/>
-      <c r="F36" s="186"/>
-      <c r="G36" s="186"/>
-      <c r="H36" s="186"/>
-      <c r="I36" s="186"/>
-      <c r="J36" s="186"/>
-      <c r="K36" s="145"/>
-      <c r="L36" s="206"/>
-      <c r="M36" s="182" t="s">
+      <c r="D36" s="237"/>
+      <c r="E36" s="171"/>
+      <c r="F36" s="171"/>
+      <c r="G36" s="171"/>
+      <c r="H36" s="171"/>
+      <c r="I36" s="171"/>
+      <c r="J36" s="171"/>
+      <c r="K36" s="185"/>
+      <c r="L36" s="210"/>
+      <c r="M36" s="251" t="s">
         <v>51</v>
       </c>
-      <c r="N36" s="144"/>
-      <c r="O36" s="145"/>
+      <c r="N36" s="208"/>
+      <c r="O36" s="185"/>
       <c r="P36" s="24"/>
-      <c r="Q36" s="144"/>
-      <c r="R36" s="145"/>
+      <c r="Q36" s="208"/>
+      <c r="R36" s="185"/>
       <c r="S36" s="25"/>
       <c r="T36" s="25"/>
       <c r="U36" s="26"/>
     </row>
     <row r="37" spans="1:22" s="2" customFormat="1" ht="49.2" customHeight="1">
-      <c r="B37" s="209" t="s">
+      <c r="B37" s="294" t="s">
         <v>52</v>
       </c>
-      <c r="C37" s="181"/>
+      <c r="C37" s="159"/>
       <c r="D37" s="127" t="s">
         <v>53</v>
       </c>
-      <c r="E37" s="190" t="s">
+      <c r="E37" s="286" t="s">
         <v>54</v>
       </c>
-      <c r="F37" s="181"/>
-      <c r="G37" s="191"/>
+      <c r="F37" s="159"/>
+      <c r="G37" s="239"/>
       <c r="H37" s="115" t="s">
         <v>55</v>
       </c>
-      <c r="I37" s="202" t="s">
+      <c r="I37" s="289" t="s">
         <v>56</v>
       </c>
-      <c r="J37" s="203"/>
+      <c r="J37" s="290"/>
       <c r="K37" s="116" t="s">
         <v>57</v>
       </c>
-      <c r="L37" s="206"/>
-      <c r="M37" s="154"/>
-      <c r="N37" s="154"/>
-      <c r="O37" s="143"/>
+      <c r="L37" s="210"/>
+      <c r="M37" s="155"/>
+      <c r="N37" s="155"/>
+      <c r="O37" s="186"/>
       <c r="P37" s="35"/>
-      <c r="Q37" s="154"/>
-      <c r="R37" s="143"/>
+      <c r="Q37" s="155"/>
+      <c r="R37" s="186"/>
       <c r="S37" s="36"/>
       <c r="T37" s="36"/>
       <c r="U37" s="32"/>
     </row>
     <row r="38" spans="1:22" s="2" customFormat="1" ht="24.6" customHeight="1">
-      <c r="B38" s="247"/>
-      <c r="C38" s="191"/>
-      <c r="D38" s="241"/>
-      <c r="E38" s="295"/>
-      <c r="F38" s="296"/>
-      <c r="G38" s="297"/>
-      <c r="H38" s="236"/>
-      <c r="I38" s="284"/>
-      <c r="J38" s="285"/>
-      <c r="K38" s="183"/>
-      <c r="L38" s="206"/>
-      <c r="M38" s="182" t="s">
+      <c r="B38" s="238"/>
+      <c r="C38" s="239"/>
+      <c r="D38" s="260"/>
+      <c r="E38" s="177"/>
+      <c r="F38" s="178"/>
+      <c r="G38" s="179"/>
+      <c r="H38" s="257"/>
+      <c r="I38" s="160"/>
+      <c r="J38" s="161"/>
+      <c r="K38" s="282"/>
+      <c r="L38" s="210"/>
+      <c r="M38" s="251" t="s">
         <v>58</v>
       </c>
-      <c r="N38" s="144"/>
-      <c r="O38" s="145"/>
+      <c r="N38" s="208"/>
+      <c r="O38" s="185"/>
       <c r="P38" s="24"/>
-      <c r="Q38" s="144"/>
-      <c r="R38" s="145"/>
+      <c r="Q38" s="208"/>
+      <c r="R38" s="185"/>
       <c r="S38" s="25"/>
       <c r="T38" s="25"/>
       <c r="U38" s="26"/>
     </row>
     <row r="39" spans="1:22" s="2" customFormat="1" ht="22.95" customHeight="1">
-      <c r="B39" s="210"/>
-      <c r="C39" s="191"/>
-      <c r="D39" s="242"/>
-      <c r="E39" s="298"/>
-      <c r="F39" s="299"/>
-      <c r="G39" s="300"/>
-      <c r="H39" s="237"/>
-      <c r="I39" s="286"/>
-      <c r="J39" s="287"/>
-      <c r="K39" s="184"/>
-      <c r="L39" s="206"/>
-      <c r="M39" s="154"/>
-      <c r="N39" s="154"/>
-      <c r="O39" s="143"/>
+      <c r="B39" s="295"/>
+      <c r="C39" s="239"/>
+      <c r="D39" s="261"/>
+      <c r="E39" s="180"/>
+      <c r="F39" s="181"/>
+      <c r="G39" s="182"/>
+      <c r="H39" s="258"/>
+      <c r="I39" s="162"/>
+      <c r="J39" s="163"/>
+      <c r="K39" s="283"/>
+      <c r="L39" s="210"/>
+      <c r="M39" s="155"/>
+      <c r="N39" s="155"/>
+      <c r="O39" s="186"/>
       <c r="P39" s="35"/>
-      <c r="Q39" s="154"/>
-      <c r="R39" s="143"/>
+      <c r="Q39" s="155"/>
+      <c r="R39" s="186"/>
       <c r="S39" s="36"/>
       <c r="T39" s="36"/>
       <c r="U39" s="32"/>
@@ -3928,24 +3938,24 @@
       <c r="A40" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="B40" s="180"/>
-      <c r="C40" s="181"/>
-      <c r="D40" s="148"/>
-      <c r="E40" s="258"/>
-      <c r="F40" s="181"/>
-      <c r="G40" s="148"/>
-      <c r="H40" s="257"/>
-      <c r="I40" s="143"/>
+      <c r="B40" s="281"/>
+      <c r="C40" s="159"/>
+      <c r="D40" s="157"/>
+      <c r="E40" s="253"/>
+      <c r="F40" s="159"/>
+      <c r="G40" s="157"/>
+      <c r="H40" s="252"/>
+      <c r="I40" s="186"/>
       <c r="K40" s="99"/>
-      <c r="L40" s="206"/>
-      <c r="M40" s="182" t="s">
+      <c r="L40" s="210"/>
+      <c r="M40" s="251" t="s">
         <v>60</v>
       </c>
-      <c r="N40" s="144"/>
-      <c r="O40" s="145"/>
+      <c r="N40" s="208"/>
+      <c r="O40" s="185"/>
       <c r="P40" s="24"/>
-      <c r="Q40" s="144"/>
-      <c r="R40" s="145"/>
+      <c r="Q40" s="208"/>
+      <c r="R40" s="185"/>
       <c r="S40" s="25"/>
       <c r="T40" s="25"/>
       <c r="U40" s="26"/>
@@ -3963,142 +3973,142 @@
       <c r="I41" s="40"/>
       <c r="J41" s="91"/>
       <c r="K41" s="96"/>
-      <c r="L41" s="207"/>
-      <c r="M41" s="154"/>
-      <c r="N41" s="154"/>
-      <c r="O41" s="143"/>
+      <c r="L41" s="211"/>
+      <c r="M41" s="155"/>
+      <c r="N41" s="155"/>
+      <c r="O41" s="186"/>
       <c r="P41" s="35"/>
-      <c r="Q41" s="154"/>
-      <c r="R41" s="143"/>
+      <c r="Q41" s="155"/>
+      <c r="R41" s="186"/>
       <c r="S41" s="36"/>
       <c r="T41" s="36"/>
       <c r="U41" s="32"/>
     </row>
     <row r="42" spans="1:22" ht="18" customHeight="1">
-      <c r="B42" s="238" t="s">
+      <c r="B42" s="225" t="s">
         <v>62</v>
       </c>
       <c r="C42" s="41"/>
       <c r="D42" s="41"/>
-      <c r="E42" s="158" t="s">
+      <c r="E42" s="278" t="s">
         <v>63</v>
       </c>
-      <c r="F42" s="145"/>
-      <c r="G42" s="157" t="s">
+      <c r="F42" s="185"/>
+      <c r="G42" s="259" t="s">
         <v>64</v>
       </c>
-      <c r="H42" s="145"/>
-      <c r="I42" s="152" t="s">
+      <c r="H42" s="185"/>
+      <c r="I42" s="153" t="s">
         <v>65</v>
       </c>
       <c r="J42" s="95" t="s">
         <v>66</v>
       </c>
-      <c r="K42" s="157" t="s">
+      <c r="K42" s="259" t="s">
         <v>67</v>
       </c>
-      <c r="L42" s="186"/>
-      <c r="M42" s="145"/>
-      <c r="N42" s="152" t="s">
+      <c r="L42" s="171"/>
+      <c r="M42" s="185"/>
+      <c r="N42" s="153" t="s">
         <v>68</v>
       </c>
       <c r="O42" s="42" t="s">
         <v>66</v>
       </c>
-      <c r="P42" s="152" t="s">
+      <c r="P42" s="153" t="s">
         <v>69</v>
       </c>
       <c r="Q42" s="41"/>
-      <c r="R42" s="152" t="s">
+      <c r="R42" s="153" t="s">
         <v>70</v>
       </c>
-      <c r="S42" s="186"/>
-      <c r="T42" s="145"/>
-      <c r="U42" s="309" t="s">
+      <c r="S42" s="171"/>
+      <c r="T42" s="185"/>
+      <c r="U42" s="196" t="s">
         <v>71</v>
       </c>
       <c r="V42" s="43"/>
     </row>
     <row r="43" spans="1:22" ht="50.4" customHeight="1">
-      <c r="B43" s="239"/>
+      <c r="B43" s="226"/>
       <c r="C43" s="95" t="s">
         <v>72</v>
       </c>
       <c r="D43" s="118" t="s">
         <v>73</v>
       </c>
-      <c r="E43" s="159"/>
-      <c r="F43" s="141"/>
-      <c r="G43" s="151"/>
-      <c r="H43" s="143"/>
-      <c r="I43" s="153"/>
-      <c r="J43" s="234" t="s">
+      <c r="E43" s="172"/>
+      <c r="F43" s="188"/>
+      <c r="G43" s="175"/>
+      <c r="H43" s="186"/>
+      <c r="I43" s="154"/>
+      <c r="J43" s="280" t="s">
         <v>74</v>
       </c>
-      <c r="K43" s="151"/>
-      <c r="L43" s="188"/>
-      <c r="M43" s="143"/>
-      <c r="N43" s="153"/>
-      <c r="O43" s="178" t="s">
+      <c r="K43" s="175"/>
+      <c r="L43" s="176"/>
+      <c r="M43" s="186"/>
+      <c r="N43" s="154"/>
+      <c r="O43" s="233" t="s">
         <v>74</v>
       </c>
-      <c r="P43" s="153"/>
+      <c r="P43" s="154"/>
       <c r="Q43" s="44" t="s">
         <v>75</v>
       </c>
-      <c r="R43" s="159"/>
-      <c r="S43" s="187"/>
-      <c r="T43" s="141"/>
-      <c r="U43" s="227"/>
+      <c r="R43" s="172"/>
+      <c r="S43" s="173"/>
+      <c r="T43" s="188"/>
+      <c r="U43" s="197"/>
       <c r="V43" s="43"/>
     </row>
     <row r="44" spans="1:22" ht="55.5" customHeight="1">
-      <c r="B44" s="239"/>
+      <c r="B44" s="226"/>
       <c r="C44" s="112" t="s">
         <v>76</v>
       </c>
       <c r="D44" s="111" t="s">
         <v>77</v>
       </c>
-      <c r="E44" s="151"/>
-      <c r="F44" s="143"/>
+      <c r="E44" s="175"/>
+      <c r="F44" s="186"/>
       <c r="G44" s="46" t="s">
         <v>78</v>
       </c>
       <c r="H44" s="73" t="s">
         <v>79</v>
       </c>
-      <c r="I44" s="154"/>
-      <c r="J44" s="154"/>
+      <c r="I44" s="155"/>
+      <c r="J44" s="155"/>
       <c r="K44" s="117" t="s">
         <v>80</v>
       </c>
-      <c r="L44" s="301" t="s">
+      <c r="L44" s="183" t="s">
         <v>79</v>
       </c>
-      <c r="M44" s="148"/>
-      <c r="N44" s="154"/>
-      <c r="O44" s="154"/>
-      <c r="P44" s="154"/>
+      <c r="M44" s="157"/>
+      <c r="N44" s="155"/>
+      <c r="O44" s="155"/>
+      <c r="P44" s="155"/>
       <c r="Q44" s="47" t="s">
         <v>81</v>
       </c>
-      <c r="R44" s="151"/>
-      <c r="S44" s="188"/>
-      <c r="T44" s="143"/>
-      <c r="U44" s="228"/>
+      <c r="R44" s="175"/>
+      <c r="S44" s="176"/>
+      <c r="T44" s="186"/>
+      <c r="U44" s="198"/>
       <c r="V44" s="43"/>
     </row>
     <row r="45" spans="1:22" ht="50.1" customHeight="1">
-      <c r="B45" s="239"/>
+      <c r="B45" s="226"/>
       <c r="C45" s="113">
         <v>1</v>
       </c>
       <c r="D45" s="107" t="s">
         <v>82</v>
       </c>
-      <c r="E45" s="160"/>
-      <c r="F45" s="148"/>
+      <c r="E45" s="156"/>
+      <c r="F45" s="157"/>
       <c r="G45" s="50" t="s">
         <v>83</v>
       </c>
@@ -4108,28 +4118,28 @@
       <c r="K45" s="50" t="s">
         <v>83</v>
       </c>
-      <c r="L45" s="147"/>
-      <c r="M45" s="148"/>
+      <c r="L45" s="195"/>
+      <c r="M45" s="157"/>
       <c r="N45" s="53"/>
       <c r="O45" s="53"/>
       <c r="P45" s="54"/>
       <c r="Q45" s="55"/>
-      <c r="R45" s="233"/>
-      <c r="S45" s="181"/>
-      <c r="T45" s="148"/>
+      <c r="R45" s="158"/>
+      <c r="S45" s="159"/>
+      <c r="T45" s="157"/>
       <c r="U45" s="58"/>
       <c r="V45" s="59"/>
     </row>
     <row r="46" spans="1:22" ht="50.1" customHeight="1">
-      <c r="B46" s="239"/>
+      <c r="B46" s="226"/>
       <c r="C46" s="114">
         <v>2</v>
       </c>
       <c r="D46" s="108" t="s">
         <v>84</v>
       </c>
-      <c r="E46" s="160"/>
-      <c r="F46" s="148"/>
+      <c r="E46" s="156"/>
+      <c r="F46" s="157"/>
       <c r="G46" s="50" t="s">
         <v>83</v>
       </c>
@@ -4139,28 +4149,28 @@
       <c r="K46" s="50" t="s">
         <v>83</v>
       </c>
-      <c r="L46" s="147"/>
-      <c r="M46" s="148"/>
+      <c r="L46" s="195"/>
+      <c r="M46" s="157"/>
       <c r="N46" s="51"/>
       <c r="O46" s="51"/>
       <c r="P46" s="61"/>
       <c r="Q46" s="62"/>
-      <c r="R46" s="233"/>
-      <c r="S46" s="181"/>
-      <c r="T46" s="148"/>
+      <c r="R46" s="158"/>
+      <c r="S46" s="159"/>
+      <c r="T46" s="157"/>
       <c r="U46" s="58"/>
       <c r="V46" s="59"/>
     </row>
     <row r="47" spans="1:22" ht="50.1" customHeight="1">
-      <c r="B47" s="239"/>
+      <c r="B47" s="226"/>
       <c r="C47" s="114">
         <v>3</v>
       </c>
       <c r="D47" s="108" t="s">
         <v>85</v>
       </c>
-      <c r="E47" s="160"/>
-      <c r="F47" s="148"/>
+      <c r="E47" s="156"/>
+      <c r="F47" s="157"/>
       <c r="G47" s="50" t="s">
         <v>83</v>
       </c>
@@ -4170,28 +4180,28 @@
       <c r="K47" s="50" t="s">
         <v>83</v>
       </c>
-      <c r="L47" s="147"/>
-      <c r="M47" s="148"/>
+      <c r="L47" s="195"/>
+      <c r="M47" s="157"/>
       <c r="N47" s="51"/>
       <c r="O47" s="51"/>
       <c r="P47" s="54"/>
       <c r="Q47" s="62"/>
-      <c r="R47" s="233"/>
-      <c r="S47" s="181"/>
-      <c r="T47" s="148"/>
+      <c r="R47" s="158"/>
+      <c r="S47" s="159"/>
+      <c r="T47" s="157"/>
       <c r="U47" s="58"/>
       <c r="V47" s="59"/>
     </row>
     <row r="48" spans="1:22" ht="50.1" customHeight="1">
-      <c r="B48" s="239"/>
+      <c r="B48" s="226"/>
       <c r="C48" s="114">
         <v>4</v>
       </c>
       <c r="D48" s="108" t="s">
         <v>86</v>
       </c>
-      <c r="E48" s="160"/>
-      <c r="F48" s="148"/>
+      <c r="E48" s="156"/>
+      <c r="F48" s="157"/>
       <c r="G48" s="50" t="s">
         <v>83</v>
       </c>
@@ -4201,28 +4211,28 @@
       <c r="K48" s="50" t="s">
         <v>83</v>
       </c>
-      <c r="L48" s="147"/>
-      <c r="M48" s="148"/>
+      <c r="L48" s="195"/>
+      <c r="M48" s="157"/>
       <c r="N48" s="51"/>
       <c r="O48" s="51"/>
       <c r="P48" s="54"/>
       <c r="Q48" s="62"/>
-      <c r="R48" s="233"/>
-      <c r="S48" s="181"/>
-      <c r="T48" s="148"/>
+      <c r="R48" s="158"/>
+      <c r="S48" s="159"/>
+      <c r="T48" s="157"/>
       <c r="U48" s="58"/>
       <c r="V48" s="59"/>
     </row>
     <row r="49" spans="2:23" ht="50.1" customHeight="1">
-      <c r="B49" s="239"/>
+      <c r="B49" s="226"/>
       <c r="C49" s="114">
         <v>5</v>
       </c>
       <c r="D49" s="109" t="s">
         <v>87</v>
       </c>
-      <c r="E49" s="160"/>
-      <c r="F49" s="148"/>
+      <c r="E49" s="156"/>
+      <c r="F49" s="157"/>
       <c r="G49" s="50" t="s">
         <v>83</v>
       </c>
@@ -4232,28 +4242,28 @@
       <c r="K49" s="50" t="s">
         <v>83</v>
       </c>
-      <c r="L49" s="147"/>
-      <c r="M49" s="148"/>
+      <c r="L49" s="195"/>
+      <c r="M49" s="157"/>
       <c r="N49" s="51"/>
       <c r="O49" s="51"/>
       <c r="P49" s="54"/>
       <c r="Q49" s="62"/>
-      <c r="R49" s="233"/>
-      <c r="S49" s="181"/>
-      <c r="T49" s="148"/>
+      <c r="R49" s="158"/>
+      <c r="S49" s="159"/>
+      <c r="T49" s="157"/>
       <c r="U49" s="58"/>
       <c r="V49" s="59"/>
     </row>
     <row r="50" spans="2:23" ht="53.4" customHeight="1">
-      <c r="B50" s="239"/>
+      <c r="B50" s="226"/>
       <c r="C50" s="114">
         <v>6</v>
       </c>
       <c r="D50" s="110" t="s">
         <v>88</v>
       </c>
-      <c r="E50" s="160"/>
-      <c r="F50" s="148"/>
+      <c r="E50" s="156"/>
+      <c r="F50" s="157"/>
       <c r="G50" s="50" t="s">
         <v>83</v>
       </c>
@@ -4263,28 +4273,28 @@
       <c r="K50" s="50" t="s">
         <v>83</v>
       </c>
-      <c r="L50" s="147"/>
-      <c r="M50" s="148"/>
+      <c r="L50" s="195"/>
+      <c r="M50" s="157"/>
       <c r="N50" s="51"/>
       <c r="O50" s="51"/>
       <c r="P50" s="54"/>
       <c r="Q50" s="62"/>
-      <c r="R50" s="233"/>
-      <c r="S50" s="181"/>
-      <c r="T50" s="148"/>
+      <c r="R50" s="158"/>
+      <c r="S50" s="159"/>
+      <c r="T50" s="157"/>
       <c r="U50" s="58"/>
       <c r="V50" s="59"/>
     </row>
     <row r="51" spans="2:23" ht="50.1" customHeight="1">
-      <c r="B51" s="240"/>
+      <c r="B51" s="227"/>
       <c r="C51" s="113">
         <v>7</v>
       </c>
       <c r="D51" s="110" t="s">
         <v>89</v>
       </c>
-      <c r="E51" s="160"/>
-      <c r="F51" s="148"/>
+      <c r="E51" s="156"/>
+      <c r="F51" s="157"/>
       <c r="G51" s="50" t="s">
         <v>83</v>
       </c>
@@ -4294,15 +4304,15 @@
       <c r="K51" s="50" t="s">
         <v>83</v>
       </c>
-      <c r="L51" s="147"/>
-      <c r="M51" s="148"/>
+      <c r="L51" s="195"/>
+      <c r="M51" s="157"/>
       <c r="N51" s="53"/>
       <c r="O51" s="53"/>
       <c r="P51" s="61"/>
       <c r="Q51" s="55"/>
-      <c r="R51" s="233"/>
-      <c r="S51" s="181"/>
-      <c r="T51" s="148"/>
+      <c r="R51" s="158"/>
+      <c r="S51" s="159"/>
+      <c r="T51" s="157"/>
       <c r="U51" s="58"/>
       <c r="V51" s="59"/>
     </row>
@@ -4330,128 +4340,128 @@
       <c r="V52" s="59"/>
     </row>
     <row r="53" spans="2:23" ht="18" customHeight="1">
-      <c r="B53" s="238" t="s">
+      <c r="B53" s="225" t="s">
         <v>90</v>
       </c>
       <c r="C53" s="72"/>
       <c r="D53" s="72"/>
-      <c r="E53" s="158" t="s">
+      <c r="E53" s="278" t="s">
         <v>63</v>
       </c>
-      <c r="F53" s="145"/>
-      <c r="G53" s="150" t="s">
+      <c r="F53" s="185"/>
+      <c r="G53" s="279" t="s">
         <v>91</v>
       </c>
-      <c r="H53" s="145"/>
-      <c r="I53" s="152" t="s">
+      <c r="H53" s="185"/>
+      <c r="I53" s="153" t="s">
         <v>92</v>
       </c>
-      <c r="J53" s="225" t="s">
+      <c r="J53" s="273" t="s">
         <v>93</v>
       </c>
-      <c r="K53" s="150" t="s">
+      <c r="K53" s="279" t="s">
         <v>67</v>
       </c>
-      <c r="L53" s="186"/>
-      <c r="M53" s="145"/>
-      <c r="N53" s="152" t="s">
+      <c r="L53" s="171"/>
+      <c r="M53" s="185"/>
+      <c r="N53" s="153" t="s">
         <v>68</v>
       </c>
       <c r="O53" s="42" t="s">
         <v>66</v>
       </c>
-      <c r="P53" s="152" t="s">
+      <c r="P53" s="153" t="s">
         <v>69</v>
       </c>
       <c r="Q53" s="41"/>
-      <c r="R53" s="152" t="s">
+      <c r="R53" s="153" t="s">
         <v>70</v>
       </c>
-      <c r="S53" s="186"/>
-      <c r="T53" s="145"/>
-      <c r="U53" s="226" t="s">
+      <c r="S53" s="171"/>
+      <c r="T53" s="185"/>
+      <c r="U53" s="274" t="s">
         <v>71</v>
       </c>
       <c r="V53" s="43"/>
     </row>
     <row r="54" spans="2:23" ht="50.4" customHeight="1">
-      <c r="B54" s="239"/>
+      <c r="B54" s="226"/>
       <c r="C54" s="41" t="s">
         <v>72</v>
       </c>
       <c r="D54" s="41" t="s">
         <v>73</v>
       </c>
-      <c r="E54" s="159"/>
-      <c r="F54" s="141"/>
-      <c r="G54" s="151"/>
-      <c r="H54" s="143"/>
-      <c r="I54" s="153"/>
-      <c r="J54" s="153"/>
-      <c r="K54" s="151"/>
-      <c r="L54" s="188"/>
-      <c r="M54" s="143"/>
-      <c r="N54" s="153"/>
-      <c r="O54" s="178" t="s">
+      <c r="E54" s="172"/>
+      <c r="F54" s="188"/>
+      <c r="G54" s="175"/>
+      <c r="H54" s="186"/>
+      <c r="I54" s="154"/>
+      <c r="J54" s="154"/>
+      <c r="K54" s="175"/>
+      <c r="L54" s="176"/>
+      <c r="M54" s="186"/>
+      <c r="N54" s="154"/>
+      <c r="O54" s="233" t="s">
         <v>74</v>
       </c>
-      <c r="P54" s="153"/>
+      <c r="P54" s="154"/>
       <c r="Q54" s="44" t="s">
         <v>75</v>
       </c>
-      <c r="R54" s="159"/>
-      <c r="S54" s="187"/>
-      <c r="T54" s="141"/>
-      <c r="U54" s="227"/>
+      <c r="R54" s="172"/>
+      <c r="S54" s="173"/>
+      <c r="T54" s="188"/>
+      <c r="U54" s="197"/>
       <c r="V54" s="43"/>
     </row>
     <row r="55" spans="2:23" ht="50.4" customHeight="1">
-      <c r="B55" s="239"/>
+      <c r="B55" s="226"/>
       <c r="C55" s="45" t="s">
         <v>76</v>
       </c>
       <c r="D55" s="45" t="s">
         <v>77</v>
       </c>
-      <c r="E55" s="151"/>
-      <c r="F55" s="143"/>
+      <c r="E55" s="175"/>
+      <c r="F55" s="186"/>
       <c r="G55" s="46" t="s">
         <v>80</v>
       </c>
       <c r="H55" s="73" t="s">
         <v>79</v>
       </c>
-      <c r="I55" s="154"/>
-      <c r="J55" s="154"/>
+      <c r="I55" s="155"/>
+      <c r="J55" s="155"/>
       <c r="K55" s="46" t="s">
         <v>80</v>
       </c>
-      <c r="L55" s="150" t="s">
+      <c r="L55" s="279" t="s">
         <v>79</v>
       </c>
-      <c r="M55" s="148"/>
-      <c r="N55" s="154"/>
-      <c r="O55" s="154"/>
-      <c r="P55" s="154"/>
+      <c r="M55" s="157"/>
+      <c r="N55" s="155"/>
+      <c r="O55" s="155"/>
+      <c r="P55" s="155"/>
       <c r="Q55" s="47" t="s">
         <v>81</v>
       </c>
-      <c r="R55" s="151"/>
-      <c r="S55" s="188"/>
-      <c r="T55" s="143"/>
-      <c r="U55" s="228"/>
+      <c r="R55" s="175"/>
+      <c r="S55" s="176"/>
+      <c r="T55" s="186"/>
+      <c r="U55" s="198"/>
       <c r="V55" s="43"/>
     </row>
     <row r="56" spans="2:23" ht="30" customHeight="1">
-      <c r="B56" s="239"/>
+      <c r="B56" s="226"/>
       <c r="C56" s="48">
         <v>1</v>
       </c>
       <c r="D56" s="49" t="s">
         <v>82</v>
       </c>
-      <c r="E56" s="160"/>
-      <c r="F56" s="148"/>
+      <c r="E56" s="156"/>
+      <c r="F56" s="157"/>
       <c r="G56" s="50" t="s">
         <v>83</v>
       </c>
@@ -4461,8 +4471,8 @@
       <c r="K56" s="50" t="s">
         <v>83</v>
       </c>
-      <c r="L56" s="147"/>
-      <c r="M56" s="148"/>
+      <c r="L56" s="195"/>
+      <c r="M56" s="157"/>
       <c r="N56" s="53"/>
       <c r="O56" s="53"/>
       <c r="P56" s="61"/>
@@ -4474,15 +4484,15 @@
       <c r="V56" s="59"/>
     </row>
     <row r="57" spans="2:23" ht="30" customHeight="1">
-      <c r="B57" s="239"/>
+      <c r="B57" s="226"/>
       <c r="C57" s="56">
         <v>2</v>
       </c>
       <c r="D57" s="75" t="s">
         <v>94</v>
       </c>
-      <c r="E57" s="160"/>
-      <c r="F57" s="148"/>
+      <c r="E57" s="156"/>
+      <c r="F57" s="157"/>
       <c r="G57" s="50" t="s">
         <v>83</v>
       </c>
@@ -4492,8 +4502,8 @@
       <c r="K57" s="50" t="s">
         <v>83</v>
       </c>
-      <c r="L57" s="147"/>
-      <c r="M57" s="148"/>
+      <c r="L57" s="195"/>
+      <c r="M57" s="157"/>
       <c r="N57" s="51"/>
       <c r="O57" s="51"/>
       <c r="P57" s="54"/>
@@ -4505,15 +4515,15 @@
       <c r="V57" s="59"/>
     </row>
     <row r="58" spans="2:23" ht="30" customHeight="1">
-      <c r="B58" s="239"/>
+      <c r="B58" s="226"/>
       <c r="C58" s="56">
         <v>3</v>
       </c>
       <c r="D58" s="77" t="s">
         <v>95</v>
       </c>
-      <c r="E58" s="160"/>
-      <c r="F58" s="148"/>
+      <c r="E58" s="156"/>
+      <c r="F58" s="157"/>
       <c r="G58" s="50" t="s">
         <v>83</v>
       </c>
@@ -4523,8 +4533,8 @@
       <c r="K58" s="50" t="s">
         <v>83</v>
       </c>
-      <c r="L58" s="147"/>
-      <c r="M58" s="148"/>
+      <c r="L58" s="195"/>
+      <c r="M58" s="157"/>
       <c r="N58" s="51"/>
       <c r="O58" s="51"/>
       <c r="P58" s="54"/>
@@ -4536,15 +4546,15 @@
       <c r="V58" s="59"/>
     </row>
     <row r="59" spans="2:23" ht="30" customHeight="1">
-      <c r="B59" s="239"/>
+      <c r="B59" s="226"/>
       <c r="C59" s="78">
         <v>4</v>
       </c>
       <c r="D59" s="79" t="s">
         <v>96</v>
       </c>
-      <c r="E59" s="160"/>
-      <c r="F59" s="148"/>
+      <c r="E59" s="156"/>
+      <c r="F59" s="157"/>
       <c r="G59" s="50" t="s">
         <v>83</v>
       </c>
@@ -4554,8 +4564,8 @@
       <c r="K59" s="59" t="s">
         <v>83</v>
       </c>
-      <c r="L59" s="147"/>
-      <c r="M59" s="148"/>
+      <c r="L59" s="195"/>
+      <c r="M59" s="157"/>
       <c r="N59" s="51"/>
       <c r="O59" s="51"/>
       <c r="P59" s="54"/>
@@ -4567,15 +4577,15 @@
       <c r="V59" s="59"/>
     </row>
     <row r="60" spans="2:23" ht="30" customHeight="1">
-      <c r="B60" s="239"/>
+      <c r="B60" s="226"/>
       <c r="C60" s="78">
         <v>5</v>
       </c>
       <c r="D60" s="79" t="s">
         <v>86</v>
       </c>
-      <c r="E60" s="160"/>
-      <c r="F60" s="148"/>
+      <c r="E60" s="156"/>
+      <c r="F60" s="157"/>
       <c r="G60" s="50" t="s">
         <v>83</v>
       </c>
@@ -4585,8 +4595,8 @@
       <c r="K60" s="59" t="s">
         <v>83</v>
       </c>
-      <c r="L60" s="147"/>
-      <c r="M60" s="148"/>
+      <c r="L60" s="195"/>
+      <c r="M60" s="157"/>
       <c r="N60" s="51"/>
       <c r="O60" s="51"/>
       <c r="P60" s="54"/>
@@ -4598,15 +4608,15 @@
       <c r="V60" s="59"/>
     </row>
     <row r="61" spans="2:23" ht="30" customHeight="1">
-      <c r="B61" s="240"/>
+      <c r="B61" s="227"/>
       <c r="C61" s="84">
         <v>6</v>
       </c>
       <c r="D61" s="85" t="s">
         <v>89</v>
       </c>
-      <c r="E61" s="160"/>
-      <c r="F61" s="148"/>
+      <c r="E61" s="156"/>
+      <c r="F61" s="157"/>
       <c r="G61" s="59" t="s">
         <v>83</v>
       </c>
@@ -4616,8 +4626,8 @@
       <c r="K61" s="84" t="s">
         <v>83</v>
       </c>
-      <c r="L61" s="147"/>
-      <c r="M61" s="148"/>
+      <c r="L61" s="195"/>
+      <c r="M61" s="157"/>
       <c r="N61" s="87"/>
       <c r="O61" s="87"/>
       <c r="P61" s="84"/>
@@ -4629,32 +4639,32 @@
       <c r="V61" s="59"/>
     </row>
     <row r="62" spans="2:23" s="88" customFormat="1" ht="23.25" customHeight="1" thickBot="1">
-      <c r="B62" s="229" t="s">
+      <c r="B62" s="275" t="s">
         <v>97</v>
       </c>
-      <c r="C62" s="223"/>
-      <c r="D62" s="223"/>
-      <c r="E62" s="223"/>
-      <c r="F62" s="230"/>
-      <c r="G62" s="232" t="s">
+      <c r="C62" s="271"/>
+      <c r="D62" s="271"/>
+      <c r="E62" s="271"/>
+      <c r="F62" s="276"/>
+      <c r="G62" s="277" t="s">
         <v>98</v>
       </c>
-      <c r="H62" s="223"/>
-      <c r="I62" s="223"/>
-      <c r="J62" s="223"/>
-      <c r="K62" s="223"/>
-      <c r="L62" s="223"/>
-      <c r="M62" s="230"/>
-      <c r="N62" s="222" t="s">
+      <c r="H62" s="271"/>
+      <c r="I62" s="271"/>
+      <c r="J62" s="271"/>
+      <c r="K62" s="271"/>
+      <c r="L62" s="271"/>
+      <c r="M62" s="276"/>
+      <c r="N62" s="270" t="s">
         <v>99</v>
       </c>
-      <c r="O62" s="223"/>
-      <c r="P62" s="223"/>
-      <c r="Q62" s="223"/>
-      <c r="R62" s="223"/>
-      <c r="S62" s="223"/>
-      <c r="T62" s="223"/>
-      <c r="U62" s="224"/>
+      <c r="O62" s="271"/>
+      <c r="P62" s="271"/>
+      <c r="Q62" s="271"/>
+      <c r="R62" s="271"/>
+      <c r="S62" s="271"/>
+      <c r="T62" s="271"/>
+      <c r="U62" s="272"/>
       <c r="W62" s="89"/>
     </row>
     <row r="63" spans="2:23" ht="14.4" customHeight="1"/>
@@ -4679,6 +4689,148 @@
     </row>
   </sheetData>
   <mergeCells count="166">
+    <mergeCell ref="B1:C5"/>
+    <mergeCell ref="Q36:R36"/>
+    <mergeCell ref="B18:C19"/>
+    <mergeCell ref="L56:M56"/>
+    <mergeCell ref="B8:C9"/>
+    <mergeCell ref="N34:O34"/>
+    <mergeCell ref="L49:M49"/>
+    <mergeCell ref="G53:H54"/>
+    <mergeCell ref="N42:N44"/>
+    <mergeCell ref="N27:O27"/>
+    <mergeCell ref="D3:D5"/>
+    <mergeCell ref="E53:F55"/>
+    <mergeCell ref="N36:O36"/>
+    <mergeCell ref="E47:F47"/>
+    <mergeCell ref="E8:F10"/>
+    <mergeCell ref="G8:H10"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="D6:D7"/>
+    <mergeCell ref="B6:C7"/>
+    <mergeCell ref="L55:M55"/>
+    <mergeCell ref="O43:O44"/>
+    <mergeCell ref="L51:M51"/>
+    <mergeCell ref="B12:C13"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="M36:M37"/>
+    <mergeCell ref="M30:M31"/>
+    <mergeCell ref="B16:C17"/>
+    <mergeCell ref="K38:K39"/>
+    <mergeCell ref="E12:H15"/>
+    <mergeCell ref="B14:C15"/>
+    <mergeCell ref="N37:O37"/>
+    <mergeCell ref="E37:G37"/>
+    <mergeCell ref="L16:R19"/>
+    <mergeCell ref="E29:K30"/>
+    <mergeCell ref="Q33:R33"/>
+    <mergeCell ref="B22:C24"/>
+    <mergeCell ref="M38:M39"/>
+    <mergeCell ref="E16:I19"/>
+    <mergeCell ref="N33:O33"/>
+    <mergeCell ref="I37:J37"/>
+    <mergeCell ref="K12:K15"/>
+    <mergeCell ref="L27:L29"/>
+    <mergeCell ref="B34:K35"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="P53:P55"/>
+    <mergeCell ref="N25:O25"/>
+    <mergeCell ref="L25:M26"/>
+    <mergeCell ref="D14:D15"/>
+    <mergeCell ref="I8:J11"/>
+    <mergeCell ref="E45:F45"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="N62:U62"/>
+    <mergeCell ref="Q31:R31"/>
+    <mergeCell ref="Q40:R40"/>
+    <mergeCell ref="J53:J55"/>
+    <mergeCell ref="N53:N55"/>
+    <mergeCell ref="U53:U55"/>
+    <mergeCell ref="B62:F62"/>
+    <mergeCell ref="Q28:R28"/>
+    <mergeCell ref="G62:M62"/>
+    <mergeCell ref="R49:T49"/>
+    <mergeCell ref="Q37:R37"/>
+    <mergeCell ref="E42:F44"/>
+    <mergeCell ref="K53:M54"/>
+    <mergeCell ref="L57:M57"/>
+    <mergeCell ref="J43:J44"/>
+    <mergeCell ref="E57:F57"/>
+    <mergeCell ref="E48:F48"/>
+    <mergeCell ref="E60:F60"/>
+    <mergeCell ref="L59:M59"/>
+    <mergeCell ref="B32:K33"/>
+    <mergeCell ref="L46:M46"/>
+    <mergeCell ref="L61:M61"/>
+    <mergeCell ref="E58:F58"/>
+    <mergeCell ref="I42:I44"/>
+    <mergeCell ref="L48:M48"/>
+    <mergeCell ref="E50:F50"/>
+    <mergeCell ref="H38:H39"/>
+    <mergeCell ref="E61:F61"/>
+    <mergeCell ref="E59:F59"/>
+    <mergeCell ref="L58:M58"/>
+    <mergeCell ref="E56:F56"/>
+    <mergeCell ref="B53:B61"/>
+    <mergeCell ref="L60:M60"/>
+    <mergeCell ref="L45:M45"/>
+    <mergeCell ref="G42:H43"/>
+    <mergeCell ref="I53:I55"/>
+    <mergeCell ref="D38:D39"/>
+    <mergeCell ref="K42:M43"/>
+    <mergeCell ref="M34:M35"/>
+    <mergeCell ref="M32:M33"/>
+    <mergeCell ref="E46:F46"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="B29:D31"/>
+    <mergeCell ref="D36:K36"/>
+    <mergeCell ref="Q38:R38"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="D18:D19"/>
+    <mergeCell ref="D8:D9"/>
+    <mergeCell ref="R48:T48"/>
+    <mergeCell ref="Q27:R27"/>
+    <mergeCell ref="N31:O31"/>
+    <mergeCell ref="N40:O40"/>
+    <mergeCell ref="J20:K24"/>
+    <mergeCell ref="E31:K31"/>
+    <mergeCell ref="B20:C21"/>
+    <mergeCell ref="E20:I24"/>
+    <mergeCell ref="D12:D13"/>
+    <mergeCell ref="M40:M41"/>
+    <mergeCell ref="N41:O41"/>
+    <mergeCell ref="H40:I40"/>
+    <mergeCell ref="L47:M47"/>
+    <mergeCell ref="E40:G40"/>
+    <mergeCell ref="R45:T45"/>
+    <mergeCell ref="B10:C11"/>
+    <mergeCell ref="D20:D21"/>
+    <mergeCell ref="R53:T55"/>
+    <mergeCell ref="Q35:R35"/>
+    <mergeCell ref="N39:O39"/>
+    <mergeCell ref="R46:T46"/>
+    <mergeCell ref="D22:D24"/>
+    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="I7:J7"/>
+    <mergeCell ref="E6:H7"/>
+    <mergeCell ref="Q39:R39"/>
+    <mergeCell ref="B25:D26"/>
+    <mergeCell ref="J16:K19"/>
+    <mergeCell ref="Q29:R29"/>
+    <mergeCell ref="B27:D28"/>
+    <mergeCell ref="Q32:R32"/>
+    <mergeCell ref="N29:O29"/>
+    <mergeCell ref="N38:O38"/>
+    <mergeCell ref="E49:F49"/>
+    <mergeCell ref="B42:B51"/>
+    <mergeCell ref="R51:T51"/>
+    <mergeCell ref="K8:K11"/>
+    <mergeCell ref="N28:O28"/>
+    <mergeCell ref="D10:D11"/>
+    <mergeCell ref="N26:O26"/>
+    <mergeCell ref="O54:O55"/>
     <mergeCell ref="S16:U19"/>
     <mergeCell ref="E1:N2"/>
     <mergeCell ref="P42:P44"/>
@@ -4703,148 +4855,6 @@
     <mergeCell ref="Q26:R26"/>
     <mergeCell ref="Q34:R34"/>
     <mergeCell ref="L30:L41"/>
-    <mergeCell ref="R53:T55"/>
-    <mergeCell ref="Q35:R35"/>
-    <mergeCell ref="N39:O39"/>
-    <mergeCell ref="R46:T46"/>
-    <mergeCell ref="D22:D24"/>
-    <mergeCell ref="I6:J6"/>
-    <mergeCell ref="I7:J7"/>
-    <mergeCell ref="E6:H7"/>
-    <mergeCell ref="Q39:R39"/>
-    <mergeCell ref="B25:D26"/>
-    <mergeCell ref="J16:K19"/>
-    <mergeCell ref="Q29:R29"/>
-    <mergeCell ref="B27:D28"/>
-    <mergeCell ref="Q32:R32"/>
-    <mergeCell ref="N29:O29"/>
-    <mergeCell ref="N38:O38"/>
-    <mergeCell ref="E49:F49"/>
-    <mergeCell ref="B42:B51"/>
-    <mergeCell ref="R51:T51"/>
-    <mergeCell ref="K8:K11"/>
-    <mergeCell ref="N28:O28"/>
-    <mergeCell ref="D10:D11"/>
-    <mergeCell ref="N26:O26"/>
-    <mergeCell ref="O54:O55"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="B29:D31"/>
-    <mergeCell ref="D36:K36"/>
-    <mergeCell ref="Q38:R38"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="D18:D19"/>
-    <mergeCell ref="D8:D9"/>
-    <mergeCell ref="R48:T48"/>
-    <mergeCell ref="Q27:R27"/>
-    <mergeCell ref="N31:O31"/>
-    <mergeCell ref="N40:O40"/>
-    <mergeCell ref="J20:K24"/>
-    <mergeCell ref="E31:K31"/>
-    <mergeCell ref="B20:C21"/>
-    <mergeCell ref="E20:I24"/>
-    <mergeCell ref="D12:D13"/>
-    <mergeCell ref="M40:M41"/>
-    <mergeCell ref="N41:O41"/>
-    <mergeCell ref="H40:I40"/>
-    <mergeCell ref="L47:M47"/>
-    <mergeCell ref="E40:G40"/>
-    <mergeCell ref="R45:T45"/>
-    <mergeCell ref="B10:C11"/>
-    <mergeCell ref="D20:D21"/>
-    <mergeCell ref="E60:F60"/>
-    <mergeCell ref="L59:M59"/>
-    <mergeCell ref="B32:K33"/>
-    <mergeCell ref="L46:M46"/>
-    <mergeCell ref="L61:M61"/>
-    <mergeCell ref="E58:F58"/>
-    <mergeCell ref="I42:I44"/>
-    <mergeCell ref="L48:M48"/>
-    <mergeCell ref="E50:F50"/>
-    <mergeCell ref="H38:H39"/>
-    <mergeCell ref="E61:F61"/>
-    <mergeCell ref="E59:F59"/>
-    <mergeCell ref="L58:M58"/>
-    <mergeCell ref="E56:F56"/>
-    <mergeCell ref="B53:B61"/>
-    <mergeCell ref="L60:M60"/>
-    <mergeCell ref="L45:M45"/>
-    <mergeCell ref="G42:H43"/>
-    <mergeCell ref="I53:I55"/>
-    <mergeCell ref="D38:D39"/>
-    <mergeCell ref="K42:M43"/>
-    <mergeCell ref="M34:M35"/>
-    <mergeCell ref="M32:M33"/>
-    <mergeCell ref="E46:F46"/>
-    <mergeCell ref="P53:P55"/>
-    <mergeCell ref="N25:O25"/>
-    <mergeCell ref="L25:M26"/>
-    <mergeCell ref="D14:D15"/>
-    <mergeCell ref="I8:J11"/>
-    <mergeCell ref="E45:F45"/>
-    <mergeCell ref="D16:D17"/>
-    <mergeCell ref="N62:U62"/>
-    <mergeCell ref="Q31:R31"/>
-    <mergeCell ref="Q40:R40"/>
-    <mergeCell ref="J53:J55"/>
-    <mergeCell ref="N53:N55"/>
-    <mergeCell ref="U53:U55"/>
-    <mergeCell ref="B62:F62"/>
-    <mergeCell ref="Q28:R28"/>
-    <mergeCell ref="G62:M62"/>
-    <mergeCell ref="R49:T49"/>
-    <mergeCell ref="Q37:R37"/>
-    <mergeCell ref="E42:F44"/>
-    <mergeCell ref="K53:M54"/>
-    <mergeCell ref="L57:M57"/>
-    <mergeCell ref="J43:J44"/>
-    <mergeCell ref="E57:F57"/>
-    <mergeCell ref="E48:F48"/>
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="M36:M37"/>
-    <mergeCell ref="M30:M31"/>
-    <mergeCell ref="B16:C17"/>
-    <mergeCell ref="K38:K39"/>
-    <mergeCell ref="E12:H15"/>
-    <mergeCell ref="B14:C15"/>
-    <mergeCell ref="N37:O37"/>
-    <mergeCell ref="E37:G37"/>
-    <mergeCell ref="L16:R19"/>
-    <mergeCell ref="E29:K30"/>
-    <mergeCell ref="Q33:R33"/>
-    <mergeCell ref="B22:C24"/>
-    <mergeCell ref="M38:M39"/>
-    <mergeCell ref="E16:I19"/>
-    <mergeCell ref="N33:O33"/>
-    <mergeCell ref="I37:J37"/>
-    <mergeCell ref="K12:K15"/>
-    <mergeCell ref="L27:L29"/>
-    <mergeCell ref="B34:K35"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B1:C5"/>
-    <mergeCell ref="Q36:R36"/>
-    <mergeCell ref="B18:C19"/>
-    <mergeCell ref="L56:M56"/>
-    <mergeCell ref="B8:C9"/>
-    <mergeCell ref="N34:O34"/>
-    <mergeCell ref="L49:M49"/>
-    <mergeCell ref="G53:H54"/>
-    <mergeCell ref="N42:N44"/>
-    <mergeCell ref="N27:O27"/>
-    <mergeCell ref="D3:D5"/>
-    <mergeCell ref="E53:F55"/>
-    <mergeCell ref="N36:O36"/>
-    <mergeCell ref="E47:F47"/>
-    <mergeCell ref="E8:F10"/>
-    <mergeCell ref="G8:H10"/>
-    <mergeCell ref="E11:F11"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="D6:D7"/>
-    <mergeCell ref="B6:C7"/>
-    <mergeCell ref="L55:M55"/>
-    <mergeCell ref="O43:O44"/>
-    <mergeCell ref="L51:M51"/>
-    <mergeCell ref="B12:C13"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1" gridLines="1"/>
   <pageMargins left="3.9370078740157501E-2" right="3.9370078740157501E-2" top="0.35433070866141703" bottom="0.35433070866141703" header="0.118110236220472" footer="0.118110236220472"/>

--- a/jo.xlsx
+++ b/jo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\production_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F90296E-414C-44DF-BBC5-A2555E5355EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0ECFBA8-1EB4-4FAD-B5B3-EB5A20227A7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -394,7 +394,7 @@
     </r>
   </si>
   <si>
-    <t>H248</t>
+    <t>H248 MAIN LHD</t>
   </si>
 </sst>
 </file>
@@ -2244,6 +2244,9 @@
     <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="69" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="41" fillId="0" borderId="34" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2650,9 +2653,6 @@
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="69" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="29">
@@ -2997,70 +2997,70 @@
       <c r="A1" s="1">
         <v>24</v>
       </c>
-      <c r="B1" s="296"/>
-      <c r="C1" s="297"/>
-      <c r="D1" s="234" t="s">
+      <c r="B1" s="297"/>
+      <c r="C1" s="298"/>
+      <c r="D1" s="235" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="147" t="s">
+      <c r="E1" s="148" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="148"/>
-      <c r="G1" s="148"/>
-      <c r="H1" s="148"/>
-      <c r="I1" s="148"/>
-      <c r="J1" s="148"/>
-      <c r="K1" s="148"/>
-      <c r="L1" s="148"/>
-      <c r="M1" s="148"/>
-      <c r="N1" s="149"/>
-      <c r="O1" s="164" t="s">
+      <c r="F1" s="149"/>
+      <c r="G1" s="149"/>
+      <c r="H1" s="149"/>
+      <c r="I1" s="149"/>
+      <c r="J1" s="149"/>
+      <c r="K1" s="149"/>
+      <c r="L1" s="149"/>
+      <c r="M1" s="149"/>
+      <c r="N1" s="150"/>
+      <c r="O1" s="165" t="s">
         <v>2</v>
       </c>
-      <c r="P1" s="165"/>
-      <c r="Q1" s="165"/>
-      <c r="R1" s="165"/>
-      <c r="S1" s="165"/>
-      <c r="T1" s="165"/>
-      <c r="U1" s="166"/>
+      <c r="P1" s="166"/>
+      <c r="Q1" s="166"/>
+      <c r="R1" s="166"/>
+      <c r="S1" s="166"/>
+      <c r="T1" s="166"/>
+      <c r="U1" s="167"/>
     </row>
     <row r="2" spans="1:22" s="1" customFormat="1" ht="18.75" customHeight="1">
-      <c r="B2" s="236"/>
-      <c r="C2" s="188"/>
-      <c r="D2" s="232"/>
-      <c r="E2" s="150"/>
-      <c r="F2" s="151"/>
-      <c r="G2" s="151"/>
-      <c r="H2" s="151"/>
-      <c r="I2" s="151"/>
-      <c r="J2" s="151"/>
-      <c r="K2" s="151"/>
-      <c r="L2" s="151"/>
-      <c r="M2" s="151"/>
-      <c r="N2" s="152"/>
-      <c r="O2" s="167"/>
-      <c r="P2" s="168"/>
-      <c r="Q2" s="168"/>
-      <c r="R2" s="168"/>
-      <c r="S2" s="168"/>
-      <c r="T2" s="168"/>
-      <c r="U2" s="169"/>
+      <c r="B2" s="237"/>
+      <c r="C2" s="189"/>
+      <c r="D2" s="233"/>
+      <c r="E2" s="151"/>
+      <c r="F2" s="152"/>
+      <c r="G2" s="152"/>
+      <c r="H2" s="152"/>
+      <c r="I2" s="152"/>
+      <c r="J2" s="152"/>
+      <c r="K2" s="152"/>
+      <c r="L2" s="152"/>
+      <c r="M2" s="152"/>
+      <c r="N2" s="153"/>
+      <c r="O2" s="168"/>
+      <c r="P2" s="169"/>
+      <c r="Q2" s="169"/>
+      <c r="R2" s="169"/>
+      <c r="S2" s="169"/>
+      <c r="T2" s="169"/>
+      <c r="U2" s="170"/>
     </row>
     <row r="3" spans="1:22" ht="12.45" customHeight="1">
-      <c r="B3" s="236"/>
-      <c r="C3" s="188"/>
-      <c r="D3" s="259" t="s">
+      <c r="B3" s="237"/>
+      <c r="C3" s="189"/>
+      <c r="D3" s="260" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="170" t="s">
+      <c r="E3" s="171" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="171"/>
-      <c r="G3" s="171"/>
-      <c r="H3" s="171"/>
-      <c r="I3" s="171"/>
-      <c r="J3" s="171"/>
-      <c r="K3" s="171"/>
+      <c r="F3" s="172"/>
+      <c r="G3" s="172"/>
+      <c r="H3" s="172"/>
+      <c r="I3" s="172"/>
+      <c r="J3" s="172"/>
+      <c r="K3" s="172"/>
       <c r="L3" s="128"/>
       <c r="M3" s="5"/>
       <c r="N3" s="5"/>
@@ -3073,49 +3073,49 @@
       <c r="U3" s="129"/>
     </row>
     <row r="4" spans="1:22" ht="14.85" customHeight="1">
-      <c r="B4" s="236"/>
-      <c r="C4" s="188"/>
-      <c r="D4" s="154"/>
-      <c r="E4" s="172"/>
-      <c r="F4" s="173"/>
-      <c r="G4" s="173"/>
-      <c r="H4" s="173"/>
-      <c r="I4" s="173"/>
-      <c r="J4" s="173"/>
-      <c r="K4" s="174"/>
+      <c r="B4" s="237"/>
+      <c r="C4" s="189"/>
+      <c r="D4" s="155"/>
+      <c r="E4" s="173"/>
+      <c r="F4" s="174"/>
+      <c r="G4" s="174"/>
+      <c r="H4" s="174"/>
+      <c r="I4" s="174"/>
+      <c r="J4" s="174"/>
+      <c r="K4" s="175"/>
       <c r="L4" s="130"/>
       <c r="U4" s="131"/>
     </row>
     <row r="5" spans="1:22" ht="14.85" customHeight="1">
-      <c r="B5" s="217"/>
-      <c r="C5" s="186"/>
-      <c r="D5" s="155"/>
-      <c r="E5" s="175"/>
-      <c r="F5" s="176"/>
-      <c r="G5" s="176"/>
-      <c r="H5" s="176"/>
-      <c r="I5" s="176"/>
-      <c r="J5" s="176"/>
-      <c r="K5" s="176"/>
+      <c r="B5" s="218"/>
+      <c r="C5" s="187"/>
+      <c r="D5" s="156"/>
+      <c r="E5" s="176"/>
+      <c r="F5" s="177"/>
+      <c r="G5" s="177"/>
+      <c r="H5" s="177"/>
+      <c r="I5" s="177"/>
+      <c r="J5" s="177"/>
+      <c r="K5" s="177"/>
       <c r="L5" s="130"/>
       <c r="U5" s="131"/>
     </row>
     <row r="6" spans="1:22" s="2" customFormat="1" ht="27.75" customHeight="1">
-      <c r="B6" s="247" t="s">
+      <c r="B6" s="248" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="185"/>
-      <c r="D6" s="317"/>
-      <c r="E6" s="215" t="s">
+      <c r="C6" s="186"/>
+      <c r="D6" s="318"/>
+      <c r="E6" s="216" t="s">
         <v>6</v>
       </c>
-      <c r="F6" s="171"/>
-      <c r="G6" s="171"/>
-      <c r="H6" s="185"/>
-      <c r="I6" s="213" t="s">
+      <c r="F6" s="172"/>
+      <c r="G6" s="172"/>
+      <c r="H6" s="186"/>
+      <c r="I6" s="214" t="s">
         <v>7</v>
       </c>
-      <c r="J6" s="157"/>
+      <c r="J6" s="158"/>
       <c r="K6" s="102" t="s">
         <v>8</v>
       </c>
@@ -3123,55 +3123,55 @@
       <c r="U6" s="131"/>
     </row>
     <row r="7" spans="1:22" s="2" customFormat="1" ht="28.5" customHeight="1">
-      <c r="B7" s="217"/>
-      <c r="C7" s="186"/>
-      <c r="D7" s="155"/>
-      <c r="E7" s="172"/>
-      <c r="F7" s="174"/>
-      <c r="G7" s="174"/>
-      <c r="H7" s="188"/>
-      <c r="I7" s="214"/>
-      <c r="J7" s="157"/>
+      <c r="B7" s="218"/>
+      <c r="C7" s="187"/>
+      <c r="D7" s="156"/>
+      <c r="E7" s="173"/>
+      <c r="F7" s="175"/>
+      <c r="G7" s="175"/>
+      <c r="H7" s="189"/>
+      <c r="I7" s="215"/>
+      <c r="J7" s="158"/>
       <c r="K7" s="103"/>
       <c r="L7" s="130"/>
       <c r="P7" s="135"/>
       <c r="U7" s="131"/>
     </row>
     <row r="8" spans="1:22" s="2" customFormat="1" ht="31.95" customHeight="1">
-      <c r="B8" s="247" t="s">
+      <c r="B8" s="248" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="185"/>
-      <c r="D8" s="242"/>
-      <c r="E8" s="301" t="s">
+      <c r="C8" s="186"/>
+      <c r="D8" s="243"/>
+      <c r="E8" s="302" t="s">
         <v>101</v>
       </c>
-      <c r="F8" s="302"/>
-      <c r="G8" s="307" t="s">
+      <c r="F8" s="303"/>
+      <c r="G8" s="308" t="s">
         <v>100</v>
       </c>
-      <c r="H8" s="308"/>
-      <c r="I8" s="263" t="s">
+      <c r="H8" s="309"/>
+      <c r="I8" s="264" t="s">
         <v>103</v>
       </c>
-      <c r="J8" s="264"/>
-      <c r="K8" s="228"/>
+      <c r="J8" s="265"/>
+      <c r="K8" s="229"/>
       <c r="L8" s="130"/>
       <c r="P8" s="135"/>
       <c r="U8" s="131"/>
       <c r="V8" s="101"/>
     </row>
     <row r="9" spans="1:22" s="2" customFormat="1" ht="3.75" hidden="1" customHeight="1">
-      <c r="B9" s="217"/>
-      <c r="C9" s="186"/>
-      <c r="D9" s="175"/>
-      <c r="E9" s="303"/>
-      <c r="F9" s="304"/>
-      <c r="G9" s="309"/>
-      <c r="H9" s="310"/>
-      <c r="I9" s="265"/>
-      <c r="J9" s="266"/>
-      <c r="K9" s="229"/>
+      <c r="B9" s="218"/>
+      <c r="C9" s="187"/>
+      <c r="D9" s="176"/>
+      <c r="E9" s="304"/>
+      <c r="F9" s="305"/>
+      <c r="G9" s="310"/>
+      <c r="H9" s="311"/>
+      <c r="I9" s="266"/>
+      <c r="J9" s="267"/>
+      <c r="K9" s="230"/>
       <c r="L9" s="130"/>
       <c r="P9" s="135" t="str">
         <f t="shared" ref="P9" si="0">"*"&amp;J18&amp;"*"</f>
@@ -3181,34 +3181,34 @@
       <c r="V9" s="101"/>
     </row>
     <row r="10" spans="1:22" s="2" customFormat="1" ht="15" customHeight="1">
-      <c r="B10" s="254" t="s">
+      <c r="B10" s="255" t="s">
         <v>11</v>
       </c>
-      <c r="C10" s="185"/>
-      <c r="D10" s="231"/>
-      <c r="E10" s="305"/>
-      <c r="F10" s="306"/>
-      <c r="G10" s="311"/>
-      <c r="H10" s="312"/>
-      <c r="I10" s="265"/>
-      <c r="J10" s="266"/>
-      <c r="K10" s="229"/>
+      <c r="C10" s="186"/>
+      <c r="D10" s="232"/>
+      <c r="E10" s="306"/>
+      <c r="F10" s="307"/>
+      <c r="G10" s="312"/>
+      <c r="H10" s="313"/>
+      <c r="I10" s="266"/>
+      <c r="J10" s="267"/>
+      <c r="K10" s="230"/>
       <c r="L10" s="130"/>
       <c r="P10" s="135"/>
       <c r="U10" s="131"/>
       <c r="V10" s="101"/>
     </row>
     <row r="11" spans="1:22" s="2" customFormat="1" ht="78.599999999999994" customHeight="1">
-      <c r="B11" s="217"/>
-      <c r="C11" s="186"/>
-      <c r="D11" s="232"/>
-      <c r="E11" s="313"/>
-      <c r="F11" s="314"/>
-      <c r="G11" s="315"/>
-      <c r="H11" s="316"/>
-      <c r="I11" s="267"/>
-      <c r="J11" s="268"/>
-      <c r="K11" s="230"/>
+      <c r="B11" s="218"/>
+      <c r="C11" s="187"/>
+      <c r="D11" s="233"/>
+      <c r="E11" s="314"/>
+      <c r="F11" s="315"/>
+      <c r="G11" s="316"/>
+      <c r="H11" s="317"/>
+      <c r="I11" s="268"/>
+      <c r="J11" s="269"/>
+      <c r="K11" s="231"/>
       <c r="L11" s="130"/>
       <c r="M11" s="136" t="str">
         <f>"*"&amp;J16&amp;"*"</f>
@@ -3223,71 +3223,71 @@
       <c r="V11" s="101"/>
     </row>
     <row r="12" spans="1:22" s="2" customFormat="1" ht="28.5" customHeight="1">
-      <c r="B12" s="318" t="s">
+      <c r="B12" s="319" t="s">
         <v>12</v>
       </c>
-      <c r="C12" s="185"/>
-      <c r="D12" s="249" t="s">
+      <c r="C12" s="186"/>
+      <c r="D12" s="250" t="s">
         <v>102</v>
       </c>
-      <c r="E12" s="284"/>
-      <c r="F12" s="171"/>
-      <c r="G12" s="171"/>
-      <c r="H12" s="185"/>
-      <c r="I12" s="189" t="s">
+      <c r="E12" s="285"/>
+      <c r="F12" s="172"/>
+      <c r="G12" s="172"/>
+      <c r="H12" s="186"/>
+      <c r="I12" s="190" t="s">
         <v>13</v>
       </c>
-      <c r="J12" s="190"/>
-      <c r="K12" s="291"/>
+      <c r="J12" s="191"/>
+      <c r="K12" s="292"/>
       <c r="L12" s="130"/>
       <c r="U12" s="131"/>
     </row>
     <row r="13" spans="1:22" s="2" customFormat="1" ht="13.5" customHeight="1">
-      <c r="B13" s="217"/>
-      <c r="C13" s="186"/>
-      <c r="D13" s="250"/>
-      <c r="E13" s="172"/>
-      <c r="F13" s="173"/>
-      <c r="G13" s="173"/>
-      <c r="H13" s="188"/>
-      <c r="I13" s="191"/>
-      <c r="J13" s="192"/>
-      <c r="K13" s="172"/>
+      <c r="B13" s="218"/>
+      <c r="C13" s="187"/>
+      <c r="D13" s="251"/>
+      <c r="E13" s="173"/>
+      <c r="F13" s="174"/>
+      <c r="G13" s="174"/>
+      <c r="H13" s="189"/>
+      <c r="I13" s="192"/>
+      <c r="J13" s="193"/>
+      <c r="K13" s="173"/>
       <c r="L13" s="130"/>
       <c r="U13" s="131"/>
     </row>
     <row r="14" spans="1:22" s="2" customFormat="1" ht="15" customHeight="1">
-      <c r="B14" s="285" t="s">
+      <c r="B14" s="286" t="s">
         <v>14</v>
       </c>
-      <c r="C14" s="185"/>
-      <c r="D14" s="262" t="s">
+      <c r="C14" s="186"/>
+      <c r="D14" s="263" t="s">
         <v>107</v>
       </c>
-      <c r="E14" s="172"/>
-      <c r="F14" s="173"/>
-      <c r="G14" s="173"/>
-      <c r="H14" s="188"/>
-      <c r="I14" s="191"/>
-      <c r="J14" s="192"/>
-      <c r="K14" s="172"/>
+      <c r="E14" s="173"/>
+      <c r="F14" s="174"/>
+      <c r="G14" s="174"/>
+      <c r="H14" s="189"/>
+      <c r="I14" s="192"/>
+      <c r="J14" s="193"/>
+      <c r="K14" s="173"/>
       <c r="L14" s="130"/>
       <c r="U14" s="131"/>
     </row>
     <row r="15" spans="1:22" s="2" customFormat="1" ht="48" customHeight="1">
-      <c r="B15" s="217"/>
-      <c r="C15" s="186"/>
-      <c r="D15" s="250"/>
-      <c r="E15" s="175"/>
-      <c r="F15" s="176"/>
-      <c r="G15" s="176"/>
-      <c r="H15" s="186"/>
-      <c r="I15" s="193"/>
-      <c r="J15" s="194"/>
-      <c r="K15" s="175"/>
+      <c r="B15" s="218"/>
+      <c r="C15" s="187"/>
+      <c r="D15" s="251"/>
+      <c r="E15" s="176"/>
+      <c r="F15" s="177"/>
+      <c r="G15" s="177"/>
+      <c r="H15" s="187"/>
+      <c r="I15" s="194"/>
+      <c r="J15" s="195"/>
+      <c r="K15" s="176"/>
       <c r="L15" s="132"/>
       <c r="M15" s="133"/>
-      <c r="N15" s="319"/>
+      <c r="N15" s="138"/>
       <c r="O15" s="133"/>
       <c r="P15" s="133"/>
       <c r="Q15" s="133"/>
@@ -3297,145 +3297,145 @@
       <c r="U15" s="134"/>
     </row>
     <row r="16" spans="1:22" s="2" customFormat="1" ht="15" customHeight="1">
-      <c r="B16" s="247" t="s">
+      <c r="B16" s="248" t="s">
         <v>15</v>
       </c>
-      <c r="C16" s="185"/>
-      <c r="D16" s="269"/>
-      <c r="E16" s="248" t="s">
+      <c r="C16" s="186"/>
+      <c r="D16" s="270"/>
+      <c r="E16" s="249" t="s">
         <v>16</v>
       </c>
-      <c r="F16" s="171"/>
-      <c r="G16" s="171"/>
-      <c r="H16" s="171"/>
-      <c r="I16" s="185"/>
-      <c r="J16" s="218">
+      <c r="F16" s="172"/>
+      <c r="G16" s="172"/>
+      <c r="H16" s="172"/>
+      <c r="I16" s="186"/>
+      <c r="J16" s="219">
         <v>232323</v>
       </c>
-      <c r="K16" s="219"/>
-      <c r="L16" s="138" t="s">
+      <c r="K16" s="220"/>
+      <c r="L16" s="139" t="s">
         <v>104</v>
       </c>
-      <c r="M16" s="139"/>
-      <c r="N16" s="139"/>
-      <c r="O16" s="139"/>
-      <c r="P16" s="139"/>
-      <c r="Q16" s="139"/>
-      <c r="R16" s="139"/>
-      <c r="S16" s="138" t="s">
+      <c r="M16" s="140"/>
+      <c r="N16" s="140"/>
+      <c r="O16" s="140"/>
+      <c r="P16" s="140"/>
+      <c r="Q16" s="140"/>
+      <c r="R16" s="140"/>
+      <c r="S16" s="139" t="s">
         <v>105</v>
       </c>
-      <c r="T16" s="139"/>
-      <c r="U16" s="140"/>
+      <c r="T16" s="140"/>
+      <c r="U16" s="141"/>
     </row>
     <row r="17" spans="2:22" s="2" customFormat="1" ht="15" customHeight="1">
-      <c r="B17" s="217"/>
-      <c r="C17" s="186"/>
-      <c r="D17" s="250"/>
-      <c r="E17" s="172"/>
-      <c r="F17" s="173"/>
-      <c r="G17" s="173"/>
-      <c r="H17" s="173"/>
-      <c r="I17" s="188"/>
-      <c r="J17" s="172"/>
-      <c r="K17" s="220"/>
-      <c r="L17" s="141"/>
-      <c r="M17" s="142"/>
-      <c r="N17" s="142"/>
-      <c r="O17" s="142"/>
-      <c r="P17" s="142"/>
-      <c r="Q17" s="142"/>
-      <c r="R17" s="142"/>
-      <c r="S17" s="141"/>
-      <c r="T17" s="142"/>
-      <c r="U17" s="143"/>
+      <c r="B17" s="218"/>
+      <c r="C17" s="187"/>
+      <c r="D17" s="251"/>
+      <c r="E17" s="173"/>
+      <c r="F17" s="174"/>
+      <c r="G17" s="174"/>
+      <c r="H17" s="174"/>
+      <c r="I17" s="189"/>
+      <c r="J17" s="173"/>
+      <c r="K17" s="221"/>
+      <c r="L17" s="142"/>
+      <c r="M17" s="143"/>
+      <c r="N17" s="143"/>
+      <c r="O17" s="143"/>
+      <c r="P17" s="143"/>
+      <c r="Q17" s="143"/>
+      <c r="R17" s="143"/>
+      <c r="S17" s="142"/>
+      <c r="T17" s="143"/>
+      <c r="U17" s="144"/>
     </row>
     <row r="18" spans="2:22" s="2" customFormat="1" ht="15" customHeight="1">
-      <c r="B18" s="298" t="s">
+      <c r="B18" s="299" t="s">
         <v>17</v>
       </c>
-      <c r="C18" s="185"/>
-      <c r="D18" s="240" t="s">
+      <c r="C18" s="186"/>
+      <c r="D18" s="241" t="s">
         <v>109</v>
       </c>
-      <c r="E18" s="172"/>
-      <c r="F18" s="173"/>
-      <c r="G18" s="173"/>
-      <c r="H18" s="173"/>
-      <c r="I18" s="188"/>
-      <c r="J18" s="172"/>
-      <c r="K18" s="220"/>
-      <c r="L18" s="141"/>
-      <c r="M18" s="142"/>
-      <c r="N18" s="142"/>
-      <c r="O18" s="142"/>
-      <c r="P18" s="142"/>
-      <c r="Q18" s="142"/>
-      <c r="R18" s="142"/>
-      <c r="S18" s="141"/>
-      <c r="T18" s="142"/>
-      <c r="U18" s="143"/>
+      <c r="E18" s="173"/>
+      <c r="F18" s="174"/>
+      <c r="G18" s="174"/>
+      <c r="H18" s="174"/>
+      <c r="I18" s="189"/>
+      <c r="J18" s="173"/>
+      <c r="K18" s="221"/>
+      <c r="L18" s="142"/>
+      <c r="M18" s="143"/>
+      <c r="N18" s="143"/>
+      <c r="O18" s="143"/>
+      <c r="P18" s="143"/>
+      <c r="Q18" s="143"/>
+      <c r="R18" s="143"/>
+      <c r="S18" s="142"/>
+      <c r="T18" s="143"/>
+      <c r="U18" s="144"/>
     </row>
     <row r="19" spans="2:22" s="2" customFormat="1" ht="15" customHeight="1">
-      <c r="B19" s="217"/>
-      <c r="C19" s="186"/>
-      <c r="D19" s="241"/>
-      <c r="E19" s="175"/>
-      <c r="F19" s="176"/>
-      <c r="G19" s="176"/>
-      <c r="H19" s="176"/>
-      <c r="I19" s="186"/>
-      <c r="J19" s="175"/>
-      <c r="K19" s="221"/>
-      <c r="L19" s="144"/>
-      <c r="M19" s="145"/>
-      <c r="N19" s="145"/>
-      <c r="O19" s="145"/>
-      <c r="P19" s="145"/>
-      <c r="Q19" s="145"/>
-      <c r="R19" s="145"/>
-      <c r="S19" s="144"/>
-      <c r="T19" s="145"/>
-      <c r="U19" s="146"/>
+      <c r="B19" s="218"/>
+      <c r="C19" s="187"/>
+      <c r="D19" s="242"/>
+      <c r="E19" s="176"/>
+      <c r="F19" s="177"/>
+      <c r="G19" s="177"/>
+      <c r="H19" s="177"/>
+      <c r="I19" s="187"/>
+      <c r="J19" s="176"/>
+      <c r="K19" s="222"/>
+      <c r="L19" s="145"/>
+      <c r="M19" s="146"/>
+      <c r="N19" s="146"/>
+      <c r="O19" s="146"/>
+      <c r="P19" s="146"/>
+      <c r="Q19" s="146"/>
+      <c r="R19" s="146"/>
+      <c r="S19" s="145"/>
+      <c r="T19" s="146"/>
+      <c r="U19" s="147"/>
     </row>
     <row r="20" spans="2:22" s="2" customFormat="1" ht="15" customHeight="1">
-      <c r="B20" s="247" t="s">
+      <c r="B20" s="248" t="s">
         <v>18</v>
       </c>
-      <c r="C20" s="185"/>
-      <c r="D20" s="255"/>
-      <c r="E20" s="248" t="s">
+      <c r="C20" s="186"/>
+      <c r="D20" s="256"/>
+      <c r="E20" s="249" t="s">
         <v>106</v>
       </c>
-      <c r="F20" s="171"/>
-      <c r="G20" s="171"/>
-      <c r="H20" s="171"/>
-      <c r="I20" s="185"/>
-      <c r="J20" s="244"/>
-      <c r="K20" s="219"/>
-      <c r="L20" s="205"/>
-      <c r="M20" s="206"/>
-      <c r="N20" s="206"/>
-      <c r="O20" s="206"/>
-      <c r="P20" s="206"/>
-      <c r="Q20" s="206"/>
-      <c r="R20" s="206"/>
-      <c r="S20" s="206"/>
-      <c r="T20" s="206"/>
-      <c r="U20" s="206"/>
+      <c r="F20" s="172"/>
+      <c r="G20" s="172"/>
+      <c r="H20" s="172"/>
+      <c r="I20" s="186"/>
+      <c r="J20" s="245"/>
+      <c r="K20" s="220"/>
+      <c r="L20" s="206"/>
+      <c r="M20" s="207"/>
+      <c r="N20" s="207"/>
+      <c r="O20" s="207"/>
+      <c r="P20" s="207"/>
+      <c r="Q20" s="207"/>
+      <c r="R20" s="207"/>
+      <c r="S20" s="207"/>
+      <c r="T20" s="207"/>
+      <c r="U20" s="207"/>
       <c r="V20" s="122"/>
     </row>
     <row r="21" spans="2:22" s="2" customFormat="1" ht="62.4" customHeight="1">
-      <c r="B21" s="217"/>
-      <c r="C21" s="186"/>
-      <c r="D21" s="155"/>
-      <c r="E21" s="172"/>
-      <c r="F21" s="173"/>
-      <c r="G21" s="173"/>
-      <c r="H21" s="173"/>
-      <c r="I21" s="188"/>
-      <c r="J21" s="172"/>
-      <c r="K21" s="245"/>
+      <c r="B21" s="218"/>
+      <c r="C21" s="187"/>
+      <c r="D21" s="156"/>
+      <c r="E21" s="173"/>
+      <c r="F21" s="174"/>
+      <c r="G21" s="174"/>
+      <c r="H21" s="174"/>
+      <c r="I21" s="189"/>
+      <c r="J21" s="173"/>
+      <c r="K21" s="246"/>
       <c r="L21" s="123"/>
       <c r="M21" s="124"/>
       <c r="N21" s="124"/>
@@ -3449,79 +3449,79 @@
       <c r="V21" s="122"/>
     </row>
     <row r="22" spans="2:22" s="2" customFormat="1" ht="15" customHeight="1">
-      <c r="B22" s="247" t="s">
+      <c r="B22" s="248" t="s">
         <v>19</v>
       </c>
-      <c r="C22" s="185"/>
-      <c r="D22" s="212"/>
-      <c r="E22" s="172"/>
-      <c r="F22" s="173"/>
-      <c r="G22" s="173"/>
-      <c r="H22" s="173"/>
-      <c r="I22" s="188"/>
-      <c r="J22" s="172"/>
-      <c r="K22" s="245"/>
-      <c r="L22" s="199"/>
-      <c r="M22" s="199"/>
-      <c r="N22" s="199"/>
-      <c r="O22" s="199"/>
-      <c r="P22" s="199"/>
-      <c r="Q22" s="199"/>
-      <c r="R22" s="199"/>
-      <c r="S22" s="199"/>
-      <c r="T22" s="199"/>
-      <c r="U22" s="200"/>
+      <c r="C22" s="186"/>
+      <c r="D22" s="213"/>
+      <c r="E22" s="173"/>
+      <c r="F22" s="174"/>
+      <c r="G22" s="174"/>
+      <c r="H22" s="174"/>
+      <c r="I22" s="189"/>
+      <c r="J22" s="173"/>
+      <c r="K22" s="246"/>
+      <c r="L22" s="200"/>
+      <c r="M22" s="200"/>
+      <c r="N22" s="200"/>
+      <c r="O22" s="200"/>
+      <c r="P22" s="200"/>
+      <c r="Q22" s="200"/>
+      <c r="R22" s="200"/>
+      <c r="S22" s="200"/>
+      <c r="T22" s="200"/>
+      <c r="U22" s="201"/>
     </row>
     <row r="23" spans="2:22" s="2" customFormat="1" ht="15" customHeight="1">
-      <c r="B23" s="236"/>
-      <c r="C23" s="188"/>
-      <c r="D23" s="154"/>
-      <c r="E23" s="172"/>
-      <c r="F23" s="173"/>
-      <c r="G23" s="173"/>
-      <c r="H23" s="173"/>
-      <c r="I23" s="188"/>
-      <c r="J23" s="172"/>
-      <c r="K23" s="245"/>
-      <c r="L23" s="201"/>
-      <c r="M23" s="201"/>
-      <c r="N23" s="201"/>
-      <c r="O23" s="201"/>
-      <c r="P23" s="201"/>
-      <c r="Q23" s="201"/>
-      <c r="R23" s="201"/>
-      <c r="S23" s="201"/>
-      <c r="T23" s="201"/>
-      <c r="U23" s="202"/>
+      <c r="B23" s="237"/>
+      <c r="C23" s="189"/>
+      <c r="D23" s="155"/>
+      <c r="E23" s="173"/>
+      <c r="F23" s="174"/>
+      <c r="G23" s="174"/>
+      <c r="H23" s="174"/>
+      <c r="I23" s="189"/>
+      <c r="J23" s="173"/>
+      <c r="K23" s="246"/>
+      <c r="L23" s="202"/>
+      <c r="M23" s="202"/>
+      <c r="N23" s="202"/>
+      <c r="O23" s="202"/>
+      <c r="P23" s="202"/>
+      <c r="Q23" s="202"/>
+      <c r="R23" s="202"/>
+      <c r="S23" s="202"/>
+      <c r="T23" s="202"/>
+      <c r="U23" s="203"/>
     </row>
     <row r="24" spans="2:22" s="2" customFormat="1" ht="7.5" customHeight="1">
-      <c r="B24" s="217"/>
-      <c r="C24" s="186"/>
-      <c r="D24" s="155"/>
-      <c r="E24" s="175"/>
-      <c r="F24" s="176"/>
-      <c r="G24" s="176"/>
-      <c r="H24" s="176"/>
-      <c r="I24" s="186"/>
-      <c r="J24" s="175"/>
-      <c r="K24" s="221"/>
-      <c r="L24" s="203"/>
-      <c r="M24" s="203"/>
-      <c r="N24" s="203"/>
-      <c r="O24" s="203"/>
-      <c r="P24" s="203"/>
-      <c r="Q24" s="203"/>
-      <c r="R24" s="203"/>
-      <c r="S24" s="203"/>
-      <c r="T24" s="203"/>
-      <c r="U24" s="204"/>
+      <c r="B24" s="218"/>
+      <c r="C24" s="187"/>
+      <c r="D24" s="156"/>
+      <c r="E24" s="176"/>
+      <c r="F24" s="177"/>
+      <c r="G24" s="177"/>
+      <c r="H24" s="177"/>
+      <c r="I24" s="187"/>
+      <c r="J24" s="176"/>
+      <c r="K24" s="222"/>
+      <c r="L24" s="204"/>
+      <c r="M24" s="204"/>
+      <c r="N24" s="204"/>
+      <c r="O24" s="204"/>
+      <c r="P24" s="204"/>
+      <c r="Q24" s="204"/>
+      <c r="R24" s="204"/>
+      <c r="S24" s="204"/>
+      <c r="T24" s="204"/>
+      <c r="U24" s="205"/>
     </row>
     <row r="25" spans="2:22" s="2" customFormat="1" ht="30" customHeight="1">
-      <c r="B25" s="216" t="s">
+      <c r="B25" s="217" t="s">
         <v>20</v>
       </c>
-      <c r="C25" s="171"/>
-      <c r="D25" s="185"/>
+      <c r="C25" s="172"/>
+      <c r="D25" s="186"/>
       <c r="E25" s="3" t="s">
         <v>21</v>
       </c>
@@ -3537,21 +3537,21 @@
       <c r="K25" s="104" t="s">
         <v>24</v>
       </c>
-      <c r="L25" s="207" t="s">
+      <c r="L25" s="208" t="s">
         <v>25</v>
       </c>
-      <c r="M25" s="188"/>
-      <c r="N25" s="187" t="s">
+      <c r="M25" s="189"/>
+      <c r="N25" s="188" t="s">
         <v>26</v>
       </c>
-      <c r="O25" s="188"/>
+      <c r="O25" s="189"/>
       <c r="P25" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="Q25" s="187" t="s">
+      <c r="Q25" s="188" t="s">
         <v>28</v>
       </c>
-      <c r="R25" s="188"/>
+      <c r="R25" s="189"/>
       <c r="S25" s="7" t="s">
         <v>29</v>
       </c>
@@ -3563,9 +3563,9 @@
       </c>
     </row>
     <row r="26" spans="2:22" s="2" customFormat="1" ht="39" customHeight="1">
-      <c r="B26" s="217"/>
-      <c r="C26" s="176"/>
-      <c r="D26" s="186"/>
+      <c r="B26" s="218"/>
+      <c r="C26" s="177"/>
+      <c r="D26" s="187"/>
       <c r="E26" s="10"/>
       <c r="F26" s="11"/>
       <c r="G26" s="12"/>
@@ -3573,19 +3573,19 @@
       <c r="I26" s="12"/>
       <c r="J26" s="11"/>
       <c r="K26" s="13"/>
-      <c r="L26" s="175"/>
-      <c r="M26" s="186"/>
-      <c r="N26" s="207" t="s">
+      <c r="L26" s="176"/>
+      <c r="M26" s="187"/>
+      <c r="N26" s="208" t="s">
         <v>31</v>
       </c>
-      <c r="O26" s="186"/>
+      <c r="O26" s="187"/>
       <c r="P26" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="Q26" s="207" t="s">
+      <c r="Q26" s="208" t="s">
         <v>33</v>
       </c>
-      <c r="R26" s="186"/>
+      <c r="R26" s="187"/>
       <c r="S26" s="14" t="s">
         <v>34</v>
       </c>
@@ -3597,11 +3597,11 @@
       </c>
     </row>
     <row r="27" spans="2:22" s="2" customFormat="1" ht="46.05" customHeight="1">
-      <c r="B27" s="216" t="s">
+      <c r="B27" s="217" t="s">
         <v>36</v>
       </c>
-      <c r="C27" s="171"/>
-      <c r="D27" s="185"/>
+      <c r="C27" s="172"/>
+      <c r="D27" s="186"/>
       <c r="E27" s="3" t="s">
         <v>21</v>
       </c>
@@ -3615,25 +3615,25 @@
       </c>
       <c r="J27" s="5"/>
       <c r="K27" s="6"/>
-      <c r="L27" s="292" t="s">
+      <c r="L27" s="293" t="s">
         <v>39</v>
       </c>
       <c r="M27" s="120" t="s">
         <v>9</v>
       </c>
-      <c r="N27" s="299"/>
-      <c r="O27" s="300"/>
+      <c r="N27" s="300"/>
+      <c r="O27" s="301"/>
       <c r="P27" s="93"/>
-      <c r="Q27" s="222"/>
-      <c r="R27" s="157"/>
+      <c r="Q27" s="223"/>
+      <c r="R27" s="158"/>
       <c r="S27" s="17"/>
       <c r="T27" s="18"/>
       <c r="U27" s="19"/>
     </row>
     <row r="28" spans="2:22" s="2" customFormat="1" ht="46.05" customHeight="1">
-      <c r="B28" s="217"/>
-      <c r="C28" s="176"/>
-      <c r="D28" s="186"/>
+      <c r="B28" s="218"/>
+      <c r="C28" s="177"/>
+      <c r="D28" s="187"/>
       <c r="E28" s="20"/>
       <c r="F28" s="21"/>
       <c r="G28" s="21"/>
@@ -3641,62 +3641,62 @@
       <c r="I28" s="22"/>
       <c r="J28" s="22"/>
       <c r="K28" s="23"/>
-      <c r="L28" s="210"/>
+      <c r="L28" s="211"/>
       <c r="M28" s="120" t="s">
         <v>40</v>
       </c>
-      <c r="N28" s="223"/>
-      <c r="O28" s="224"/>
+      <c r="N28" s="224"/>
+      <c r="O28" s="225"/>
       <c r="P28" s="93"/>
-      <c r="Q28" s="222"/>
-      <c r="R28" s="157"/>
+      <c r="Q28" s="223"/>
+      <c r="R28" s="158"/>
       <c r="S28" s="17"/>
       <c r="T28" s="18"/>
       <c r="U28" s="19"/>
     </row>
     <row r="29" spans="2:22" s="2" customFormat="1" ht="46.5" customHeight="1">
-      <c r="B29" s="235" t="s">
+      <c r="B29" s="236" t="s">
         <v>41</v>
       </c>
-      <c r="C29" s="171"/>
-      <c r="D29" s="185"/>
-      <c r="E29" s="246" t="s">
+      <c r="C29" s="172"/>
+      <c r="D29" s="186"/>
+      <c r="E29" s="247" t="s">
         <v>42</v>
       </c>
-      <c r="F29" s="171"/>
-      <c r="G29" s="171"/>
-      <c r="H29" s="171"/>
-      <c r="I29" s="171"/>
-      <c r="J29" s="171"/>
-      <c r="K29" s="185"/>
-      <c r="L29" s="211"/>
+      <c r="F29" s="172"/>
+      <c r="G29" s="172"/>
+      <c r="H29" s="172"/>
+      <c r="I29" s="172"/>
+      <c r="J29" s="172"/>
+      <c r="K29" s="186"/>
+      <c r="L29" s="212"/>
       <c r="M29" s="121" t="s">
         <v>43</v>
       </c>
-      <c r="N29" s="223"/>
-      <c r="O29" s="224"/>
+      <c r="N29" s="224"/>
+      <c r="O29" s="225"/>
       <c r="P29" s="94"/>
-      <c r="Q29" s="222"/>
-      <c r="R29" s="157"/>
+      <c r="Q29" s="223"/>
+      <c r="R29" s="158"/>
       <c r="S29" s="25"/>
       <c r="T29" s="5"/>
       <c r="U29" s="26"/>
     </row>
     <row r="30" spans="2:22" s="2" customFormat="1" ht="15" customHeight="1">
-      <c r="B30" s="236"/>
-      <c r="C30" s="173"/>
-      <c r="D30" s="188"/>
-      <c r="E30" s="175"/>
-      <c r="F30" s="176"/>
-      <c r="G30" s="176"/>
-      <c r="H30" s="176"/>
-      <c r="I30" s="176"/>
-      <c r="J30" s="176"/>
-      <c r="K30" s="186"/>
-      <c r="L30" s="209" t="s">
+      <c r="B30" s="237"/>
+      <c r="C30" s="174"/>
+      <c r="D30" s="189"/>
+      <c r="E30" s="176"/>
+      <c r="F30" s="177"/>
+      <c r="G30" s="177"/>
+      <c r="H30" s="177"/>
+      <c r="I30" s="177"/>
+      <c r="J30" s="177"/>
+      <c r="K30" s="187"/>
+      <c r="L30" s="210" t="s">
         <v>44</v>
       </c>
-      <c r="M30" s="251" t="s">
+      <c r="M30" s="252" t="s">
         <v>45</v>
       </c>
       <c r="N30" s="27"/>
@@ -3709,121 +3709,121 @@
       <c r="U30" s="26"/>
     </row>
     <row r="31" spans="2:22" s="2" customFormat="1" ht="42" customHeight="1">
-      <c r="B31" s="217"/>
-      <c r="C31" s="176"/>
-      <c r="D31" s="186"/>
-      <c r="E31" s="246" t="s">
+      <c r="B31" s="218"/>
+      <c r="C31" s="177"/>
+      <c r="D31" s="187"/>
+      <c r="E31" s="247" t="s">
         <v>108</v>
       </c>
-      <c r="F31" s="159"/>
-      <c r="G31" s="159"/>
-      <c r="H31" s="159"/>
-      <c r="I31" s="159"/>
-      <c r="J31" s="159"/>
-      <c r="K31" s="157"/>
-      <c r="L31" s="210"/>
-      <c r="M31" s="155"/>
-      <c r="N31" s="243"/>
-      <c r="O31" s="186"/>
+      <c r="F31" s="160"/>
+      <c r="G31" s="160"/>
+      <c r="H31" s="160"/>
+      <c r="I31" s="160"/>
+      <c r="J31" s="160"/>
+      <c r="K31" s="158"/>
+      <c r="L31" s="211"/>
+      <c r="M31" s="156"/>
+      <c r="N31" s="244"/>
+      <c r="O31" s="187"/>
       <c r="P31" s="98"/>
-      <c r="Q31" s="155"/>
-      <c r="R31" s="186"/>
+      <c r="Q31" s="156"/>
+      <c r="R31" s="187"/>
       <c r="S31" s="31"/>
       <c r="T31" s="31"/>
       <c r="U31" s="32"/>
     </row>
     <row r="32" spans="2:22" s="2" customFormat="1" ht="21" customHeight="1">
-      <c r="B32" s="256" t="s">
+      <c r="B32" s="257" t="s">
         <v>46</v>
       </c>
-      <c r="C32" s="171"/>
-      <c r="D32" s="171"/>
-      <c r="E32" s="171"/>
-      <c r="F32" s="171"/>
-      <c r="G32" s="171"/>
-      <c r="H32" s="171"/>
-      <c r="I32" s="171"/>
-      <c r="J32" s="171"/>
-      <c r="K32" s="185"/>
-      <c r="L32" s="210"/>
-      <c r="M32" s="251" t="s">
+      <c r="C32" s="172"/>
+      <c r="D32" s="172"/>
+      <c r="E32" s="172"/>
+      <c r="F32" s="172"/>
+      <c r="G32" s="172"/>
+      <c r="H32" s="172"/>
+      <c r="I32" s="172"/>
+      <c r="J32" s="172"/>
+      <c r="K32" s="186"/>
+      <c r="L32" s="211"/>
+      <c r="M32" s="252" t="s">
         <v>47</v>
       </c>
-      <c r="N32" s="184"/>
-      <c r="O32" s="185"/>
+      <c r="N32" s="185"/>
+      <c r="O32" s="186"/>
       <c r="P32" s="97"/>
-      <c r="Q32" s="208"/>
-      <c r="R32" s="185"/>
+      <c r="Q32" s="209"/>
+      <c r="R32" s="186"/>
       <c r="S32" s="33"/>
       <c r="T32" s="33"/>
       <c r="U32" s="34"/>
     </row>
     <row r="33" spans="1:22" s="2" customFormat="1" ht="21" customHeight="1">
-      <c r="B33" s="217"/>
-      <c r="C33" s="176"/>
-      <c r="D33" s="176"/>
-      <c r="E33" s="176"/>
-      <c r="F33" s="176"/>
-      <c r="G33" s="176"/>
-      <c r="H33" s="176"/>
-      <c r="I33" s="176"/>
-      <c r="J33" s="176"/>
-      <c r="K33" s="186"/>
-      <c r="L33" s="210"/>
-      <c r="M33" s="155"/>
-      <c r="N33" s="288"/>
-      <c r="O33" s="186"/>
+      <c r="B33" s="218"/>
+      <c r="C33" s="177"/>
+      <c r="D33" s="177"/>
+      <c r="E33" s="177"/>
+      <c r="F33" s="177"/>
+      <c r="G33" s="177"/>
+      <c r="H33" s="177"/>
+      <c r="I33" s="177"/>
+      <c r="J33" s="177"/>
+      <c r="K33" s="187"/>
+      <c r="L33" s="211"/>
+      <c r="M33" s="156"/>
+      <c r="N33" s="289"/>
+      <c r="O33" s="187"/>
       <c r="P33" s="100"/>
-      <c r="Q33" s="287"/>
-      <c r="R33" s="186"/>
+      <c r="Q33" s="288"/>
+      <c r="R33" s="187"/>
       <c r="S33" s="36"/>
       <c r="T33" s="36"/>
       <c r="U33" s="32"/>
     </row>
     <row r="34" spans="1:22" s="2" customFormat="1" ht="21" customHeight="1">
-      <c r="B34" s="293" t="s">
+      <c r="B34" s="294" t="s">
         <v>48</v>
       </c>
-      <c r="C34" s="171"/>
-      <c r="D34" s="171"/>
-      <c r="E34" s="171"/>
-      <c r="F34" s="171"/>
-      <c r="G34" s="171"/>
-      <c r="H34" s="171"/>
-      <c r="I34" s="171"/>
-      <c r="J34" s="171"/>
-      <c r="K34" s="185"/>
-      <c r="L34" s="210"/>
-      <c r="M34" s="251" t="s">
+      <c r="C34" s="172"/>
+      <c r="D34" s="172"/>
+      <c r="E34" s="172"/>
+      <c r="F34" s="172"/>
+      <c r="G34" s="172"/>
+      <c r="H34" s="172"/>
+      <c r="I34" s="172"/>
+      <c r="J34" s="172"/>
+      <c r="K34" s="186"/>
+      <c r="L34" s="211"/>
+      <c r="M34" s="252" t="s">
         <v>49</v>
       </c>
-      <c r="N34" s="208"/>
-      <c r="O34" s="185"/>
+      <c r="N34" s="209"/>
+      <c r="O34" s="186"/>
       <c r="P34" s="24"/>
-      <c r="Q34" s="208"/>
-      <c r="R34" s="185"/>
+      <c r="Q34" s="209"/>
+      <c r="R34" s="186"/>
       <c r="S34" s="25"/>
       <c r="T34" s="25"/>
       <c r="U34" s="26"/>
     </row>
     <row r="35" spans="1:22" s="2" customFormat="1" ht="21" customHeight="1">
-      <c r="B35" s="217"/>
-      <c r="C35" s="176"/>
-      <c r="D35" s="176"/>
-      <c r="E35" s="176"/>
-      <c r="F35" s="176"/>
-      <c r="G35" s="176"/>
-      <c r="H35" s="176"/>
-      <c r="I35" s="176"/>
-      <c r="J35" s="176"/>
-      <c r="K35" s="186"/>
-      <c r="L35" s="210"/>
-      <c r="M35" s="155"/>
-      <c r="N35" s="155"/>
-      <c r="O35" s="186"/>
+      <c r="B35" s="218"/>
+      <c r="C35" s="177"/>
+      <c r="D35" s="177"/>
+      <c r="E35" s="177"/>
+      <c r="F35" s="177"/>
+      <c r="G35" s="177"/>
+      <c r="H35" s="177"/>
+      <c r="I35" s="177"/>
+      <c r="J35" s="177"/>
+      <c r="K35" s="187"/>
+      <c r="L35" s="211"/>
+      <c r="M35" s="156"/>
+      <c r="N35" s="156"/>
+      <c r="O35" s="187"/>
       <c r="P35" s="35"/>
-      <c r="Q35" s="155"/>
-      <c r="R35" s="186"/>
+      <c r="Q35" s="156"/>
+      <c r="R35" s="187"/>
       <c r="S35" s="36"/>
       <c r="T35" s="36"/>
       <c r="U35" s="32"/>
@@ -3833,103 +3833,103 @@
         <v>50</v>
       </c>
       <c r="C36" s="38"/>
-      <c r="D36" s="237"/>
-      <c r="E36" s="171"/>
-      <c r="F36" s="171"/>
-      <c r="G36" s="171"/>
-      <c r="H36" s="171"/>
-      <c r="I36" s="171"/>
-      <c r="J36" s="171"/>
-      <c r="K36" s="185"/>
-      <c r="L36" s="210"/>
-      <c r="M36" s="251" t="s">
+      <c r="D36" s="238"/>
+      <c r="E36" s="172"/>
+      <c r="F36" s="172"/>
+      <c r="G36" s="172"/>
+      <c r="H36" s="172"/>
+      <c r="I36" s="172"/>
+      <c r="J36" s="172"/>
+      <c r="K36" s="186"/>
+      <c r="L36" s="211"/>
+      <c r="M36" s="252" t="s">
         <v>51</v>
       </c>
-      <c r="N36" s="208"/>
-      <c r="O36" s="185"/>
+      <c r="N36" s="209"/>
+      <c r="O36" s="186"/>
       <c r="P36" s="24"/>
-      <c r="Q36" s="208"/>
-      <c r="R36" s="185"/>
+      <c r="Q36" s="209"/>
+      <c r="R36" s="186"/>
       <c r="S36" s="25"/>
       <c r="T36" s="25"/>
       <c r="U36" s="26"/>
     </row>
     <row r="37" spans="1:22" s="2" customFormat="1" ht="49.2" customHeight="1">
-      <c r="B37" s="294" t="s">
+      <c r="B37" s="295" t="s">
         <v>52</v>
       </c>
-      <c r="C37" s="159"/>
+      <c r="C37" s="160"/>
       <c r="D37" s="127" t="s">
         <v>53</v>
       </c>
-      <c r="E37" s="286" t="s">
+      <c r="E37" s="287" t="s">
         <v>54</v>
       </c>
-      <c r="F37" s="159"/>
-      <c r="G37" s="239"/>
+      <c r="F37" s="160"/>
+      <c r="G37" s="240"/>
       <c r="H37" s="115" t="s">
         <v>55</v>
       </c>
-      <c r="I37" s="289" t="s">
+      <c r="I37" s="290" t="s">
         <v>56</v>
       </c>
-      <c r="J37" s="290"/>
+      <c r="J37" s="291"/>
       <c r="K37" s="116" t="s">
         <v>57</v>
       </c>
-      <c r="L37" s="210"/>
-      <c r="M37" s="155"/>
-      <c r="N37" s="155"/>
-      <c r="O37" s="186"/>
+      <c r="L37" s="211"/>
+      <c r="M37" s="156"/>
+      <c r="N37" s="156"/>
+      <c r="O37" s="187"/>
       <c r="P37" s="35"/>
-      <c r="Q37" s="155"/>
-      <c r="R37" s="186"/>
+      <c r="Q37" s="156"/>
+      <c r="R37" s="187"/>
       <c r="S37" s="36"/>
       <c r="T37" s="36"/>
       <c r="U37" s="32"/>
     </row>
     <row r="38" spans="1:22" s="2" customFormat="1" ht="24.6" customHeight="1">
-      <c r="B38" s="238"/>
-      <c r="C38" s="239"/>
-      <c r="D38" s="260"/>
-      <c r="E38" s="177"/>
-      <c r="F38" s="178"/>
-      <c r="G38" s="179"/>
-      <c r="H38" s="257"/>
-      <c r="I38" s="160"/>
-      <c r="J38" s="161"/>
-      <c r="K38" s="282"/>
-      <c r="L38" s="210"/>
-      <c r="M38" s="251" t="s">
+      <c r="B38" s="239"/>
+      <c r="C38" s="240"/>
+      <c r="D38" s="261"/>
+      <c r="E38" s="178"/>
+      <c r="F38" s="179"/>
+      <c r="G38" s="180"/>
+      <c r="H38" s="258"/>
+      <c r="I38" s="161"/>
+      <c r="J38" s="162"/>
+      <c r="K38" s="283"/>
+      <c r="L38" s="211"/>
+      <c r="M38" s="252" t="s">
         <v>58</v>
       </c>
-      <c r="N38" s="208"/>
-      <c r="O38" s="185"/>
+      <c r="N38" s="209"/>
+      <c r="O38" s="186"/>
       <c r="P38" s="24"/>
-      <c r="Q38" s="208"/>
-      <c r="R38" s="185"/>
+      <c r="Q38" s="209"/>
+      <c r="R38" s="186"/>
       <c r="S38" s="25"/>
       <c r="T38" s="25"/>
       <c r="U38" s="26"/>
     </row>
     <row r="39" spans="1:22" s="2" customFormat="1" ht="22.95" customHeight="1">
-      <c r="B39" s="295"/>
-      <c r="C39" s="239"/>
-      <c r="D39" s="261"/>
-      <c r="E39" s="180"/>
-      <c r="F39" s="181"/>
-      <c r="G39" s="182"/>
-      <c r="H39" s="258"/>
-      <c r="I39" s="162"/>
-      <c r="J39" s="163"/>
-      <c r="K39" s="283"/>
-      <c r="L39" s="210"/>
-      <c r="M39" s="155"/>
-      <c r="N39" s="155"/>
-      <c r="O39" s="186"/>
+      <c r="B39" s="296"/>
+      <c r="C39" s="240"/>
+      <c r="D39" s="262"/>
+      <c r="E39" s="181"/>
+      <c r="F39" s="182"/>
+      <c r="G39" s="183"/>
+      <c r="H39" s="259"/>
+      <c r="I39" s="163"/>
+      <c r="J39" s="164"/>
+      <c r="K39" s="284"/>
+      <c r="L39" s="211"/>
+      <c r="M39" s="156"/>
+      <c r="N39" s="156"/>
+      <c r="O39" s="187"/>
       <c r="P39" s="35"/>
-      <c r="Q39" s="155"/>
-      <c r="R39" s="186"/>
+      <c r="Q39" s="156"/>
+      <c r="R39" s="187"/>
       <c r="S39" s="36"/>
       <c r="T39" s="36"/>
       <c r="U39" s="32"/>
@@ -3938,24 +3938,24 @@
       <c r="A40" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="B40" s="281"/>
-      <c r="C40" s="159"/>
-      <c r="D40" s="157"/>
-      <c r="E40" s="253"/>
-      <c r="F40" s="159"/>
-      <c r="G40" s="157"/>
-      <c r="H40" s="252"/>
-      <c r="I40" s="186"/>
+      <c r="B40" s="282"/>
+      <c r="C40" s="160"/>
+      <c r="D40" s="158"/>
+      <c r="E40" s="254"/>
+      <c r="F40" s="160"/>
+      <c r="G40" s="158"/>
+      <c r="H40" s="253"/>
+      <c r="I40" s="187"/>
       <c r="K40" s="99"/>
-      <c r="L40" s="210"/>
-      <c r="M40" s="251" t="s">
+      <c r="L40" s="211"/>
+      <c r="M40" s="252" t="s">
         <v>60</v>
       </c>
-      <c r="N40" s="208"/>
-      <c r="O40" s="185"/>
+      <c r="N40" s="209"/>
+      <c r="O40" s="186"/>
       <c r="P40" s="24"/>
-      <c r="Q40" s="208"/>
-      <c r="R40" s="185"/>
+      <c r="Q40" s="209"/>
+      <c r="R40" s="186"/>
       <c r="S40" s="25"/>
       <c r="T40" s="25"/>
       <c r="U40" s="26"/>
@@ -3973,142 +3973,142 @@
       <c r="I41" s="40"/>
       <c r="J41" s="91"/>
       <c r="K41" s="96"/>
-      <c r="L41" s="211"/>
-      <c r="M41" s="155"/>
-      <c r="N41" s="155"/>
-      <c r="O41" s="186"/>
+      <c r="L41" s="212"/>
+      <c r="M41" s="156"/>
+      <c r="N41" s="156"/>
+      <c r="O41" s="187"/>
       <c r="P41" s="35"/>
-      <c r="Q41" s="155"/>
-      <c r="R41" s="186"/>
+      <c r="Q41" s="156"/>
+      <c r="R41" s="187"/>
       <c r="S41" s="36"/>
       <c r="T41" s="36"/>
       <c r="U41" s="32"/>
     </row>
     <row r="42" spans="1:22" ht="18" customHeight="1">
-      <c r="B42" s="225" t="s">
+      <c r="B42" s="226" t="s">
         <v>62</v>
       </c>
       <c r="C42" s="41"/>
       <c r="D42" s="41"/>
-      <c r="E42" s="278" t="s">
+      <c r="E42" s="279" t="s">
         <v>63</v>
       </c>
-      <c r="F42" s="185"/>
-      <c r="G42" s="259" t="s">
+      <c r="F42" s="186"/>
+      <c r="G42" s="260" t="s">
         <v>64</v>
       </c>
-      <c r="H42" s="185"/>
-      <c r="I42" s="153" t="s">
+      <c r="H42" s="186"/>
+      <c r="I42" s="154" t="s">
         <v>65</v>
       </c>
       <c r="J42" s="95" t="s">
         <v>66</v>
       </c>
-      <c r="K42" s="259" t="s">
+      <c r="K42" s="260" t="s">
         <v>67</v>
       </c>
-      <c r="L42" s="171"/>
-      <c r="M42" s="185"/>
-      <c r="N42" s="153" t="s">
+      <c r="L42" s="172"/>
+      <c r="M42" s="186"/>
+      <c r="N42" s="154" t="s">
         <v>68</v>
       </c>
       <c r="O42" s="42" t="s">
         <v>66</v>
       </c>
-      <c r="P42" s="153" t="s">
+      <c r="P42" s="154" t="s">
         <v>69</v>
       </c>
       <c r="Q42" s="41"/>
-      <c r="R42" s="153" t="s">
+      <c r="R42" s="154" t="s">
         <v>70</v>
       </c>
-      <c r="S42" s="171"/>
-      <c r="T42" s="185"/>
-      <c r="U42" s="196" t="s">
+      <c r="S42" s="172"/>
+      <c r="T42" s="186"/>
+      <c r="U42" s="197" t="s">
         <v>71</v>
       </c>
       <c r="V42" s="43"/>
     </row>
     <row r="43" spans="1:22" ht="50.4" customHeight="1">
-      <c r="B43" s="226"/>
+      <c r="B43" s="227"/>
       <c r="C43" s="95" t="s">
         <v>72</v>
       </c>
       <c r="D43" s="118" t="s">
         <v>73</v>
       </c>
-      <c r="E43" s="172"/>
-      <c r="F43" s="188"/>
-      <c r="G43" s="175"/>
-      <c r="H43" s="186"/>
-      <c r="I43" s="154"/>
-      <c r="J43" s="280" t="s">
+      <c r="E43" s="173"/>
+      <c r="F43" s="189"/>
+      <c r="G43" s="176"/>
+      <c r="H43" s="187"/>
+      <c r="I43" s="155"/>
+      <c r="J43" s="281" t="s">
         <v>74</v>
       </c>
-      <c r="K43" s="175"/>
-      <c r="L43" s="176"/>
-      <c r="M43" s="186"/>
-      <c r="N43" s="154"/>
-      <c r="O43" s="233" t="s">
+      <c r="K43" s="176"/>
+      <c r="L43" s="177"/>
+      <c r="M43" s="187"/>
+      <c r="N43" s="155"/>
+      <c r="O43" s="234" t="s">
         <v>74</v>
       </c>
-      <c r="P43" s="154"/>
+      <c r="P43" s="155"/>
       <c r="Q43" s="44" t="s">
         <v>75</v>
       </c>
-      <c r="R43" s="172"/>
-      <c r="S43" s="173"/>
-      <c r="T43" s="188"/>
-      <c r="U43" s="197"/>
+      <c r="R43" s="173"/>
+      <c r="S43" s="174"/>
+      <c r="T43" s="189"/>
+      <c r="U43" s="198"/>
       <c r="V43" s="43"/>
     </row>
     <row r="44" spans="1:22" ht="55.5" customHeight="1">
-      <c r="B44" s="226"/>
+      <c r="B44" s="227"/>
       <c r="C44" s="112" t="s">
         <v>76</v>
       </c>
       <c r="D44" s="111" t="s">
         <v>77</v>
       </c>
-      <c r="E44" s="175"/>
-      <c r="F44" s="186"/>
+      <c r="E44" s="176"/>
+      <c r="F44" s="187"/>
       <c r="G44" s="46" t="s">
         <v>78</v>
       </c>
       <c r="H44" s="73" t="s">
         <v>79</v>
       </c>
-      <c r="I44" s="155"/>
-      <c r="J44" s="155"/>
+      <c r="I44" s="156"/>
+      <c r="J44" s="156"/>
       <c r="K44" s="117" t="s">
         <v>80</v>
       </c>
-      <c r="L44" s="183" t="s">
+      <c r="L44" s="184" t="s">
         <v>79</v>
       </c>
-      <c r="M44" s="157"/>
-      <c r="N44" s="155"/>
-      <c r="O44" s="155"/>
-      <c r="P44" s="155"/>
+      <c r="M44" s="158"/>
+      <c r="N44" s="156"/>
+      <c r="O44" s="156"/>
+      <c r="P44" s="156"/>
       <c r="Q44" s="47" t="s">
         <v>81</v>
       </c>
-      <c r="R44" s="175"/>
-      <c r="S44" s="176"/>
-      <c r="T44" s="186"/>
-      <c r="U44" s="198"/>
+      <c r="R44" s="176"/>
+      <c r="S44" s="177"/>
+      <c r="T44" s="187"/>
+      <c r="U44" s="199"/>
       <c r="V44" s="43"/>
     </row>
     <row r="45" spans="1:22" ht="50.1" customHeight="1">
-      <c r="B45" s="226"/>
+      <c r="B45" s="227"/>
       <c r="C45" s="113">
         <v>1</v>
       </c>
       <c r="D45" s="107" t="s">
         <v>82</v>
       </c>
-      <c r="E45" s="156"/>
-      <c r="F45" s="157"/>
+      <c r="E45" s="157"/>
+      <c r="F45" s="158"/>
       <c r="G45" s="50" t="s">
         <v>83</v>
       </c>
@@ -4118,28 +4118,28 @@
       <c r="K45" s="50" t="s">
         <v>83</v>
       </c>
-      <c r="L45" s="195"/>
-      <c r="M45" s="157"/>
+      <c r="L45" s="196"/>
+      <c r="M45" s="158"/>
       <c r="N45" s="53"/>
       <c r="O45" s="53"/>
       <c r="P45" s="54"/>
       <c r="Q45" s="55"/>
-      <c r="R45" s="158"/>
-      <c r="S45" s="159"/>
-      <c r="T45" s="157"/>
+      <c r="R45" s="159"/>
+      <c r="S45" s="160"/>
+      <c r="T45" s="158"/>
       <c r="U45" s="58"/>
       <c r="V45" s="59"/>
     </row>
     <row r="46" spans="1:22" ht="50.1" customHeight="1">
-      <c r="B46" s="226"/>
+      <c r="B46" s="227"/>
       <c r="C46" s="114">
         <v>2</v>
       </c>
       <c r="D46" s="108" t="s">
         <v>84</v>
       </c>
-      <c r="E46" s="156"/>
-      <c r="F46" s="157"/>
+      <c r="E46" s="157"/>
+      <c r="F46" s="158"/>
       <c r="G46" s="50" t="s">
         <v>83</v>
       </c>
@@ -4149,28 +4149,28 @@
       <c r="K46" s="50" t="s">
         <v>83</v>
       </c>
-      <c r="L46" s="195"/>
-      <c r="M46" s="157"/>
+      <c r="L46" s="196"/>
+      <c r="M46" s="158"/>
       <c r="N46" s="51"/>
       <c r="O46" s="51"/>
       <c r="P46" s="61"/>
       <c r="Q46" s="62"/>
-      <c r="R46" s="158"/>
-      <c r="S46" s="159"/>
-      <c r="T46" s="157"/>
+      <c r="R46" s="159"/>
+      <c r="S46" s="160"/>
+      <c r="T46" s="158"/>
       <c r="U46" s="58"/>
       <c r="V46" s="59"/>
     </row>
     <row r="47" spans="1:22" ht="50.1" customHeight="1">
-      <c r="B47" s="226"/>
+      <c r="B47" s="227"/>
       <c r="C47" s="114">
         <v>3</v>
       </c>
       <c r="D47" s="108" t="s">
         <v>85</v>
       </c>
-      <c r="E47" s="156"/>
-      <c r="F47" s="157"/>
+      <c r="E47" s="157"/>
+      <c r="F47" s="158"/>
       <c r="G47" s="50" t="s">
         <v>83</v>
       </c>
@@ -4180,28 +4180,28 @@
       <c r="K47" s="50" t="s">
         <v>83</v>
       </c>
-      <c r="L47" s="195"/>
-      <c r="M47" s="157"/>
+      <c r="L47" s="196"/>
+      <c r="M47" s="158"/>
       <c r="N47" s="51"/>
       <c r="O47" s="51"/>
       <c r="P47" s="54"/>
       <c r="Q47" s="62"/>
-      <c r="R47" s="158"/>
-      <c r="S47" s="159"/>
-      <c r="T47" s="157"/>
+      <c r="R47" s="159"/>
+      <c r="S47" s="160"/>
+      <c r="T47" s="158"/>
       <c r="U47" s="58"/>
       <c r="V47" s="59"/>
     </row>
     <row r="48" spans="1:22" ht="50.1" customHeight="1">
-      <c r="B48" s="226"/>
+      <c r="B48" s="227"/>
       <c r="C48" s="114">
         <v>4</v>
       </c>
       <c r="D48" s="108" t="s">
         <v>86</v>
       </c>
-      <c r="E48" s="156"/>
-      <c r="F48" s="157"/>
+      <c r="E48" s="157"/>
+      <c r="F48" s="158"/>
       <c r="G48" s="50" t="s">
         <v>83</v>
       </c>
@@ -4211,28 +4211,28 @@
       <c r="K48" s="50" t="s">
         <v>83</v>
       </c>
-      <c r="L48" s="195"/>
-      <c r="M48" s="157"/>
+      <c r="L48" s="196"/>
+      <c r="M48" s="158"/>
       <c r="N48" s="51"/>
       <c r="O48" s="51"/>
       <c r="P48" s="54"/>
       <c r="Q48" s="62"/>
-      <c r="R48" s="158"/>
-      <c r="S48" s="159"/>
-      <c r="T48" s="157"/>
+      <c r="R48" s="159"/>
+      <c r="S48" s="160"/>
+      <c r="T48" s="158"/>
       <c r="U48" s="58"/>
       <c r="V48" s="59"/>
     </row>
     <row r="49" spans="2:23" ht="50.1" customHeight="1">
-      <c r="B49" s="226"/>
+      <c r="B49" s="227"/>
       <c r="C49" s="114">
         <v>5</v>
       </c>
       <c r="D49" s="109" t="s">
         <v>87</v>
       </c>
-      <c r="E49" s="156"/>
-      <c r="F49" s="157"/>
+      <c r="E49" s="157"/>
+      <c r="F49" s="158"/>
       <c r="G49" s="50" t="s">
         <v>83</v>
       </c>
@@ -4242,28 +4242,28 @@
       <c r="K49" s="50" t="s">
         <v>83</v>
       </c>
-      <c r="L49" s="195"/>
-      <c r="M49" s="157"/>
+      <c r="L49" s="196"/>
+      <c r="M49" s="158"/>
       <c r="N49" s="51"/>
       <c r="O49" s="51"/>
       <c r="P49" s="54"/>
       <c r="Q49" s="62"/>
-      <c r="R49" s="158"/>
-      <c r="S49" s="159"/>
-      <c r="T49" s="157"/>
+      <c r="R49" s="159"/>
+      <c r="S49" s="160"/>
+      <c r="T49" s="158"/>
       <c r="U49" s="58"/>
       <c r="V49" s="59"/>
     </row>
     <row r="50" spans="2:23" ht="53.4" customHeight="1">
-      <c r="B50" s="226"/>
+      <c r="B50" s="227"/>
       <c r="C50" s="114">
         <v>6</v>
       </c>
       <c r="D50" s="110" t="s">
         <v>88</v>
       </c>
-      <c r="E50" s="156"/>
-      <c r="F50" s="157"/>
+      <c r="E50" s="157"/>
+      <c r="F50" s="158"/>
       <c r="G50" s="50" t="s">
         <v>83</v>
       </c>
@@ -4273,28 +4273,28 @@
       <c r="K50" s="50" t="s">
         <v>83</v>
       </c>
-      <c r="L50" s="195"/>
-      <c r="M50" s="157"/>
+      <c r="L50" s="196"/>
+      <c r="M50" s="158"/>
       <c r="N50" s="51"/>
       <c r="O50" s="51"/>
       <c r="P50" s="54"/>
       <c r="Q50" s="62"/>
-      <c r="R50" s="158"/>
-      <c r="S50" s="159"/>
-      <c r="T50" s="157"/>
+      <c r="R50" s="159"/>
+      <c r="S50" s="160"/>
+      <c r="T50" s="158"/>
       <c r="U50" s="58"/>
       <c r="V50" s="59"/>
     </row>
     <row r="51" spans="2:23" ht="50.1" customHeight="1">
-      <c r="B51" s="227"/>
+      <c r="B51" s="228"/>
       <c r="C51" s="113">
         <v>7</v>
       </c>
       <c r="D51" s="110" t="s">
         <v>89</v>
       </c>
-      <c r="E51" s="156"/>
-      <c r="F51" s="157"/>
+      <c r="E51" s="157"/>
+      <c r="F51" s="158"/>
       <c r="G51" s="50" t="s">
         <v>83</v>
       </c>
@@ -4304,15 +4304,15 @@
       <c r="K51" s="50" t="s">
         <v>83</v>
       </c>
-      <c r="L51" s="195"/>
-      <c r="M51" s="157"/>
+      <c r="L51" s="196"/>
+      <c r="M51" s="158"/>
       <c r="N51" s="53"/>
       <c r="O51" s="53"/>
       <c r="P51" s="61"/>
       <c r="Q51" s="55"/>
-      <c r="R51" s="158"/>
-      <c r="S51" s="159"/>
-      <c r="T51" s="157"/>
+      <c r="R51" s="159"/>
+      <c r="S51" s="160"/>
+      <c r="T51" s="158"/>
       <c r="U51" s="58"/>
       <c r="V51" s="59"/>
     </row>
@@ -4340,128 +4340,128 @@
       <c r="V52" s="59"/>
     </row>
     <row r="53" spans="2:23" ht="18" customHeight="1">
-      <c r="B53" s="225" t="s">
+      <c r="B53" s="226" t="s">
         <v>90</v>
       </c>
       <c r="C53" s="72"/>
       <c r="D53" s="72"/>
-      <c r="E53" s="278" t="s">
+      <c r="E53" s="279" t="s">
         <v>63</v>
       </c>
-      <c r="F53" s="185"/>
-      <c r="G53" s="279" t="s">
+      <c r="F53" s="186"/>
+      <c r="G53" s="280" t="s">
         <v>91</v>
       </c>
-      <c r="H53" s="185"/>
-      <c r="I53" s="153" t="s">
+      <c r="H53" s="186"/>
+      <c r="I53" s="154" t="s">
         <v>92</v>
       </c>
-      <c r="J53" s="273" t="s">
+      <c r="J53" s="274" t="s">
         <v>93</v>
       </c>
-      <c r="K53" s="279" t="s">
+      <c r="K53" s="280" t="s">
         <v>67</v>
       </c>
-      <c r="L53" s="171"/>
-      <c r="M53" s="185"/>
-      <c r="N53" s="153" t="s">
+      <c r="L53" s="172"/>
+      <c r="M53" s="186"/>
+      <c r="N53" s="154" t="s">
         <v>68</v>
       </c>
       <c r="O53" s="42" t="s">
         <v>66</v>
       </c>
-      <c r="P53" s="153" t="s">
+      <c r="P53" s="154" t="s">
         <v>69</v>
       </c>
       <c r="Q53" s="41"/>
-      <c r="R53" s="153" t="s">
+      <c r="R53" s="154" t="s">
         <v>70</v>
       </c>
-      <c r="S53" s="171"/>
-      <c r="T53" s="185"/>
-      <c r="U53" s="274" t="s">
+      <c r="S53" s="172"/>
+      <c r="T53" s="186"/>
+      <c r="U53" s="275" t="s">
         <v>71</v>
       </c>
       <c r="V53" s="43"/>
     </row>
     <row r="54" spans="2:23" ht="50.4" customHeight="1">
-      <c r="B54" s="226"/>
+      <c r="B54" s="227"/>
       <c r="C54" s="41" t="s">
         <v>72</v>
       </c>
       <c r="D54" s="41" t="s">
         <v>73</v>
       </c>
-      <c r="E54" s="172"/>
-      <c r="F54" s="188"/>
-      <c r="G54" s="175"/>
-      <c r="H54" s="186"/>
-      <c r="I54" s="154"/>
-      <c r="J54" s="154"/>
-      <c r="K54" s="175"/>
-      <c r="L54" s="176"/>
-      <c r="M54" s="186"/>
-      <c r="N54" s="154"/>
-      <c r="O54" s="233" t="s">
+      <c r="E54" s="173"/>
+      <c r="F54" s="189"/>
+      <c r="G54" s="176"/>
+      <c r="H54" s="187"/>
+      <c r="I54" s="155"/>
+      <c r="J54" s="155"/>
+      <c r="K54" s="176"/>
+      <c r="L54" s="177"/>
+      <c r="M54" s="187"/>
+      <c r="N54" s="155"/>
+      <c r="O54" s="234" t="s">
         <v>74</v>
       </c>
-      <c r="P54" s="154"/>
+      <c r="P54" s="155"/>
       <c r="Q54" s="44" t="s">
         <v>75</v>
       </c>
-      <c r="R54" s="172"/>
-      <c r="S54" s="173"/>
-      <c r="T54" s="188"/>
-      <c r="U54" s="197"/>
+      <c r="R54" s="173"/>
+      <c r="S54" s="174"/>
+      <c r="T54" s="189"/>
+      <c r="U54" s="198"/>
       <c r="V54" s="43"/>
     </row>
     <row r="55" spans="2:23" ht="50.4" customHeight="1">
-      <c r="B55" s="226"/>
+      <c r="B55" s="227"/>
       <c r="C55" s="45" t="s">
         <v>76</v>
       </c>
       <c r="D55" s="45" t="s">
         <v>77</v>
       </c>
-      <c r="E55" s="175"/>
-      <c r="F55" s="186"/>
+      <c r="E55" s="176"/>
+      <c r="F55" s="187"/>
       <c r="G55" s="46" t="s">
         <v>80</v>
       </c>
       <c r="H55" s="73" t="s">
         <v>79</v>
       </c>
-      <c r="I55" s="155"/>
-      <c r="J55" s="155"/>
+      <c r="I55" s="156"/>
+      <c r="J55" s="156"/>
       <c r="K55" s="46" t="s">
         <v>80</v>
       </c>
-      <c r="L55" s="279" t="s">
+      <c r="L55" s="280" t="s">
         <v>79</v>
       </c>
-      <c r="M55" s="157"/>
-      <c r="N55" s="155"/>
-      <c r="O55" s="155"/>
-      <c r="P55" s="155"/>
+      <c r="M55" s="158"/>
+      <c r="N55" s="156"/>
+      <c r="O55" s="156"/>
+      <c r="P55" s="156"/>
       <c r="Q55" s="47" t="s">
         <v>81</v>
       </c>
-      <c r="R55" s="175"/>
-      <c r="S55" s="176"/>
-      <c r="T55" s="186"/>
-      <c r="U55" s="198"/>
+      <c r="R55" s="176"/>
+      <c r="S55" s="177"/>
+      <c r="T55" s="187"/>
+      <c r="U55" s="199"/>
       <c r="V55" s="43"/>
     </row>
     <row r="56" spans="2:23" ht="30" customHeight="1">
-      <c r="B56" s="226"/>
+      <c r="B56" s="227"/>
       <c r="C56" s="48">
         <v>1</v>
       </c>
       <c r="D56" s="49" t="s">
         <v>82</v>
       </c>
-      <c r="E56" s="156"/>
-      <c r="F56" s="157"/>
+      <c r="E56" s="157"/>
+      <c r="F56" s="158"/>
       <c r="G56" s="50" t="s">
         <v>83</v>
       </c>
@@ -4471,8 +4471,8 @@
       <c r="K56" s="50" t="s">
         <v>83</v>
       </c>
-      <c r="L56" s="195"/>
-      <c r="M56" s="157"/>
+      <c r="L56" s="196"/>
+      <c r="M56" s="158"/>
       <c r="N56" s="53"/>
       <c r="O56" s="53"/>
       <c r="P56" s="61"/>
@@ -4484,15 +4484,15 @@
       <c r="V56" s="59"/>
     </row>
     <row r="57" spans="2:23" ht="30" customHeight="1">
-      <c r="B57" s="226"/>
+      <c r="B57" s="227"/>
       <c r="C57" s="56">
         <v>2</v>
       </c>
       <c r="D57" s="75" t="s">
         <v>94</v>
       </c>
-      <c r="E57" s="156"/>
-      <c r="F57" s="157"/>
+      <c r="E57" s="157"/>
+      <c r="F57" s="158"/>
       <c r="G57" s="50" t="s">
         <v>83</v>
       </c>
@@ -4502,8 +4502,8 @@
       <c r="K57" s="50" t="s">
         <v>83</v>
       </c>
-      <c r="L57" s="195"/>
-      <c r="M57" s="157"/>
+      <c r="L57" s="196"/>
+      <c r="M57" s="158"/>
       <c r="N57" s="51"/>
       <c r="O57" s="51"/>
       <c r="P57" s="54"/>
@@ -4515,15 +4515,15 @@
       <c r="V57" s="59"/>
     </row>
     <row r="58" spans="2:23" ht="30" customHeight="1">
-      <c r="B58" s="226"/>
+      <c r="B58" s="227"/>
       <c r="C58" s="56">
         <v>3</v>
       </c>
       <c r="D58" s="77" t="s">
         <v>95</v>
       </c>
-      <c r="E58" s="156"/>
-      <c r="F58" s="157"/>
+      <c r="E58" s="157"/>
+      <c r="F58" s="158"/>
       <c r="G58" s="50" t="s">
         <v>83</v>
       </c>
@@ -4533,8 +4533,8 @@
       <c r="K58" s="50" t="s">
         <v>83</v>
       </c>
-      <c r="L58" s="195"/>
-      <c r="M58" s="157"/>
+      <c r="L58" s="196"/>
+      <c r="M58" s="158"/>
       <c r="N58" s="51"/>
       <c r="O58" s="51"/>
       <c r="P58" s="54"/>
@@ -4546,15 +4546,15 @@
       <c r="V58" s="59"/>
     </row>
     <row r="59" spans="2:23" ht="30" customHeight="1">
-      <c r="B59" s="226"/>
+      <c r="B59" s="227"/>
       <c r="C59" s="78">
         <v>4</v>
       </c>
       <c r="D59" s="79" t="s">
         <v>96</v>
       </c>
-      <c r="E59" s="156"/>
-      <c r="F59" s="157"/>
+      <c r="E59" s="157"/>
+      <c r="F59" s="158"/>
       <c r="G59" s="50" t="s">
         <v>83</v>
       </c>
@@ -4564,8 +4564,8 @@
       <c r="K59" s="59" t="s">
         <v>83</v>
       </c>
-      <c r="L59" s="195"/>
-      <c r="M59" s="157"/>
+      <c r="L59" s="196"/>
+      <c r="M59" s="158"/>
       <c r="N59" s="51"/>
       <c r="O59" s="51"/>
       <c r="P59" s="54"/>
@@ -4577,15 +4577,15 @@
       <c r="V59" s="59"/>
     </row>
     <row r="60" spans="2:23" ht="30" customHeight="1">
-      <c r="B60" s="226"/>
+      <c r="B60" s="227"/>
       <c r="C60" s="78">
         <v>5</v>
       </c>
       <c r="D60" s="79" t="s">
         <v>86</v>
       </c>
-      <c r="E60" s="156"/>
-      <c r="F60" s="157"/>
+      <c r="E60" s="157"/>
+      <c r="F60" s="158"/>
       <c r="G60" s="50" t="s">
         <v>83</v>
       </c>
@@ -4595,8 +4595,8 @@
       <c r="K60" s="59" t="s">
         <v>83</v>
       </c>
-      <c r="L60" s="195"/>
-      <c r="M60" s="157"/>
+      <c r="L60" s="196"/>
+      <c r="M60" s="158"/>
       <c r="N60" s="51"/>
       <c r="O60" s="51"/>
       <c r="P60" s="54"/>
@@ -4608,15 +4608,15 @@
       <c r="V60" s="59"/>
     </row>
     <row r="61" spans="2:23" ht="30" customHeight="1">
-      <c r="B61" s="227"/>
+      <c r="B61" s="228"/>
       <c r="C61" s="84">
         <v>6</v>
       </c>
       <c r="D61" s="85" t="s">
         <v>89</v>
       </c>
-      <c r="E61" s="156"/>
-      <c r="F61" s="157"/>
+      <c r="E61" s="157"/>
+      <c r="F61" s="158"/>
       <c r="G61" s="59" t="s">
         <v>83</v>
       </c>
@@ -4626,8 +4626,8 @@
       <c r="K61" s="84" t="s">
         <v>83</v>
       </c>
-      <c r="L61" s="195"/>
-      <c r="M61" s="157"/>
+      <c r="L61" s="196"/>
+      <c r="M61" s="158"/>
       <c r="N61" s="87"/>
       <c r="O61" s="87"/>
       <c r="P61" s="84"/>
@@ -4639,32 +4639,32 @@
       <c r="V61" s="59"/>
     </row>
     <row r="62" spans="2:23" s="88" customFormat="1" ht="23.25" customHeight="1" thickBot="1">
-      <c r="B62" s="275" t="s">
+      <c r="B62" s="276" t="s">
         <v>97</v>
       </c>
-      <c r="C62" s="271"/>
-      <c r="D62" s="271"/>
-      <c r="E62" s="271"/>
-      <c r="F62" s="276"/>
-      <c r="G62" s="277" t="s">
+      <c r="C62" s="272"/>
+      <c r="D62" s="272"/>
+      <c r="E62" s="272"/>
+      <c r="F62" s="277"/>
+      <c r="G62" s="278" t="s">
         <v>98</v>
       </c>
-      <c r="H62" s="271"/>
-      <c r="I62" s="271"/>
-      <c r="J62" s="271"/>
-      <c r="K62" s="271"/>
-      <c r="L62" s="271"/>
-      <c r="M62" s="276"/>
-      <c r="N62" s="270" t="s">
+      <c r="H62" s="272"/>
+      <c r="I62" s="272"/>
+      <c r="J62" s="272"/>
+      <c r="K62" s="272"/>
+      <c r="L62" s="272"/>
+      <c r="M62" s="277"/>
+      <c r="N62" s="271" t="s">
         <v>99</v>
       </c>
-      <c r="O62" s="271"/>
-      <c r="P62" s="271"/>
-      <c r="Q62" s="271"/>
-      <c r="R62" s="271"/>
-      <c r="S62" s="271"/>
-      <c r="T62" s="271"/>
-      <c r="U62" s="272"/>
+      <c r="O62" s="272"/>
+      <c r="P62" s="272"/>
+      <c r="Q62" s="272"/>
+      <c r="R62" s="272"/>
+      <c r="S62" s="272"/>
+      <c r="T62" s="272"/>
+      <c r="U62" s="273"/>
       <c r="W62" s="89"/>
     </row>
     <row r="63" spans="2:23" ht="14.4" customHeight="1"/>

--- a/jo.xlsx
+++ b/jo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\production_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0ECFBA8-1EB4-4FAD-B5B3-EB5A20227A7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF352896-969D-46C4-AF24-923A5D0D4257}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,14 +17,14 @@
   </sheets>
   <definedNames>
     <definedName name="A">"'[1]2008 işemri bilgileri'!#ref!"</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Job_order!$B$1:$V$62</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Job_order!$B$1:$V$63</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="111">
   <si>
     <t>ПУК 8.5</t>
   </si>
@@ -385,7 +385,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="22"/>
+        <sz val="28"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
         <family val="2"/>
@@ -394,7 +394,10 @@
     </r>
   </si>
   <si>
-    <t>H248 MAIN LHD</t>
+    <t>H248 SA BOARDS</t>
+  </si>
+  <si>
+    <t>I10111-I10121</t>
   </si>
 </sst>
 </file>
@@ -409,7 +412,7 @@
     <numFmt numFmtId="167" formatCode="&quot; &quot;#,##0&quot; &quot;;&quot; (&quot;#,##0&quot;)&quot;;&quot; - &quot;;@&quot; &quot;"/>
     <numFmt numFmtId="168" formatCode="[$-402]0%"/>
   </numFmts>
-  <fonts count="70">
+  <fonts count="72">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -912,6 +915,19 @@
       <name val="Arial"/>
       <family val="2"/>
       <charset val="204"/>
+    </font>
+    <font>
+      <sz val="26"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="28"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="16">
@@ -1006,7 +1022,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="74">
+  <borders count="73">
     <border>
       <left/>
       <right/>
@@ -1840,15 +1856,6 @@
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -1933,7 +1940,7 @@
     <xf numFmtId="0" fontId="49" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="320">
+  <cellXfs count="323">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2019,9 +2026,6 @@
     <xf numFmtId="0" fontId="25" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2157,9 +2161,6 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="36" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2216,7 +2217,6 @@
     <xf numFmtId="0" fontId="57" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="58" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -2228,11 +2228,10 @@
     <xf numFmtId="0" fontId="47" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="70" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="66" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2247,28 +2246,347 @@
     <xf numFmtId="0" fontId="69" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="70" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="42" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="55" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="24" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="55" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="61" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="34" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="35" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="40" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="57" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="36" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="37" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="50" fillId="0" borderId="34" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="50" fillId="0" borderId="35" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="50" fillId="0" borderId="40" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="50" fillId="0" borderId="57" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="50" fillId="0" borderId="36" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="50" fillId="0" borderId="37" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="44" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="45" fillId="0" borderId="31" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="41" fillId="0" borderId="34" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="41" fillId="0" borderId="42" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="40" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="36" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="44" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="51" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="52" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="53" xfId="0" applyBorder="1"/>
+    <xf numFmtId="3" fontId="48" fillId="0" borderId="54" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="33" fillId="0" borderId="65" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="71" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="72" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="68" fillId="0" borderId="20" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="64" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="64" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="41" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="17" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="38" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="57" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1"/>
+    <xf numFmtId="43" fontId="60" fillId="0" borderId="5" xfId="26" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="20" xfId="26" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="60" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="24" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="62" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="50" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="68" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="44" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="27" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="58" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="59" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="60" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="41" fillId="0" borderId="43" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="40" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="41" fillId="0" borderId="41" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="36" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="44" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="41" fillId="0" borderId="45" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2282,19 +2600,6 @@
     <xf numFmtId="0" fontId="56" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="56" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="56" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="48" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2312,12 +2617,6 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="63" fillId="7" borderId="65" xfId="26" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2330,12 +2629,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="34" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2344,12 +2637,9 @@
     <xf numFmtId="0" fontId="62" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2368,292 +2658,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="50" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="68" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="55" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="44" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="20" xfId="26" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="52" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="53" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="33" fillId="0" borderId="65" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="72" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="73" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="68" fillId="0" borderId="20" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="64" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="64" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" applyBorder="1"/>
-    <xf numFmtId="3" fontId="41" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="17" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="38" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="57" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="60" fillId="0" borderId="5" xfId="26" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="48" fillId="0" borderId="54" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" xfId="0" applyBorder="1"/>
-    <xf numFmtId="3" fontId="60" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="24" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="62" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="58" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="60" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="27" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="59" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="45" fillId="0" borderId="31" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="51" xfId="0" applyBorder="1"/>
-    <xf numFmtId="49" fontId="42" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="24" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="55" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="61" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="34" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="35" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="40" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="57" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="36" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="37" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="50" fillId="0" borderId="34" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="50" fillId="0" borderId="35" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="50" fillId="0" borderId="40" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="50" fillId="0" borderId="57" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="50" fillId="0" borderId="36" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="50" fillId="0" borderId="37" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="59" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="59" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="44" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
+    <xf numFmtId="49" fontId="32" fillId="0" borderId="62" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="62" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="29">
     <cellStyle name="Comma" xfId="26" builtinId="3"/>
@@ -2965,7 +2977,7 @@
   <sheetPr codeName="Sheet2">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AMI166"/>
+  <dimension ref="A1:AMI167"/>
   <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="16.8984375" customWidth="1"/>
@@ -2997,71 +3009,73 @@
       <c r="A1" s="1">
         <v>24</v>
       </c>
-      <c r="B1" s="297"/>
-      <c r="C1" s="298"/>
-      <c r="D1" s="235" t="s">
+      <c r="B1" s="160"/>
+      <c r="C1" s="161"/>
+      <c r="D1" s="226" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="148" t="s">
+      <c r="E1" s="281" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="149"/>
-      <c r="G1" s="149"/>
-      <c r="H1" s="149"/>
-      <c r="I1" s="149"/>
-      <c r="J1" s="149"/>
-      <c r="K1" s="149"/>
-      <c r="L1" s="149"/>
-      <c r="M1" s="149"/>
-      <c r="N1" s="150"/>
-      <c r="O1" s="165" t="s">
+      <c r="F1" s="282"/>
+      <c r="G1" s="282"/>
+      <c r="H1" s="282"/>
+      <c r="I1" s="282"/>
+      <c r="J1" s="282"/>
+      <c r="K1" s="282"/>
+      <c r="L1" s="282"/>
+      <c r="M1" s="282"/>
+      <c r="N1" s="283"/>
+      <c r="O1" s="291" t="s">
         <v>2</v>
       </c>
-      <c r="P1" s="166"/>
-      <c r="Q1" s="166"/>
-      <c r="R1" s="166"/>
-      <c r="S1" s="166"/>
-      <c r="T1" s="166"/>
-      <c r="U1" s="167"/>
+      <c r="P1" s="292"/>
+      <c r="Q1" s="292"/>
+      <c r="R1" s="292"/>
+      <c r="S1" s="292"/>
+      <c r="T1" s="292"/>
+      <c r="U1" s="293"/>
+      <c r="V1" s="271"/>
     </row>
     <row r="2" spans="1:22" s="1" customFormat="1" ht="18.75" customHeight="1">
-      <c r="B2" s="237"/>
-      <c r="C2" s="189"/>
-      <c r="D2" s="233"/>
-      <c r="E2" s="151"/>
-      <c r="F2" s="152"/>
-      <c r="G2" s="152"/>
-      <c r="H2" s="152"/>
-      <c r="I2" s="152"/>
-      <c r="J2" s="152"/>
-      <c r="K2" s="152"/>
-      <c r="L2" s="152"/>
-      <c r="M2" s="152"/>
-      <c r="N2" s="153"/>
-      <c r="O2" s="168"/>
-      <c r="P2" s="169"/>
-      <c r="Q2" s="169"/>
-      <c r="R2" s="169"/>
-      <c r="S2" s="169"/>
-      <c r="T2" s="169"/>
-      <c r="U2" s="170"/>
+      <c r="B2" s="162"/>
+      <c r="C2" s="163"/>
+      <c r="D2" s="224"/>
+      <c r="E2" s="284"/>
+      <c r="F2" s="285"/>
+      <c r="G2" s="285"/>
+      <c r="H2" s="285"/>
+      <c r="I2" s="285"/>
+      <c r="J2" s="285"/>
+      <c r="K2" s="285"/>
+      <c r="L2" s="285"/>
+      <c r="M2" s="285"/>
+      <c r="N2" s="286"/>
+      <c r="O2" s="294"/>
+      <c r="P2" s="295"/>
+      <c r="Q2" s="295"/>
+      <c r="R2" s="295"/>
+      <c r="S2" s="295"/>
+      <c r="T2" s="295"/>
+      <c r="U2" s="296"/>
+      <c r="V2" s="271"/>
     </row>
     <row r="3" spans="1:22" ht="12.45" customHeight="1">
-      <c r="B3" s="237"/>
-      <c r="C3" s="189"/>
-      <c r="D3" s="260" t="s">
+      <c r="B3" s="162"/>
+      <c r="C3" s="163"/>
+      <c r="D3" s="170" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="171" t="s">
+      <c r="E3" s="297" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="172"/>
-      <c r="G3" s="172"/>
-      <c r="H3" s="172"/>
-      <c r="I3" s="172"/>
-      <c r="J3" s="172"/>
-      <c r="K3" s="172"/>
-      <c r="L3" s="128"/>
+      <c r="F3" s="154"/>
+      <c r="G3" s="154"/>
+      <c r="H3" s="154"/>
+      <c r="I3" s="154"/>
+      <c r="J3" s="154"/>
+      <c r="K3" s="154"/>
+      <c r="L3" s="125"/>
       <c r="M3" s="5"/>
       <c r="N3" s="5"/>
       <c r="O3" s="5"/>
@@ -3070,488 +3084,506 @@
       <c r="R3" s="5"/>
       <c r="S3" s="5"/>
       <c r="T3" s="5"/>
-      <c r="U3" s="129"/>
+      <c r="U3" s="126"/>
+      <c r="V3" s="271"/>
     </row>
     <row r="4" spans="1:22" ht="14.85" customHeight="1">
-      <c r="B4" s="237"/>
-      <c r="C4" s="189"/>
-      <c r="D4" s="155"/>
-      <c r="E4" s="173"/>
-      <c r="F4" s="174"/>
-      <c r="G4" s="174"/>
-      <c r="H4" s="174"/>
-      <c r="I4" s="174"/>
-      <c r="J4" s="174"/>
-      <c r="K4" s="175"/>
-      <c r="L4" s="130"/>
-      <c r="U4" s="131"/>
+      <c r="B4" s="162"/>
+      <c r="C4" s="163"/>
+      <c r="D4" s="167"/>
+      <c r="E4" s="148"/>
+      <c r="F4" s="205"/>
+      <c r="G4" s="205"/>
+      <c r="H4" s="205"/>
+      <c r="I4" s="205"/>
+      <c r="J4" s="205"/>
+      <c r="K4" s="244"/>
+      <c r="L4" s="127"/>
+      <c r="U4" s="128"/>
+      <c r="V4" s="271"/>
     </row>
     <row r="5" spans="1:22" ht="14.85" customHeight="1">
-      <c r="B5" s="218"/>
-      <c r="C5" s="187"/>
-      <c r="D5" s="156"/>
-      <c r="E5" s="176"/>
-      <c r="F5" s="177"/>
-      <c r="G5" s="177"/>
-      <c r="H5" s="177"/>
-      <c r="I5" s="177"/>
-      <c r="J5" s="177"/>
-      <c r="K5" s="177"/>
-      <c r="L5" s="130"/>
-      <c r="U5" s="131"/>
+      <c r="B5" s="139"/>
+      <c r="C5" s="140"/>
+      <c r="D5" s="144"/>
+      <c r="E5" s="149"/>
+      <c r="F5" s="155"/>
+      <c r="G5" s="155"/>
+      <c r="H5" s="155"/>
+      <c r="I5" s="155"/>
+      <c r="J5" s="155"/>
+      <c r="K5" s="155"/>
+      <c r="L5" s="127"/>
+      <c r="U5" s="128"/>
+      <c r="V5" s="271"/>
     </row>
     <row r="6" spans="1:22" s="2" customFormat="1" ht="27.75" customHeight="1">
-      <c r="B6" s="248" t="s">
+      <c r="B6" s="137" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="186"/>
-      <c r="D6" s="318"/>
-      <c r="E6" s="216" t="s">
+      <c r="C6" s="138"/>
+      <c r="D6" s="189"/>
+      <c r="E6" s="243" t="s">
         <v>6</v>
       </c>
-      <c r="F6" s="172"/>
-      <c r="G6" s="172"/>
-      <c r="H6" s="186"/>
-      <c r="I6" s="214" t="s">
+      <c r="F6" s="154"/>
+      <c r="G6" s="154"/>
+      <c r="H6" s="138"/>
+      <c r="I6" s="241" t="s">
         <v>7</v>
       </c>
-      <c r="J6" s="158"/>
-      <c r="K6" s="102" t="s">
+      <c r="J6" s="142"/>
+      <c r="K6" s="100" t="s">
         <v>8</v>
       </c>
-      <c r="L6" s="130"/>
-      <c r="U6" s="131"/>
+      <c r="L6" s="127"/>
+      <c r="U6" s="128"/>
+      <c r="V6" s="271"/>
     </row>
     <row r="7" spans="1:22" s="2" customFormat="1" ht="28.5" customHeight="1">
-      <c r="B7" s="218"/>
-      <c r="C7" s="187"/>
-      <c r="D7" s="156"/>
-      <c r="E7" s="173"/>
-      <c r="F7" s="175"/>
-      <c r="G7" s="175"/>
-      <c r="H7" s="189"/>
-      <c r="I7" s="215"/>
-      <c r="J7" s="158"/>
-      <c r="K7" s="103"/>
-      <c r="L7" s="130"/>
-      <c r="P7" s="135"/>
-      <c r="U7" s="131"/>
+      <c r="B7" s="139"/>
+      <c r="C7" s="140"/>
+      <c r="D7" s="144"/>
+      <c r="E7" s="148"/>
+      <c r="F7" s="244"/>
+      <c r="G7" s="244"/>
+      <c r="H7" s="163"/>
+      <c r="I7" s="242"/>
+      <c r="J7" s="142"/>
+      <c r="K7" s="101"/>
+      <c r="L7" s="127"/>
+      <c r="P7" s="131"/>
+      <c r="U7" s="128"/>
+      <c r="V7" s="271"/>
     </row>
     <row r="8" spans="1:22" s="2" customFormat="1" ht="31.95" customHeight="1">
-      <c r="B8" s="248" t="s">
+      <c r="B8" s="137" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="186"/>
-      <c r="D8" s="243"/>
-      <c r="E8" s="302" t="s">
+      <c r="C8" s="138"/>
+      <c r="D8" s="232"/>
+      <c r="E8" s="173" t="s">
         <v>101</v>
       </c>
-      <c r="F8" s="303"/>
-      <c r="G8" s="308" t="s">
+      <c r="F8" s="174"/>
+      <c r="G8" s="179" t="s">
         <v>100</v>
       </c>
-      <c r="H8" s="309"/>
-      <c r="I8" s="264" t="s">
+      <c r="H8" s="180"/>
+      <c r="I8" s="252" t="s">
         <v>103</v>
       </c>
-      <c r="J8" s="265"/>
-      <c r="K8" s="229"/>
-      <c r="L8" s="130"/>
-      <c r="P8" s="135"/>
-      <c r="U8" s="131"/>
-      <c r="V8" s="101"/>
+      <c r="J8" s="253"/>
+      <c r="K8" s="218"/>
+      <c r="L8" s="127"/>
+      <c r="P8" s="131"/>
+      <c r="U8" s="128"/>
+      <c r="V8" s="271"/>
     </row>
     <row r="9" spans="1:22" s="2" customFormat="1" ht="3.75" hidden="1" customHeight="1">
-      <c r="B9" s="218"/>
-      <c r="C9" s="187"/>
-      <c r="D9" s="176"/>
-      <c r="E9" s="304"/>
-      <c r="F9" s="305"/>
-      <c r="G9" s="310"/>
-      <c r="H9" s="311"/>
-      <c r="I9" s="266"/>
-      <c r="J9" s="267"/>
-      <c r="K9" s="230"/>
-      <c r="L9" s="130"/>
-      <c r="P9" s="135" t="str">
+      <c r="B9" s="139"/>
+      <c r="C9" s="140"/>
+      <c r="D9" s="149"/>
+      <c r="E9" s="175"/>
+      <c r="F9" s="176"/>
+      <c r="G9" s="181"/>
+      <c r="H9" s="182"/>
+      <c r="I9" s="254"/>
+      <c r="J9" s="255"/>
+      <c r="K9" s="219"/>
+      <c r="L9" s="127"/>
+      <c r="P9" s="131" t="str">
         <f t="shared" ref="P9" si="0">"*"&amp;J18&amp;"*"</f>
         <v>**</v>
       </c>
-      <c r="U9" s="131"/>
-      <c r="V9" s="101"/>
+      <c r="U9" s="128"/>
+      <c r="V9" s="271"/>
     </row>
     <row r="10" spans="1:22" s="2" customFormat="1" ht="15" customHeight="1">
-      <c r="B10" s="255" t="s">
+      <c r="B10" s="248" t="s">
         <v>11</v>
       </c>
-      <c r="C10" s="186"/>
-      <c r="D10" s="232"/>
-      <c r="E10" s="306"/>
-      <c r="F10" s="307"/>
-      <c r="G10" s="312"/>
-      <c r="H10" s="313"/>
-      <c r="I10" s="266"/>
-      <c r="J10" s="267"/>
-      <c r="K10" s="230"/>
-      <c r="L10" s="130"/>
-      <c r="P10" s="135"/>
-      <c r="U10" s="131"/>
-      <c r="V10" s="101"/>
+      <c r="C10" s="138"/>
+      <c r="D10" s="223"/>
+      <c r="E10" s="177"/>
+      <c r="F10" s="178"/>
+      <c r="G10" s="183"/>
+      <c r="H10" s="184"/>
+      <c r="I10" s="254"/>
+      <c r="J10" s="255"/>
+      <c r="K10" s="219"/>
+      <c r="L10" s="127"/>
+      <c r="P10" s="131"/>
+      <c r="U10" s="128"/>
+      <c r="V10" s="271"/>
     </row>
     <row r="11" spans="1:22" s="2" customFormat="1" ht="78.599999999999994" customHeight="1">
-      <c r="B11" s="218"/>
-      <c r="C11" s="187"/>
-      <c r="D11" s="233"/>
-      <c r="E11" s="314"/>
-      <c r="F11" s="315"/>
-      <c r="G11" s="316"/>
-      <c r="H11" s="317"/>
-      <c r="I11" s="268"/>
-      <c r="J11" s="269"/>
-      <c r="K11" s="231"/>
-      <c r="L11" s="130"/>
-      <c r="M11" s="136" t="str">
+      <c r="B11" s="139"/>
+      <c r="C11" s="140"/>
+      <c r="D11" s="224"/>
+      <c r="E11" s="185"/>
+      <c r="F11" s="186"/>
+      <c r="G11" s="187" t="s">
+        <v>110</v>
+      </c>
+      <c r="H11" s="188"/>
+      <c r="I11" s="256"/>
+      <c r="J11" s="257"/>
+      <c r="K11" s="220"/>
+      <c r="L11" s="127"/>
+      <c r="M11" s="132" t="str">
         <f>"*"&amp;J16&amp;"*"</f>
         <v>*232323*</v>
       </c>
-      <c r="N11" s="136"/>
-      <c r="O11" s="136"/>
-      <c r="P11" s="136"/>
-      <c r="Q11" s="136"/>
-      <c r="S11" s="137"/>
-      <c r="U11" s="131"/>
-      <c r="V11" s="101"/>
+      <c r="N11" s="132"/>
+      <c r="O11" s="132"/>
+      <c r="P11" s="132"/>
+      <c r="Q11" s="132"/>
+      <c r="S11" s="133"/>
+      <c r="U11" s="128"/>
+      <c r="V11" s="271"/>
     </row>
     <row r="12" spans="1:22" s="2" customFormat="1" ht="28.5" customHeight="1">
-      <c r="B12" s="319" t="s">
+      <c r="B12" s="146" t="s">
         <v>12</v>
       </c>
-      <c r="C12" s="186"/>
-      <c r="D12" s="250" t="s">
+      <c r="C12" s="138"/>
+      <c r="D12" s="239" t="s">
         <v>102</v>
       </c>
-      <c r="E12" s="285"/>
-      <c r="F12" s="172"/>
-      <c r="G12" s="172"/>
-      <c r="H12" s="186"/>
-      <c r="I12" s="190" t="s">
+      <c r="E12" s="259"/>
+      <c r="F12" s="154"/>
+      <c r="G12" s="154"/>
+      <c r="H12" s="138"/>
+      <c r="I12" s="306" t="s">
         <v>13</v>
       </c>
-      <c r="J12" s="191"/>
-      <c r="K12" s="292"/>
-      <c r="L12" s="130"/>
-      <c r="U12" s="131"/>
+      <c r="J12" s="307"/>
+      <c r="K12" s="147"/>
+      <c r="L12" s="127"/>
+      <c r="U12" s="128"/>
+      <c r="V12" s="271"/>
     </row>
     <row r="13" spans="1:22" s="2" customFormat="1" ht="13.5" customHeight="1">
-      <c r="B13" s="218"/>
-      <c r="C13" s="187"/>
-      <c r="D13" s="251"/>
-      <c r="E13" s="173"/>
-      <c r="F13" s="174"/>
-      <c r="G13" s="174"/>
-      <c r="H13" s="189"/>
-      <c r="I13" s="192"/>
-      <c r="J13" s="193"/>
-      <c r="K13" s="173"/>
-      <c r="L13" s="130"/>
-      <c r="U13" s="131"/>
+      <c r="B13" s="139"/>
+      <c r="C13" s="140"/>
+      <c r="D13" s="240"/>
+      <c r="E13" s="148"/>
+      <c r="F13" s="205"/>
+      <c r="G13" s="205"/>
+      <c r="H13" s="163"/>
+      <c r="I13" s="308"/>
+      <c r="J13" s="309"/>
+      <c r="K13" s="148"/>
+      <c r="L13" s="127"/>
+      <c r="U13" s="128"/>
+      <c r="V13" s="271"/>
     </row>
     <row r="14" spans="1:22" s="2" customFormat="1" ht="15" customHeight="1">
-      <c r="B14" s="286" t="s">
+      <c r="B14" s="260" t="s">
         <v>14</v>
       </c>
-      <c r="C14" s="186"/>
-      <c r="D14" s="263" t="s">
+      <c r="C14" s="138"/>
+      <c r="D14" s="251" t="s">
         <v>107</v>
       </c>
-      <c r="E14" s="173"/>
-      <c r="F14" s="174"/>
-      <c r="G14" s="174"/>
-      <c r="H14" s="189"/>
-      <c r="I14" s="192"/>
-      <c r="J14" s="193"/>
-      <c r="K14" s="173"/>
-      <c r="L14" s="130"/>
-      <c r="U14" s="131"/>
+      <c r="E14" s="148"/>
+      <c r="F14" s="205"/>
+      <c r="G14" s="205"/>
+      <c r="H14" s="163"/>
+      <c r="I14" s="308"/>
+      <c r="J14" s="309"/>
+      <c r="K14" s="148"/>
+      <c r="L14" s="127"/>
+      <c r="U14" s="128"/>
+      <c r="V14" s="271"/>
     </row>
     <row r="15" spans="1:22" s="2" customFormat="1" ht="48" customHeight="1">
-      <c r="B15" s="218"/>
-      <c r="C15" s="187"/>
-      <c r="D15" s="251"/>
-      <c r="E15" s="176"/>
-      <c r="F15" s="177"/>
-      <c r="G15" s="177"/>
-      <c r="H15" s="187"/>
-      <c r="I15" s="194"/>
-      <c r="J15" s="195"/>
-      <c r="K15" s="176"/>
-      <c r="L15" s="132"/>
-      <c r="M15" s="133"/>
-      <c r="N15" s="138"/>
-      <c r="O15" s="133"/>
-      <c r="P15" s="133"/>
-      <c r="Q15" s="133"/>
-      <c r="R15" s="133"/>
-      <c r="S15" s="133"/>
-      <c r="T15" s="133"/>
-      <c r="U15" s="134"/>
+      <c r="B15" s="139"/>
+      <c r="C15" s="140"/>
+      <c r="D15" s="240"/>
+      <c r="E15" s="149"/>
+      <c r="F15" s="155"/>
+      <c r="G15" s="155"/>
+      <c r="H15" s="140"/>
+      <c r="I15" s="310"/>
+      <c r="J15" s="311"/>
+      <c r="K15" s="149"/>
+      <c r="L15" s="135"/>
+      <c r="M15" s="129"/>
+      <c r="N15" s="134"/>
+      <c r="O15" s="129"/>
+      <c r="P15" s="129"/>
+      <c r="Q15" s="129"/>
+      <c r="R15" s="129"/>
+      <c r="S15" s="129"/>
+      <c r="T15" s="129"/>
+      <c r="U15" s="130"/>
+      <c r="V15" s="271"/>
     </row>
     <row r="16" spans="1:22" s="2" customFormat="1" ht="15" customHeight="1">
-      <c r="B16" s="248" t="s">
+      <c r="B16" s="137" t="s">
         <v>15</v>
       </c>
-      <c r="C16" s="186"/>
-      <c r="D16" s="270"/>
-      <c r="E16" s="249" t="s">
+      <c r="C16" s="138"/>
+      <c r="D16" s="258"/>
+      <c r="E16" s="204" t="s">
         <v>16</v>
       </c>
-      <c r="F16" s="172"/>
-      <c r="G16" s="172"/>
-      <c r="H16" s="172"/>
-      <c r="I16" s="186"/>
-      <c r="J16" s="219">
+      <c r="F16" s="154"/>
+      <c r="G16" s="154"/>
+      <c r="H16" s="154"/>
+      <c r="I16" s="138"/>
+      <c r="J16" s="246">
         <v>232323</v>
       </c>
-      <c r="K16" s="220"/>
-      <c r="L16" s="139" t="s">
+      <c r="K16" s="236"/>
+      <c r="L16" s="196" t="s">
         <v>104</v>
       </c>
-      <c r="M16" s="140"/>
-      <c r="N16" s="140"/>
-      <c r="O16" s="140"/>
-      <c r="P16" s="140"/>
-      <c r="Q16" s="140"/>
-      <c r="R16" s="140"/>
-      <c r="S16" s="139" t="s">
+      <c r="M16" s="197"/>
+      <c r="N16" s="197"/>
+      <c r="O16" s="197"/>
+      <c r="P16" s="197"/>
+      <c r="Q16" s="197"/>
+      <c r="R16" s="197"/>
+      <c r="S16" s="196" t="s">
         <v>105</v>
       </c>
-      <c r="T16" s="140"/>
-      <c r="U16" s="141"/>
+      <c r="T16" s="197"/>
+      <c r="U16" s="278"/>
+      <c r="V16" s="271"/>
     </row>
     <row r="17" spans="2:22" s="2" customFormat="1" ht="15" customHeight="1">
-      <c r="B17" s="218"/>
-      <c r="C17" s="187"/>
-      <c r="D17" s="251"/>
-      <c r="E17" s="173"/>
-      <c r="F17" s="174"/>
-      <c r="G17" s="174"/>
-      <c r="H17" s="174"/>
-      <c r="I17" s="189"/>
-      <c r="J17" s="173"/>
-      <c r="K17" s="221"/>
-      <c r="L17" s="142"/>
-      <c r="M17" s="143"/>
-      <c r="N17" s="143"/>
-      <c r="O17" s="143"/>
-      <c r="P17" s="143"/>
-      <c r="Q17" s="143"/>
-      <c r="R17" s="143"/>
-      <c r="S17" s="142"/>
-      <c r="T17" s="143"/>
-      <c r="U17" s="144"/>
+      <c r="B17" s="139"/>
+      <c r="C17" s="140"/>
+      <c r="D17" s="240"/>
+      <c r="E17" s="148"/>
+      <c r="F17" s="205"/>
+      <c r="G17" s="205"/>
+      <c r="H17" s="205"/>
+      <c r="I17" s="163"/>
+      <c r="J17" s="148"/>
+      <c r="K17" s="247"/>
+      <c r="L17" s="198"/>
+      <c r="M17" s="199"/>
+      <c r="N17" s="199"/>
+      <c r="O17" s="199"/>
+      <c r="P17" s="199"/>
+      <c r="Q17" s="199"/>
+      <c r="R17" s="199"/>
+      <c r="S17" s="198"/>
+      <c r="T17" s="199"/>
+      <c r="U17" s="279"/>
+      <c r="V17" s="271"/>
     </row>
     <row r="18" spans="2:22" s="2" customFormat="1" ht="15" customHeight="1">
-      <c r="B18" s="299" t="s">
+      <c r="B18" s="165" t="s">
         <v>17</v>
       </c>
-      <c r="C18" s="186"/>
-      <c r="D18" s="241" t="s">
+      <c r="C18" s="138"/>
+      <c r="D18" s="230" t="s">
         <v>109</v>
       </c>
-      <c r="E18" s="173"/>
-      <c r="F18" s="174"/>
-      <c r="G18" s="174"/>
-      <c r="H18" s="174"/>
-      <c r="I18" s="189"/>
-      <c r="J18" s="173"/>
-      <c r="K18" s="221"/>
-      <c r="L18" s="142"/>
-      <c r="M18" s="143"/>
-      <c r="N18" s="143"/>
-      <c r="O18" s="143"/>
-      <c r="P18" s="143"/>
-      <c r="Q18" s="143"/>
-      <c r="R18" s="143"/>
-      <c r="S18" s="142"/>
-      <c r="T18" s="143"/>
-      <c r="U18" s="144"/>
+      <c r="E18" s="148"/>
+      <c r="F18" s="205"/>
+      <c r="G18" s="205"/>
+      <c r="H18" s="205"/>
+      <c r="I18" s="163"/>
+      <c r="J18" s="148"/>
+      <c r="K18" s="247"/>
+      <c r="L18" s="198"/>
+      <c r="M18" s="199"/>
+      <c r="N18" s="199"/>
+      <c r="O18" s="199"/>
+      <c r="P18" s="199"/>
+      <c r="Q18" s="199"/>
+      <c r="R18" s="199"/>
+      <c r="S18" s="198"/>
+      <c r="T18" s="199"/>
+      <c r="U18" s="279"/>
+      <c r="V18" s="271"/>
     </row>
     <row r="19" spans="2:22" s="2" customFormat="1" ht="15" customHeight="1">
-      <c r="B19" s="218"/>
-      <c r="C19" s="187"/>
-      <c r="D19" s="242"/>
-      <c r="E19" s="176"/>
-      <c r="F19" s="177"/>
-      <c r="G19" s="177"/>
-      <c r="H19" s="177"/>
-      <c r="I19" s="187"/>
-      <c r="J19" s="176"/>
-      <c r="K19" s="222"/>
-      <c r="L19" s="145"/>
-      <c r="M19" s="146"/>
-      <c r="N19" s="146"/>
-      <c r="O19" s="146"/>
-      <c r="P19" s="146"/>
-      <c r="Q19" s="146"/>
-      <c r="R19" s="146"/>
-      <c r="S19" s="145"/>
-      <c r="T19" s="146"/>
-      <c r="U19" s="147"/>
+      <c r="B19" s="139"/>
+      <c r="C19" s="140"/>
+      <c r="D19" s="231"/>
+      <c r="E19" s="149"/>
+      <c r="F19" s="155"/>
+      <c r="G19" s="155"/>
+      <c r="H19" s="155"/>
+      <c r="I19" s="140"/>
+      <c r="J19" s="149"/>
+      <c r="K19" s="238"/>
+      <c r="L19" s="200"/>
+      <c r="M19" s="201"/>
+      <c r="N19" s="201"/>
+      <c r="O19" s="201"/>
+      <c r="P19" s="201"/>
+      <c r="Q19" s="201"/>
+      <c r="R19" s="201"/>
+      <c r="S19" s="200"/>
+      <c r="T19" s="201"/>
+      <c r="U19" s="280"/>
+      <c r="V19" s="271"/>
     </row>
     <row r="20" spans="2:22" s="2" customFormat="1" ht="15" customHeight="1">
-      <c r="B20" s="248" t="s">
+      <c r="B20" s="137" t="s">
         <v>18</v>
       </c>
-      <c r="C20" s="186"/>
-      <c r="D20" s="256"/>
-      <c r="E20" s="249" t="s">
+      <c r="C20" s="138"/>
+      <c r="D20" s="249"/>
+      <c r="E20" s="204" t="s">
         <v>106</v>
       </c>
-      <c r="F20" s="172"/>
-      <c r="G20" s="172"/>
-      <c r="H20" s="172"/>
-      <c r="I20" s="186"/>
-      <c r="J20" s="245"/>
-      <c r="K20" s="220"/>
-      <c r="L20" s="206"/>
-      <c r="M20" s="207"/>
-      <c r="N20" s="207"/>
-      <c r="O20" s="207"/>
-      <c r="P20" s="207"/>
-      <c r="Q20" s="207"/>
-      <c r="R20" s="207"/>
-      <c r="S20" s="207"/>
-      <c r="T20" s="207"/>
-      <c r="U20" s="207"/>
-      <c r="V20" s="122"/>
+      <c r="F20" s="154"/>
+      <c r="G20" s="154"/>
+      <c r="H20" s="154"/>
+      <c r="I20" s="138"/>
+      <c r="J20" s="235"/>
+      <c r="K20" s="236"/>
+      <c r="L20" s="261"/>
+      <c r="M20" s="262"/>
+      <c r="N20" s="262"/>
+      <c r="O20" s="262"/>
+      <c r="P20" s="262"/>
+      <c r="Q20" s="262"/>
+      <c r="R20" s="262"/>
+      <c r="S20" s="262"/>
+      <c r="T20" s="262"/>
+      <c r="U20" s="262"/>
+      <c r="V20" s="271"/>
     </row>
     <row r="21" spans="2:22" s="2" customFormat="1" ht="62.4" customHeight="1">
-      <c r="B21" s="218"/>
-      <c r="C21" s="187"/>
-      <c r="D21" s="156"/>
-      <c r="E21" s="173"/>
-      <c r="F21" s="174"/>
-      <c r="G21" s="174"/>
-      <c r="H21" s="174"/>
-      <c r="I21" s="189"/>
-      <c r="J21" s="173"/>
-      <c r="K21" s="246"/>
-      <c r="L21" s="123"/>
-      <c r="M21" s="124"/>
-      <c r="N21" s="124"/>
-      <c r="O21" s="124"/>
-      <c r="P21" s="124"/>
-      <c r="Q21" s="124"/>
-      <c r="R21" s="124"/>
-      <c r="S21" s="126"/>
-      <c r="T21" s="124"/>
-      <c r="U21" s="125"/>
-      <c r="V21" s="122"/>
+      <c r="B21" s="139"/>
+      <c r="C21" s="140"/>
+      <c r="D21" s="144"/>
+      <c r="E21" s="148"/>
+      <c r="F21" s="205"/>
+      <c r="G21" s="205"/>
+      <c r="H21" s="205"/>
+      <c r="I21" s="163"/>
+      <c r="J21" s="148"/>
+      <c r="K21" s="237"/>
+      <c r="L21" s="120"/>
+      <c r="M21" s="121"/>
+      <c r="N21" s="121"/>
+      <c r="O21" s="121"/>
+      <c r="P21" s="121"/>
+      <c r="Q21" s="121"/>
+      <c r="R21" s="121"/>
+      <c r="S21" s="123"/>
+      <c r="T21" s="121"/>
+      <c r="U21" s="122"/>
+      <c r="V21" s="271"/>
     </row>
     <row r="22" spans="2:22" s="2" customFormat="1" ht="15" customHeight="1">
-      <c r="B22" s="248" t="s">
+      <c r="B22" s="137" t="s">
         <v>19</v>
       </c>
-      <c r="C22" s="186"/>
-      <c r="D22" s="213"/>
-      <c r="E22" s="173"/>
-      <c r="F22" s="174"/>
-      <c r="G22" s="174"/>
-      <c r="H22" s="174"/>
-      <c r="I22" s="189"/>
-      <c r="J22" s="173"/>
-      <c r="K22" s="246"/>
-      <c r="L22" s="200"/>
-      <c r="M22" s="200"/>
-      <c r="N22" s="200"/>
-      <c r="O22" s="200"/>
-      <c r="P22" s="200"/>
-      <c r="Q22" s="200"/>
-      <c r="R22" s="200"/>
-      <c r="S22" s="200"/>
-      <c r="T22" s="200"/>
-      <c r="U22" s="201"/>
+      <c r="C22" s="138"/>
+      <c r="D22" s="264"/>
+      <c r="E22" s="148"/>
+      <c r="F22" s="205"/>
+      <c r="G22" s="205"/>
+      <c r="H22" s="205"/>
+      <c r="I22" s="163"/>
+      <c r="J22" s="148"/>
+      <c r="K22" s="237"/>
+      <c r="L22" s="313"/>
+      <c r="M22" s="313"/>
+      <c r="N22" s="313"/>
+      <c r="O22" s="313"/>
+      <c r="P22" s="313"/>
+      <c r="Q22" s="313"/>
+      <c r="R22" s="313"/>
+      <c r="S22" s="313"/>
+      <c r="T22" s="313"/>
+      <c r="U22" s="314"/>
+      <c r="V22" s="271"/>
     </row>
     <row r="23" spans="2:22" s="2" customFormat="1" ht="15" customHeight="1">
-      <c r="B23" s="237"/>
-      <c r="C23" s="189"/>
-      <c r="D23" s="155"/>
-      <c r="E23" s="173"/>
-      <c r="F23" s="174"/>
-      <c r="G23" s="174"/>
-      <c r="H23" s="174"/>
-      <c r="I23" s="189"/>
-      <c r="J23" s="173"/>
-      <c r="K23" s="246"/>
-      <c r="L23" s="202"/>
-      <c r="M23" s="202"/>
-      <c r="N23" s="202"/>
-      <c r="O23" s="202"/>
-      <c r="P23" s="202"/>
-      <c r="Q23" s="202"/>
-      <c r="R23" s="202"/>
-      <c r="S23" s="202"/>
-      <c r="T23" s="202"/>
-      <c r="U23" s="203"/>
+      <c r="B23" s="162"/>
+      <c r="C23" s="163"/>
+      <c r="D23" s="167"/>
+      <c r="E23" s="148"/>
+      <c r="F23" s="205"/>
+      <c r="G23" s="205"/>
+      <c r="H23" s="205"/>
+      <c r="I23" s="163"/>
+      <c r="J23" s="148"/>
+      <c r="K23" s="237"/>
+      <c r="L23" s="315"/>
+      <c r="M23" s="315"/>
+      <c r="N23" s="315"/>
+      <c r="O23" s="315"/>
+      <c r="P23" s="315"/>
+      <c r="Q23" s="315"/>
+      <c r="R23" s="315"/>
+      <c r="S23" s="315"/>
+      <c r="T23" s="315"/>
+      <c r="U23" s="316"/>
+      <c r="V23" s="271"/>
     </row>
     <row r="24" spans="2:22" s="2" customFormat="1" ht="7.5" customHeight="1">
-      <c r="B24" s="218"/>
-      <c r="C24" s="187"/>
-      <c r="D24" s="156"/>
-      <c r="E24" s="176"/>
-      <c r="F24" s="177"/>
-      <c r="G24" s="177"/>
-      <c r="H24" s="177"/>
-      <c r="I24" s="187"/>
-      <c r="J24" s="176"/>
-      <c r="K24" s="222"/>
-      <c r="L24" s="204"/>
-      <c r="M24" s="204"/>
-      <c r="N24" s="204"/>
-      <c r="O24" s="204"/>
-      <c r="P24" s="204"/>
-      <c r="Q24" s="204"/>
-      <c r="R24" s="204"/>
-      <c r="S24" s="204"/>
-      <c r="T24" s="204"/>
-      <c r="U24" s="205"/>
+      <c r="B24" s="139"/>
+      <c r="C24" s="140"/>
+      <c r="D24" s="144"/>
+      <c r="E24" s="149"/>
+      <c r="F24" s="155"/>
+      <c r="G24" s="155"/>
+      <c r="H24" s="155"/>
+      <c r="I24" s="140"/>
+      <c r="J24" s="149"/>
+      <c r="K24" s="238"/>
+      <c r="L24" s="317"/>
+      <c r="M24" s="317"/>
+      <c r="N24" s="317"/>
+      <c r="O24" s="317"/>
+      <c r="P24" s="317"/>
+      <c r="Q24" s="317"/>
+      <c r="R24" s="317"/>
+      <c r="S24" s="317"/>
+      <c r="T24" s="317"/>
+      <c r="U24" s="318"/>
+      <c r="V24" s="271"/>
     </row>
     <row r="25" spans="2:22" s="2" customFormat="1" ht="30" customHeight="1">
-      <c r="B25" s="217" t="s">
+      <c r="B25" s="245" t="s">
         <v>20</v>
       </c>
-      <c r="C25" s="172"/>
-      <c r="D25" s="186"/>
+      <c r="C25" s="154"/>
+      <c r="D25" s="138"/>
       <c r="E25" s="3" t="s">
         <v>21</v>
       </c>
       <c r="F25" s="4"/>
-      <c r="G25" s="105" t="s">
+      <c r="G25" s="103" t="s">
         <v>22</v>
       </c>
       <c r="H25" s="4"/>
-      <c r="I25" s="105" t="s">
+      <c r="I25" s="103" t="s">
         <v>23</v>
       </c>
       <c r="J25" s="5"/>
-      <c r="K25" s="104" t="s">
+      <c r="K25" s="102" t="s">
         <v>24</v>
       </c>
-      <c r="L25" s="208" t="s">
+      <c r="L25" s="225" t="s">
         <v>25</v>
       </c>
-      <c r="M25" s="189"/>
-      <c r="N25" s="188" t="s">
+      <c r="M25" s="163"/>
+      <c r="N25" s="250" t="s">
         <v>26</v>
       </c>
-      <c r="O25" s="189"/>
+      <c r="O25" s="163"/>
       <c r="P25" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="Q25" s="188" t="s">
+      <c r="Q25" s="250" t="s">
         <v>28</v>
       </c>
-      <c r="R25" s="189"/>
+      <c r="R25" s="163"/>
       <c r="S25" s="7" t="s">
         <v>29</v>
       </c>
@@ -3561,11 +3593,12 @@
       <c r="U25" s="9" t="s">
         <v>29</v>
       </c>
+      <c r="V25" s="271"/>
     </row>
     <row r="26" spans="2:22" s="2" customFormat="1" ht="39" customHeight="1">
-      <c r="B26" s="218"/>
-      <c r="C26" s="177"/>
-      <c r="D26" s="187"/>
+      <c r="B26" s="139"/>
+      <c r="C26" s="155"/>
+      <c r="D26" s="140"/>
       <c r="E26" s="10"/>
       <c r="F26" s="11"/>
       <c r="G26" s="12"/>
@@ -3573,19 +3606,19 @@
       <c r="I26" s="12"/>
       <c r="J26" s="11"/>
       <c r="K26" s="13"/>
-      <c r="L26" s="176"/>
-      <c r="M26" s="187"/>
-      <c r="N26" s="208" t="s">
+      <c r="L26" s="149"/>
+      <c r="M26" s="140"/>
+      <c r="N26" s="225" t="s">
         <v>31</v>
       </c>
-      <c r="O26" s="187"/>
+      <c r="O26" s="140"/>
       <c r="P26" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="Q26" s="208" t="s">
+      <c r="Q26" s="225" t="s">
         <v>33</v>
       </c>
-      <c r="R26" s="187"/>
+      <c r="R26" s="140"/>
       <c r="S26" s="14" t="s">
         <v>34</v>
       </c>
@@ -3595,45 +3628,47 @@
       <c r="U26" s="16" t="s">
         <v>34</v>
       </c>
+      <c r="V26" s="271"/>
     </row>
     <row r="27" spans="2:22" s="2" customFormat="1" ht="46.05" customHeight="1">
-      <c r="B27" s="217" t="s">
+      <c r="B27" s="245" t="s">
         <v>36</v>
       </c>
-      <c r="C27" s="172"/>
-      <c r="D27" s="186"/>
+      <c r="C27" s="154"/>
+      <c r="D27" s="138"/>
       <c r="E27" s="3" t="s">
         <v>21</v>
       </c>
       <c r="F27" s="4"/>
-      <c r="G27" s="105" t="s">
+      <c r="G27" s="103" t="s">
         <v>37</v>
       </c>
       <c r="H27" s="4"/>
-      <c r="I27" s="105" t="s">
+      <c r="I27" s="103" t="s">
         <v>38</v>
       </c>
       <c r="J27" s="5"/>
       <c r="K27" s="6"/>
-      <c r="L27" s="293" t="s">
+      <c r="L27" s="150" t="s">
         <v>39</v>
       </c>
-      <c r="M27" s="120" t="s">
+      <c r="M27" s="118" t="s">
         <v>9</v>
       </c>
-      <c r="N27" s="300"/>
-      <c r="O27" s="301"/>
-      <c r="P27" s="93"/>
-      <c r="Q27" s="223"/>
-      <c r="R27" s="158"/>
+      <c r="N27" s="168"/>
+      <c r="O27" s="169"/>
+      <c r="P27" s="92"/>
+      <c r="Q27" s="233"/>
+      <c r="R27" s="142"/>
       <c r="S27" s="17"/>
       <c r="T27" s="18"/>
       <c r="U27" s="19"/>
+      <c r="V27" s="271"/>
     </row>
     <row r="28" spans="2:22" s="2" customFormat="1" ht="46.05" customHeight="1">
-      <c r="B28" s="218"/>
-      <c r="C28" s="177"/>
-      <c r="D28" s="187"/>
+      <c r="B28" s="139"/>
+      <c r="C28" s="155"/>
+      <c r="D28" s="140"/>
       <c r="E28" s="20"/>
       <c r="F28" s="21"/>
       <c r="G28" s="21"/>
@@ -3641,62 +3676,64 @@
       <c r="I28" s="22"/>
       <c r="J28" s="22"/>
       <c r="K28" s="23"/>
-      <c r="L28" s="211"/>
-      <c r="M28" s="120" t="s">
+      <c r="L28" s="151"/>
+      <c r="M28" s="118" t="s">
         <v>40</v>
       </c>
-      <c r="N28" s="224"/>
-      <c r="O28" s="225"/>
-      <c r="P28" s="93"/>
-      <c r="Q28" s="223"/>
-      <c r="R28" s="158"/>
+      <c r="N28" s="221"/>
+      <c r="O28" s="222"/>
+      <c r="P28" s="92"/>
+      <c r="Q28" s="233"/>
+      <c r="R28" s="142"/>
       <c r="S28" s="17"/>
       <c r="T28" s="18"/>
       <c r="U28" s="19"/>
+      <c r="V28" s="271"/>
     </row>
     <row r="29" spans="2:22" s="2" customFormat="1" ht="46.5" customHeight="1">
-      <c r="B29" s="236" t="s">
+      <c r="B29" s="227" t="s">
         <v>41</v>
       </c>
-      <c r="C29" s="172"/>
-      <c r="D29" s="186"/>
-      <c r="E29" s="247" t="s">
+      <c r="C29" s="154"/>
+      <c r="D29" s="138"/>
+      <c r="E29" s="202" t="s">
         <v>42</v>
       </c>
-      <c r="F29" s="172"/>
-      <c r="G29" s="172"/>
-      <c r="H29" s="172"/>
-      <c r="I29" s="172"/>
-      <c r="J29" s="172"/>
-      <c r="K29" s="186"/>
-      <c r="L29" s="212"/>
-      <c r="M29" s="121" t="s">
+      <c r="F29" s="154"/>
+      <c r="G29" s="154"/>
+      <c r="H29" s="154"/>
+      <c r="I29" s="154"/>
+      <c r="J29" s="154"/>
+      <c r="K29" s="138"/>
+      <c r="L29" s="152"/>
+      <c r="M29" s="119" t="s">
         <v>43</v>
       </c>
-      <c r="N29" s="224"/>
-      <c r="O29" s="225"/>
-      <c r="P29" s="94"/>
-      <c r="Q29" s="223"/>
-      <c r="R29" s="158"/>
+      <c r="N29" s="221"/>
+      <c r="O29" s="222"/>
+      <c r="P29" s="93"/>
+      <c r="Q29" s="233"/>
+      <c r="R29" s="142"/>
       <c r="S29" s="25"/>
       <c r="T29" s="5"/>
       <c r="U29" s="26"/>
+      <c r="V29" s="271"/>
     </row>
     <row r="30" spans="2:22" s="2" customFormat="1" ht="15" customHeight="1">
-      <c r="B30" s="237"/>
-      <c r="C30" s="174"/>
-      <c r="D30" s="189"/>
-      <c r="E30" s="176"/>
-      <c r="F30" s="177"/>
-      <c r="G30" s="177"/>
-      <c r="H30" s="177"/>
-      <c r="I30" s="177"/>
-      <c r="J30" s="177"/>
-      <c r="K30" s="187"/>
-      <c r="L30" s="210" t="s">
+      <c r="B30" s="162"/>
+      <c r="C30" s="205"/>
+      <c r="D30" s="163"/>
+      <c r="E30" s="149"/>
+      <c r="F30" s="155"/>
+      <c r="G30" s="155"/>
+      <c r="H30" s="155"/>
+      <c r="I30" s="155"/>
+      <c r="J30" s="155"/>
+      <c r="K30" s="140"/>
+      <c r="L30" s="263" t="s">
         <v>44</v>
       </c>
-      <c r="M30" s="252" t="s">
+      <c r="M30" s="192" t="s">
         <v>45</v>
       </c>
       <c r="N30" s="27"/>
@@ -3707,258 +3744,269 @@
       <c r="S30" s="30"/>
       <c r="T30" s="30"/>
       <c r="U30" s="26"/>
+      <c r="V30" s="271"/>
     </row>
     <row r="31" spans="2:22" s="2" customFormat="1" ht="42" customHeight="1">
-      <c r="B31" s="218"/>
-      <c r="C31" s="177"/>
-      <c r="D31" s="187"/>
-      <c r="E31" s="247" t="s">
+      <c r="B31" s="139"/>
+      <c r="C31" s="155"/>
+      <c r="D31" s="140"/>
+      <c r="E31" s="202" t="s">
         <v>108</v>
       </c>
-      <c r="F31" s="160"/>
-      <c r="G31" s="160"/>
-      <c r="H31" s="160"/>
-      <c r="I31" s="160"/>
-      <c r="J31" s="160"/>
-      <c r="K31" s="158"/>
-      <c r="L31" s="211"/>
-      <c r="M31" s="156"/>
-      <c r="N31" s="244"/>
-      <c r="O31" s="187"/>
-      <c r="P31" s="98"/>
-      <c r="Q31" s="156"/>
-      <c r="R31" s="187"/>
+      <c r="F31" s="157"/>
+      <c r="G31" s="157"/>
+      <c r="H31" s="157"/>
+      <c r="I31" s="157"/>
+      <c r="J31" s="157"/>
+      <c r="K31" s="142"/>
+      <c r="L31" s="151"/>
+      <c r="M31" s="144"/>
+      <c r="N31" s="234"/>
+      <c r="O31" s="140"/>
+      <c r="P31" s="97"/>
+      <c r="Q31" s="144"/>
+      <c r="R31" s="140"/>
       <c r="S31" s="31"/>
       <c r="T31" s="31"/>
       <c r="U31" s="32"/>
+      <c r="V31" s="271"/>
     </row>
     <row r="32" spans="2:22" s="2" customFormat="1" ht="21" customHeight="1">
-      <c r="B32" s="257" t="s">
+      <c r="B32" s="209" t="s">
         <v>46</v>
       </c>
-      <c r="C32" s="172"/>
-      <c r="D32" s="172"/>
-      <c r="E32" s="172"/>
-      <c r="F32" s="172"/>
-      <c r="G32" s="172"/>
-      <c r="H32" s="172"/>
-      <c r="I32" s="172"/>
-      <c r="J32" s="172"/>
-      <c r="K32" s="186"/>
-      <c r="L32" s="211"/>
-      <c r="M32" s="252" t="s">
+      <c r="C32" s="154"/>
+      <c r="D32" s="154"/>
+      <c r="E32" s="154"/>
+      <c r="F32" s="154"/>
+      <c r="G32" s="154"/>
+      <c r="H32" s="154"/>
+      <c r="I32" s="154"/>
+      <c r="J32" s="154"/>
+      <c r="K32" s="138"/>
+      <c r="L32" s="151"/>
+      <c r="M32" s="192" t="s">
         <v>47</v>
       </c>
-      <c r="N32" s="185"/>
-      <c r="O32" s="186"/>
-      <c r="P32" s="97"/>
-      <c r="Q32" s="209"/>
-      <c r="R32" s="186"/>
+      <c r="N32" s="305"/>
+      <c r="O32" s="138"/>
+      <c r="P32" s="96"/>
+      <c r="Q32" s="164"/>
+      <c r="R32" s="138"/>
       <c r="S32" s="33"/>
       <c r="T32" s="33"/>
       <c r="U32" s="34"/>
+      <c r="V32" s="271"/>
     </row>
     <row r="33" spans="1:22" s="2" customFormat="1" ht="21" customHeight="1">
-      <c r="B33" s="218"/>
-      <c r="C33" s="177"/>
-      <c r="D33" s="177"/>
-      <c r="E33" s="177"/>
-      <c r="F33" s="177"/>
-      <c r="G33" s="177"/>
-      <c r="H33" s="177"/>
-      <c r="I33" s="177"/>
-      <c r="J33" s="177"/>
-      <c r="K33" s="187"/>
-      <c r="L33" s="211"/>
-      <c r="M33" s="156"/>
-      <c r="N33" s="289"/>
-      <c r="O33" s="187"/>
-      <c r="P33" s="100"/>
-      <c r="Q33" s="288"/>
-      <c r="R33" s="187"/>
+      <c r="B33" s="139"/>
+      <c r="C33" s="155"/>
+      <c r="D33" s="155"/>
+      <c r="E33" s="155"/>
+      <c r="F33" s="155"/>
+      <c r="G33" s="155"/>
+      <c r="H33" s="155"/>
+      <c r="I33" s="155"/>
+      <c r="J33" s="155"/>
+      <c r="K33" s="140"/>
+      <c r="L33" s="151"/>
+      <c r="M33" s="144"/>
+      <c r="N33" s="206"/>
+      <c r="O33" s="140"/>
+      <c r="P33" s="99"/>
+      <c r="Q33" s="203"/>
+      <c r="R33" s="140"/>
       <c r="S33" s="36"/>
       <c r="T33" s="36"/>
       <c r="U33" s="32"/>
+      <c r="V33" s="271"/>
     </row>
     <row r="34" spans="1:22" s="2" customFormat="1" ht="21" customHeight="1">
-      <c r="B34" s="294" t="s">
+      <c r="B34" s="153" t="s">
         <v>48</v>
       </c>
-      <c r="C34" s="172"/>
-      <c r="D34" s="172"/>
-      <c r="E34" s="172"/>
-      <c r="F34" s="172"/>
-      <c r="G34" s="172"/>
-      <c r="H34" s="172"/>
-      <c r="I34" s="172"/>
-      <c r="J34" s="172"/>
-      <c r="K34" s="186"/>
-      <c r="L34" s="211"/>
-      <c r="M34" s="252" t="s">
+      <c r="C34" s="154"/>
+      <c r="D34" s="154"/>
+      <c r="E34" s="154"/>
+      <c r="F34" s="154"/>
+      <c r="G34" s="154"/>
+      <c r="H34" s="154"/>
+      <c r="I34" s="154"/>
+      <c r="J34" s="154"/>
+      <c r="K34" s="138"/>
+      <c r="L34" s="151"/>
+      <c r="M34" s="192" t="s">
         <v>49</v>
       </c>
-      <c r="N34" s="209"/>
-      <c r="O34" s="186"/>
+      <c r="N34" s="164"/>
+      <c r="O34" s="138"/>
       <c r="P34" s="24"/>
-      <c r="Q34" s="209"/>
-      <c r="R34" s="186"/>
+      <c r="Q34" s="164"/>
+      <c r="R34" s="138"/>
       <c r="S34" s="25"/>
       <c r="T34" s="25"/>
       <c r="U34" s="26"/>
+      <c r="V34" s="271"/>
     </row>
     <row r="35" spans="1:22" s="2" customFormat="1" ht="21" customHeight="1">
-      <c r="B35" s="218"/>
-      <c r="C35" s="177"/>
-      <c r="D35" s="177"/>
-      <c r="E35" s="177"/>
-      <c r="F35" s="177"/>
-      <c r="G35" s="177"/>
-      <c r="H35" s="177"/>
-      <c r="I35" s="177"/>
-      <c r="J35" s="177"/>
-      <c r="K35" s="187"/>
-      <c r="L35" s="211"/>
-      <c r="M35" s="156"/>
-      <c r="N35" s="156"/>
-      <c r="O35" s="187"/>
+      <c r="B35" s="139"/>
+      <c r="C35" s="155"/>
+      <c r="D35" s="155"/>
+      <c r="E35" s="155"/>
+      <c r="F35" s="155"/>
+      <c r="G35" s="155"/>
+      <c r="H35" s="155"/>
+      <c r="I35" s="155"/>
+      <c r="J35" s="155"/>
+      <c r="K35" s="140"/>
+      <c r="L35" s="151"/>
+      <c r="M35" s="144"/>
+      <c r="N35" s="144"/>
+      <c r="O35" s="140"/>
       <c r="P35" s="35"/>
-      <c r="Q35" s="156"/>
-      <c r="R35" s="187"/>
+      <c r="Q35" s="144"/>
+      <c r="R35" s="140"/>
       <c r="S35" s="36"/>
       <c r="T35" s="36"/>
       <c r="U35" s="32"/>
+      <c r="V35" s="271"/>
     </row>
     <row r="36" spans="1:22" s="2" customFormat="1" ht="21" customHeight="1">
       <c r="B36" s="37" t="s">
         <v>50</v>
       </c>
       <c r="C36" s="38"/>
-      <c r="D36" s="238"/>
-      <c r="E36" s="172"/>
-      <c r="F36" s="172"/>
-      <c r="G36" s="172"/>
-      <c r="H36" s="172"/>
-      <c r="I36" s="172"/>
-      <c r="J36" s="172"/>
-      <c r="K36" s="186"/>
-      <c r="L36" s="211"/>
-      <c r="M36" s="252" t="s">
+      <c r="D36" s="228"/>
+      <c r="E36" s="154"/>
+      <c r="F36" s="154"/>
+      <c r="G36" s="154"/>
+      <c r="H36" s="154"/>
+      <c r="I36" s="154"/>
+      <c r="J36" s="154"/>
+      <c r="K36" s="138"/>
+      <c r="L36" s="151"/>
+      <c r="M36" s="192" t="s">
         <v>51</v>
       </c>
-      <c r="N36" s="209"/>
-      <c r="O36" s="186"/>
+      <c r="N36" s="164"/>
+      <c r="O36" s="138"/>
       <c r="P36" s="24"/>
-      <c r="Q36" s="209"/>
-      <c r="R36" s="186"/>
+      <c r="Q36" s="164"/>
+      <c r="R36" s="138"/>
       <c r="S36" s="25"/>
       <c r="T36" s="25"/>
       <c r="U36" s="26"/>
+      <c r="V36" s="271"/>
     </row>
     <row r="37" spans="1:22" s="2" customFormat="1" ht="49.2" customHeight="1">
-      <c r="B37" s="295" t="s">
+      <c r="B37" s="156" t="s">
         <v>52</v>
       </c>
-      <c r="C37" s="160"/>
-      <c r="D37" s="127" t="s">
+      <c r="C37" s="157"/>
+      <c r="D37" s="124" t="s">
         <v>53</v>
       </c>
-      <c r="E37" s="287" t="s">
+      <c r="E37" s="195" t="s">
         <v>54</v>
       </c>
-      <c r="F37" s="160"/>
-      <c r="G37" s="240"/>
-      <c r="H37" s="115" t="s">
+      <c r="F37" s="157"/>
+      <c r="G37" s="159"/>
+      <c r="H37" s="113" t="s">
         <v>55</v>
       </c>
-      <c r="I37" s="290" t="s">
+      <c r="I37" s="207" t="s">
         <v>56</v>
       </c>
-      <c r="J37" s="291"/>
-      <c r="K37" s="116" t="s">
+      <c r="J37" s="208"/>
+      <c r="K37" s="114" t="s">
         <v>57</v>
       </c>
-      <c r="L37" s="211"/>
-      <c r="M37" s="156"/>
-      <c r="N37" s="156"/>
-      <c r="O37" s="187"/>
+      <c r="L37" s="151"/>
+      <c r="M37" s="144"/>
+      <c r="N37" s="144"/>
+      <c r="O37" s="140"/>
       <c r="P37" s="35"/>
-      <c r="Q37" s="156"/>
-      <c r="R37" s="187"/>
+      <c r="Q37" s="144"/>
+      <c r="R37" s="140"/>
       <c r="S37" s="36"/>
       <c r="T37" s="36"/>
       <c r="U37" s="32"/>
+      <c r="V37" s="271"/>
     </row>
     <row r="38" spans="1:22" s="2" customFormat="1" ht="24.6" customHeight="1">
-      <c r="B38" s="239"/>
-      <c r="C38" s="240"/>
-      <c r="D38" s="261"/>
-      <c r="E38" s="178"/>
-      <c r="F38" s="179"/>
-      <c r="G38" s="180"/>
-      <c r="H38" s="258"/>
-      <c r="I38" s="161"/>
-      <c r="J38" s="162"/>
-      <c r="K38" s="283"/>
-      <c r="L38" s="211"/>
-      <c r="M38" s="252" t="s">
+      <c r="B38" s="229"/>
+      <c r="C38" s="159"/>
+      <c r="D38" s="215"/>
+      <c r="E38" s="298"/>
+      <c r="F38" s="299"/>
+      <c r="G38" s="300"/>
+      <c r="H38" s="210"/>
+      <c r="I38" s="287"/>
+      <c r="J38" s="288"/>
+      <c r="K38" s="193"/>
+      <c r="L38" s="151"/>
+      <c r="M38" s="192" t="s">
         <v>58</v>
       </c>
-      <c r="N38" s="209"/>
-      <c r="O38" s="186"/>
+      <c r="N38" s="164"/>
+      <c r="O38" s="138"/>
       <c r="P38" s="24"/>
-      <c r="Q38" s="209"/>
-      <c r="R38" s="186"/>
+      <c r="Q38" s="164"/>
+      <c r="R38" s="138"/>
       <c r="S38" s="25"/>
       <c r="T38" s="25"/>
       <c r="U38" s="26"/>
+      <c r="V38" s="271"/>
     </row>
     <row r="39" spans="1:22" s="2" customFormat="1" ht="22.95" customHeight="1">
-      <c r="B39" s="296"/>
-      <c r="C39" s="240"/>
-      <c r="D39" s="262"/>
-      <c r="E39" s="181"/>
-      <c r="F39" s="182"/>
-      <c r="G39" s="183"/>
-      <c r="H39" s="259"/>
-      <c r="I39" s="163"/>
-      <c r="J39" s="164"/>
-      <c r="K39" s="284"/>
-      <c r="L39" s="211"/>
-      <c r="M39" s="156"/>
-      <c r="N39" s="156"/>
-      <c r="O39" s="187"/>
+      <c r="B39" s="158"/>
+      <c r="C39" s="159"/>
+      <c r="D39" s="216"/>
+      <c r="E39" s="301"/>
+      <c r="F39" s="302"/>
+      <c r="G39" s="303"/>
+      <c r="H39" s="211"/>
+      <c r="I39" s="289"/>
+      <c r="J39" s="290"/>
+      <c r="K39" s="194"/>
+      <c r="L39" s="151"/>
+      <c r="M39" s="144"/>
+      <c r="N39" s="144"/>
+      <c r="O39" s="140"/>
       <c r="P39" s="35"/>
-      <c r="Q39" s="156"/>
-      <c r="R39" s="187"/>
+      <c r="Q39" s="144"/>
+      <c r="R39" s="140"/>
       <c r="S39" s="36"/>
       <c r="T39" s="36"/>
       <c r="U39" s="32"/>
+      <c r="V39" s="271"/>
     </row>
     <row r="40" spans="1:22" s="2" customFormat="1" ht="29.25" customHeight="1">
       <c r="A40" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="B40" s="282"/>
-      <c r="C40" s="160"/>
-      <c r="D40" s="158"/>
-      <c r="E40" s="254"/>
-      <c r="F40" s="160"/>
-      <c r="G40" s="158"/>
-      <c r="H40" s="253"/>
-      <c r="I40" s="187"/>
-      <c r="K40" s="99"/>
-      <c r="L40" s="211"/>
-      <c r="M40" s="252" t="s">
+      <c r="B40" s="191"/>
+      <c r="C40" s="157"/>
+      <c r="D40" s="142"/>
+      <c r="E40" s="266"/>
+      <c r="F40" s="157"/>
+      <c r="G40" s="142"/>
+      <c r="H40" s="265"/>
+      <c r="I40" s="140"/>
+      <c r="K40" s="98"/>
+      <c r="L40" s="151"/>
+      <c r="M40" s="192" t="s">
         <v>60</v>
       </c>
-      <c r="N40" s="209"/>
-      <c r="O40" s="186"/>
+      <c r="N40" s="164"/>
+      <c r="O40" s="138"/>
       <c r="P40" s="24"/>
-      <c r="Q40" s="209"/>
-      <c r="R40" s="186"/>
+      <c r="Q40" s="164"/>
+      <c r="R40" s="138"/>
       <c r="S40" s="25"/>
       <c r="T40" s="25"/>
       <c r="U40" s="26"/>
+      <c r="V40" s="271"/>
     </row>
     <row r="41" spans="1:22" s="2" customFormat="1" ht="21" customHeight="1">
       <c r="B41" s="39"/>
@@ -3967,798 +4015,831 @@
       <c r="E41" s="40"/>
       <c r="F41" s="40"/>
       <c r="G41" s="40"/>
-      <c r="H41" s="92" t="s">
+      <c r="H41" s="91" t="s">
         <v>61</v>
       </c>
       <c r="I41" s="40"/>
-      <c r="J41" s="91"/>
-      <c r="K41" s="96"/>
-      <c r="L41" s="212"/>
-      <c r="M41" s="156"/>
-      <c r="N41" s="156"/>
-      <c r="O41" s="187"/>
+      <c r="J41" s="90"/>
+      <c r="K41" s="95"/>
+      <c r="L41" s="152"/>
+      <c r="M41" s="144"/>
+      <c r="N41" s="144"/>
+      <c r="O41" s="140"/>
       <c r="P41" s="35"/>
-      <c r="Q41" s="156"/>
-      <c r="R41" s="187"/>
+      <c r="Q41" s="144"/>
+      <c r="R41" s="140"/>
       <c r="S41" s="36"/>
       <c r="T41" s="36"/>
       <c r="U41" s="32"/>
+      <c r="V41" s="271"/>
     </row>
     <row r="42" spans="1:22" ht="18" customHeight="1">
-      <c r="B42" s="226" t="s">
+      <c r="B42" s="212" t="s">
         <v>62</v>
       </c>
       <c r="C42" s="41"/>
       <c r="D42" s="41"/>
-      <c r="E42" s="279" t="s">
+      <c r="E42" s="171" t="s">
         <v>63</v>
       </c>
-      <c r="F42" s="186"/>
-      <c r="G42" s="260" t="s">
+      <c r="F42" s="138"/>
+      <c r="G42" s="170" t="s">
         <v>64</v>
       </c>
-      <c r="H42" s="186"/>
-      <c r="I42" s="154" t="s">
+      <c r="H42" s="138"/>
+      <c r="I42" s="166" t="s">
         <v>65</v>
       </c>
-      <c r="J42" s="95" t="s">
+      <c r="J42" s="94" t="s">
         <v>66</v>
       </c>
-      <c r="K42" s="260" t="s">
+      <c r="K42" s="170" t="s">
         <v>67</v>
       </c>
-      <c r="L42" s="172"/>
-      <c r="M42" s="186"/>
-      <c r="N42" s="154" t="s">
+      <c r="L42" s="154"/>
+      <c r="M42" s="138"/>
+      <c r="N42" s="166" t="s">
         <v>68</v>
       </c>
       <c r="O42" s="42" t="s">
         <v>66</v>
       </c>
-      <c r="P42" s="154" t="s">
+      <c r="P42" s="166" t="s">
         <v>69</v>
       </c>
       <c r="Q42" s="41"/>
-      <c r="R42" s="154" t="s">
+      <c r="R42" s="166" t="s">
         <v>70</v>
       </c>
-      <c r="S42" s="172"/>
-      <c r="T42" s="186"/>
-      <c r="U42" s="197" t="s">
+      <c r="S42" s="154"/>
+      <c r="T42" s="138"/>
+      <c r="U42" s="312" t="s">
         <v>71</v>
       </c>
-      <c r="V42" s="43"/>
+      <c r="V42" s="271"/>
     </row>
     <row r="43" spans="1:22" ht="50.4" customHeight="1">
-      <c r="B43" s="227"/>
-      <c r="C43" s="95" t="s">
+      <c r="B43" s="213"/>
+      <c r="C43" s="94" t="s">
         <v>72</v>
       </c>
-      <c r="D43" s="118" t="s">
+      <c r="D43" s="116" t="s">
         <v>73</v>
       </c>
-      <c r="E43" s="173"/>
-      <c r="F43" s="189"/>
-      <c r="G43" s="176"/>
-      <c r="H43" s="187"/>
-      <c r="I43" s="155"/>
-      <c r="J43" s="281" t="s">
+      <c r="E43" s="148"/>
+      <c r="F43" s="163"/>
+      <c r="G43" s="149"/>
+      <c r="H43" s="140"/>
+      <c r="I43" s="167"/>
+      <c r="J43" s="190" t="s">
         <v>74</v>
       </c>
-      <c r="K43" s="176"/>
-      <c r="L43" s="177"/>
-      <c r="M43" s="187"/>
-      <c r="N43" s="155"/>
-      <c r="O43" s="234" t="s">
+      <c r="K43" s="149"/>
+      <c r="L43" s="155"/>
+      <c r="M43" s="140"/>
+      <c r="N43" s="167"/>
+      <c r="O43" s="143" t="s">
         <v>74</v>
       </c>
-      <c r="P43" s="155"/>
-      <c r="Q43" s="44" t="s">
+      <c r="P43" s="167"/>
+      <c r="Q43" s="43" t="s">
         <v>75</v>
       </c>
-      <c r="R43" s="173"/>
-      <c r="S43" s="174"/>
-      <c r="T43" s="189"/>
-      <c r="U43" s="198"/>
-      <c r="V43" s="43"/>
+      <c r="R43" s="148"/>
+      <c r="S43" s="205"/>
+      <c r="T43" s="163"/>
+      <c r="U43" s="269"/>
+      <c r="V43" s="271"/>
     </row>
     <row r="44" spans="1:22" ht="55.5" customHeight="1">
-      <c r="B44" s="227"/>
-      <c r="C44" s="112" t="s">
+      <c r="B44" s="213"/>
+      <c r="C44" s="110" t="s">
         <v>76</v>
       </c>
-      <c r="D44" s="111" t="s">
+      <c r="D44" s="109" t="s">
         <v>77</v>
       </c>
-      <c r="E44" s="176"/>
-      <c r="F44" s="187"/>
-      <c r="G44" s="46" t="s">
+      <c r="E44" s="149"/>
+      <c r="F44" s="140"/>
+      <c r="G44" s="45" t="s">
         <v>78</v>
       </c>
-      <c r="H44" s="73" t="s">
+      <c r="H44" s="72" t="s">
         <v>79</v>
       </c>
-      <c r="I44" s="156"/>
-      <c r="J44" s="156"/>
-      <c r="K44" s="117" t="s">
+      <c r="I44" s="144"/>
+      <c r="J44" s="144"/>
+      <c r="K44" s="115" t="s">
         <v>80</v>
       </c>
-      <c r="L44" s="184" t="s">
+      <c r="L44" s="304" t="s">
         <v>79</v>
       </c>
-      <c r="M44" s="158"/>
-      <c r="N44" s="156"/>
-      <c r="O44" s="156"/>
-      <c r="P44" s="156"/>
-      <c r="Q44" s="47" t="s">
+      <c r="M44" s="142"/>
+      <c r="N44" s="144"/>
+      <c r="O44" s="144"/>
+      <c r="P44" s="144"/>
+      <c r="Q44" s="46" t="s">
         <v>81</v>
       </c>
-      <c r="R44" s="176"/>
-      <c r="S44" s="177"/>
-      <c r="T44" s="187"/>
-      <c r="U44" s="199"/>
-      <c r="V44" s="43"/>
+      <c r="R44" s="149"/>
+      <c r="S44" s="155"/>
+      <c r="T44" s="140"/>
+      <c r="U44" s="270"/>
+      <c r="V44" s="271"/>
     </row>
     <row r="45" spans="1:22" ht="50.1" customHeight="1">
-      <c r="B45" s="227"/>
-      <c r="C45" s="113">
+      <c r="B45" s="213"/>
+      <c r="C45" s="111">
         <v>1</v>
       </c>
-      <c r="D45" s="107" t="s">
+      <c r="D45" s="105" t="s">
         <v>82</v>
       </c>
-      <c r="E45" s="157"/>
-      <c r="F45" s="158"/>
-      <c r="G45" s="50" t="s">
+      <c r="E45" s="172"/>
+      <c r="F45" s="142"/>
+      <c r="G45" s="49" t="s">
         <v>83</v>
       </c>
-      <c r="H45" s="51"/>
-      <c r="I45" s="52"/>
-      <c r="J45" s="53"/>
-      <c r="K45" s="50" t="s">
+      <c r="H45" s="50"/>
+      <c r="I45" s="51"/>
+      <c r="J45" s="52"/>
+      <c r="K45" s="49" t="s">
         <v>83</v>
       </c>
-      <c r="L45" s="196"/>
-      <c r="M45" s="158"/>
-      <c r="N45" s="53"/>
-      <c r="O45" s="53"/>
-      <c r="P45" s="54"/>
-      <c r="Q45" s="55"/>
-      <c r="R45" s="159"/>
-      <c r="S45" s="160"/>
-      <c r="T45" s="158"/>
-      <c r="U45" s="58"/>
-      <c r="V45" s="59"/>
+      <c r="L45" s="145"/>
+      <c r="M45" s="142"/>
+      <c r="N45" s="52"/>
+      <c r="O45" s="52"/>
+      <c r="P45" s="53"/>
+      <c r="Q45" s="54"/>
+      <c r="R45" s="217"/>
+      <c r="S45" s="157"/>
+      <c r="T45" s="142"/>
+      <c r="U45" s="57"/>
+      <c r="V45" s="271"/>
     </row>
     <row r="46" spans="1:22" ht="50.1" customHeight="1">
-      <c r="B46" s="227"/>
-      <c r="C46" s="114">
+      <c r="B46" s="213"/>
+      <c r="C46" s="112">
         <v>2</v>
       </c>
-      <c r="D46" s="108" t="s">
+      <c r="D46" s="106" t="s">
         <v>84</v>
       </c>
-      <c r="E46" s="157"/>
-      <c r="F46" s="158"/>
-      <c r="G46" s="50" t="s">
+      <c r="E46" s="172"/>
+      <c r="F46" s="142"/>
+      <c r="G46" s="49" t="s">
         <v>83</v>
       </c>
-      <c r="H46" s="51"/>
-      <c r="I46" s="60"/>
-      <c r="J46" s="51"/>
-      <c r="K46" s="50" t="s">
+      <c r="H46" s="50"/>
+      <c r="I46" s="59"/>
+      <c r="J46" s="50"/>
+      <c r="K46" s="49" t="s">
         <v>83</v>
       </c>
-      <c r="L46" s="196"/>
-      <c r="M46" s="158"/>
-      <c r="N46" s="51"/>
-      <c r="O46" s="51"/>
-      <c r="P46" s="61"/>
-      <c r="Q46" s="62"/>
-      <c r="R46" s="159"/>
-      <c r="S46" s="160"/>
-      <c r="T46" s="158"/>
-      <c r="U46" s="58"/>
-      <c r="V46" s="59"/>
+      <c r="L46" s="145"/>
+      <c r="M46" s="142"/>
+      <c r="N46" s="50"/>
+      <c r="O46" s="50"/>
+      <c r="P46" s="60"/>
+      <c r="Q46" s="61"/>
+      <c r="R46" s="217"/>
+      <c r="S46" s="157"/>
+      <c r="T46" s="142"/>
+      <c r="U46" s="57"/>
+      <c r="V46" s="271"/>
     </row>
     <row r="47" spans="1:22" ht="50.1" customHeight="1">
-      <c r="B47" s="227"/>
-      <c r="C47" s="114">
+      <c r="B47" s="213"/>
+      <c r="C47" s="112">
         <v>3</v>
       </c>
-      <c r="D47" s="108" t="s">
+      <c r="D47" s="106" t="s">
         <v>85</v>
       </c>
-      <c r="E47" s="157"/>
-      <c r="F47" s="158"/>
-      <c r="G47" s="50" t="s">
+      <c r="E47" s="172"/>
+      <c r="F47" s="142"/>
+      <c r="G47" s="49" t="s">
         <v>83</v>
       </c>
-      <c r="H47" s="51"/>
-      <c r="I47" s="60"/>
-      <c r="J47" s="51"/>
-      <c r="K47" s="50" t="s">
+      <c r="H47" s="50"/>
+      <c r="I47" s="59"/>
+      <c r="J47" s="50"/>
+      <c r="K47" s="49" t="s">
         <v>83</v>
       </c>
-      <c r="L47" s="196"/>
-      <c r="M47" s="158"/>
-      <c r="N47" s="51"/>
-      <c r="O47" s="51"/>
-      <c r="P47" s="54"/>
-      <c r="Q47" s="62"/>
-      <c r="R47" s="159"/>
-      <c r="S47" s="160"/>
-      <c r="T47" s="158"/>
-      <c r="U47" s="58"/>
-      <c r="V47" s="59"/>
+      <c r="L47" s="145"/>
+      <c r="M47" s="142"/>
+      <c r="N47" s="50"/>
+      <c r="O47" s="50"/>
+      <c r="P47" s="53"/>
+      <c r="Q47" s="61"/>
+      <c r="R47" s="217"/>
+      <c r="S47" s="157"/>
+      <c r="T47" s="142"/>
+      <c r="U47" s="57"/>
+      <c r="V47" s="271"/>
     </row>
     <row r="48" spans="1:22" ht="50.1" customHeight="1">
-      <c r="B48" s="227"/>
-      <c r="C48" s="114">
+      <c r="B48" s="213"/>
+      <c r="C48" s="112">
         <v>4</v>
       </c>
-      <c r="D48" s="108" t="s">
+      <c r="D48" s="106" t="s">
         <v>86</v>
       </c>
-      <c r="E48" s="157"/>
-      <c r="F48" s="158"/>
-      <c r="G48" s="50" t="s">
+      <c r="E48" s="172"/>
+      <c r="F48" s="142"/>
+      <c r="G48" s="49" t="s">
         <v>83</v>
       </c>
-      <c r="H48" s="51"/>
-      <c r="I48" s="60"/>
-      <c r="J48" s="51"/>
-      <c r="K48" s="50" t="s">
+      <c r="H48" s="50"/>
+      <c r="I48" s="59"/>
+      <c r="J48" s="50"/>
+      <c r="K48" s="49" t="s">
         <v>83</v>
       </c>
-      <c r="L48" s="196"/>
-      <c r="M48" s="158"/>
-      <c r="N48" s="51"/>
-      <c r="O48" s="51"/>
-      <c r="P48" s="54"/>
-      <c r="Q48" s="62"/>
-      <c r="R48" s="159"/>
-      <c r="S48" s="160"/>
-      <c r="T48" s="158"/>
-      <c r="U48" s="58"/>
-      <c r="V48" s="59"/>
+      <c r="L48" s="145"/>
+      <c r="M48" s="142"/>
+      <c r="N48" s="50"/>
+      <c r="O48" s="50"/>
+      <c r="P48" s="53"/>
+      <c r="Q48" s="61"/>
+      <c r="R48" s="217"/>
+      <c r="S48" s="157"/>
+      <c r="T48" s="142"/>
+      <c r="U48" s="57"/>
+      <c r="V48" s="271"/>
     </row>
     <row r="49" spans="2:23" ht="50.1" customHeight="1">
-      <c r="B49" s="227"/>
-      <c r="C49" s="114">
+      <c r="B49" s="213"/>
+      <c r="C49" s="112">
         <v>5</v>
       </c>
-      <c r="D49" s="109" t="s">
+      <c r="D49" s="107" t="s">
         <v>87</v>
       </c>
-      <c r="E49" s="157"/>
-      <c r="F49" s="158"/>
-      <c r="G49" s="50" t="s">
+      <c r="E49" s="172"/>
+      <c r="F49" s="142"/>
+      <c r="G49" s="49" t="s">
         <v>83</v>
       </c>
-      <c r="H49" s="51"/>
-      <c r="I49" s="60"/>
-      <c r="J49" s="51"/>
-      <c r="K49" s="50" t="s">
+      <c r="H49" s="50"/>
+      <c r="I49" s="59"/>
+      <c r="J49" s="50"/>
+      <c r="K49" s="49" t="s">
         <v>83</v>
       </c>
-      <c r="L49" s="196"/>
-      <c r="M49" s="158"/>
-      <c r="N49" s="51"/>
-      <c r="O49" s="51"/>
-      <c r="P49" s="54"/>
-      <c r="Q49" s="62"/>
-      <c r="R49" s="159"/>
-      <c r="S49" s="160"/>
-      <c r="T49" s="158"/>
-      <c r="U49" s="58"/>
-      <c r="V49" s="59"/>
+      <c r="L49" s="145"/>
+      <c r="M49" s="142"/>
+      <c r="N49" s="50"/>
+      <c r="O49" s="50"/>
+      <c r="P49" s="53"/>
+      <c r="Q49" s="61"/>
+      <c r="R49" s="217"/>
+      <c r="S49" s="157"/>
+      <c r="T49" s="142"/>
+      <c r="U49" s="57"/>
+      <c r="V49" s="271"/>
     </row>
     <row r="50" spans="2:23" ht="53.4" customHeight="1">
-      <c r="B50" s="227"/>
-      <c r="C50" s="114">
+      <c r="B50" s="213"/>
+      <c r="C50" s="112">
         <v>6</v>
       </c>
-      <c r="D50" s="110" t="s">
+      <c r="D50" s="108" t="s">
         <v>88</v>
       </c>
-      <c r="E50" s="157"/>
-      <c r="F50" s="158"/>
-      <c r="G50" s="50" t="s">
+      <c r="E50" s="172"/>
+      <c r="F50" s="142"/>
+      <c r="G50" s="49" t="s">
         <v>83</v>
       </c>
-      <c r="H50" s="51"/>
-      <c r="I50" s="60"/>
-      <c r="J50" s="51"/>
-      <c r="K50" s="50" t="s">
+      <c r="H50" s="50"/>
+      <c r="I50" s="59"/>
+      <c r="J50" s="50"/>
+      <c r="K50" s="49" t="s">
         <v>83</v>
       </c>
-      <c r="L50" s="196"/>
-      <c r="M50" s="158"/>
-      <c r="N50" s="51"/>
-      <c r="O50" s="51"/>
-      <c r="P50" s="54"/>
-      <c r="Q50" s="62"/>
-      <c r="R50" s="159"/>
-      <c r="S50" s="160"/>
-      <c r="T50" s="158"/>
-      <c r="U50" s="58"/>
-      <c r="V50" s="59"/>
+      <c r="L50" s="145"/>
+      <c r="M50" s="142"/>
+      <c r="N50" s="50"/>
+      <c r="O50" s="50"/>
+      <c r="P50" s="53"/>
+      <c r="Q50" s="61"/>
+      <c r="R50" s="217"/>
+      <c r="S50" s="157"/>
+      <c r="T50" s="142"/>
+      <c r="U50" s="57"/>
+      <c r="V50" s="271"/>
     </row>
     <row r="51" spans="2:23" ht="50.1" customHeight="1">
-      <c r="B51" s="228"/>
-      <c r="C51" s="113">
+      <c r="B51" s="214"/>
+      <c r="C51" s="111">
         <v>7</v>
       </c>
-      <c r="D51" s="110" t="s">
+      <c r="D51" s="108" t="s">
         <v>89</v>
       </c>
-      <c r="E51" s="157"/>
-      <c r="F51" s="158"/>
-      <c r="G51" s="50" t="s">
+      <c r="E51" s="172"/>
+      <c r="F51" s="142"/>
+      <c r="G51" s="49" t="s">
         <v>83</v>
       </c>
-      <c r="H51" s="51"/>
-      <c r="I51" s="52"/>
-      <c r="J51" s="53"/>
-      <c r="K51" s="50" t="s">
+      <c r="H51" s="50"/>
+      <c r="I51" s="51"/>
+      <c r="J51" s="52"/>
+      <c r="K51" s="49" t="s">
         <v>83</v>
       </c>
-      <c r="L51" s="196"/>
-      <c r="M51" s="158"/>
-      <c r="N51" s="53"/>
-      <c r="O51" s="53"/>
-      <c r="P51" s="61"/>
-      <c r="Q51" s="55"/>
-      <c r="R51" s="159"/>
-      <c r="S51" s="160"/>
-      <c r="T51" s="158"/>
-      <c r="U51" s="58"/>
-      <c r="V51" s="59"/>
+      <c r="L51" s="145"/>
+      <c r="M51" s="142"/>
+      <c r="N51" s="52"/>
+      <c r="O51" s="52"/>
+      <c r="P51" s="60"/>
+      <c r="Q51" s="54"/>
+      <c r="R51" s="217"/>
+      <c r="S51" s="157"/>
+      <c r="T51" s="142"/>
+      <c r="U51" s="57"/>
+      <c r="V51" s="271"/>
     </row>
     <row r="52" spans="2:23" ht="3.75" customHeight="1">
-      <c r="B52" s="63"/>
-      <c r="C52" s="64"/>
-      <c r="D52" s="65"/>
-      <c r="E52" s="66"/>
-      <c r="F52" s="67"/>
-      <c r="G52" s="64"/>
-      <c r="H52" s="68"/>
-      <c r="I52" s="69"/>
-      <c r="J52" s="69"/>
-      <c r="K52" s="64"/>
-      <c r="L52" s="69"/>
-      <c r="M52" s="69"/>
-      <c r="N52" s="69"/>
-      <c r="O52" s="69"/>
-      <c r="P52" s="64"/>
-      <c r="Q52" s="69"/>
-      <c r="R52" s="64"/>
-      <c r="S52" s="64"/>
-      <c r="T52" s="70"/>
-      <c r="U52" s="71"/>
-      <c r="V52" s="59"/>
+      <c r="B52" s="62"/>
+      <c r="C52" s="63"/>
+      <c r="D52" s="64"/>
+      <c r="E52" s="65"/>
+      <c r="F52" s="66"/>
+      <c r="G52" s="63"/>
+      <c r="H52" s="67"/>
+      <c r="I52" s="68"/>
+      <c r="J52" s="68"/>
+      <c r="K52" s="63"/>
+      <c r="L52" s="68"/>
+      <c r="M52" s="68"/>
+      <c r="N52" s="68"/>
+      <c r="O52" s="68"/>
+      <c r="P52" s="63"/>
+      <c r="Q52" s="68"/>
+      <c r="R52" s="63"/>
+      <c r="S52" s="63"/>
+      <c r="T52" s="69"/>
+      <c r="U52" s="70"/>
+      <c r="V52" s="271"/>
     </row>
     <row r="53" spans="2:23" ht="18" customHeight="1">
-      <c r="B53" s="226" t="s">
+      <c r="B53" s="212" t="s">
         <v>90</v>
       </c>
-      <c r="C53" s="72"/>
-      <c r="D53" s="72"/>
-      <c r="E53" s="279" t="s">
+      <c r="C53" s="71"/>
+      <c r="D53" s="71"/>
+      <c r="E53" s="171" t="s">
         <v>63</v>
       </c>
-      <c r="F53" s="186"/>
-      <c r="G53" s="280" t="s">
+      <c r="F53" s="138"/>
+      <c r="G53" s="141" t="s">
         <v>91</v>
       </c>
-      <c r="H53" s="186"/>
-      <c r="I53" s="154" t="s">
+      <c r="H53" s="138"/>
+      <c r="I53" s="166" t="s">
         <v>92</v>
       </c>
-      <c r="J53" s="274" t="s">
+      <c r="J53" s="267" t="s">
         <v>93</v>
       </c>
-      <c r="K53" s="280" t="s">
+      <c r="K53" s="141" t="s">
         <v>67</v>
       </c>
-      <c r="L53" s="172"/>
-      <c r="M53" s="186"/>
-      <c r="N53" s="154" t="s">
+      <c r="L53" s="154"/>
+      <c r="M53" s="138"/>
+      <c r="N53" s="166" t="s">
         <v>68</v>
       </c>
       <c r="O53" s="42" t="s">
         <v>66</v>
       </c>
-      <c r="P53" s="154" t="s">
+      <c r="P53" s="166" t="s">
         <v>69</v>
       </c>
       <c r="Q53" s="41"/>
-      <c r="R53" s="154" t="s">
+      <c r="R53" s="166" t="s">
         <v>70</v>
       </c>
-      <c r="S53" s="172"/>
-      <c r="T53" s="186"/>
-      <c r="U53" s="275" t="s">
+      <c r="S53" s="154"/>
+      <c r="T53" s="138"/>
+      <c r="U53" s="268" t="s">
         <v>71</v>
       </c>
-      <c r="V53" s="43"/>
+      <c r="V53" s="271"/>
     </row>
     <row r="54" spans="2:23" ht="50.4" customHeight="1">
-      <c r="B54" s="227"/>
+      <c r="B54" s="213"/>
       <c r="C54" s="41" t="s">
         <v>72</v>
       </c>
       <c r="D54" s="41" t="s">
         <v>73</v>
       </c>
-      <c r="E54" s="173"/>
-      <c r="F54" s="189"/>
-      <c r="G54" s="176"/>
-      <c r="H54" s="187"/>
-      <c r="I54" s="155"/>
-      <c r="J54" s="155"/>
-      <c r="K54" s="176"/>
-      <c r="L54" s="177"/>
-      <c r="M54" s="187"/>
-      <c r="N54" s="155"/>
-      <c r="O54" s="234" t="s">
+      <c r="E54" s="148"/>
+      <c r="F54" s="163"/>
+      <c r="G54" s="149"/>
+      <c r="H54" s="140"/>
+      <c r="I54" s="167"/>
+      <c r="J54" s="167"/>
+      <c r="K54" s="149"/>
+      <c r="L54" s="155"/>
+      <c r="M54" s="140"/>
+      <c r="N54" s="167"/>
+      <c r="O54" s="143" t="s">
         <v>74</v>
       </c>
-      <c r="P54" s="155"/>
-      <c r="Q54" s="44" t="s">
+      <c r="P54" s="167"/>
+      <c r="Q54" s="43" t="s">
         <v>75</v>
       </c>
-      <c r="R54" s="173"/>
-      <c r="S54" s="174"/>
-      <c r="T54" s="189"/>
-      <c r="U54" s="198"/>
-      <c r="V54" s="43"/>
+      <c r="R54" s="148"/>
+      <c r="S54" s="205"/>
+      <c r="T54" s="163"/>
+      <c r="U54" s="269"/>
+      <c r="V54" s="271"/>
     </row>
     <row r="55" spans="2:23" ht="50.4" customHeight="1">
-      <c r="B55" s="227"/>
-      <c r="C55" s="45" t="s">
+      <c r="B55" s="213"/>
+      <c r="C55" s="44" t="s">
         <v>76</v>
       </c>
-      <c r="D55" s="45" t="s">
+      <c r="D55" s="44" t="s">
         <v>77</v>
       </c>
-      <c r="E55" s="176"/>
-      <c r="F55" s="187"/>
-      <c r="G55" s="46" t="s">
+      <c r="E55" s="149"/>
+      <c r="F55" s="140"/>
+      <c r="G55" s="45" t="s">
         <v>80</v>
       </c>
-      <c r="H55" s="73" t="s">
+      <c r="H55" s="72" t="s">
         <v>79</v>
       </c>
-      <c r="I55" s="156"/>
-      <c r="J55" s="156"/>
-      <c r="K55" s="46" t="s">
+      <c r="I55" s="144"/>
+      <c r="J55" s="144"/>
+      <c r="K55" s="45" t="s">
         <v>80</v>
       </c>
-      <c r="L55" s="280" t="s">
+      <c r="L55" s="141" t="s">
         <v>79</v>
       </c>
-      <c r="M55" s="158"/>
-      <c r="N55" s="156"/>
-      <c r="O55" s="156"/>
-      <c r="P55" s="156"/>
-      <c r="Q55" s="47" t="s">
+      <c r="M55" s="142"/>
+      <c r="N55" s="144"/>
+      <c r="O55" s="144"/>
+      <c r="P55" s="144"/>
+      <c r="Q55" s="46" t="s">
         <v>81</v>
       </c>
-      <c r="R55" s="176"/>
-      <c r="S55" s="177"/>
-      <c r="T55" s="187"/>
-      <c r="U55" s="199"/>
-      <c r="V55" s="43"/>
+      <c r="R55" s="149"/>
+      <c r="S55" s="155"/>
+      <c r="T55" s="140"/>
+      <c r="U55" s="270"/>
+      <c r="V55" s="271"/>
     </row>
     <row r="56" spans="2:23" ht="30" customHeight="1">
-      <c r="B56" s="227"/>
-      <c r="C56" s="48">
+      <c r="B56" s="213"/>
+      <c r="C56" s="47">
         <v>1</v>
       </c>
-      <c r="D56" s="49" t="s">
+      <c r="D56" s="48" t="s">
         <v>82</v>
       </c>
-      <c r="E56" s="157"/>
-      <c r="F56" s="158"/>
-      <c r="G56" s="50" t="s">
+      <c r="E56" s="172"/>
+      <c r="F56" s="142"/>
+      <c r="G56" s="49" t="s">
         <v>83</v>
       </c>
-      <c r="H56" s="51"/>
-      <c r="I56" s="74"/>
-      <c r="J56" s="51"/>
-      <c r="K56" s="50" t="s">
+      <c r="H56" s="50"/>
+      <c r="I56" s="73"/>
+      <c r="J56" s="50"/>
+      <c r="K56" s="49" t="s">
         <v>83</v>
       </c>
-      <c r="L56" s="196"/>
-      <c r="M56" s="158"/>
-      <c r="N56" s="53"/>
-      <c r="O56" s="53"/>
-      <c r="P56" s="61"/>
-      <c r="Q56" s="55"/>
-      <c r="R56" s="56"/>
-      <c r="S56" s="57"/>
+      <c r="L56" s="145"/>
+      <c r="M56" s="142"/>
+      <c r="N56" s="52"/>
+      <c r="O56" s="52"/>
+      <c r="P56" s="60"/>
+      <c r="Q56" s="54"/>
+      <c r="R56" s="55"/>
+      <c r="S56" s="56"/>
       <c r="T56" s="18"/>
-      <c r="U56" s="58"/>
-      <c r="V56" s="59"/>
+      <c r="U56" s="57"/>
+      <c r="V56" s="271"/>
     </row>
     <row r="57" spans="2:23" ht="30" customHeight="1">
-      <c r="B57" s="227"/>
-      <c r="C57" s="56">
+      <c r="B57" s="213"/>
+      <c r="C57" s="55">
         <v>2</v>
       </c>
-      <c r="D57" s="75" t="s">
+      <c r="D57" s="74" t="s">
         <v>94</v>
       </c>
-      <c r="E57" s="157"/>
-      <c r="F57" s="158"/>
-      <c r="G57" s="50" t="s">
+      <c r="E57" s="172"/>
+      <c r="F57" s="142"/>
+      <c r="G57" s="49" t="s">
         <v>83</v>
       </c>
-      <c r="H57" s="51"/>
-      <c r="I57" s="76"/>
-      <c r="J57" s="53"/>
-      <c r="K57" s="50" t="s">
+      <c r="H57" s="50"/>
+      <c r="I57" s="75"/>
+      <c r="J57" s="52"/>
+      <c r="K57" s="49" t="s">
         <v>83</v>
       </c>
-      <c r="L57" s="196"/>
-      <c r="M57" s="158"/>
-      <c r="N57" s="51"/>
-      <c r="O57" s="51"/>
-      <c r="P57" s="54"/>
-      <c r="Q57" s="62"/>
-      <c r="R57" s="56"/>
-      <c r="S57" s="57"/>
+      <c r="L57" s="145"/>
+      <c r="M57" s="142"/>
+      <c r="N57" s="50"/>
+      <c r="O57" s="50"/>
+      <c r="P57" s="53"/>
+      <c r="Q57" s="61"/>
+      <c r="R57" s="55"/>
+      <c r="S57" s="56"/>
       <c r="T57" s="18"/>
-      <c r="U57" s="58"/>
-      <c r="V57" s="59"/>
+      <c r="U57" s="57"/>
+      <c r="V57" s="271"/>
     </row>
     <row r="58" spans="2:23" ht="30" customHeight="1">
-      <c r="B58" s="227"/>
-      <c r="C58" s="56">
+      <c r="B58" s="213"/>
+      <c r="C58" s="55">
         <v>3</v>
       </c>
-      <c r="D58" s="77" t="s">
+      <c r="D58" s="76" t="s">
         <v>95</v>
       </c>
-      <c r="E58" s="157"/>
-      <c r="F58" s="158"/>
-      <c r="G58" s="50" t="s">
+      <c r="E58" s="172"/>
+      <c r="F58" s="142"/>
+      <c r="G58" s="49" t="s">
         <v>83</v>
       </c>
-      <c r="H58" s="51"/>
-      <c r="I58" s="76"/>
-      <c r="J58" s="51"/>
-      <c r="K58" s="50" t="s">
+      <c r="H58" s="50"/>
+      <c r="I58" s="75"/>
+      <c r="J58" s="50"/>
+      <c r="K58" s="49" t="s">
         <v>83</v>
       </c>
-      <c r="L58" s="196"/>
-      <c r="M58" s="158"/>
-      <c r="N58" s="51"/>
-      <c r="O58" s="51"/>
-      <c r="P58" s="54"/>
-      <c r="Q58" s="62"/>
-      <c r="R58" s="56"/>
-      <c r="S58" s="57"/>
+      <c r="L58" s="145"/>
+      <c r="M58" s="142"/>
+      <c r="N58" s="50"/>
+      <c r="O58" s="50"/>
+      <c r="P58" s="53"/>
+      <c r="Q58" s="61"/>
+      <c r="R58" s="55"/>
+      <c r="S58" s="56"/>
       <c r="T58" s="18"/>
-      <c r="U58" s="58"/>
-      <c r="V58" s="59"/>
+      <c r="U58" s="57"/>
+      <c r="V58" s="271"/>
     </row>
     <row r="59" spans="2:23" ht="30" customHeight="1">
-      <c r="B59" s="227"/>
-      <c r="C59" s="78">
+      <c r="B59" s="213"/>
+      <c r="C59" s="77">
         <v>4</v>
       </c>
-      <c r="D59" s="79" t="s">
+      <c r="D59" s="78" t="s">
         <v>96</v>
       </c>
-      <c r="E59" s="157"/>
-      <c r="F59" s="158"/>
-      <c r="G59" s="50" t="s">
+      <c r="E59" s="172"/>
+      <c r="F59" s="142"/>
+      <c r="G59" s="49" t="s">
         <v>83</v>
       </c>
-      <c r="H59" s="51"/>
-      <c r="I59" s="80"/>
-      <c r="J59" s="81"/>
-      <c r="K59" s="59" t="s">
+      <c r="H59" s="50"/>
+      <c r="I59" s="79"/>
+      <c r="J59" s="80"/>
+      <c r="K59" s="58" t="s">
         <v>83</v>
       </c>
-      <c r="L59" s="196"/>
-      <c r="M59" s="158"/>
-      <c r="N59" s="51"/>
-      <c r="O59" s="51"/>
-      <c r="P59" s="54"/>
-      <c r="Q59" s="62"/>
-      <c r="R59" s="56"/>
-      <c r="S59" s="57"/>
+      <c r="L59" s="145"/>
+      <c r="M59" s="142"/>
+      <c r="N59" s="50"/>
+      <c r="O59" s="50"/>
+      <c r="P59" s="53"/>
+      <c r="Q59" s="61"/>
+      <c r="R59" s="55"/>
+      <c r="S59" s="56"/>
       <c r="T59" s="18"/>
-      <c r="U59" s="58"/>
-      <c r="V59" s="59"/>
+      <c r="U59" s="57"/>
+      <c r="V59" s="271"/>
     </row>
     <row r="60" spans="2:23" ht="30" customHeight="1">
-      <c r="B60" s="227"/>
-      <c r="C60" s="78">
+      <c r="B60" s="213"/>
+      <c r="C60" s="77">
         <v>5</v>
       </c>
-      <c r="D60" s="79" t="s">
+      <c r="D60" s="78" t="s">
         <v>86</v>
       </c>
-      <c r="E60" s="157"/>
-      <c r="F60" s="158"/>
-      <c r="G60" s="50" t="s">
+      <c r="E60" s="172"/>
+      <c r="F60" s="142"/>
+      <c r="G60" s="49" t="s">
         <v>83</v>
       </c>
-      <c r="H60" s="51"/>
-      <c r="I60" s="80"/>
-      <c r="J60" s="81"/>
-      <c r="K60" s="59" t="s">
+      <c r="H60" s="50"/>
+      <c r="I60" s="79"/>
+      <c r="J60" s="80"/>
+      <c r="K60" s="58" t="s">
         <v>83</v>
       </c>
-      <c r="L60" s="196"/>
-      <c r="M60" s="158"/>
-      <c r="N60" s="51"/>
-      <c r="O60" s="51"/>
-      <c r="P60" s="54"/>
-      <c r="Q60" s="62"/>
-      <c r="R60" s="78"/>
-      <c r="S60" s="82"/>
+      <c r="L60" s="145"/>
+      <c r="M60" s="142"/>
+      <c r="N60" s="50"/>
+      <c r="O60" s="50"/>
+      <c r="P60" s="53"/>
+      <c r="Q60" s="61"/>
+      <c r="R60" s="77"/>
+      <c r="S60" s="81"/>
       <c r="T60" s="5"/>
-      <c r="U60" s="83"/>
-      <c r="V60" s="59"/>
+      <c r="U60" s="82"/>
+      <c r="V60" s="271"/>
     </row>
     <row r="61" spans="2:23" ht="30" customHeight="1">
-      <c r="B61" s="228"/>
-      <c r="C61" s="84">
+      <c r="B61" s="214"/>
+      <c r="C61" s="83">
         <v>6</v>
       </c>
-      <c r="D61" s="85" t="s">
+      <c r="D61" s="84" t="s">
         <v>89</v>
       </c>
-      <c r="E61" s="157"/>
-      <c r="F61" s="158"/>
-      <c r="G61" s="59" t="s">
+      <c r="E61" s="172"/>
+      <c r="F61" s="142"/>
+      <c r="G61" s="58" t="s">
         <v>83</v>
       </c>
-      <c r="H61" s="86"/>
-      <c r="I61" s="81"/>
-      <c r="J61" s="86"/>
-      <c r="K61" s="84" t="s">
+      <c r="H61" s="85"/>
+      <c r="I61" s="80"/>
+      <c r="J61" s="85"/>
+      <c r="K61" s="83" t="s">
         <v>83</v>
       </c>
-      <c r="L61" s="196"/>
-      <c r="M61" s="158"/>
-      <c r="N61" s="87"/>
-      <c r="O61" s="87"/>
-      <c r="P61" s="84"/>
-      <c r="Q61" s="86"/>
-      <c r="R61" s="78"/>
-      <c r="S61" s="82"/>
+      <c r="L61" s="145"/>
+      <c r="M61" s="142"/>
+      <c r="N61" s="86"/>
+      <c r="O61" s="86"/>
+      <c r="P61" s="83"/>
+      <c r="Q61" s="85"/>
+      <c r="R61" s="77"/>
+      <c r="S61" s="81"/>
       <c r="T61" s="5"/>
-      <c r="U61" s="83"/>
-      <c r="V61" s="59"/>
-    </row>
-    <row r="62" spans="2:23" s="88" customFormat="1" ht="23.25" customHeight="1" thickBot="1">
-      <c r="B62" s="276" t="s">
+      <c r="U61" s="82"/>
+      <c r="V61" s="271"/>
+    </row>
+    <row r="62" spans="2:23" ht="30" customHeight="1" thickBot="1">
+      <c r="B62" s="272" t="s">
         <v>97</v>
       </c>
-      <c r="C62" s="272"/>
-      <c r="D62" s="272"/>
-      <c r="E62" s="272"/>
-      <c r="F62" s="277"/>
-      <c r="G62" s="278" t="s">
+      <c r="C62" s="273"/>
+      <c r="D62" s="273"/>
+      <c r="E62" s="273"/>
+      <c r="F62" s="274"/>
+      <c r="G62" s="275" t="s">
         <v>98</v>
       </c>
-      <c r="H62" s="272"/>
-      <c r="I62" s="272"/>
-      <c r="J62" s="272"/>
-      <c r="K62" s="272"/>
-      <c r="L62" s="272"/>
-      <c r="M62" s="277"/>
-      <c r="N62" s="271" t="s">
+      <c r="H62" s="273"/>
+      <c r="I62" s="273"/>
+      <c r="J62" s="273"/>
+      <c r="K62" s="273"/>
+      <c r="L62" s="273"/>
+      <c r="M62" s="274"/>
+      <c r="N62" s="276" t="s">
         <v>99</v>
       </c>
-      <c r="O62" s="272"/>
-      <c r="P62" s="272"/>
-      <c r="Q62" s="272"/>
-      <c r="R62" s="272"/>
-      <c r="S62" s="272"/>
-      <c r="T62" s="272"/>
-      <c r="U62" s="273"/>
-      <c r="W62" s="89"/>
-    </row>
-    <row r="63" spans="2:23" ht="14.4" customHeight="1"/>
-    <row r="64" spans="2:23">
-      <c r="G64" s="106"/>
-      <c r="H64" s="106"/>
-      <c r="I64" s="106"/>
-    </row>
-    <row r="65" spans="12:20">
-      <c r="L65" s="119"/>
-    </row>
-    <row r="69" spans="12:20" ht="21" customHeight="1">
-      <c r="Q69" s="90"/>
-      <c r="R69" s="90"/>
-      <c r="S69" s="90"/>
-      <c r="T69" s="90"/>
-    </row>
-    <row r="166" spans="10:10">
-      <c r="J166" s="2">
+      <c r="O62" s="273"/>
+      <c r="P62" s="273"/>
+      <c r="Q62" s="273"/>
+      <c r="R62" s="273"/>
+      <c r="S62" s="273"/>
+      <c r="T62" s="273"/>
+      <c r="U62" s="277"/>
+      <c r="V62" s="271"/>
+    </row>
+    <row r="63" spans="2:23" s="87" customFormat="1" ht="48.6" customHeight="1">
+      <c r="B63" s="319"/>
+      <c r="C63" s="320"/>
+      <c r="D63" s="320"/>
+      <c r="E63" s="320"/>
+      <c r="F63" s="320"/>
+      <c r="G63" s="321"/>
+      <c r="H63" s="322"/>
+      <c r="I63" s="322"/>
+      <c r="J63" s="322"/>
+      <c r="K63" s="322"/>
+      <c r="L63" s="322"/>
+      <c r="M63" s="322"/>
+      <c r="N63" s="321"/>
+      <c r="O63" s="322"/>
+      <c r="P63" s="322"/>
+      <c r="Q63" s="322"/>
+      <c r="R63" s="322"/>
+      <c r="S63" s="322"/>
+      <c r="T63" s="322"/>
+      <c r="U63" s="322"/>
+      <c r="V63" s="271"/>
+      <c r="W63" s="88"/>
+    </row>
+    <row r="64" spans="2:23" ht="14.4" customHeight="1"/>
+    <row r="65" spans="2:20" ht="34.799999999999997">
+      <c r="B65" s="136"/>
+      <c r="G65" s="104"/>
+      <c r="H65" s="104"/>
+      <c r="I65" s="104"/>
+    </row>
+    <row r="66" spans="2:20">
+      <c r="L66" s="117"/>
+    </row>
+    <row r="70" spans="2:20" ht="21" customHeight="1">
+      <c r="Q70" s="89"/>
+      <c r="R70" s="89"/>
+      <c r="S70" s="89"/>
+      <c r="T70" s="89"/>
+    </row>
+    <row r="167" spans="10:10">
+      <c r="J167" s="2">
         <v>2</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="166">
-    <mergeCell ref="B1:C5"/>
-    <mergeCell ref="Q36:R36"/>
-    <mergeCell ref="B18:C19"/>
-    <mergeCell ref="L56:M56"/>
-    <mergeCell ref="B8:C9"/>
-    <mergeCell ref="N34:O34"/>
-    <mergeCell ref="L49:M49"/>
-    <mergeCell ref="G53:H54"/>
-    <mergeCell ref="N42:N44"/>
-    <mergeCell ref="N27:O27"/>
-    <mergeCell ref="D3:D5"/>
-    <mergeCell ref="E53:F55"/>
-    <mergeCell ref="N36:O36"/>
-    <mergeCell ref="E47:F47"/>
-    <mergeCell ref="E8:F10"/>
-    <mergeCell ref="G8:H10"/>
-    <mergeCell ref="E11:F11"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="D6:D7"/>
-    <mergeCell ref="B6:C7"/>
-    <mergeCell ref="L55:M55"/>
-    <mergeCell ref="O43:O44"/>
-    <mergeCell ref="L51:M51"/>
-    <mergeCell ref="B12:C13"/>
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="M36:M37"/>
-    <mergeCell ref="M30:M31"/>
-    <mergeCell ref="B16:C17"/>
-    <mergeCell ref="K38:K39"/>
+  <mergeCells count="167">
+    <mergeCell ref="U42:U44"/>
+    <mergeCell ref="R42:T44"/>
+    <mergeCell ref="L22:U24"/>
+    <mergeCell ref="U53:U55"/>
+    <mergeCell ref="R49:T49"/>
+    <mergeCell ref="E42:F44"/>
+    <mergeCell ref="K53:M54"/>
+    <mergeCell ref="V1:V63"/>
+    <mergeCell ref="B62:F62"/>
+    <mergeCell ref="G62:M62"/>
+    <mergeCell ref="N62:U62"/>
+    <mergeCell ref="S16:U19"/>
+    <mergeCell ref="E1:N2"/>
+    <mergeCell ref="P42:P44"/>
+    <mergeCell ref="E51:F51"/>
+    <mergeCell ref="R47:T47"/>
+    <mergeCell ref="I38:J39"/>
+    <mergeCell ref="O1:U2"/>
+    <mergeCell ref="E3:K5"/>
+    <mergeCell ref="E38:G39"/>
+    <mergeCell ref="L44:M44"/>
+    <mergeCell ref="N32:O32"/>
+    <mergeCell ref="Q41:R41"/>
+    <mergeCell ref="Q25:R25"/>
+    <mergeCell ref="R50:T50"/>
+    <mergeCell ref="N35:O35"/>
+    <mergeCell ref="I12:J15"/>
+    <mergeCell ref="R53:T55"/>
+    <mergeCell ref="Q35:R35"/>
+    <mergeCell ref="N39:O39"/>
+    <mergeCell ref="R46:T46"/>
+    <mergeCell ref="D22:D24"/>
+    <mergeCell ref="E49:F49"/>
+    <mergeCell ref="N41:O41"/>
+    <mergeCell ref="H40:I40"/>
+    <mergeCell ref="L47:M47"/>
+    <mergeCell ref="E40:G40"/>
+    <mergeCell ref="R45:T45"/>
+    <mergeCell ref="P53:P55"/>
+    <mergeCell ref="E45:F45"/>
+    <mergeCell ref="Q40:R40"/>
+    <mergeCell ref="J53:J55"/>
+    <mergeCell ref="N53:N55"/>
+    <mergeCell ref="L50:M50"/>
+    <mergeCell ref="Q28:R28"/>
+    <mergeCell ref="Q37:R37"/>
     <mergeCell ref="E12:H15"/>
     <mergeCell ref="B14:C15"/>
     <mergeCell ref="N37:O37"/>
-    <mergeCell ref="E37:G37"/>
-    <mergeCell ref="L16:R19"/>
-    <mergeCell ref="E29:K30"/>
-    <mergeCell ref="Q33:R33"/>
-    <mergeCell ref="B22:C24"/>
-    <mergeCell ref="M38:M39"/>
-    <mergeCell ref="E16:I19"/>
-    <mergeCell ref="N33:O33"/>
-    <mergeCell ref="I37:J37"/>
-    <mergeCell ref="K12:K15"/>
-    <mergeCell ref="L27:L29"/>
-    <mergeCell ref="B34:K35"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="P53:P55"/>
+    <mergeCell ref="L20:U20"/>
+    <mergeCell ref="Q26:R26"/>
+    <mergeCell ref="Q34:R34"/>
+    <mergeCell ref="L30:L41"/>
+    <mergeCell ref="R48:T48"/>
+    <mergeCell ref="Q27:R27"/>
+    <mergeCell ref="N31:O31"/>
+    <mergeCell ref="N40:O40"/>
+    <mergeCell ref="J20:K24"/>
+    <mergeCell ref="E31:K31"/>
+    <mergeCell ref="B20:C21"/>
+    <mergeCell ref="E20:I24"/>
+    <mergeCell ref="D12:D13"/>
+    <mergeCell ref="M40:M41"/>
+    <mergeCell ref="Q39:R39"/>
+    <mergeCell ref="B25:D26"/>
+    <mergeCell ref="J16:K19"/>
+    <mergeCell ref="Q29:R29"/>
+    <mergeCell ref="B27:D28"/>
+    <mergeCell ref="Q32:R32"/>
+    <mergeCell ref="N29:O29"/>
+    <mergeCell ref="N38:O38"/>
+    <mergeCell ref="D20:D21"/>
     <mergeCell ref="N25:O25"/>
     <mergeCell ref="L25:M26"/>
     <mergeCell ref="D14:D15"/>
-    <mergeCell ref="I8:J11"/>
-    <mergeCell ref="E45:F45"/>
     <mergeCell ref="D16:D17"/>
-    <mergeCell ref="N62:U62"/>
     <mergeCell ref="Q31:R31"/>
-    <mergeCell ref="Q40:R40"/>
-    <mergeCell ref="J53:J55"/>
-    <mergeCell ref="N53:N55"/>
-    <mergeCell ref="U53:U55"/>
-    <mergeCell ref="B62:F62"/>
-    <mergeCell ref="Q28:R28"/>
-    <mergeCell ref="G62:M62"/>
-    <mergeCell ref="R49:T49"/>
-    <mergeCell ref="Q37:R37"/>
-    <mergeCell ref="E42:F44"/>
-    <mergeCell ref="K53:M54"/>
-    <mergeCell ref="L57:M57"/>
-    <mergeCell ref="J43:J44"/>
-    <mergeCell ref="E57:F57"/>
-    <mergeCell ref="E48:F48"/>
     <mergeCell ref="E60:F60"/>
     <mergeCell ref="L59:M59"/>
     <mergeCell ref="B32:K33"/>
@@ -4783,81 +4864,75 @@
     <mergeCell ref="M34:M35"/>
     <mergeCell ref="M32:M33"/>
     <mergeCell ref="E46:F46"/>
+    <mergeCell ref="L57:M57"/>
+    <mergeCell ref="J43:J44"/>
+    <mergeCell ref="E57:F57"/>
+    <mergeCell ref="E48:F48"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="M36:M37"/>
+    <mergeCell ref="M30:M31"/>
+    <mergeCell ref="B16:C17"/>
+    <mergeCell ref="K38:K39"/>
+    <mergeCell ref="E37:G37"/>
+    <mergeCell ref="L16:R19"/>
+    <mergeCell ref="E29:K30"/>
+    <mergeCell ref="Q33:R33"/>
+    <mergeCell ref="B22:C24"/>
+    <mergeCell ref="M38:M39"/>
+    <mergeCell ref="E16:I19"/>
+    <mergeCell ref="N33:O33"/>
+    <mergeCell ref="I37:J37"/>
+    <mergeCell ref="B42:B51"/>
+    <mergeCell ref="R51:T51"/>
+    <mergeCell ref="N28:O28"/>
+    <mergeCell ref="N26:O26"/>
+    <mergeCell ref="O54:O55"/>
+    <mergeCell ref="B29:D31"/>
+    <mergeCell ref="B1:C5"/>
+    <mergeCell ref="Q36:R36"/>
+    <mergeCell ref="B18:C19"/>
+    <mergeCell ref="L56:M56"/>
+    <mergeCell ref="B8:C9"/>
+    <mergeCell ref="N34:O34"/>
+    <mergeCell ref="L49:M49"/>
+    <mergeCell ref="G53:H54"/>
+    <mergeCell ref="N42:N44"/>
+    <mergeCell ref="N27:O27"/>
+    <mergeCell ref="D3:D5"/>
+    <mergeCell ref="E53:F55"/>
+    <mergeCell ref="N36:O36"/>
+    <mergeCell ref="E47:F47"/>
+    <mergeCell ref="E8:F10"/>
+    <mergeCell ref="G8:H10"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="D6:D7"/>
+    <mergeCell ref="K8:K11"/>
+    <mergeCell ref="D10:D11"/>
     <mergeCell ref="D1:D2"/>
-    <mergeCell ref="B29:D31"/>
     <mergeCell ref="D36:K36"/>
     <mergeCell ref="Q38:R38"/>
+    <mergeCell ref="B6:C7"/>
+    <mergeCell ref="L55:M55"/>
+    <mergeCell ref="O43:O44"/>
+    <mergeCell ref="L51:M51"/>
+    <mergeCell ref="B12:C13"/>
+    <mergeCell ref="K12:K15"/>
+    <mergeCell ref="L27:L29"/>
+    <mergeCell ref="B34:K35"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B39:C39"/>
     <mergeCell ref="B38:C38"/>
     <mergeCell ref="D18:D19"/>
     <mergeCell ref="D8:D9"/>
-    <mergeCell ref="R48:T48"/>
-    <mergeCell ref="Q27:R27"/>
-    <mergeCell ref="N31:O31"/>
-    <mergeCell ref="N40:O40"/>
-    <mergeCell ref="J20:K24"/>
-    <mergeCell ref="E31:K31"/>
-    <mergeCell ref="B20:C21"/>
-    <mergeCell ref="E20:I24"/>
-    <mergeCell ref="D12:D13"/>
-    <mergeCell ref="M40:M41"/>
-    <mergeCell ref="N41:O41"/>
-    <mergeCell ref="H40:I40"/>
-    <mergeCell ref="L47:M47"/>
-    <mergeCell ref="E40:G40"/>
-    <mergeCell ref="R45:T45"/>
-    <mergeCell ref="B10:C11"/>
-    <mergeCell ref="D20:D21"/>
-    <mergeCell ref="R53:T55"/>
-    <mergeCell ref="Q35:R35"/>
-    <mergeCell ref="N39:O39"/>
-    <mergeCell ref="R46:T46"/>
-    <mergeCell ref="D22:D24"/>
     <mergeCell ref="I6:J6"/>
     <mergeCell ref="I7:J7"/>
     <mergeCell ref="E6:H7"/>
-    <mergeCell ref="Q39:R39"/>
-    <mergeCell ref="B25:D26"/>
-    <mergeCell ref="J16:K19"/>
-    <mergeCell ref="Q29:R29"/>
-    <mergeCell ref="B27:D28"/>
-    <mergeCell ref="Q32:R32"/>
-    <mergeCell ref="N29:O29"/>
-    <mergeCell ref="N38:O38"/>
-    <mergeCell ref="E49:F49"/>
-    <mergeCell ref="B42:B51"/>
-    <mergeCell ref="R51:T51"/>
-    <mergeCell ref="K8:K11"/>
-    <mergeCell ref="N28:O28"/>
-    <mergeCell ref="D10:D11"/>
-    <mergeCell ref="N26:O26"/>
-    <mergeCell ref="O54:O55"/>
-    <mergeCell ref="S16:U19"/>
-    <mergeCell ref="E1:N2"/>
-    <mergeCell ref="P42:P44"/>
-    <mergeCell ref="E51:F51"/>
-    <mergeCell ref="R47:T47"/>
-    <mergeCell ref="I38:J39"/>
-    <mergeCell ref="O1:U2"/>
-    <mergeCell ref="E3:K5"/>
-    <mergeCell ref="E38:G39"/>
-    <mergeCell ref="L44:M44"/>
-    <mergeCell ref="N32:O32"/>
-    <mergeCell ref="Q41:R41"/>
-    <mergeCell ref="Q25:R25"/>
-    <mergeCell ref="R50:T50"/>
-    <mergeCell ref="N35:O35"/>
-    <mergeCell ref="I12:J15"/>
-    <mergeCell ref="L50:M50"/>
-    <mergeCell ref="U42:U44"/>
-    <mergeCell ref="R42:T44"/>
-    <mergeCell ref="L22:U24"/>
-    <mergeCell ref="L20:U20"/>
-    <mergeCell ref="Q26:R26"/>
-    <mergeCell ref="Q34:R34"/>
-    <mergeCell ref="L30:L41"/>
+    <mergeCell ref="B10:C11"/>
+    <mergeCell ref="I8:J11"/>
   </mergeCells>
-  <printOptions horizontalCentered="1" verticalCentered="1" gridLines="1"/>
+  <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="3.9370078740157501E-2" right="3.9370078740157501E-2" top="0.35433070866141703" bottom="0.35433070866141703" header="0.118110236220472" footer="0.118110236220472"/>
-  <pageSetup paperSize="9" scale="29" orientation="landscape" blackAndWhite="1" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="28" orientation="landscape" blackAndWhite="1" r:id="rId1"/>
 </worksheet>
 </file>
--- a/jo.xlsx
+++ b/jo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\production_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF352896-969D-46C4-AF24-923A5D0D4257}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DF0DA8C-3AE5-4398-84DE-75683CFF7302}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -394,10 +394,10 @@
     </r>
   </si>
   <si>
-    <t>H248 SA BOARDS</t>
-  </si>
-  <si>
     <t>I10111-I10121</t>
+  </si>
+  <si>
+    <t>H248 MAIN RHD</t>
   </si>
 </sst>
 </file>
@@ -2248,326 +2248,62 @@
     </xf>
     <xf numFmtId="0" fontId="70" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center"/>
-    </xf>
+    <xf numFmtId="49" fontId="32" fillId="0" borderId="62" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="62" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="42" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="55" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="24" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="55" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="61" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="34" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="35" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="40" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="57" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="36" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="37" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="50" fillId="0" borderId="34" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="50" fillId="0" borderId="35" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="50" fillId="0" borderId="40" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="50" fillId="0" borderId="57" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="50" fillId="0" borderId="36" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="50" fillId="0" borderId="37" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="59" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="59" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="44" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="45" fillId="0" borderId="31" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="34" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="42" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="40" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="36" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="44" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="51" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="52" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="53" xfId="0" applyBorder="1"/>
-    <xf numFmtId="3" fontId="48" fillId="0" borderId="54" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="33" fillId="0" borderId="65" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="71" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="72" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="68" fillId="0" borderId="20" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="64" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="64" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="41" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="17" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="38" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="57" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1"/>
-    <xf numFmtId="43" fontId="60" fillId="0" borderId="5" xfId="26" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="20" xfId="26" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="60" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="24" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="62" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="50" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="68" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="44" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2583,10 +2319,28 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="60" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="34" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="42" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="41" fillId="0" borderId="43" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="40" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="41" fillId="0" borderId="41" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="36" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="44" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="41" fillId="0" borderId="45" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2600,6 +2354,11 @@
     <xf numFmtId="0" fontId="56" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="56" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="56" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="48" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2617,6 +2376,7 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="63" fillId="7" borderId="65" xfId="26" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2629,6 +2389,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="34" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2637,35 +2400,272 @@
     <xf numFmtId="0" fontId="62" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="44" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="50" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="32" fillId="0" borderId="62" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="62" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="68" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="55" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="38" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="57" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="60" fillId="0" borderId="5" xfId="26" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="20" xfId="26" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="60" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="62" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="52" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="53" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="48" fillId="0" borderId="54" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="45" fillId="0" borderId="31" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="51" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="61" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="34" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="35" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="40" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="57" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="36" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="37" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="50" fillId="0" borderId="34" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="50" fillId="0" borderId="35" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="50" fillId="0" borderId="40" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="50" fillId="0" borderId="57" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="50" fillId="0" borderId="36" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="50" fillId="0" borderId="37" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="44" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="33" fillId="0" borderId="65" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="71" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="72" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="68" fillId="0" borderId="20" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="64" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="64" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="42" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="24" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="55" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="41" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="17" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="24" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="29">
     <cellStyle name="Comma" xfId="26" builtinId="3"/>
@@ -3009,72 +3009,72 @@
       <c r="A1" s="1">
         <v>24</v>
       </c>
-      <c r="B1" s="160"/>
-      <c r="C1" s="161"/>
-      <c r="D1" s="226" t="s">
+      <c r="B1" s="274"/>
+      <c r="C1" s="275"/>
+      <c r="D1" s="301" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="281" t="s">
+      <c r="E1" s="181" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="282"/>
-      <c r="G1" s="282"/>
-      <c r="H1" s="282"/>
-      <c r="I1" s="282"/>
-      <c r="J1" s="282"/>
-      <c r="K1" s="282"/>
-      <c r="L1" s="282"/>
-      <c r="M1" s="282"/>
-      <c r="N1" s="283"/>
-      <c r="O1" s="291" t="s">
+      <c r="F1" s="182"/>
+      <c r="G1" s="182"/>
+      <c r="H1" s="182"/>
+      <c r="I1" s="182"/>
+      <c r="J1" s="182"/>
+      <c r="K1" s="182"/>
+      <c r="L1" s="182"/>
+      <c r="M1" s="182"/>
+      <c r="N1" s="183"/>
+      <c r="O1" s="194" t="s">
         <v>2</v>
       </c>
-      <c r="P1" s="292"/>
-      <c r="Q1" s="292"/>
-      <c r="R1" s="292"/>
-      <c r="S1" s="292"/>
-      <c r="T1" s="292"/>
-      <c r="U1" s="293"/>
-      <c r="V1" s="271"/>
+      <c r="P1" s="195"/>
+      <c r="Q1" s="195"/>
+      <c r="R1" s="195"/>
+      <c r="S1" s="195"/>
+      <c r="T1" s="195"/>
+      <c r="U1" s="196"/>
+      <c r="V1" s="165"/>
     </row>
     <row r="2" spans="1:22" s="1" customFormat="1" ht="18.75" customHeight="1">
-      <c r="B2" s="162"/>
-      <c r="C2" s="163"/>
-      <c r="D2" s="224"/>
-      <c r="E2" s="284"/>
-      <c r="F2" s="285"/>
-      <c r="G2" s="285"/>
-      <c r="H2" s="285"/>
-      <c r="I2" s="285"/>
-      <c r="J2" s="285"/>
-      <c r="K2" s="285"/>
-      <c r="L2" s="285"/>
-      <c r="M2" s="285"/>
-      <c r="N2" s="286"/>
-      <c r="O2" s="294"/>
-      <c r="P2" s="295"/>
-      <c r="Q2" s="295"/>
-      <c r="R2" s="295"/>
-      <c r="S2" s="295"/>
-      <c r="T2" s="295"/>
-      <c r="U2" s="296"/>
-      <c r="V2" s="271"/>
+      <c r="B2" s="268"/>
+      <c r="C2" s="149"/>
+      <c r="D2" s="300"/>
+      <c r="E2" s="184"/>
+      <c r="F2" s="185"/>
+      <c r="G2" s="185"/>
+      <c r="H2" s="185"/>
+      <c r="I2" s="185"/>
+      <c r="J2" s="185"/>
+      <c r="K2" s="185"/>
+      <c r="L2" s="185"/>
+      <c r="M2" s="185"/>
+      <c r="N2" s="186"/>
+      <c r="O2" s="197"/>
+      <c r="P2" s="198"/>
+      <c r="Q2" s="198"/>
+      <c r="R2" s="198"/>
+      <c r="S2" s="198"/>
+      <c r="T2" s="198"/>
+      <c r="U2" s="199"/>
+      <c r="V2" s="165"/>
     </row>
     <row r="3" spans="1:22" ht="12.45" customHeight="1">
-      <c r="B3" s="162"/>
-      <c r="C3" s="163"/>
-      <c r="D3" s="170" t="s">
+      <c r="B3" s="268"/>
+      <c r="C3" s="149"/>
+      <c r="D3" s="258" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="297" t="s">
+      <c r="E3" s="200" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="154"/>
-      <c r="G3" s="154"/>
-      <c r="H3" s="154"/>
-      <c r="I3" s="154"/>
-      <c r="J3" s="154"/>
-      <c r="K3" s="154"/>
+      <c r="F3" s="145"/>
+      <c r="G3" s="145"/>
+      <c r="H3" s="145"/>
+      <c r="I3" s="145"/>
+      <c r="J3" s="145"/>
+      <c r="K3" s="145"/>
       <c r="L3" s="125"/>
       <c r="M3" s="5"/>
       <c r="N3" s="5"/>
@@ -3085,151 +3085,151 @@
       <c r="S3" s="5"/>
       <c r="T3" s="5"/>
       <c r="U3" s="126"/>
-      <c r="V3" s="271"/>
+      <c r="V3" s="165"/>
     </row>
     <row r="4" spans="1:22" ht="14.85" customHeight="1">
-      <c r="B4" s="162"/>
-      <c r="C4" s="163"/>
-      <c r="D4" s="167"/>
-      <c r="E4" s="148"/>
-      <c r="F4" s="205"/>
-      <c r="G4" s="205"/>
-      <c r="H4" s="205"/>
-      <c r="I4" s="205"/>
-      <c r="J4" s="205"/>
-      <c r="K4" s="244"/>
+      <c r="B4" s="268"/>
+      <c r="C4" s="149"/>
+      <c r="D4" s="187"/>
+      <c r="E4" s="147"/>
+      <c r="F4" s="148"/>
+      <c r="G4" s="148"/>
+      <c r="H4" s="148"/>
+      <c r="I4" s="148"/>
+      <c r="J4" s="148"/>
+      <c r="K4" s="201"/>
       <c r="L4" s="127"/>
       <c r="U4" s="128"/>
-      <c r="V4" s="271"/>
+      <c r="V4" s="165"/>
     </row>
     <row r="5" spans="1:22" ht="14.85" customHeight="1">
-      <c r="B5" s="139"/>
-      <c r="C5" s="140"/>
-      <c r="D5" s="144"/>
-      <c r="E5" s="149"/>
-      <c r="F5" s="155"/>
-      <c r="G5" s="155"/>
-      <c r="H5" s="155"/>
-      <c r="I5" s="155"/>
-      <c r="J5" s="155"/>
-      <c r="K5" s="155"/>
+      <c r="B5" s="226"/>
+      <c r="C5" s="152"/>
+      <c r="D5" s="188"/>
+      <c r="E5" s="150"/>
+      <c r="F5" s="151"/>
+      <c r="G5" s="151"/>
+      <c r="H5" s="151"/>
+      <c r="I5" s="151"/>
+      <c r="J5" s="151"/>
+      <c r="K5" s="151"/>
       <c r="L5" s="127"/>
       <c r="U5" s="128"/>
-      <c r="V5" s="271"/>
+      <c r="V5" s="165"/>
     </row>
     <row r="6" spans="1:22" s="2" customFormat="1" ht="27.75" customHeight="1">
-      <c r="B6" s="137" t="s">
+      <c r="B6" s="239" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="138"/>
-      <c r="D6" s="189"/>
-      <c r="E6" s="243" t="s">
+      <c r="C6" s="146"/>
+      <c r="D6" s="295"/>
+      <c r="E6" s="315" t="s">
         <v>6</v>
       </c>
-      <c r="F6" s="154"/>
-      <c r="G6" s="154"/>
-      <c r="H6" s="138"/>
-      <c r="I6" s="241" t="s">
+      <c r="F6" s="145"/>
+      <c r="G6" s="145"/>
+      <c r="H6" s="146"/>
+      <c r="I6" s="313" t="s">
         <v>7</v>
       </c>
-      <c r="J6" s="142"/>
+      <c r="J6" s="162"/>
       <c r="K6" s="100" t="s">
         <v>8</v>
       </c>
       <c r="L6" s="127"/>
       <c r="U6" s="128"/>
-      <c r="V6" s="271"/>
+      <c r="V6" s="165"/>
     </row>
     <row r="7" spans="1:22" s="2" customFormat="1" ht="28.5" customHeight="1">
-      <c r="B7" s="139"/>
-      <c r="C7" s="140"/>
-      <c r="D7" s="144"/>
-      <c r="E7" s="148"/>
-      <c r="F7" s="244"/>
-      <c r="G7" s="244"/>
-      <c r="H7" s="163"/>
-      <c r="I7" s="242"/>
-      <c r="J7" s="142"/>
+      <c r="B7" s="226"/>
+      <c r="C7" s="152"/>
+      <c r="D7" s="188"/>
+      <c r="E7" s="147"/>
+      <c r="F7" s="201"/>
+      <c r="G7" s="201"/>
+      <c r="H7" s="149"/>
+      <c r="I7" s="314"/>
+      <c r="J7" s="162"/>
       <c r="K7" s="101"/>
       <c r="L7" s="127"/>
       <c r="P7" s="131"/>
       <c r="U7" s="128"/>
-      <c r="V7" s="271"/>
+      <c r="V7" s="165"/>
     </row>
     <row r="8" spans="1:22" s="2" customFormat="1" ht="31.95" customHeight="1">
-      <c r="B8" s="137" t="s">
+      <c r="B8" s="239" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="138"/>
-      <c r="D8" s="232"/>
-      <c r="E8" s="173" t="s">
+      <c r="C8" s="146"/>
+      <c r="D8" s="312"/>
+      <c r="E8" s="279" t="s">
         <v>101</v>
       </c>
-      <c r="F8" s="174"/>
-      <c r="G8" s="179" t="s">
+      <c r="F8" s="280"/>
+      <c r="G8" s="285" t="s">
         <v>100</v>
       </c>
-      <c r="H8" s="180"/>
-      <c r="I8" s="252" t="s">
+      <c r="H8" s="286"/>
+      <c r="I8" s="317" t="s">
         <v>103</v>
       </c>
-      <c r="J8" s="253"/>
-      <c r="K8" s="218"/>
+      <c r="J8" s="318"/>
+      <c r="K8" s="296"/>
       <c r="L8" s="127"/>
       <c r="P8" s="131"/>
       <c r="U8" s="128"/>
-      <c r="V8" s="271"/>
+      <c r="V8" s="165"/>
     </row>
     <row r="9" spans="1:22" s="2" customFormat="1" ht="3.75" hidden="1" customHeight="1">
-      <c r="B9" s="139"/>
-      <c r="C9" s="140"/>
-      <c r="D9" s="149"/>
-      <c r="E9" s="175"/>
-      <c r="F9" s="176"/>
-      <c r="G9" s="181"/>
-      <c r="H9" s="182"/>
-      <c r="I9" s="254"/>
-      <c r="J9" s="255"/>
-      <c r="K9" s="219"/>
+      <c r="B9" s="226"/>
+      <c r="C9" s="152"/>
+      <c r="D9" s="150"/>
+      <c r="E9" s="281"/>
+      <c r="F9" s="282"/>
+      <c r="G9" s="287"/>
+      <c r="H9" s="288"/>
+      <c r="I9" s="319"/>
+      <c r="J9" s="320"/>
+      <c r="K9" s="297"/>
       <c r="L9" s="127"/>
       <c r="P9" s="131" t="str">
         <f t="shared" ref="P9" si="0">"*"&amp;J18&amp;"*"</f>
         <v>**</v>
       </c>
       <c r="U9" s="128"/>
-      <c r="V9" s="271"/>
+      <c r="V9" s="165"/>
     </row>
     <row r="10" spans="1:22" s="2" customFormat="1" ht="15" customHeight="1">
-      <c r="B10" s="248" t="s">
+      <c r="B10" s="316" t="s">
         <v>11</v>
       </c>
-      <c r="C10" s="138"/>
-      <c r="D10" s="223"/>
-      <c r="E10" s="177"/>
-      <c r="F10" s="178"/>
-      <c r="G10" s="183"/>
-      <c r="H10" s="184"/>
-      <c r="I10" s="254"/>
-      <c r="J10" s="255"/>
-      <c r="K10" s="219"/>
+      <c r="C10" s="146"/>
+      <c r="D10" s="299"/>
+      <c r="E10" s="283"/>
+      <c r="F10" s="284"/>
+      <c r="G10" s="289"/>
+      <c r="H10" s="290"/>
+      <c r="I10" s="319"/>
+      <c r="J10" s="320"/>
+      <c r="K10" s="297"/>
       <c r="L10" s="127"/>
       <c r="P10" s="131"/>
       <c r="U10" s="128"/>
-      <c r="V10" s="271"/>
+      <c r="V10" s="165"/>
     </row>
     <row r="11" spans="1:22" s="2" customFormat="1" ht="78.599999999999994" customHeight="1">
-      <c r="B11" s="139"/>
-      <c r="C11" s="140"/>
-      <c r="D11" s="224"/>
-      <c r="E11" s="185"/>
-      <c r="F11" s="186"/>
-      <c r="G11" s="187" t="s">
-        <v>110</v>
-      </c>
-      <c r="H11" s="188"/>
-      <c r="I11" s="256"/>
-      <c r="J11" s="257"/>
-      <c r="K11" s="220"/>
+      <c r="B11" s="226"/>
+      <c r="C11" s="152"/>
+      <c r="D11" s="300"/>
+      <c r="E11" s="291"/>
+      <c r="F11" s="292"/>
+      <c r="G11" s="293" t="s">
+        <v>109</v>
+      </c>
+      <c r="H11" s="294"/>
+      <c r="I11" s="321"/>
+      <c r="J11" s="322"/>
+      <c r="K11" s="298"/>
       <c r="L11" s="127"/>
       <c r="M11" s="132" t="str">
         <f>"*"&amp;J16&amp;"*"</f>
@@ -3241,74 +3241,74 @@
       <c r="Q11" s="132"/>
       <c r="S11" s="133"/>
       <c r="U11" s="128"/>
-      <c r="V11" s="271"/>
+      <c r="V11" s="165"/>
     </row>
     <row r="12" spans="1:22" s="2" customFormat="1" ht="28.5" customHeight="1">
-      <c r="B12" s="146" t="s">
+      <c r="B12" s="303" t="s">
         <v>12</v>
       </c>
-      <c r="C12" s="138"/>
-      <c r="D12" s="239" t="s">
+      <c r="C12" s="146"/>
+      <c r="D12" s="241" t="s">
         <v>102</v>
       </c>
-      <c r="E12" s="259"/>
-      <c r="F12" s="154"/>
-      <c r="G12" s="154"/>
-      <c r="H12" s="138"/>
-      <c r="I12" s="306" t="s">
+      <c r="E12" s="224"/>
+      <c r="F12" s="145"/>
+      <c r="G12" s="145"/>
+      <c r="H12" s="146"/>
+      <c r="I12" s="211" t="s">
         <v>13</v>
       </c>
-      <c r="J12" s="307"/>
-      <c r="K12" s="147"/>
+      <c r="J12" s="212"/>
+      <c r="K12" s="304"/>
       <c r="L12" s="127"/>
       <c r="U12" s="128"/>
-      <c r="V12" s="271"/>
+      <c r="V12" s="165"/>
     </row>
     <row r="13" spans="1:22" s="2" customFormat="1" ht="13.5" customHeight="1">
-      <c r="B13" s="139"/>
-      <c r="C13" s="140"/>
-      <c r="D13" s="240"/>
-      <c r="E13" s="148"/>
-      <c r="F13" s="205"/>
-      <c r="G13" s="205"/>
-      <c r="H13" s="163"/>
-      <c r="I13" s="308"/>
-      <c r="J13" s="309"/>
-      <c r="K13" s="148"/>
+      <c r="B13" s="226"/>
+      <c r="C13" s="152"/>
+      <c r="D13" s="242"/>
+      <c r="E13" s="147"/>
+      <c r="F13" s="148"/>
+      <c r="G13" s="148"/>
+      <c r="H13" s="149"/>
+      <c r="I13" s="213"/>
+      <c r="J13" s="214"/>
+      <c r="K13" s="147"/>
       <c r="L13" s="127"/>
       <c r="U13" s="128"/>
-      <c r="V13" s="271"/>
+      <c r="V13" s="165"/>
     </row>
     <row r="14" spans="1:22" s="2" customFormat="1" ht="15" customHeight="1">
-      <c r="B14" s="260" t="s">
+      <c r="B14" s="225" t="s">
         <v>14</v>
       </c>
-      <c r="C14" s="138"/>
-      <c r="D14" s="251" t="s">
+      <c r="C14" s="146"/>
+      <c r="D14" s="250" t="s">
         <v>107</v>
       </c>
-      <c r="E14" s="148"/>
-      <c r="F14" s="205"/>
-      <c r="G14" s="205"/>
-      <c r="H14" s="163"/>
-      <c r="I14" s="308"/>
-      <c r="J14" s="309"/>
-      <c r="K14" s="148"/>
+      <c r="E14" s="147"/>
+      <c r="F14" s="148"/>
+      <c r="G14" s="148"/>
+      <c r="H14" s="149"/>
+      <c r="I14" s="213"/>
+      <c r="J14" s="214"/>
+      <c r="K14" s="147"/>
       <c r="L14" s="127"/>
       <c r="U14" s="128"/>
-      <c r="V14" s="271"/>
+      <c r="V14" s="165"/>
     </row>
     <row r="15" spans="1:22" s="2" customFormat="1" ht="48" customHeight="1">
-      <c r="B15" s="139"/>
-      <c r="C15" s="140"/>
-      <c r="D15" s="240"/>
-      <c r="E15" s="149"/>
-      <c r="F15" s="155"/>
-      <c r="G15" s="155"/>
-      <c r="H15" s="140"/>
-      <c r="I15" s="310"/>
-      <c r="J15" s="311"/>
-      <c r="K15" s="149"/>
+      <c r="B15" s="226"/>
+      <c r="C15" s="152"/>
+      <c r="D15" s="242"/>
+      <c r="E15" s="150"/>
+      <c r="F15" s="151"/>
+      <c r="G15" s="151"/>
+      <c r="H15" s="152"/>
+      <c r="I15" s="215"/>
+      <c r="J15" s="216"/>
+      <c r="K15" s="150"/>
       <c r="L15" s="135"/>
       <c r="M15" s="129"/>
       <c r="N15" s="134"/>
@@ -3319,152 +3319,152 @@
       <c r="S15" s="129"/>
       <c r="T15" s="129"/>
       <c r="U15" s="130"/>
-      <c r="V15" s="271"/>
+      <c r="V15" s="165"/>
     </row>
     <row r="16" spans="1:22" s="2" customFormat="1" ht="15" customHeight="1">
-      <c r="B16" s="137" t="s">
+      <c r="B16" s="239" t="s">
         <v>15</v>
       </c>
-      <c r="C16" s="138"/>
-      <c r="D16" s="258"/>
-      <c r="E16" s="204" t="s">
+      <c r="C16" s="146"/>
+      <c r="D16" s="251"/>
+      <c r="E16" s="240" t="s">
         <v>16</v>
       </c>
-      <c r="F16" s="154"/>
-      <c r="G16" s="154"/>
-      <c r="H16" s="154"/>
-      <c r="I16" s="138"/>
-      <c r="J16" s="246">
+      <c r="F16" s="145"/>
+      <c r="G16" s="145"/>
+      <c r="H16" s="145"/>
+      <c r="I16" s="146"/>
+      <c r="J16" s="245">
         <v>232323</v>
       </c>
-      <c r="K16" s="236"/>
-      <c r="L16" s="196" t="s">
+      <c r="K16" s="235"/>
+      <c r="L16" s="172" t="s">
         <v>104</v>
       </c>
-      <c r="M16" s="197"/>
-      <c r="N16" s="197"/>
-      <c r="O16" s="197"/>
-      <c r="P16" s="197"/>
-      <c r="Q16" s="197"/>
-      <c r="R16" s="197"/>
-      <c r="S16" s="196" t="s">
+      <c r="M16" s="173"/>
+      <c r="N16" s="173"/>
+      <c r="O16" s="173"/>
+      <c r="P16" s="173"/>
+      <c r="Q16" s="173"/>
+      <c r="R16" s="173"/>
+      <c r="S16" s="172" t="s">
         <v>105</v>
       </c>
-      <c r="T16" s="197"/>
-      <c r="U16" s="278"/>
-      <c r="V16" s="271"/>
+      <c r="T16" s="173"/>
+      <c r="U16" s="174"/>
+      <c r="V16" s="165"/>
     </row>
     <row r="17" spans="2:22" s="2" customFormat="1" ht="15" customHeight="1">
-      <c r="B17" s="139"/>
-      <c r="C17" s="140"/>
-      <c r="D17" s="240"/>
-      <c r="E17" s="148"/>
-      <c r="F17" s="205"/>
-      <c r="G17" s="205"/>
-      <c r="H17" s="205"/>
-      <c r="I17" s="163"/>
-      <c r="J17" s="148"/>
-      <c r="K17" s="247"/>
-      <c r="L17" s="198"/>
-      <c r="M17" s="199"/>
-      <c r="N17" s="199"/>
-      <c r="O17" s="199"/>
-      <c r="P17" s="199"/>
-      <c r="Q17" s="199"/>
-      <c r="R17" s="199"/>
-      <c r="S17" s="198"/>
-      <c r="T17" s="199"/>
-      <c r="U17" s="279"/>
-      <c r="V17" s="271"/>
+      <c r="B17" s="226"/>
+      <c r="C17" s="152"/>
+      <c r="D17" s="242"/>
+      <c r="E17" s="147"/>
+      <c r="F17" s="148"/>
+      <c r="G17" s="148"/>
+      <c r="H17" s="148"/>
+      <c r="I17" s="149"/>
+      <c r="J17" s="147"/>
+      <c r="K17" s="246"/>
+      <c r="L17" s="175"/>
+      <c r="M17" s="176"/>
+      <c r="N17" s="176"/>
+      <c r="O17" s="176"/>
+      <c r="P17" s="176"/>
+      <c r="Q17" s="176"/>
+      <c r="R17" s="176"/>
+      <c r="S17" s="175"/>
+      <c r="T17" s="176"/>
+      <c r="U17" s="177"/>
+      <c r="V17" s="165"/>
     </row>
     <row r="18" spans="2:22" s="2" customFormat="1" ht="15" customHeight="1">
-      <c r="B18" s="165" t="s">
+      <c r="B18" s="276" t="s">
         <v>17</v>
       </c>
-      <c r="C18" s="138"/>
-      <c r="D18" s="230" t="s">
-        <v>109</v>
-      </c>
-      <c r="E18" s="148"/>
-      <c r="F18" s="205"/>
-      <c r="G18" s="205"/>
-      <c r="H18" s="205"/>
-      <c r="I18" s="163"/>
-      <c r="J18" s="148"/>
-      <c r="K18" s="247"/>
-      <c r="L18" s="198"/>
-      <c r="M18" s="199"/>
-      <c r="N18" s="199"/>
-      <c r="O18" s="199"/>
-      <c r="P18" s="199"/>
-      <c r="Q18" s="199"/>
-      <c r="R18" s="199"/>
-      <c r="S18" s="198"/>
-      <c r="T18" s="199"/>
-      <c r="U18" s="279"/>
-      <c r="V18" s="271"/>
+      <c r="C18" s="146"/>
+      <c r="D18" s="310" t="s">
+        <v>110</v>
+      </c>
+      <c r="E18" s="147"/>
+      <c r="F18" s="148"/>
+      <c r="G18" s="148"/>
+      <c r="H18" s="148"/>
+      <c r="I18" s="149"/>
+      <c r="J18" s="147"/>
+      <c r="K18" s="246"/>
+      <c r="L18" s="175"/>
+      <c r="M18" s="176"/>
+      <c r="N18" s="176"/>
+      <c r="O18" s="176"/>
+      <c r="P18" s="176"/>
+      <c r="Q18" s="176"/>
+      <c r="R18" s="176"/>
+      <c r="S18" s="175"/>
+      <c r="T18" s="176"/>
+      <c r="U18" s="177"/>
+      <c r="V18" s="165"/>
     </row>
     <row r="19" spans="2:22" s="2" customFormat="1" ht="15" customHeight="1">
-      <c r="B19" s="139"/>
-      <c r="C19" s="140"/>
-      <c r="D19" s="231"/>
-      <c r="E19" s="149"/>
-      <c r="F19" s="155"/>
-      <c r="G19" s="155"/>
-      <c r="H19" s="155"/>
-      <c r="I19" s="140"/>
-      <c r="J19" s="149"/>
-      <c r="K19" s="238"/>
-      <c r="L19" s="200"/>
-      <c r="M19" s="201"/>
-      <c r="N19" s="201"/>
-      <c r="O19" s="201"/>
-      <c r="P19" s="201"/>
-      <c r="Q19" s="201"/>
-      <c r="R19" s="201"/>
-      <c r="S19" s="200"/>
-      <c r="T19" s="201"/>
-      <c r="U19" s="280"/>
-      <c r="V19" s="271"/>
+      <c r="B19" s="226"/>
+      <c r="C19" s="152"/>
+      <c r="D19" s="311"/>
+      <c r="E19" s="150"/>
+      <c r="F19" s="151"/>
+      <c r="G19" s="151"/>
+      <c r="H19" s="151"/>
+      <c r="I19" s="152"/>
+      <c r="J19" s="150"/>
+      <c r="K19" s="237"/>
+      <c r="L19" s="178"/>
+      <c r="M19" s="179"/>
+      <c r="N19" s="179"/>
+      <c r="O19" s="179"/>
+      <c r="P19" s="179"/>
+      <c r="Q19" s="179"/>
+      <c r="R19" s="179"/>
+      <c r="S19" s="178"/>
+      <c r="T19" s="179"/>
+      <c r="U19" s="180"/>
+      <c r="V19" s="165"/>
     </row>
     <row r="20" spans="2:22" s="2" customFormat="1" ht="15" customHeight="1">
-      <c r="B20" s="137" t="s">
+      <c r="B20" s="239" t="s">
         <v>18</v>
       </c>
-      <c r="C20" s="138"/>
+      <c r="C20" s="146"/>
       <c r="D20" s="249"/>
-      <c r="E20" s="204" t="s">
+      <c r="E20" s="240" t="s">
         <v>106</v>
       </c>
-      <c r="F20" s="154"/>
-      <c r="G20" s="154"/>
-      <c r="H20" s="154"/>
-      <c r="I20" s="138"/>
-      <c r="J20" s="235"/>
-      <c r="K20" s="236"/>
-      <c r="L20" s="261"/>
-      <c r="M20" s="262"/>
-      <c r="N20" s="262"/>
-      <c r="O20" s="262"/>
-      <c r="P20" s="262"/>
-      <c r="Q20" s="262"/>
-      <c r="R20" s="262"/>
-      <c r="S20" s="262"/>
-      <c r="T20" s="262"/>
-      <c r="U20" s="262"/>
-      <c r="V20" s="271"/>
+      <c r="F20" s="145"/>
+      <c r="G20" s="145"/>
+      <c r="H20" s="145"/>
+      <c r="I20" s="146"/>
+      <c r="J20" s="234"/>
+      <c r="K20" s="235"/>
+      <c r="L20" s="227"/>
+      <c r="M20" s="228"/>
+      <c r="N20" s="228"/>
+      <c r="O20" s="228"/>
+      <c r="P20" s="228"/>
+      <c r="Q20" s="228"/>
+      <c r="R20" s="228"/>
+      <c r="S20" s="228"/>
+      <c r="T20" s="228"/>
+      <c r="U20" s="228"/>
+      <c r="V20" s="165"/>
     </row>
     <row r="21" spans="2:22" s="2" customFormat="1" ht="62.4" customHeight="1">
-      <c r="B21" s="139"/>
-      <c r="C21" s="140"/>
-      <c r="D21" s="144"/>
-      <c r="E21" s="148"/>
-      <c r="F21" s="205"/>
-      <c r="G21" s="205"/>
-      <c r="H21" s="205"/>
-      <c r="I21" s="163"/>
-      <c r="J21" s="148"/>
-      <c r="K21" s="237"/>
+      <c r="B21" s="226"/>
+      <c r="C21" s="152"/>
+      <c r="D21" s="188"/>
+      <c r="E21" s="147"/>
+      <c r="F21" s="148"/>
+      <c r="G21" s="148"/>
+      <c r="H21" s="148"/>
+      <c r="I21" s="149"/>
+      <c r="J21" s="147"/>
+      <c r="K21" s="236"/>
       <c r="L21" s="120"/>
       <c r="M21" s="121"/>
       <c r="N21" s="121"/>
@@ -3475,85 +3475,85 @@
       <c r="S21" s="123"/>
       <c r="T21" s="121"/>
       <c r="U21" s="122"/>
-      <c r="V21" s="271"/>
+      <c r="V21" s="165"/>
     </row>
     <row r="22" spans="2:22" s="2" customFormat="1" ht="15" customHeight="1">
-      <c r="B22" s="137" t="s">
+      <c r="B22" s="239" t="s">
         <v>19</v>
       </c>
-      <c r="C22" s="138"/>
-      <c r="D22" s="264"/>
-      <c r="E22" s="148"/>
-      <c r="F22" s="205"/>
-      <c r="G22" s="205"/>
-      <c r="H22" s="205"/>
-      <c r="I22" s="163"/>
-      <c r="J22" s="148"/>
-      <c r="K22" s="237"/>
-      <c r="L22" s="313"/>
-      <c r="M22" s="313"/>
-      <c r="N22" s="313"/>
-      <c r="O22" s="313"/>
-      <c r="P22" s="313"/>
-      <c r="Q22" s="313"/>
-      <c r="R22" s="313"/>
-      <c r="S22" s="313"/>
-      <c r="T22" s="313"/>
-      <c r="U22" s="314"/>
-      <c r="V22" s="271"/>
+      <c r="C22" s="146"/>
+      <c r="D22" s="217"/>
+      <c r="E22" s="147"/>
+      <c r="F22" s="148"/>
+      <c r="G22" s="148"/>
+      <c r="H22" s="148"/>
+      <c r="I22" s="149"/>
+      <c r="J22" s="147"/>
+      <c r="K22" s="236"/>
+      <c r="L22" s="153"/>
+      <c r="M22" s="153"/>
+      <c r="N22" s="153"/>
+      <c r="O22" s="153"/>
+      <c r="P22" s="153"/>
+      <c r="Q22" s="153"/>
+      <c r="R22" s="153"/>
+      <c r="S22" s="153"/>
+      <c r="T22" s="153"/>
+      <c r="U22" s="154"/>
+      <c r="V22" s="165"/>
     </row>
     <row r="23" spans="2:22" s="2" customFormat="1" ht="15" customHeight="1">
-      <c r="B23" s="162"/>
-      <c r="C23" s="163"/>
-      <c r="D23" s="167"/>
-      <c r="E23" s="148"/>
-      <c r="F23" s="205"/>
-      <c r="G23" s="205"/>
-      <c r="H23" s="205"/>
-      <c r="I23" s="163"/>
-      <c r="J23" s="148"/>
-      <c r="K23" s="237"/>
-      <c r="L23" s="315"/>
-      <c r="M23" s="315"/>
-      <c r="N23" s="315"/>
-      <c r="O23" s="315"/>
-      <c r="P23" s="315"/>
-      <c r="Q23" s="315"/>
-      <c r="R23" s="315"/>
-      <c r="S23" s="315"/>
-      <c r="T23" s="315"/>
-      <c r="U23" s="316"/>
-      <c r="V23" s="271"/>
+      <c r="B23" s="268"/>
+      <c r="C23" s="149"/>
+      <c r="D23" s="187"/>
+      <c r="E23" s="147"/>
+      <c r="F23" s="148"/>
+      <c r="G23" s="148"/>
+      <c r="H23" s="148"/>
+      <c r="I23" s="149"/>
+      <c r="J23" s="147"/>
+      <c r="K23" s="236"/>
+      <c r="L23" s="155"/>
+      <c r="M23" s="155"/>
+      <c r="N23" s="155"/>
+      <c r="O23" s="155"/>
+      <c r="P23" s="155"/>
+      <c r="Q23" s="155"/>
+      <c r="R23" s="155"/>
+      <c r="S23" s="155"/>
+      <c r="T23" s="155"/>
+      <c r="U23" s="156"/>
+      <c r="V23" s="165"/>
     </row>
     <row r="24" spans="2:22" s="2" customFormat="1" ht="7.5" customHeight="1">
-      <c r="B24" s="139"/>
-      <c r="C24" s="140"/>
-      <c r="D24" s="144"/>
-      <c r="E24" s="149"/>
-      <c r="F24" s="155"/>
-      <c r="G24" s="155"/>
-      <c r="H24" s="155"/>
-      <c r="I24" s="140"/>
-      <c r="J24" s="149"/>
-      <c r="K24" s="238"/>
-      <c r="L24" s="317"/>
-      <c r="M24" s="317"/>
-      <c r="N24" s="317"/>
-      <c r="O24" s="317"/>
-      <c r="P24" s="317"/>
-      <c r="Q24" s="317"/>
-      <c r="R24" s="317"/>
-      <c r="S24" s="317"/>
-      <c r="T24" s="317"/>
-      <c r="U24" s="318"/>
-      <c r="V24" s="271"/>
+      <c r="B24" s="226"/>
+      <c r="C24" s="152"/>
+      <c r="D24" s="188"/>
+      <c r="E24" s="150"/>
+      <c r="F24" s="151"/>
+      <c r="G24" s="151"/>
+      <c r="H24" s="151"/>
+      <c r="I24" s="152"/>
+      <c r="J24" s="150"/>
+      <c r="K24" s="237"/>
+      <c r="L24" s="157"/>
+      <c r="M24" s="157"/>
+      <c r="N24" s="157"/>
+      <c r="O24" s="157"/>
+      <c r="P24" s="157"/>
+      <c r="Q24" s="157"/>
+      <c r="R24" s="157"/>
+      <c r="S24" s="157"/>
+      <c r="T24" s="157"/>
+      <c r="U24" s="158"/>
+      <c r="V24" s="165"/>
     </row>
     <row r="25" spans="2:22" s="2" customFormat="1" ht="30" customHeight="1">
-      <c r="B25" s="245" t="s">
+      <c r="B25" s="244" t="s">
         <v>20</v>
       </c>
-      <c r="C25" s="154"/>
-      <c r="D25" s="138"/>
+      <c r="C25" s="145"/>
+      <c r="D25" s="146"/>
       <c r="E25" s="3" t="s">
         <v>21</v>
       </c>
@@ -3569,21 +3569,21 @@
       <c r="K25" s="102" t="s">
         <v>24</v>
       </c>
-      <c r="L25" s="225" t="s">
+      <c r="L25" s="229" t="s">
         <v>25</v>
       </c>
-      <c r="M25" s="163"/>
-      <c r="N25" s="250" t="s">
+      <c r="M25" s="149"/>
+      <c r="N25" s="210" t="s">
         <v>26</v>
       </c>
-      <c r="O25" s="163"/>
+      <c r="O25" s="149"/>
       <c r="P25" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="Q25" s="250" t="s">
+      <c r="Q25" s="210" t="s">
         <v>28</v>
       </c>
-      <c r="R25" s="163"/>
+      <c r="R25" s="149"/>
       <c r="S25" s="7" t="s">
         <v>29</v>
       </c>
@@ -3593,12 +3593,12 @@
       <c r="U25" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="V25" s="271"/>
+      <c r="V25" s="165"/>
     </row>
     <row r="26" spans="2:22" s="2" customFormat="1" ht="39" customHeight="1">
-      <c r="B26" s="139"/>
-      <c r="C26" s="155"/>
-      <c r="D26" s="140"/>
+      <c r="B26" s="226"/>
+      <c r="C26" s="151"/>
+      <c r="D26" s="152"/>
       <c r="E26" s="10"/>
       <c r="F26" s="11"/>
       <c r="G26" s="12"/>
@@ -3606,19 +3606,19 @@
       <c r="I26" s="12"/>
       <c r="J26" s="11"/>
       <c r="K26" s="13"/>
-      <c r="L26" s="149"/>
-      <c r="M26" s="140"/>
-      <c r="N26" s="225" t="s">
+      <c r="L26" s="150"/>
+      <c r="M26" s="152"/>
+      <c r="N26" s="229" t="s">
         <v>31</v>
       </c>
-      <c r="O26" s="140"/>
+      <c r="O26" s="152"/>
       <c r="P26" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="Q26" s="225" t="s">
+      <c r="Q26" s="229" t="s">
         <v>33</v>
       </c>
-      <c r="R26" s="140"/>
+      <c r="R26" s="152"/>
       <c r="S26" s="14" t="s">
         <v>34</v>
       </c>
@@ -3628,14 +3628,14 @@
       <c r="U26" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="V26" s="271"/>
+      <c r="V26" s="165"/>
     </row>
     <row r="27" spans="2:22" s="2" customFormat="1" ht="46.05" customHeight="1">
-      <c r="B27" s="245" t="s">
+      <c r="B27" s="244" t="s">
         <v>36</v>
       </c>
-      <c r="C27" s="154"/>
-      <c r="D27" s="138"/>
+      <c r="C27" s="145"/>
+      <c r="D27" s="146"/>
       <c r="E27" s="3" t="s">
         <v>21</v>
       </c>
@@ -3649,26 +3649,26 @@
       </c>
       <c r="J27" s="5"/>
       <c r="K27" s="6"/>
-      <c r="L27" s="150" t="s">
+      <c r="L27" s="305" t="s">
         <v>39</v>
       </c>
       <c r="M27" s="118" t="s">
         <v>9</v>
       </c>
-      <c r="N27" s="168"/>
-      <c r="O27" s="169"/>
+      <c r="N27" s="277"/>
+      <c r="O27" s="278"/>
       <c r="P27" s="92"/>
-      <c r="Q27" s="233"/>
-      <c r="R27" s="142"/>
+      <c r="Q27" s="223"/>
+      <c r="R27" s="162"/>
       <c r="S27" s="17"/>
       <c r="T27" s="18"/>
       <c r="U27" s="19"/>
-      <c r="V27" s="271"/>
+      <c r="V27" s="165"/>
     </row>
     <row r="28" spans="2:22" s="2" customFormat="1" ht="46.05" customHeight="1">
-      <c r="B28" s="139"/>
-      <c r="C28" s="155"/>
-      <c r="D28" s="140"/>
+      <c r="B28" s="226"/>
+      <c r="C28" s="151"/>
+      <c r="D28" s="152"/>
       <c r="E28" s="20"/>
       <c r="F28" s="21"/>
       <c r="G28" s="21"/>
@@ -3676,64 +3676,64 @@
       <c r="I28" s="22"/>
       <c r="J28" s="22"/>
       <c r="K28" s="23"/>
-      <c r="L28" s="151"/>
+      <c r="L28" s="231"/>
       <c r="M28" s="118" t="s">
         <v>40</v>
       </c>
-      <c r="N28" s="221"/>
-      <c r="O28" s="222"/>
+      <c r="N28" s="247"/>
+      <c r="O28" s="248"/>
       <c r="P28" s="92"/>
-      <c r="Q28" s="233"/>
-      <c r="R28" s="142"/>
+      <c r="Q28" s="223"/>
+      <c r="R28" s="162"/>
       <c r="S28" s="17"/>
       <c r="T28" s="18"/>
       <c r="U28" s="19"/>
-      <c r="V28" s="271"/>
+      <c r="V28" s="165"/>
     </row>
     <row r="29" spans="2:22" s="2" customFormat="1" ht="46.5" customHeight="1">
-      <c r="B29" s="227" t="s">
+      <c r="B29" s="273" t="s">
         <v>41</v>
       </c>
-      <c r="C29" s="154"/>
-      <c r="D29" s="138"/>
-      <c r="E29" s="202" t="s">
+      <c r="C29" s="145"/>
+      <c r="D29" s="146"/>
+      <c r="E29" s="238" t="s">
         <v>42</v>
       </c>
-      <c r="F29" s="154"/>
-      <c r="G29" s="154"/>
-      <c r="H29" s="154"/>
-      <c r="I29" s="154"/>
-      <c r="J29" s="154"/>
-      <c r="K29" s="138"/>
-      <c r="L29" s="152"/>
+      <c r="F29" s="145"/>
+      <c r="G29" s="145"/>
+      <c r="H29" s="145"/>
+      <c r="I29" s="145"/>
+      <c r="J29" s="145"/>
+      <c r="K29" s="146"/>
+      <c r="L29" s="232"/>
       <c r="M29" s="119" t="s">
         <v>43</v>
       </c>
-      <c r="N29" s="221"/>
-      <c r="O29" s="222"/>
+      <c r="N29" s="247"/>
+      <c r="O29" s="248"/>
       <c r="P29" s="93"/>
-      <c r="Q29" s="233"/>
-      <c r="R29" s="142"/>
+      <c r="Q29" s="223"/>
+      <c r="R29" s="162"/>
       <c r="S29" s="25"/>
       <c r="T29" s="5"/>
       <c r="U29" s="26"/>
-      <c r="V29" s="271"/>
+      <c r="V29" s="165"/>
     </row>
     <row r="30" spans="2:22" s="2" customFormat="1" ht="15" customHeight="1">
-      <c r="B30" s="162"/>
-      <c r="C30" s="205"/>
-      <c r="D30" s="163"/>
-      <c r="E30" s="149"/>
-      <c r="F30" s="155"/>
-      <c r="G30" s="155"/>
-      <c r="H30" s="155"/>
-      <c r="I30" s="155"/>
-      <c r="J30" s="155"/>
-      <c r="K30" s="140"/>
-      <c r="L30" s="263" t="s">
+      <c r="B30" s="268"/>
+      <c r="C30" s="148"/>
+      <c r="D30" s="149"/>
+      <c r="E30" s="150"/>
+      <c r="F30" s="151"/>
+      <c r="G30" s="151"/>
+      <c r="H30" s="151"/>
+      <c r="I30" s="151"/>
+      <c r="J30" s="151"/>
+      <c r="K30" s="152"/>
+      <c r="L30" s="230" t="s">
         <v>44</v>
       </c>
-      <c r="M30" s="192" t="s">
+      <c r="M30" s="243" t="s">
         <v>45</v>
       </c>
       <c r="N30" s="27"/>
@@ -3744,269 +3744,269 @@
       <c r="S30" s="30"/>
       <c r="T30" s="30"/>
       <c r="U30" s="26"/>
-      <c r="V30" s="271"/>
+      <c r="V30" s="165"/>
     </row>
     <row r="31" spans="2:22" s="2" customFormat="1" ht="42" customHeight="1">
-      <c r="B31" s="139"/>
-      <c r="C31" s="155"/>
-      <c r="D31" s="140"/>
-      <c r="E31" s="202" t="s">
+      <c r="B31" s="226"/>
+      <c r="C31" s="151"/>
+      <c r="D31" s="152"/>
+      <c r="E31" s="238" t="s">
         <v>108</v>
       </c>
-      <c r="F31" s="157"/>
-      <c r="G31" s="157"/>
-      <c r="H31" s="157"/>
-      <c r="I31" s="157"/>
-      <c r="J31" s="157"/>
-      <c r="K31" s="142"/>
-      <c r="L31" s="151"/>
-      <c r="M31" s="144"/>
-      <c r="N31" s="234"/>
-      <c r="O31" s="140"/>
+      <c r="F31" s="161"/>
+      <c r="G31" s="161"/>
+      <c r="H31" s="161"/>
+      <c r="I31" s="161"/>
+      <c r="J31" s="161"/>
+      <c r="K31" s="162"/>
+      <c r="L31" s="231"/>
+      <c r="M31" s="188"/>
+      <c r="N31" s="233"/>
+      <c r="O31" s="152"/>
       <c r="P31" s="97"/>
-      <c r="Q31" s="144"/>
-      <c r="R31" s="140"/>
+      <c r="Q31" s="188"/>
+      <c r="R31" s="152"/>
       <c r="S31" s="31"/>
       <c r="T31" s="31"/>
       <c r="U31" s="32"/>
-      <c r="V31" s="271"/>
+      <c r="V31" s="165"/>
     </row>
     <row r="32" spans="2:22" s="2" customFormat="1" ht="21" customHeight="1">
-      <c r="B32" s="209" t="s">
+      <c r="B32" s="252" t="s">
         <v>46</v>
       </c>
-      <c r="C32" s="154"/>
-      <c r="D32" s="154"/>
-      <c r="E32" s="154"/>
-      <c r="F32" s="154"/>
-      <c r="G32" s="154"/>
-      <c r="H32" s="154"/>
-      <c r="I32" s="154"/>
-      <c r="J32" s="154"/>
-      <c r="K32" s="138"/>
-      <c r="L32" s="151"/>
-      <c r="M32" s="192" t="s">
+      <c r="C32" s="145"/>
+      <c r="D32" s="145"/>
+      <c r="E32" s="145"/>
+      <c r="F32" s="145"/>
+      <c r="G32" s="145"/>
+      <c r="H32" s="145"/>
+      <c r="I32" s="145"/>
+      <c r="J32" s="145"/>
+      <c r="K32" s="146"/>
+      <c r="L32" s="231"/>
+      <c r="M32" s="243" t="s">
         <v>47</v>
       </c>
-      <c r="N32" s="305"/>
-      <c r="O32" s="138"/>
+      <c r="N32" s="209"/>
+      <c r="O32" s="146"/>
       <c r="P32" s="96"/>
-      <c r="Q32" s="164"/>
-      <c r="R32" s="138"/>
+      <c r="Q32" s="221"/>
+      <c r="R32" s="146"/>
       <c r="S32" s="33"/>
       <c r="T32" s="33"/>
       <c r="U32" s="34"/>
-      <c r="V32" s="271"/>
+      <c r="V32" s="165"/>
     </row>
     <row r="33" spans="1:22" s="2" customFormat="1" ht="21" customHeight="1">
-      <c r="B33" s="139"/>
-      <c r="C33" s="155"/>
-      <c r="D33" s="155"/>
-      <c r="E33" s="155"/>
-      <c r="F33" s="155"/>
-      <c r="G33" s="155"/>
-      <c r="H33" s="155"/>
-      <c r="I33" s="155"/>
-      <c r="J33" s="155"/>
-      <c r="K33" s="140"/>
-      <c r="L33" s="151"/>
-      <c r="M33" s="144"/>
-      <c r="N33" s="206"/>
-      <c r="O33" s="140"/>
+      <c r="B33" s="226"/>
+      <c r="C33" s="151"/>
+      <c r="D33" s="151"/>
+      <c r="E33" s="151"/>
+      <c r="F33" s="151"/>
+      <c r="G33" s="151"/>
+      <c r="H33" s="151"/>
+      <c r="I33" s="151"/>
+      <c r="J33" s="151"/>
+      <c r="K33" s="152"/>
+      <c r="L33" s="231"/>
+      <c r="M33" s="188"/>
+      <c r="N33" s="269"/>
+      <c r="O33" s="152"/>
       <c r="P33" s="99"/>
-      <c r="Q33" s="203"/>
-      <c r="R33" s="140"/>
+      <c r="Q33" s="267"/>
+      <c r="R33" s="152"/>
       <c r="S33" s="36"/>
       <c r="T33" s="36"/>
       <c r="U33" s="32"/>
-      <c r="V33" s="271"/>
+      <c r="V33" s="165"/>
     </row>
     <row r="34" spans="1:22" s="2" customFormat="1" ht="21" customHeight="1">
-      <c r="B34" s="153" t="s">
+      <c r="B34" s="306" t="s">
         <v>48</v>
       </c>
-      <c r="C34" s="154"/>
-      <c r="D34" s="154"/>
-      <c r="E34" s="154"/>
-      <c r="F34" s="154"/>
-      <c r="G34" s="154"/>
-      <c r="H34" s="154"/>
-      <c r="I34" s="154"/>
-      <c r="J34" s="154"/>
-      <c r="K34" s="138"/>
-      <c r="L34" s="151"/>
-      <c r="M34" s="192" t="s">
+      <c r="C34" s="145"/>
+      <c r="D34" s="145"/>
+      <c r="E34" s="145"/>
+      <c r="F34" s="145"/>
+      <c r="G34" s="145"/>
+      <c r="H34" s="145"/>
+      <c r="I34" s="145"/>
+      <c r="J34" s="145"/>
+      <c r="K34" s="146"/>
+      <c r="L34" s="231"/>
+      <c r="M34" s="243" t="s">
         <v>49</v>
       </c>
-      <c r="N34" s="164"/>
-      <c r="O34" s="138"/>
+      <c r="N34" s="221"/>
+      <c r="O34" s="146"/>
       <c r="P34" s="24"/>
-      <c r="Q34" s="164"/>
-      <c r="R34" s="138"/>
+      <c r="Q34" s="221"/>
+      <c r="R34" s="146"/>
       <c r="S34" s="25"/>
       <c r="T34" s="25"/>
       <c r="U34" s="26"/>
-      <c r="V34" s="271"/>
+      <c r="V34" s="165"/>
     </row>
     <row r="35" spans="1:22" s="2" customFormat="1" ht="21" customHeight="1">
-      <c r="B35" s="139"/>
-      <c r="C35" s="155"/>
-      <c r="D35" s="155"/>
-      <c r="E35" s="155"/>
-      <c r="F35" s="155"/>
-      <c r="G35" s="155"/>
-      <c r="H35" s="155"/>
-      <c r="I35" s="155"/>
-      <c r="J35" s="155"/>
-      <c r="K35" s="140"/>
-      <c r="L35" s="151"/>
-      <c r="M35" s="144"/>
-      <c r="N35" s="144"/>
-      <c r="O35" s="140"/>
+      <c r="B35" s="226"/>
+      <c r="C35" s="151"/>
+      <c r="D35" s="151"/>
+      <c r="E35" s="151"/>
+      <c r="F35" s="151"/>
+      <c r="G35" s="151"/>
+      <c r="H35" s="151"/>
+      <c r="I35" s="151"/>
+      <c r="J35" s="151"/>
+      <c r="K35" s="152"/>
+      <c r="L35" s="231"/>
+      <c r="M35" s="188"/>
+      <c r="N35" s="188"/>
+      <c r="O35" s="152"/>
       <c r="P35" s="35"/>
-      <c r="Q35" s="144"/>
-      <c r="R35" s="140"/>
+      <c r="Q35" s="188"/>
+      <c r="R35" s="152"/>
       <c r="S35" s="36"/>
       <c r="T35" s="36"/>
       <c r="U35" s="32"/>
-      <c r="V35" s="271"/>
+      <c r="V35" s="165"/>
     </row>
     <row r="36" spans="1:22" s="2" customFormat="1" ht="21" customHeight="1">
       <c r="B36" s="37" t="s">
         <v>50</v>
       </c>
       <c r="C36" s="38"/>
-      <c r="D36" s="228"/>
-      <c r="E36" s="154"/>
-      <c r="F36" s="154"/>
-      <c r="G36" s="154"/>
-      <c r="H36" s="154"/>
-      <c r="I36" s="154"/>
-      <c r="J36" s="154"/>
-      <c r="K36" s="138"/>
-      <c r="L36" s="151"/>
-      <c r="M36" s="192" t="s">
+      <c r="D36" s="302"/>
+      <c r="E36" s="145"/>
+      <c r="F36" s="145"/>
+      <c r="G36" s="145"/>
+      <c r="H36" s="145"/>
+      <c r="I36" s="145"/>
+      <c r="J36" s="145"/>
+      <c r="K36" s="146"/>
+      <c r="L36" s="231"/>
+      <c r="M36" s="243" t="s">
         <v>51</v>
       </c>
-      <c r="N36" s="164"/>
-      <c r="O36" s="138"/>
+      <c r="N36" s="221"/>
+      <c r="O36" s="146"/>
       <c r="P36" s="24"/>
-      <c r="Q36" s="164"/>
-      <c r="R36" s="138"/>
+      <c r="Q36" s="221"/>
+      <c r="R36" s="146"/>
       <c r="S36" s="25"/>
       <c r="T36" s="25"/>
       <c r="U36" s="26"/>
-      <c r="V36" s="271"/>
+      <c r="V36" s="165"/>
     </row>
     <row r="37" spans="1:22" s="2" customFormat="1" ht="49.2" customHeight="1">
-      <c r="B37" s="156" t="s">
+      <c r="B37" s="307" t="s">
         <v>52</v>
       </c>
-      <c r="C37" s="157"/>
+      <c r="C37" s="161"/>
       <c r="D37" s="124" t="s">
         <v>53</v>
       </c>
-      <c r="E37" s="195" t="s">
+      <c r="E37" s="265" t="s">
         <v>54</v>
       </c>
-      <c r="F37" s="157"/>
-      <c r="G37" s="159"/>
+      <c r="F37" s="161"/>
+      <c r="G37" s="266"/>
       <c r="H37" s="113" t="s">
         <v>55</v>
       </c>
-      <c r="I37" s="207" t="s">
+      <c r="I37" s="270" t="s">
         <v>56</v>
       </c>
-      <c r="J37" s="208"/>
+      <c r="J37" s="271"/>
       <c r="K37" s="114" t="s">
         <v>57</v>
       </c>
-      <c r="L37" s="151"/>
-      <c r="M37" s="144"/>
-      <c r="N37" s="144"/>
-      <c r="O37" s="140"/>
+      <c r="L37" s="231"/>
+      <c r="M37" s="188"/>
+      <c r="N37" s="188"/>
+      <c r="O37" s="152"/>
       <c r="P37" s="35"/>
-      <c r="Q37" s="144"/>
-      <c r="R37" s="140"/>
+      <c r="Q37" s="188"/>
+      <c r="R37" s="152"/>
       <c r="S37" s="36"/>
       <c r="T37" s="36"/>
       <c r="U37" s="32"/>
-      <c r="V37" s="271"/>
+      <c r="V37" s="165"/>
     </row>
     <row r="38" spans="1:22" s="2" customFormat="1" ht="24.6" customHeight="1">
-      <c r="B38" s="229"/>
-      <c r="C38" s="159"/>
-      <c r="D38" s="215"/>
-      <c r="E38" s="298"/>
-      <c r="F38" s="299"/>
-      <c r="G38" s="300"/>
-      <c r="H38" s="210"/>
-      <c r="I38" s="287"/>
-      <c r="J38" s="288"/>
-      <c r="K38" s="193"/>
-      <c r="L38" s="151"/>
-      <c r="M38" s="192" t="s">
+      <c r="B38" s="309"/>
+      <c r="C38" s="266"/>
+      <c r="D38" s="259"/>
+      <c r="E38" s="202"/>
+      <c r="F38" s="203"/>
+      <c r="G38" s="204"/>
+      <c r="H38" s="253"/>
+      <c r="I38" s="190"/>
+      <c r="J38" s="191"/>
+      <c r="K38" s="263"/>
+      <c r="L38" s="231"/>
+      <c r="M38" s="243" t="s">
         <v>58</v>
       </c>
-      <c r="N38" s="164"/>
-      <c r="O38" s="138"/>
+      <c r="N38" s="221"/>
+      <c r="O38" s="146"/>
       <c r="P38" s="24"/>
-      <c r="Q38" s="164"/>
-      <c r="R38" s="138"/>
+      <c r="Q38" s="221"/>
+      <c r="R38" s="146"/>
       <c r="S38" s="25"/>
       <c r="T38" s="25"/>
       <c r="U38" s="26"/>
-      <c r="V38" s="271"/>
+      <c r="V38" s="165"/>
     </row>
     <row r="39" spans="1:22" s="2" customFormat="1" ht="22.95" customHeight="1">
-      <c r="B39" s="158"/>
-      <c r="C39" s="159"/>
-      <c r="D39" s="216"/>
-      <c r="E39" s="301"/>
-      <c r="F39" s="302"/>
-      <c r="G39" s="303"/>
-      <c r="H39" s="211"/>
-      <c r="I39" s="289"/>
-      <c r="J39" s="290"/>
-      <c r="K39" s="194"/>
-      <c r="L39" s="151"/>
-      <c r="M39" s="144"/>
-      <c r="N39" s="144"/>
-      <c r="O39" s="140"/>
+      <c r="B39" s="308"/>
+      <c r="C39" s="266"/>
+      <c r="D39" s="260"/>
+      <c r="E39" s="205"/>
+      <c r="F39" s="206"/>
+      <c r="G39" s="207"/>
+      <c r="H39" s="254"/>
+      <c r="I39" s="192"/>
+      <c r="J39" s="193"/>
+      <c r="K39" s="264"/>
+      <c r="L39" s="231"/>
+      <c r="M39" s="188"/>
+      <c r="N39" s="188"/>
+      <c r="O39" s="152"/>
       <c r="P39" s="35"/>
-      <c r="Q39" s="144"/>
-      <c r="R39" s="140"/>
+      <c r="Q39" s="188"/>
+      <c r="R39" s="152"/>
       <c r="S39" s="36"/>
       <c r="T39" s="36"/>
       <c r="U39" s="32"/>
-      <c r="V39" s="271"/>
+      <c r="V39" s="165"/>
     </row>
     <row r="40" spans="1:22" s="2" customFormat="1" ht="29.25" customHeight="1">
       <c r="A40" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="B40" s="191"/>
-      <c r="C40" s="157"/>
-      <c r="D40" s="142"/>
-      <c r="E40" s="266"/>
-      <c r="F40" s="157"/>
-      <c r="G40" s="142"/>
-      <c r="H40" s="265"/>
-      <c r="I40" s="140"/>
+      <c r="B40" s="262"/>
+      <c r="C40" s="161"/>
+      <c r="D40" s="162"/>
+      <c r="E40" s="220"/>
+      <c r="F40" s="161"/>
+      <c r="G40" s="162"/>
+      <c r="H40" s="218"/>
+      <c r="I40" s="152"/>
       <c r="K40" s="98"/>
-      <c r="L40" s="151"/>
-      <c r="M40" s="192" t="s">
+      <c r="L40" s="231"/>
+      <c r="M40" s="243" t="s">
         <v>60</v>
       </c>
-      <c r="N40" s="164"/>
-      <c r="O40" s="138"/>
+      <c r="N40" s="221"/>
+      <c r="O40" s="146"/>
       <c r="P40" s="24"/>
-      <c r="Q40" s="164"/>
-      <c r="R40" s="138"/>
+      <c r="Q40" s="221"/>
+      <c r="R40" s="146"/>
       <c r="S40" s="25"/>
       <c r="T40" s="25"/>
       <c r="U40" s="26"/>
-      <c r="V40" s="271"/>
+      <c r="V40" s="165"/>
     </row>
     <row r="41" spans="1:22" s="2" customFormat="1" ht="21" customHeight="1">
       <c r="B41" s="39"/>
@@ -4021,143 +4021,143 @@
       <c r="I41" s="40"/>
       <c r="J41" s="90"/>
       <c r="K41" s="95"/>
-      <c r="L41" s="152"/>
-      <c r="M41" s="144"/>
-      <c r="N41" s="144"/>
-      <c r="O41" s="140"/>
+      <c r="L41" s="232"/>
+      <c r="M41" s="188"/>
+      <c r="N41" s="188"/>
+      <c r="O41" s="152"/>
       <c r="P41" s="35"/>
-      <c r="Q41" s="144"/>
-      <c r="R41" s="140"/>
+      <c r="Q41" s="188"/>
+      <c r="R41" s="152"/>
       <c r="S41" s="36"/>
       <c r="T41" s="36"/>
       <c r="U41" s="32"/>
-      <c r="V41" s="271"/>
+      <c r="V41" s="165"/>
     </row>
     <row r="42" spans="1:22" ht="18" customHeight="1">
-      <c r="B42" s="212" t="s">
+      <c r="B42" s="255" t="s">
         <v>62</v>
       </c>
       <c r="C42" s="41"/>
       <c r="D42" s="41"/>
-      <c r="E42" s="171" t="s">
+      <c r="E42" s="163" t="s">
         <v>63</v>
       </c>
-      <c r="F42" s="138"/>
-      <c r="G42" s="170" t="s">
+      <c r="F42" s="146"/>
+      <c r="G42" s="258" t="s">
         <v>64</v>
       </c>
-      <c r="H42" s="138"/>
-      <c r="I42" s="166" t="s">
+      <c r="H42" s="146"/>
+      <c r="I42" s="144" t="s">
         <v>65</v>
       </c>
       <c r="J42" s="94" t="s">
         <v>66</v>
       </c>
-      <c r="K42" s="170" t="s">
+      <c r="K42" s="258" t="s">
         <v>67</v>
       </c>
-      <c r="L42" s="154"/>
-      <c r="M42" s="138"/>
-      <c r="N42" s="166" t="s">
+      <c r="L42" s="145"/>
+      <c r="M42" s="146"/>
+      <c r="N42" s="144" t="s">
         <v>68</v>
       </c>
       <c r="O42" s="42" t="s">
         <v>66</v>
       </c>
-      <c r="P42" s="166" t="s">
+      <c r="P42" s="144" t="s">
         <v>69</v>
       </c>
       <c r="Q42" s="41"/>
-      <c r="R42" s="166" t="s">
+      <c r="R42" s="144" t="s">
         <v>70</v>
       </c>
-      <c r="S42" s="154"/>
-      <c r="T42" s="138"/>
-      <c r="U42" s="312" t="s">
+      <c r="S42" s="145"/>
+      <c r="T42" s="146"/>
+      <c r="U42" s="141" t="s">
         <v>71</v>
       </c>
-      <c r="V42" s="271"/>
+      <c r="V42" s="165"/>
     </row>
     <row r="43" spans="1:22" ht="50.4" customHeight="1">
-      <c r="B43" s="213"/>
+      <c r="B43" s="256"/>
       <c r="C43" s="94" t="s">
         <v>72</v>
       </c>
       <c r="D43" s="116" t="s">
         <v>73</v>
       </c>
-      <c r="E43" s="148"/>
-      <c r="F43" s="163"/>
-      <c r="G43" s="149"/>
-      <c r="H43" s="140"/>
-      <c r="I43" s="167"/>
-      <c r="J43" s="190" t="s">
+      <c r="E43" s="147"/>
+      <c r="F43" s="149"/>
+      <c r="G43" s="150"/>
+      <c r="H43" s="152"/>
+      <c r="I43" s="187"/>
+      <c r="J43" s="261" t="s">
         <v>74</v>
       </c>
-      <c r="K43" s="149"/>
-      <c r="L43" s="155"/>
-      <c r="M43" s="140"/>
-      <c r="N43" s="167"/>
-      <c r="O43" s="143" t="s">
+      <c r="K43" s="150"/>
+      <c r="L43" s="151"/>
+      <c r="M43" s="152"/>
+      <c r="N43" s="187"/>
+      <c r="O43" s="272" t="s">
         <v>74</v>
       </c>
-      <c r="P43" s="167"/>
+      <c r="P43" s="187"/>
       <c r="Q43" s="43" t="s">
         <v>75</v>
       </c>
-      <c r="R43" s="148"/>
-      <c r="S43" s="205"/>
-      <c r="T43" s="163"/>
-      <c r="U43" s="269"/>
-      <c r="V43" s="271"/>
+      <c r="R43" s="147"/>
+      <c r="S43" s="148"/>
+      <c r="T43" s="149"/>
+      <c r="U43" s="142"/>
+      <c r="V43" s="165"/>
     </row>
     <row r="44" spans="1:22" ht="55.5" customHeight="1">
-      <c r="B44" s="213"/>
+      <c r="B44" s="256"/>
       <c r="C44" s="110" t="s">
         <v>76</v>
       </c>
       <c r="D44" s="109" t="s">
         <v>77</v>
       </c>
-      <c r="E44" s="149"/>
-      <c r="F44" s="140"/>
+      <c r="E44" s="150"/>
+      <c r="F44" s="152"/>
       <c r="G44" s="45" t="s">
         <v>78</v>
       </c>
       <c r="H44" s="72" t="s">
         <v>79</v>
       </c>
-      <c r="I44" s="144"/>
-      <c r="J44" s="144"/>
+      <c r="I44" s="188"/>
+      <c r="J44" s="188"/>
       <c r="K44" s="115" t="s">
         <v>80</v>
       </c>
-      <c r="L44" s="304" t="s">
+      <c r="L44" s="208" t="s">
         <v>79</v>
       </c>
-      <c r="M44" s="142"/>
-      <c r="N44" s="144"/>
-      <c r="O44" s="144"/>
-      <c r="P44" s="144"/>
+      <c r="M44" s="162"/>
+      <c r="N44" s="188"/>
+      <c r="O44" s="188"/>
+      <c r="P44" s="188"/>
       <c r="Q44" s="46" t="s">
         <v>81</v>
       </c>
-      <c r="R44" s="149"/>
-      <c r="S44" s="155"/>
-      <c r="T44" s="140"/>
-      <c r="U44" s="270"/>
-      <c r="V44" s="271"/>
+      <c r="R44" s="150"/>
+      <c r="S44" s="151"/>
+      <c r="T44" s="152"/>
+      <c r="U44" s="143"/>
+      <c r="V44" s="165"/>
     </row>
     <row r="45" spans="1:22" ht="50.1" customHeight="1">
-      <c r="B45" s="213"/>
+      <c r="B45" s="256"/>
       <c r="C45" s="111">
         <v>1</v>
       </c>
       <c r="D45" s="105" t="s">
         <v>82</v>
       </c>
-      <c r="E45" s="172"/>
-      <c r="F45" s="142"/>
+      <c r="E45" s="189"/>
+      <c r="F45" s="162"/>
       <c r="G45" s="49" t="s">
         <v>83</v>
       </c>
@@ -4167,28 +4167,28 @@
       <c r="K45" s="49" t="s">
         <v>83</v>
       </c>
-      <c r="L45" s="145"/>
-      <c r="M45" s="142"/>
+      <c r="L45" s="219"/>
+      <c r="M45" s="162"/>
       <c r="N45" s="52"/>
       <c r="O45" s="52"/>
       <c r="P45" s="53"/>
       <c r="Q45" s="54"/>
-      <c r="R45" s="217"/>
-      <c r="S45" s="157"/>
-      <c r="T45" s="142"/>
+      <c r="R45" s="160"/>
+      <c r="S45" s="161"/>
+      <c r="T45" s="162"/>
       <c r="U45" s="57"/>
-      <c r="V45" s="271"/>
+      <c r="V45" s="165"/>
     </row>
     <row r="46" spans="1:22" ht="50.1" customHeight="1">
-      <c r="B46" s="213"/>
+      <c r="B46" s="256"/>
       <c r="C46" s="112">
         <v>2</v>
       </c>
       <c r="D46" s="106" t="s">
         <v>84</v>
       </c>
-      <c r="E46" s="172"/>
-      <c r="F46" s="142"/>
+      <c r="E46" s="189"/>
+      <c r="F46" s="162"/>
       <c r="G46" s="49" t="s">
         <v>83</v>
       </c>
@@ -4198,28 +4198,28 @@
       <c r="K46" s="49" t="s">
         <v>83</v>
       </c>
-      <c r="L46" s="145"/>
-      <c r="M46" s="142"/>
+      <c r="L46" s="219"/>
+      <c r="M46" s="162"/>
       <c r="N46" s="50"/>
       <c r="O46" s="50"/>
       <c r="P46" s="60"/>
       <c r="Q46" s="61"/>
-      <c r="R46" s="217"/>
-      <c r="S46" s="157"/>
-      <c r="T46" s="142"/>
+      <c r="R46" s="160"/>
+      <c r="S46" s="161"/>
+      <c r="T46" s="162"/>
       <c r="U46" s="57"/>
-      <c r="V46" s="271"/>
+      <c r="V46" s="165"/>
     </row>
     <row r="47" spans="1:22" ht="50.1" customHeight="1">
-      <c r="B47" s="213"/>
+      <c r="B47" s="256"/>
       <c r="C47" s="112">
         <v>3</v>
       </c>
       <c r="D47" s="106" t="s">
         <v>85</v>
       </c>
-      <c r="E47" s="172"/>
-      <c r="F47" s="142"/>
+      <c r="E47" s="189"/>
+      <c r="F47" s="162"/>
       <c r="G47" s="49" t="s">
         <v>83</v>
       </c>
@@ -4229,28 +4229,28 @@
       <c r="K47" s="49" t="s">
         <v>83</v>
       </c>
-      <c r="L47" s="145"/>
-      <c r="M47" s="142"/>
+      <c r="L47" s="219"/>
+      <c r="M47" s="162"/>
       <c r="N47" s="50"/>
       <c r="O47" s="50"/>
       <c r="P47" s="53"/>
       <c r="Q47" s="61"/>
-      <c r="R47" s="217"/>
-      <c r="S47" s="157"/>
-      <c r="T47" s="142"/>
+      <c r="R47" s="160"/>
+      <c r="S47" s="161"/>
+      <c r="T47" s="162"/>
       <c r="U47" s="57"/>
-      <c r="V47" s="271"/>
+      <c r="V47" s="165"/>
     </row>
     <row r="48" spans="1:22" ht="50.1" customHeight="1">
-      <c r="B48" s="213"/>
+      <c r="B48" s="256"/>
       <c r="C48" s="112">
         <v>4</v>
       </c>
       <c r="D48" s="106" t="s">
         <v>86</v>
       </c>
-      <c r="E48" s="172"/>
-      <c r="F48" s="142"/>
+      <c r="E48" s="189"/>
+      <c r="F48" s="162"/>
       <c r="G48" s="49" t="s">
         <v>83</v>
       </c>
@@ -4260,28 +4260,28 @@
       <c r="K48" s="49" t="s">
         <v>83</v>
       </c>
-      <c r="L48" s="145"/>
-      <c r="M48" s="142"/>
+      <c r="L48" s="219"/>
+      <c r="M48" s="162"/>
       <c r="N48" s="50"/>
       <c r="O48" s="50"/>
       <c r="P48" s="53"/>
       <c r="Q48" s="61"/>
-      <c r="R48" s="217"/>
-      <c r="S48" s="157"/>
-      <c r="T48" s="142"/>
+      <c r="R48" s="160"/>
+      <c r="S48" s="161"/>
+      <c r="T48" s="162"/>
       <c r="U48" s="57"/>
-      <c r="V48" s="271"/>
+      <c r="V48" s="165"/>
     </row>
     <row r="49" spans="2:23" ht="50.1" customHeight="1">
-      <c r="B49" s="213"/>
+      <c r="B49" s="256"/>
       <c r="C49" s="112">
         <v>5</v>
       </c>
       <c r="D49" s="107" t="s">
         <v>87</v>
       </c>
-      <c r="E49" s="172"/>
-      <c r="F49" s="142"/>
+      <c r="E49" s="189"/>
+      <c r="F49" s="162"/>
       <c r="G49" s="49" t="s">
         <v>83</v>
       </c>
@@ -4291,28 +4291,28 @@
       <c r="K49" s="49" t="s">
         <v>83</v>
       </c>
-      <c r="L49" s="145"/>
-      <c r="M49" s="142"/>
+      <c r="L49" s="219"/>
+      <c r="M49" s="162"/>
       <c r="N49" s="50"/>
       <c r="O49" s="50"/>
       <c r="P49" s="53"/>
       <c r="Q49" s="61"/>
-      <c r="R49" s="217"/>
-      <c r="S49" s="157"/>
-      <c r="T49" s="142"/>
+      <c r="R49" s="160"/>
+      <c r="S49" s="161"/>
+      <c r="T49" s="162"/>
       <c r="U49" s="57"/>
-      <c r="V49" s="271"/>
+      <c r="V49" s="165"/>
     </row>
     <row r="50" spans="2:23" ht="53.4" customHeight="1">
-      <c r="B50" s="213"/>
+      <c r="B50" s="256"/>
       <c r="C50" s="112">
         <v>6</v>
       </c>
       <c r="D50" s="108" t="s">
         <v>88</v>
       </c>
-      <c r="E50" s="172"/>
-      <c r="F50" s="142"/>
+      <c r="E50" s="189"/>
+      <c r="F50" s="162"/>
       <c r="G50" s="49" t="s">
         <v>83</v>
       </c>
@@ -4322,28 +4322,28 @@
       <c r="K50" s="49" t="s">
         <v>83</v>
       </c>
-      <c r="L50" s="145"/>
-      <c r="M50" s="142"/>
+      <c r="L50" s="219"/>
+      <c r="M50" s="162"/>
       <c r="N50" s="50"/>
       <c r="O50" s="50"/>
       <c r="P50" s="53"/>
       <c r="Q50" s="61"/>
-      <c r="R50" s="217"/>
-      <c r="S50" s="157"/>
-      <c r="T50" s="142"/>
+      <c r="R50" s="160"/>
+      <c r="S50" s="161"/>
+      <c r="T50" s="162"/>
       <c r="U50" s="57"/>
-      <c r="V50" s="271"/>
+      <c r="V50" s="165"/>
     </row>
     <row r="51" spans="2:23" ht="50.1" customHeight="1">
-      <c r="B51" s="214"/>
+      <c r="B51" s="257"/>
       <c r="C51" s="111">
         <v>7</v>
       </c>
       <c r="D51" s="108" t="s">
         <v>89</v>
       </c>
-      <c r="E51" s="172"/>
-      <c r="F51" s="142"/>
+      <c r="E51" s="189"/>
+      <c r="F51" s="162"/>
       <c r="G51" s="49" t="s">
         <v>83</v>
       </c>
@@ -4353,17 +4353,17 @@
       <c r="K51" s="49" t="s">
         <v>83</v>
       </c>
-      <c r="L51" s="145"/>
-      <c r="M51" s="142"/>
+      <c r="L51" s="219"/>
+      <c r="M51" s="162"/>
       <c r="N51" s="52"/>
       <c r="O51" s="52"/>
       <c r="P51" s="60"/>
       <c r="Q51" s="54"/>
-      <c r="R51" s="217"/>
-      <c r="S51" s="157"/>
-      <c r="T51" s="142"/>
+      <c r="R51" s="160"/>
+      <c r="S51" s="161"/>
+      <c r="T51" s="162"/>
       <c r="U51" s="57"/>
-      <c r="V51" s="271"/>
+      <c r="V51" s="165"/>
     </row>
     <row r="52" spans="2:23" ht="3.75" customHeight="1">
       <c r="B52" s="62"/>
@@ -4386,131 +4386,131 @@
       <c r="S52" s="63"/>
       <c r="T52" s="69"/>
       <c r="U52" s="70"/>
-      <c r="V52" s="271"/>
+      <c r="V52" s="165"/>
     </row>
     <row r="53" spans="2:23" ht="18" customHeight="1">
-      <c r="B53" s="212" t="s">
+      <c r="B53" s="255" t="s">
         <v>90</v>
       </c>
       <c r="C53" s="71"/>
       <c r="D53" s="71"/>
-      <c r="E53" s="171" t="s">
+      <c r="E53" s="163" t="s">
         <v>63</v>
       </c>
-      <c r="F53" s="138"/>
-      <c r="G53" s="141" t="s">
+      <c r="F53" s="146"/>
+      <c r="G53" s="164" t="s">
         <v>91</v>
       </c>
-      <c r="H53" s="138"/>
-      <c r="I53" s="166" t="s">
+      <c r="H53" s="146"/>
+      <c r="I53" s="144" t="s">
         <v>92</v>
       </c>
-      <c r="J53" s="267" t="s">
+      <c r="J53" s="222" t="s">
         <v>93</v>
       </c>
-      <c r="K53" s="141" t="s">
+      <c r="K53" s="164" t="s">
         <v>67</v>
       </c>
-      <c r="L53" s="154"/>
-      <c r="M53" s="138"/>
-      <c r="N53" s="166" t="s">
+      <c r="L53" s="145"/>
+      <c r="M53" s="146"/>
+      <c r="N53" s="144" t="s">
         <v>68</v>
       </c>
       <c r="O53" s="42" t="s">
         <v>66</v>
       </c>
-      <c r="P53" s="166" t="s">
+      <c r="P53" s="144" t="s">
         <v>69</v>
       </c>
       <c r="Q53" s="41"/>
-      <c r="R53" s="166" t="s">
+      <c r="R53" s="144" t="s">
         <v>70</v>
       </c>
-      <c r="S53" s="154"/>
-      <c r="T53" s="138"/>
-      <c r="U53" s="268" t="s">
+      <c r="S53" s="145"/>
+      <c r="T53" s="146"/>
+      <c r="U53" s="159" t="s">
         <v>71</v>
       </c>
-      <c r="V53" s="271"/>
+      <c r="V53" s="165"/>
     </row>
     <row r="54" spans="2:23" ht="50.4" customHeight="1">
-      <c r="B54" s="213"/>
+      <c r="B54" s="256"/>
       <c r="C54" s="41" t="s">
         <v>72</v>
       </c>
       <c r="D54" s="41" t="s">
         <v>73</v>
       </c>
-      <c r="E54" s="148"/>
-      <c r="F54" s="163"/>
-      <c r="G54" s="149"/>
-      <c r="H54" s="140"/>
-      <c r="I54" s="167"/>
-      <c r="J54" s="167"/>
-      <c r="K54" s="149"/>
-      <c r="L54" s="155"/>
-      <c r="M54" s="140"/>
-      <c r="N54" s="167"/>
-      <c r="O54" s="143" t="s">
+      <c r="E54" s="147"/>
+      <c r="F54" s="149"/>
+      <c r="G54" s="150"/>
+      <c r="H54" s="152"/>
+      <c r="I54" s="187"/>
+      <c r="J54" s="187"/>
+      <c r="K54" s="150"/>
+      <c r="L54" s="151"/>
+      <c r="M54" s="152"/>
+      <c r="N54" s="187"/>
+      <c r="O54" s="272" t="s">
         <v>74</v>
       </c>
-      <c r="P54" s="167"/>
+      <c r="P54" s="187"/>
       <c r="Q54" s="43" t="s">
         <v>75</v>
       </c>
-      <c r="R54" s="148"/>
-      <c r="S54" s="205"/>
-      <c r="T54" s="163"/>
-      <c r="U54" s="269"/>
-      <c r="V54" s="271"/>
+      <c r="R54" s="147"/>
+      <c r="S54" s="148"/>
+      <c r="T54" s="149"/>
+      <c r="U54" s="142"/>
+      <c r="V54" s="165"/>
     </row>
     <row r="55" spans="2:23" ht="50.4" customHeight="1">
-      <c r="B55" s="213"/>
+      <c r="B55" s="256"/>
       <c r="C55" s="44" t="s">
         <v>76</v>
       </c>
       <c r="D55" s="44" t="s">
         <v>77</v>
       </c>
-      <c r="E55" s="149"/>
-      <c r="F55" s="140"/>
+      <c r="E55" s="150"/>
+      <c r="F55" s="152"/>
       <c r="G55" s="45" t="s">
         <v>80</v>
       </c>
       <c r="H55" s="72" t="s">
         <v>79</v>
       </c>
-      <c r="I55" s="144"/>
-      <c r="J55" s="144"/>
+      <c r="I55" s="188"/>
+      <c r="J55" s="188"/>
       <c r="K55" s="45" t="s">
         <v>80</v>
       </c>
-      <c r="L55" s="141" t="s">
+      <c r="L55" s="164" t="s">
         <v>79</v>
       </c>
-      <c r="M55" s="142"/>
-      <c r="N55" s="144"/>
-      <c r="O55" s="144"/>
-      <c r="P55" s="144"/>
+      <c r="M55" s="162"/>
+      <c r="N55" s="188"/>
+      <c r="O55" s="188"/>
+      <c r="P55" s="188"/>
       <c r="Q55" s="46" t="s">
         <v>81</v>
       </c>
-      <c r="R55" s="149"/>
-      <c r="S55" s="155"/>
-      <c r="T55" s="140"/>
-      <c r="U55" s="270"/>
-      <c r="V55" s="271"/>
+      <c r="R55" s="150"/>
+      <c r="S55" s="151"/>
+      <c r="T55" s="152"/>
+      <c r="U55" s="143"/>
+      <c r="V55" s="165"/>
     </row>
     <row r="56" spans="2:23" ht="30" customHeight="1">
-      <c r="B56" s="213"/>
+      <c r="B56" s="256"/>
       <c r="C56" s="47">
         <v>1</v>
       </c>
       <c r="D56" s="48" t="s">
         <v>82</v>
       </c>
-      <c r="E56" s="172"/>
-      <c r="F56" s="142"/>
+      <c r="E56" s="189"/>
+      <c r="F56" s="162"/>
       <c r="G56" s="49" t="s">
         <v>83</v>
       </c>
@@ -4520,8 +4520,8 @@
       <c r="K56" s="49" t="s">
         <v>83</v>
       </c>
-      <c r="L56" s="145"/>
-      <c r="M56" s="142"/>
+      <c r="L56" s="219"/>
+      <c r="M56" s="162"/>
       <c r="N56" s="52"/>
       <c r="O56" s="52"/>
       <c r="P56" s="60"/>
@@ -4530,18 +4530,18 @@
       <c r="S56" s="56"/>
       <c r="T56" s="18"/>
       <c r="U56" s="57"/>
-      <c r="V56" s="271"/>
+      <c r="V56" s="165"/>
     </row>
     <row r="57" spans="2:23" ht="30" customHeight="1">
-      <c r="B57" s="213"/>
+      <c r="B57" s="256"/>
       <c r="C57" s="55">
         <v>2</v>
       </c>
       <c r="D57" s="74" t="s">
         <v>94</v>
       </c>
-      <c r="E57" s="172"/>
-      <c r="F57" s="142"/>
+      <c r="E57" s="189"/>
+      <c r="F57" s="162"/>
       <c r="G57" s="49" t="s">
         <v>83</v>
       </c>
@@ -4551,8 +4551,8 @@
       <c r="K57" s="49" t="s">
         <v>83</v>
       </c>
-      <c r="L57" s="145"/>
-      <c r="M57" s="142"/>
+      <c r="L57" s="219"/>
+      <c r="M57" s="162"/>
       <c r="N57" s="50"/>
       <c r="O57" s="50"/>
       <c r="P57" s="53"/>
@@ -4561,18 +4561,18 @@
       <c r="S57" s="56"/>
       <c r="T57" s="18"/>
       <c r="U57" s="57"/>
-      <c r="V57" s="271"/>
+      <c r="V57" s="165"/>
     </row>
     <row r="58" spans="2:23" ht="30" customHeight="1">
-      <c r="B58" s="213"/>
+      <c r="B58" s="256"/>
       <c r="C58" s="55">
         <v>3</v>
       </c>
       <c r="D58" s="76" t="s">
         <v>95</v>
       </c>
-      <c r="E58" s="172"/>
-      <c r="F58" s="142"/>
+      <c r="E58" s="189"/>
+      <c r="F58" s="162"/>
       <c r="G58" s="49" t="s">
         <v>83</v>
       </c>
@@ -4582,8 +4582,8 @@
       <c r="K58" s="49" t="s">
         <v>83</v>
       </c>
-      <c r="L58" s="145"/>
-      <c r="M58" s="142"/>
+      <c r="L58" s="219"/>
+      <c r="M58" s="162"/>
       <c r="N58" s="50"/>
       <c r="O58" s="50"/>
       <c r="P58" s="53"/>
@@ -4592,18 +4592,18 @@
       <c r="S58" s="56"/>
       <c r="T58" s="18"/>
       <c r="U58" s="57"/>
-      <c r="V58" s="271"/>
+      <c r="V58" s="165"/>
     </row>
     <row r="59" spans="2:23" ht="30" customHeight="1">
-      <c r="B59" s="213"/>
+      <c r="B59" s="256"/>
       <c r="C59" s="77">
         <v>4</v>
       </c>
       <c r="D59" s="78" t="s">
         <v>96</v>
       </c>
-      <c r="E59" s="172"/>
-      <c r="F59" s="142"/>
+      <c r="E59" s="189"/>
+      <c r="F59" s="162"/>
       <c r="G59" s="49" t="s">
         <v>83</v>
       </c>
@@ -4613,8 +4613,8 @@
       <c r="K59" s="58" t="s">
         <v>83</v>
       </c>
-      <c r="L59" s="145"/>
-      <c r="M59" s="142"/>
+      <c r="L59" s="219"/>
+      <c r="M59" s="162"/>
       <c r="N59" s="50"/>
       <c r="O59" s="50"/>
       <c r="P59" s="53"/>
@@ -4623,18 +4623,18 @@
       <c r="S59" s="56"/>
       <c r="T59" s="18"/>
       <c r="U59" s="57"/>
-      <c r="V59" s="271"/>
+      <c r="V59" s="165"/>
     </row>
     <row r="60" spans="2:23" ht="30" customHeight="1">
-      <c r="B60" s="213"/>
+      <c r="B60" s="256"/>
       <c r="C60" s="77">
         <v>5</v>
       </c>
       <c r="D60" s="78" t="s">
         <v>86</v>
       </c>
-      <c r="E60" s="172"/>
-      <c r="F60" s="142"/>
+      <c r="E60" s="189"/>
+      <c r="F60" s="162"/>
       <c r="G60" s="49" t="s">
         <v>83</v>
       </c>
@@ -4644,8 +4644,8 @@
       <c r="K60" s="58" t="s">
         <v>83</v>
       </c>
-      <c r="L60" s="145"/>
-      <c r="M60" s="142"/>
+      <c r="L60" s="219"/>
+      <c r="M60" s="162"/>
       <c r="N60" s="50"/>
       <c r="O60" s="50"/>
       <c r="P60" s="53"/>
@@ -4654,18 +4654,18 @@
       <c r="S60" s="81"/>
       <c r="T60" s="5"/>
       <c r="U60" s="82"/>
-      <c r="V60" s="271"/>
+      <c r="V60" s="165"/>
     </row>
     <row r="61" spans="2:23" ht="30" customHeight="1">
-      <c r="B61" s="214"/>
+      <c r="B61" s="257"/>
       <c r="C61" s="83">
         <v>6</v>
       </c>
       <c r="D61" s="84" t="s">
         <v>89</v>
       </c>
-      <c r="E61" s="172"/>
-      <c r="F61" s="142"/>
+      <c r="E61" s="189"/>
+      <c r="F61" s="162"/>
       <c r="G61" s="58" t="s">
         <v>83</v>
       </c>
@@ -4675,8 +4675,8 @@
       <c r="K61" s="83" t="s">
         <v>83</v>
       </c>
-      <c r="L61" s="145"/>
-      <c r="M61" s="142"/>
+      <c r="L61" s="219"/>
+      <c r="M61" s="162"/>
       <c r="N61" s="86"/>
       <c r="O61" s="86"/>
       <c r="P61" s="83"/>
@@ -4685,59 +4685,59 @@
       <c r="S61" s="81"/>
       <c r="T61" s="5"/>
       <c r="U61" s="82"/>
-      <c r="V61" s="271"/>
+      <c r="V61" s="165"/>
     </row>
     <row r="62" spans="2:23" ht="30" customHeight="1" thickBot="1">
-      <c r="B62" s="272" t="s">
+      <c r="B62" s="166" t="s">
         <v>97</v>
       </c>
-      <c r="C62" s="273"/>
-      <c r="D62" s="273"/>
-      <c r="E62" s="273"/>
-      <c r="F62" s="274"/>
-      <c r="G62" s="275" t="s">
+      <c r="C62" s="167"/>
+      <c r="D62" s="167"/>
+      <c r="E62" s="167"/>
+      <c r="F62" s="168"/>
+      <c r="G62" s="169" t="s">
         <v>98</v>
       </c>
-      <c r="H62" s="273"/>
-      <c r="I62" s="273"/>
-      <c r="J62" s="273"/>
-      <c r="K62" s="273"/>
-      <c r="L62" s="273"/>
-      <c r="M62" s="274"/>
-      <c r="N62" s="276" t="s">
+      <c r="H62" s="167"/>
+      <c r="I62" s="167"/>
+      <c r="J62" s="167"/>
+      <c r="K62" s="167"/>
+      <c r="L62" s="167"/>
+      <c r="M62" s="168"/>
+      <c r="N62" s="170" t="s">
         <v>99</v>
       </c>
-      <c r="O62" s="273"/>
-      <c r="P62" s="273"/>
-      <c r="Q62" s="273"/>
-      <c r="R62" s="273"/>
-      <c r="S62" s="273"/>
-      <c r="T62" s="273"/>
-      <c r="U62" s="277"/>
-      <c r="V62" s="271"/>
+      <c r="O62" s="167"/>
+      <c r="P62" s="167"/>
+      <c r="Q62" s="167"/>
+      <c r="R62" s="167"/>
+      <c r="S62" s="167"/>
+      <c r="T62" s="167"/>
+      <c r="U62" s="171"/>
+      <c r="V62" s="165"/>
     </row>
     <row r="63" spans="2:23" s="87" customFormat="1" ht="48.6" customHeight="1">
-      <c r="B63" s="319"/>
-      <c r="C63" s="320"/>
-      <c r="D63" s="320"/>
-      <c r="E63" s="320"/>
-      <c r="F63" s="320"/>
-      <c r="G63" s="321"/>
-      <c r="H63" s="322"/>
-      <c r="I63" s="322"/>
-      <c r="J63" s="322"/>
-      <c r="K63" s="322"/>
-      <c r="L63" s="322"/>
-      <c r="M63" s="322"/>
-      <c r="N63" s="321"/>
-      <c r="O63" s="322"/>
-      <c r="P63" s="322"/>
-      <c r="Q63" s="322"/>
-      <c r="R63" s="322"/>
-      <c r="S63" s="322"/>
-      <c r="T63" s="322"/>
-      <c r="U63" s="322"/>
-      <c r="V63" s="271"/>
+      <c r="B63" s="137"/>
+      <c r="C63" s="138"/>
+      <c r="D63" s="138"/>
+      <c r="E63" s="138"/>
+      <c r="F63" s="138"/>
+      <c r="G63" s="139"/>
+      <c r="H63" s="140"/>
+      <c r="I63" s="140"/>
+      <c r="J63" s="140"/>
+      <c r="K63" s="140"/>
+      <c r="L63" s="140"/>
+      <c r="M63" s="140"/>
+      <c r="N63" s="139"/>
+      <c r="O63" s="140"/>
+      <c r="P63" s="140"/>
+      <c r="Q63" s="140"/>
+      <c r="R63" s="140"/>
+      <c r="S63" s="140"/>
+      <c r="T63" s="140"/>
+      <c r="U63" s="140"/>
+      <c r="V63" s="165"/>
       <c r="W63" s="88"/>
     </row>
     <row r="64" spans="2:23" ht="14.4" customHeight="1"/>
@@ -4763,6 +4763,149 @@
     </row>
   </sheetData>
   <mergeCells count="167">
+    <mergeCell ref="D6:D7"/>
+    <mergeCell ref="K8:K11"/>
+    <mergeCell ref="D10:D11"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="D36:K36"/>
+    <mergeCell ref="Q38:R38"/>
+    <mergeCell ref="B6:C7"/>
+    <mergeCell ref="L55:M55"/>
+    <mergeCell ref="O43:O44"/>
+    <mergeCell ref="L51:M51"/>
+    <mergeCell ref="B12:C13"/>
+    <mergeCell ref="K12:K15"/>
+    <mergeCell ref="L27:L29"/>
+    <mergeCell ref="B34:K35"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="D18:D19"/>
+    <mergeCell ref="D8:D9"/>
+    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="I7:J7"/>
+    <mergeCell ref="E6:H7"/>
+    <mergeCell ref="B10:C11"/>
+    <mergeCell ref="I8:J11"/>
+    <mergeCell ref="I37:J37"/>
+    <mergeCell ref="B42:B51"/>
+    <mergeCell ref="R51:T51"/>
+    <mergeCell ref="N28:O28"/>
+    <mergeCell ref="N26:O26"/>
+    <mergeCell ref="O54:O55"/>
+    <mergeCell ref="B29:D31"/>
+    <mergeCell ref="B1:C5"/>
+    <mergeCell ref="Q36:R36"/>
+    <mergeCell ref="B18:C19"/>
+    <mergeCell ref="B8:C9"/>
+    <mergeCell ref="N34:O34"/>
+    <mergeCell ref="L49:M49"/>
+    <mergeCell ref="G53:H54"/>
+    <mergeCell ref="N42:N44"/>
+    <mergeCell ref="N27:O27"/>
+    <mergeCell ref="D3:D5"/>
+    <mergeCell ref="E53:F55"/>
+    <mergeCell ref="N36:O36"/>
+    <mergeCell ref="E47:F47"/>
+    <mergeCell ref="E8:F10"/>
+    <mergeCell ref="G8:H10"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="L61:M61"/>
+    <mergeCell ref="E58:F58"/>
+    <mergeCell ref="I42:I44"/>
+    <mergeCell ref="L48:M48"/>
+    <mergeCell ref="E50:F50"/>
+    <mergeCell ref="H38:H39"/>
+    <mergeCell ref="E61:F61"/>
+    <mergeCell ref="E59:F59"/>
+    <mergeCell ref="L58:M58"/>
+    <mergeCell ref="E56:F56"/>
+    <mergeCell ref="L60:M60"/>
+    <mergeCell ref="L45:M45"/>
+    <mergeCell ref="G42:H43"/>
+    <mergeCell ref="I53:I55"/>
+    <mergeCell ref="K42:M43"/>
+    <mergeCell ref="E46:F46"/>
+    <mergeCell ref="L57:M57"/>
+    <mergeCell ref="J43:J44"/>
+    <mergeCell ref="E57:F57"/>
+    <mergeCell ref="E48:F48"/>
+    <mergeCell ref="K38:K39"/>
+    <mergeCell ref="M38:M39"/>
+    <mergeCell ref="L56:M56"/>
+    <mergeCell ref="N25:O25"/>
+    <mergeCell ref="L25:M26"/>
+    <mergeCell ref="D14:D15"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="Q31:R31"/>
+    <mergeCell ref="E60:F60"/>
+    <mergeCell ref="L59:M59"/>
+    <mergeCell ref="B32:K33"/>
+    <mergeCell ref="L46:M46"/>
+    <mergeCell ref="B53:B61"/>
+    <mergeCell ref="D38:D39"/>
+    <mergeCell ref="M34:M35"/>
+    <mergeCell ref="M32:M33"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="M36:M37"/>
+    <mergeCell ref="M30:M31"/>
+    <mergeCell ref="B16:C17"/>
+    <mergeCell ref="E37:G37"/>
+    <mergeCell ref="L16:R19"/>
+    <mergeCell ref="E29:K30"/>
+    <mergeCell ref="Q33:R33"/>
+    <mergeCell ref="B22:C24"/>
+    <mergeCell ref="E16:I19"/>
+    <mergeCell ref="N33:O33"/>
+    <mergeCell ref="B14:C15"/>
+    <mergeCell ref="N37:O37"/>
+    <mergeCell ref="L20:U20"/>
+    <mergeCell ref="Q26:R26"/>
+    <mergeCell ref="Q34:R34"/>
+    <mergeCell ref="L30:L41"/>
+    <mergeCell ref="R48:T48"/>
+    <mergeCell ref="Q27:R27"/>
+    <mergeCell ref="N31:O31"/>
+    <mergeCell ref="N40:O40"/>
+    <mergeCell ref="J20:K24"/>
+    <mergeCell ref="E31:K31"/>
+    <mergeCell ref="B20:C21"/>
+    <mergeCell ref="E20:I24"/>
+    <mergeCell ref="M40:M41"/>
+    <mergeCell ref="Q39:R39"/>
+    <mergeCell ref="B25:D26"/>
+    <mergeCell ref="J16:K19"/>
+    <mergeCell ref="Q29:R29"/>
+    <mergeCell ref="B27:D28"/>
+    <mergeCell ref="Q32:R32"/>
+    <mergeCell ref="N29:O29"/>
+    <mergeCell ref="N38:O38"/>
+    <mergeCell ref="D20:D21"/>
+    <mergeCell ref="R50:T50"/>
+    <mergeCell ref="N35:O35"/>
+    <mergeCell ref="I12:J15"/>
+    <mergeCell ref="R53:T55"/>
+    <mergeCell ref="Q35:R35"/>
+    <mergeCell ref="N39:O39"/>
+    <mergeCell ref="R46:T46"/>
+    <mergeCell ref="D22:D24"/>
+    <mergeCell ref="E49:F49"/>
+    <mergeCell ref="N41:O41"/>
+    <mergeCell ref="H40:I40"/>
+    <mergeCell ref="L47:M47"/>
+    <mergeCell ref="E40:G40"/>
+    <mergeCell ref="R45:T45"/>
+    <mergeCell ref="P53:P55"/>
+    <mergeCell ref="E45:F45"/>
+    <mergeCell ref="Q40:R40"/>
+    <mergeCell ref="J53:J55"/>
+    <mergeCell ref="N53:N55"/>
+    <mergeCell ref="L50:M50"/>
+    <mergeCell ref="Q28:R28"/>
+    <mergeCell ref="Q37:R37"/>
+    <mergeCell ref="E12:H15"/>
+    <mergeCell ref="D12:D13"/>
     <mergeCell ref="U42:U44"/>
     <mergeCell ref="R42:T44"/>
     <mergeCell ref="L22:U24"/>
@@ -4787,149 +4930,6 @@
     <mergeCell ref="N32:O32"/>
     <mergeCell ref="Q41:R41"/>
     <mergeCell ref="Q25:R25"/>
-    <mergeCell ref="R50:T50"/>
-    <mergeCell ref="N35:O35"/>
-    <mergeCell ref="I12:J15"/>
-    <mergeCell ref="R53:T55"/>
-    <mergeCell ref="Q35:R35"/>
-    <mergeCell ref="N39:O39"/>
-    <mergeCell ref="R46:T46"/>
-    <mergeCell ref="D22:D24"/>
-    <mergeCell ref="E49:F49"/>
-    <mergeCell ref="N41:O41"/>
-    <mergeCell ref="H40:I40"/>
-    <mergeCell ref="L47:M47"/>
-    <mergeCell ref="E40:G40"/>
-    <mergeCell ref="R45:T45"/>
-    <mergeCell ref="P53:P55"/>
-    <mergeCell ref="E45:F45"/>
-    <mergeCell ref="Q40:R40"/>
-    <mergeCell ref="J53:J55"/>
-    <mergeCell ref="N53:N55"/>
-    <mergeCell ref="L50:M50"/>
-    <mergeCell ref="Q28:R28"/>
-    <mergeCell ref="Q37:R37"/>
-    <mergeCell ref="E12:H15"/>
-    <mergeCell ref="B14:C15"/>
-    <mergeCell ref="N37:O37"/>
-    <mergeCell ref="L20:U20"/>
-    <mergeCell ref="Q26:R26"/>
-    <mergeCell ref="Q34:R34"/>
-    <mergeCell ref="L30:L41"/>
-    <mergeCell ref="R48:T48"/>
-    <mergeCell ref="Q27:R27"/>
-    <mergeCell ref="N31:O31"/>
-    <mergeCell ref="N40:O40"/>
-    <mergeCell ref="J20:K24"/>
-    <mergeCell ref="E31:K31"/>
-    <mergeCell ref="B20:C21"/>
-    <mergeCell ref="E20:I24"/>
-    <mergeCell ref="D12:D13"/>
-    <mergeCell ref="M40:M41"/>
-    <mergeCell ref="Q39:R39"/>
-    <mergeCell ref="B25:D26"/>
-    <mergeCell ref="J16:K19"/>
-    <mergeCell ref="Q29:R29"/>
-    <mergeCell ref="B27:D28"/>
-    <mergeCell ref="Q32:R32"/>
-    <mergeCell ref="N29:O29"/>
-    <mergeCell ref="N38:O38"/>
-    <mergeCell ref="D20:D21"/>
-    <mergeCell ref="N25:O25"/>
-    <mergeCell ref="L25:M26"/>
-    <mergeCell ref="D14:D15"/>
-    <mergeCell ref="D16:D17"/>
-    <mergeCell ref="Q31:R31"/>
-    <mergeCell ref="E60:F60"/>
-    <mergeCell ref="L59:M59"/>
-    <mergeCell ref="B32:K33"/>
-    <mergeCell ref="L46:M46"/>
-    <mergeCell ref="L61:M61"/>
-    <mergeCell ref="E58:F58"/>
-    <mergeCell ref="I42:I44"/>
-    <mergeCell ref="L48:M48"/>
-    <mergeCell ref="E50:F50"/>
-    <mergeCell ref="H38:H39"/>
-    <mergeCell ref="E61:F61"/>
-    <mergeCell ref="E59:F59"/>
-    <mergeCell ref="L58:M58"/>
-    <mergeCell ref="E56:F56"/>
-    <mergeCell ref="B53:B61"/>
-    <mergeCell ref="L60:M60"/>
-    <mergeCell ref="L45:M45"/>
-    <mergeCell ref="G42:H43"/>
-    <mergeCell ref="I53:I55"/>
-    <mergeCell ref="D38:D39"/>
-    <mergeCell ref="K42:M43"/>
-    <mergeCell ref="M34:M35"/>
-    <mergeCell ref="M32:M33"/>
-    <mergeCell ref="E46:F46"/>
-    <mergeCell ref="L57:M57"/>
-    <mergeCell ref="J43:J44"/>
-    <mergeCell ref="E57:F57"/>
-    <mergeCell ref="E48:F48"/>
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="M36:M37"/>
-    <mergeCell ref="M30:M31"/>
-    <mergeCell ref="B16:C17"/>
-    <mergeCell ref="K38:K39"/>
-    <mergeCell ref="E37:G37"/>
-    <mergeCell ref="L16:R19"/>
-    <mergeCell ref="E29:K30"/>
-    <mergeCell ref="Q33:R33"/>
-    <mergeCell ref="B22:C24"/>
-    <mergeCell ref="M38:M39"/>
-    <mergeCell ref="E16:I19"/>
-    <mergeCell ref="N33:O33"/>
-    <mergeCell ref="I37:J37"/>
-    <mergeCell ref="B42:B51"/>
-    <mergeCell ref="R51:T51"/>
-    <mergeCell ref="N28:O28"/>
-    <mergeCell ref="N26:O26"/>
-    <mergeCell ref="O54:O55"/>
-    <mergeCell ref="B29:D31"/>
-    <mergeCell ref="B1:C5"/>
-    <mergeCell ref="Q36:R36"/>
-    <mergeCell ref="B18:C19"/>
-    <mergeCell ref="L56:M56"/>
-    <mergeCell ref="B8:C9"/>
-    <mergeCell ref="N34:O34"/>
-    <mergeCell ref="L49:M49"/>
-    <mergeCell ref="G53:H54"/>
-    <mergeCell ref="N42:N44"/>
-    <mergeCell ref="N27:O27"/>
-    <mergeCell ref="D3:D5"/>
-    <mergeCell ref="E53:F55"/>
-    <mergeCell ref="N36:O36"/>
-    <mergeCell ref="E47:F47"/>
-    <mergeCell ref="E8:F10"/>
-    <mergeCell ref="G8:H10"/>
-    <mergeCell ref="E11:F11"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="D6:D7"/>
-    <mergeCell ref="K8:K11"/>
-    <mergeCell ref="D10:D11"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="D36:K36"/>
-    <mergeCell ref="Q38:R38"/>
-    <mergeCell ref="B6:C7"/>
-    <mergeCell ref="L55:M55"/>
-    <mergeCell ref="O43:O44"/>
-    <mergeCell ref="L51:M51"/>
-    <mergeCell ref="B12:C13"/>
-    <mergeCell ref="K12:K15"/>
-    <mergeCell ref="L27:L29"/>
-    <mergeCell ref="B34:K35"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="D18:D19"/>
-    <mergeCell ref="D8:D9"/>
-    <mergeCell ref="I6:J6"/>
-    <mergeCell ref="I7:J7"/>
-    <mergeCell ref="E6:H7"/>
-    <mergeCell ref="B10:C11"/>
-    <mergeCell ref="I8:J11"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="3.9370078740157501E-2" right="3.9370078740157501E-2" top="0.35433070866141703" bottom="0.35433070866141703" header="0.118110236220472" footer="0.118110236220472"/>

--- a/jo.xlsx
+++ b/jo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\production_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DF0DA8C-3AE5-4398-84DE-75683CFF7302}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AD6FAC3-B365-4BD8-ABBD-7CBAED4CB922}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -397,7 +397,7 @@
     <t>I10111-I10121</t>
   </si>
   <si>
-    <t>H248 MAIN RHD</t>
+    <t>H248 MAIN LHD</t>
   </si>
 </sst>
 </file>
@@ -2256,22 +2256,334 @@
     </xf>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="62" xfId="0" applyBorder="1"/>
+    <xf numFmtId="14" fontId="44" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="33" fillId="0" borderId="65" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="71" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="72" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="68" fillId="0" borderId="20" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="64" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="64" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="42" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="55" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="24" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="55" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="41" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="17" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="24" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="51" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="52" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="53" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="61" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="34" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="35" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="40" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="57" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="36" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="37" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="50" fillId="0" borderId="34" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="50" fillId="0" borderId="35" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="50" fillId="0" borderId="40" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="50" fillId="0" borderId="57" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="50" fillId="0" borderId="36" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="50" fillId="0" borderId="37" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="45" fillId="0" borderId="31" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="60" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="62" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="48" fillId="0" borderId="54" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="34" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="42" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="40" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="36" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="44" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="50" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="68" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="38" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="57" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="20" xfId="26" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="44" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="43" fontId="60" fillId="0" borderId="5" xfId="26" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2292,17 +2604,6 @@
     </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2319,28 +2620,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="60" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="34" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="42" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="41" fillId="0" borderId="43" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="40" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="41" fillId="0" borderId="41" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="36" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="44" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="41" fillId="0" borderId="45" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2354,11 +2637,6 @@
     <xf numFmtId="0" fontId="56" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="56" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="56" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="48" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2376,7 +2654,6 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="63" fillId="7" borderId="65" xfId="26" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2389,283 +2666,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="34" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="44" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="50" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="68" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="55" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="38" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="57" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="60" fillId="0" borderId="5" xfId="26" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="20" xfId="26" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="60" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="62" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="52" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="53" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="48" fillId="0" borderId="54" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="45" fillId="0" borderId="31" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="51" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="61" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="34" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="35" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="40" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="57" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="36" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="37" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="50" fillId="0" borderId="34" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="50" fillId="0" borderId="35" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="50" fillId="0" borderId="40" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="50" fillId="0" borderId="57" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="50" fillId="0" borderId="36" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="50" fillId="0" borderId="37" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="59" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="59" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="44" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="33" fillId="0" borderId="65" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="71" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="72" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="68" fillId="0" borderId="20" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="64" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="64" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="42" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="24" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="55" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="41" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="17" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="24" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="29">
     <cellStyle name="Comma" xfId="26" builtinId="3"/>
@@ -3009,72 +3009,72 @@
       <c r="A1" s="1">
         <v>24</v>
       </c>
-      <c r="B1" s="274"/>
-      <c r="C1" s="275"/>
-      <c r="D1" s="301" t="s">
+      <c r="B1" s="201"/>
+      <c r="C1" s="202"/>
+      <c r="D1" s="148" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="181" t="s">
+      <c r="E1" s="298" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="182"/>
-      <c r="G1" s="182"/>
-      <c r="H1" s="182"/>
-      <c r="I1" s="182"/>
-      <c r="J1" s="182"/>
-      <c r="K1" s="182"/>
-      <c r="L1" s="182"/>
-      <c r="M1" s="182"/>
-      <c r="N1" s="183"/>
-      <c r="O1" s="194" t="s">
+      <c r="F1" s="299"/>
+      <c r="G1" s="299"/>
+      <c r="H1" s="299"/>
+      <c r="I1" s="299"/>
+      <c r="J1" s="299"/>
+      <c r="K1" s="299"/>
+      <c r="L1" s="299"/>
+      <c r="M1" s="299"/>
+      <c r="N1" s="300"/>
+      <c r="O1" s="308" t="s">
         <v>2</v>
       </c>
-      <c r="P1" s="195"/>
-      <c r="Q1" s="195"/>
-      <c r="R1" s="195"/>
-      <c r="S1" s="195"/>
-      <c r="T1" s="195"/>
-      <c r="U1" s="196"/>
-      <c r="V1" s="165"/>
+      <c r="P1" s="309"/>
+      <c r="Q1" s="309"/>
+      <c r="R1" s="309"/>
+      <c r="S1" s="309"/>
+      <c r="T1" s="309"/>
+      <c r="U1" s="310"/>
+      <c r="V1" s="288"/>
     </row>
     <row r="2" spans="1:22" s="1" customFormat="1" ht="18.75" customHeight="1">
-      <c r="B2" s="268"/>
-      <c r="C2" s="149"/>
-      <c r="D2" s="300"/>
-      <c r="E2" s="184"/>
-      <c r="F2" s="185"/>
-      <c r="G2" s="185"/>
-      <c r="H2" s="185"/>
-      <c r="I2" s="185"/>
-      <c r="J2" s="185"/>
-      <c r="K2" s="185"/>
-      <c r="L2" s="185"/>
-      <c r="M2" s="185"/>
-      <c r="N2" s="186"/>
-      <c r="O2" s="197"/>
-      <c r="P2" s="198"/>
-      <c r="Q2" s="198"/>
-      <c r="R2" s="198"/>
-      <c r="S2" s="198"/>
-      <c r="T2" s="198"/>
-      <c r="U2" s="199"/>
-      <c r="V2" s="165"/>
+      <c r="B2" s="199"/>
+      <c r="C2" s="181"/>
+      <c r="D2" s="147"/>
+      <c r="E2" s="301"/>
+      <c r="F2" s="302"/>
+      <c r="G2" s="302"/>
+      <c r="H2" s="302"/>
+      <c r="I2" s="302"/>
+      <c r="J2" s="302"/>
+      <c r="K2" s="302"/>
+      <c r="L2" s="302"/>
+      <c r="M2" s="302"/>
+      <c r="N2" s="303"/>
+      <c r="O2" s="311"/>
+      <c r="P2" s="312"/>
+      <c r="Q2" s="312"/>
+      <c r="R2" s="312"/>
+      <c r="S2" s="312"/>
+      <c r="T2" s="312"/>
+      <c r="U2" s="313"/>
+      <c r="V2" s="288"/>
     </row>
     <row r="3" spans="1:22" ht="12.45" customHeight="1">
-      <c r="B3" s="268"/>
-      <c r="C3" s="149"/>
-      <c r="D3" s="258" t="s">
+      <c r="B3" s="199"/>
+      <c r="C3" s="181"/>
+      <c r="D3" s="208" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="200" t="s">
+      <c r="E3" s="314" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="145"/>
-      <c r="G3" s="145"/>
-      <c r="H3" s="145"/>
-      <c r="I3" s="145"/>
-      <c r="J3" s="145"/>
-      <c r="K3" s="145"/>
+      <c r="F3" s="150"/>
+      <c r="G3" s="150"/>
+      <c r="H3" s="150"/>
+      <c r="I3" s="150"/>
+      <c r="J3" s="150"/>
+      <c r="K3" s="150"/>
       <c r="L3" s="125"/>
       <c r="M3" s="5"/>
       <c r="N3" s="5"/>
@@ -3085,151 +3085,151 @@
       <c r="S3" s="5"/>
       <c r="T3" s="5"/>
       <c r="U3" s="126"/>
-      <c r="V3" s="165"/>
+      <c r="V3" s="288"/>
     </row>
     <row r="4" spans="1:22" ht="14.85" customHeight="1">
-      <c r="B4" s="268"/>
-      <c r="C4" s="149"/>
-      <c r="D4" s="187"/>
-      <c r="E4" s="147"/>
-      <c r="F4" s="148"/>
-      <c r="G4" s="148"/>
-      <c r="H4" s="148"/>
-      <c r="I4" s="148"/>
-      <c r="J4" s="148"/>
-      <c r="K4" s="201"/>
+      <c r="B4" s="199"/>
+      <c r="C4" s="181"/>
+      <c r="D4" s="205"/>
+      <c r="E4" s="162"/>
+      <c r="F4" s="200"/>
+      <c r="G4" s="200"/>
+      <c r="H4" s="200"/>
+      <c r="I4" s="200"/>
+      <c r="J4" s="200"/>
+      <c r="K4" s="180"/>
       <c r="L4" s="127"/>
       <c r="U4" s="128"/>
-      <c r="V4" s="165"/>
+      <c r="V4" s="288"/>
     </row>
     <row r="5" spans="1:22" ht="14.85" customHeight="1">
-      <c r="B5" s="226"/>
-      <c r="C5" s="152"/>
-      <c r="D5" s="188"/>
-      <c r="E5" s="150"/>
-      <c r="F5" s="151"/>
-      <c r="G5" s="151"/>
-      <c r="H5" s="151"/>
-      <c r="I5" s="151"/>
-      <c r="J5" s="151"/>
-      <c r="K5" s="151"/>
+      <c r="B5" s="154"/>
+      <c r="C5" s="155"/>
+      <c r="D5" s="142"/>
+      <c r="E5" s="163"/>
+      <c r="F5" s="168"/>
+      <c r="G5" s="168"/>
+      <c r="H5" s="168"/>
+      <c r="I5" s="168"/>
+      <c r="J5" s="168"/>
+      <c r="K5" s="168"/>
       <c r="L5" s="127"/>
       <c r="U5" s="128"/>
-      <c r="V5" s="165"/>
+      <c r="V5" s="288"/>
     </row>
     <row r="6" spans="1:22" s="2" customFormat="1" ht="27.75" customHeight="1">
-      <c r="B6" s="239" t="s">
+      <c r="B6" s="153" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="146"/>
-      <c r="D6" s="295"/>
-      <c r="E6" s="315" t="s">
+      <c r="C6" s="151"/>
+      <c r="D6" s="141"/>
+      <c r="E6" s="179" t="s">
         <v>6</v>
       </c>
-      <c r="F6" s="145"/>
-      <c r="G6" s="145"/>
-      <c r="H6" s="146"/>
-      <c r="I6" s="313" t="s">
+      <c r="F6" s="150"/>
+      <c r="G6" s="150"/>
+      <c r="H6" s="151"/>
+      <c r="I6" s="177" t="s">
         <v>7</v>
       </c>
-      <c r="J6" s="162"/>
+      <c r="J6" s="157"/>
       <c r="K6" s="100" t="s">
         <v>8</v>
       </c>
       <c r="L6" s="127"/>
       <c r="U6" s="128"/>
-      <c r="V6" s="165"/>
+      <c r="V6" s="288"/>
     </row>
     <row r="7" spans="1:22" s="2" customFormat="1" ht="28.5" customHeight="1">
-      <c r="B7" s="226"/>
-      <c r="C7" s="152"/>
-      <c r="D7" s="188"/>
-      <c r="E7" s="147"/>
-      <c r="F7" s="201"/>
-      <c r="G7" s="201"/>
-      <c r="H7" s="149"/>
-      <c r="I7" s="314"/>
-      <c r="J7" s="162"/>
+      <c r="B7" s="154"/>
+      <c r="C7" s="155"/>
+      <c r="D7" s="142"/>
+      <c r="E7" s="162"/>
+      <c r="F7" s="180"/>
+      <c r="G7" s="180"/>
+      <c r="H7" s="181"/>
+      <c r="I7" s="178"/>
+      <c r="J7" s="157"/>
       <c r="K7" s="101"/>
       <c r="L7" s="127"/>
       <c r="P7" s="131"/>
       <c r="U7" s="128"/>
-      <c r="V7" s="165"/>
+      <c r="V7" s="288"/>
     </row>
     <row r="8" spans="1:22" s="2" customFormat="1" ht="31.95" customHeight="1">
-      <c r="B8" s="239" t="s">
+      <c r="B8" s="153" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="146"/>
-      <c r="D8" s="312"/>
-      <c r="E8" s="279" t="s">
+      <c r="C8" s="151"/>
+      <c r="D8" s="176"/>
+      <c r="E8" s="211" t="s">
         <v>101</v>
       </c>
-      <c r="F8" s="280"/>
-      <c r="G8" s="285" t="s">
+      <c r="F8" s="212"/>
+      <c r="G8" s="217" t="s">
         <v>100</v>
       </c>
-      <c r="H8" s="286"/>
-      <c r="I8" s="317" t="s">
+      <c r="H8" s="218"/>
+      <c r="I8" s="183" t="s">
         <v>103</v>
       </c>
-      <c r="J8" s="318"/>
-      <c r="K8" s="296"/>
+      <c r="J8" s="184"/>
+      <c r="K8" s="143"/>
       <c r="L8" s="127"/>
       <c r="P8" s="131"/>
       <c r="U8" s="128"/>
-      <c r="V8" s="165"/>
+      <c r="V8" s="288"/>
     </row>
     <row r="9" spans="1:22" s="2" customFormat="1" ht="3.75" hidden="1" customHeight="1">
-      <c r="B9" s="226"/>
-      <c r="C9" s="152"/>
-      <c r="D9" s="150"/>
-      <c r="E9" s="281"/>
-      <c r="F9" s="282"/>
-      <c r="G9" s="287"/>
-      <c r="H9" s="288"/>
-      <c r="I9" s="319"/>
-      <c r="J9" s="320"/>
-      <c r="K9" s="297"/>
+      <c r="B9" s="154"/>
+      <c r="C9" s="155"/>
+      <c r="D9" s="163"/>
+      <c r="E9" s="213"/>
+      <c r="F9" s="214"/>
+      <c r="G9" s="219"/>
+      <c r="H9" s="220"/>
+      <c r="I9" s="185"/>
+      <c r="J9" s="186"/>
+      <c r="K9" s="144"/>
       <c r="L9" s="127"/>
       <c r="P9" s="131" t="str">
         <f t="shared" ref="P9" si="0">"*"&amp;J18&amp;"*"</f>
         <v>**</v>
       </c>
       <c r="U9" s="128"/>
-      <c r="V9" s="165"/>
+      <c r="V9" s="288"/>
     </row>
     <row r="10" spans="1:22" s="2" customFormat="1" ht="15" customHeight="1">
-      <c r="B10" s="316" t="s">
+      <c r="B10" s="182" t="s">
         <v>11</v>
       </c>
-      <c r="C10" s="146"/>
-      <c r="D10" s="299"/>
-      <c r="E10" s="283"/>
-      <c r="F10" s="284"/>
-      <c r="G10" s="289"/>
-      <c r="H10" s="290"/>
-      <c r="I10" s="319"/>
-      <c r="J10" s="320"/>
-      <c r="K10" s="297"/>
+      <c r="C10" s="151"/>
+      <c r="D10" s="146"/>
+      <c r="E10" s="215"/>
+      <c r="F10" s="216"/>
+      <c r="G10" s="221"/>
+      <c r="H10" s="222"/>
+      <c r="I10" s="185"/>
+      <c r="J10" s="186"/>
+      <c r="K10" s="144"/>
       <c r="L10" s="127"/>
       <c r="P10" s="131"/>
       <c r="U10" s="128"/>
-      <c r="V10" s="165"/>
+      <c r="V10" s="288"/>
     </row>
     <row r="11" spans="1:22" s="2" customFormat="1" ht="78.599999999999994" customHeight="1">
-      <c r="B11" s="226"/>
-      <c r="C11" s="152"/>
-      <c r="D11" s="300"/>
-      <c r="E11" s="291"/>
-      <c r="F11" s="292"/>
-      <c r="G11" s="293" t="s">
+      <c r="B11" s="154"/>
+      <c r="C11" s="155"/>
+      <c r="D11" s="147"/>
+      <c r="E11" s="223"/>
+      <c r="F11" s="224"/>
+      <c r="G11" s="225" t="s">
         <v>109</v>
       </c>
-      <c r="H11" s="294"/>
-      <c r="I11" s="321"/>
-      <c r="J11" s="322"/>
-      <c r="K11" s="298"/>
+      <c r="H11" s="226"/>
+      <c r="I11" s="187"/>
+      <c r="J11" s="188"/>
+      <c r="K11" s="145"/>
       <c r="L11" s="127"/>
       <c r="M11" s="132" t="str">
         <f>"*"&amp;J16&amp;"*"</f>
@@ -3241,74 +3241,74 @@
       <c r="Q11" s="132"/>
       <c r="S11" s="133"/>
       <c r="U11" s="128"/>
-      <c r="V11" s="165"/>
+      <c r="V11" s="288"/>
     </row>
     <row r="12" spans="1:22" s="2" customFormat="1" ht="28.5" customHeight="1">
-      <c r="B12" s="303" t="s">
+      <c r="B12" s="160" t="s">
         <v>12</v>
       </c>
-      <c r="C12" s="146"/>
-      <c r="D12" s="241" t="s">
+      <c r="C12" s="151"/>
+      <c r="D12" s="277" t="s">
         <v>102</v>
       </c>
-      <c r="E12" s="224"/>
-      <c r="F12" s="145"/>
-      <c r="G12" s="145"/>
-      <c r="H12" s="146"/>
-      <c r="I12" s="211" t="s">
+      <c r="E12" s="276"/>
+      <c r="F12" s="150"/>
+      <c r="G12" s="150"/>
+      <c r="H12" s="151"/>
+      <c r="I12" s="266" t="s">
         <v>13</v>
       </c>
-      <c r="J12" s="212"/>
-      <c r="K12" s="304"/>
+      <c r="J12" s="267"/>
+      <c r="K12" s="161"/>
       <c r="L12" s="127"/>
       <c r="U12" s="128"/>
-      <c r="V12" s="165"/>
+      <c r="V12" s="288"/>
     </row>
     <row r="13" spans="1:22" s="2" customFormat="1" ht="13.5" customHeight="1">
-      <c r="B13" s="226"/>
-      <c r="C13" s="152"/>
-      <c r="D13" s="242"/>
-      <c r="E13" s="147"/>
-      <c r="F13" s="148"/>
-      <c r="G13" s="148"/>
-      <c r="H13" s="149"/>
-      <c r="I13" s="213"/>
-      <c r="J13" s="214"/>
-      <c r="K13" s="147"/>
+      <c r="B13" s="154"/>
+      <c r="C13" s="155"/>
+      <c r="D13" s="235"/>
+      <c r="E13" s="162"/>
+      <c r="F13" s="200"/>
+      <c r="G13" s="200"/>
+      <c r="H13" s="181"/>
+      <c r="I13" s="268"/>
+      <c r="J13" s="269"/>
+      <c r="K13" s="162"/>
       <c r="L13" s="127"/>
       <c r="U13" s="128"/>
-      <c r="V13" s="165"/>
+      <c r="V13" s="288"/>
     </row>
     <row r="14" spans="1:22" s="2" customFormat="1" ht="15" customHeight="1">
-      <c r="B14" s="225" t="s">
+      <c r="B14" s="252" t="s">
         <v>14</v>
       </c>
-      <c r="C14" s="146"/>
-      <c r="D14" s="250" t="s">
+      <c r="C14" s="151"/>
+      <c r="D14" s="234" t="s">
         <v>107</v>
       </c>
-      <c r="E14" s="147"/>
-      <c r="F14" s="148"/>
-      <c r="G14" s="148"/>
-      <c r="H14" s="149"/>
-      <c r="I14" s="213"/>
-      <c r="J14" s="214"/>
-      <c r="K14" s="147"/>
+      <c r="E14" s="162"/>
+      <c r="F14" s="200"/>
+      <c r="G14" s="200"/>
+      <c r="H14" s="181"/>
+      <c r="I14" s="268"/>
+      <c r="J14" s="269"/>
+      <c r="K14" s="162"/>
       <c r="L14" s="127"/>
       <c r="U14" s="128"/>
-      <c r="V14" s="165"/>
+      <c r="V14" s="288"/>
     </row>
     <row r="15" spans="1:22" s="2" customFormat="1" ht="48" customHeight="1">
-      <c r="B15" s="226"/>
-      <c r="C15" s="152"/>
-      <c r="D15" s="242"/>
-      <c r="E15" s="150"/>
-      <c r="F15" s="151"/>
-      <c r="G15" s="151"/>
-      <c r="H15" s="152"/>
-      <c r="I15" s="215"/>
-      <c r="J15" s="216"/>
-      <c r="K15" s="150"/>
+      <c r="B15" s="154"/>
+      <c r="C15" s="155"/>
+      <c r="D15" s="235"/>
+      <c r="E15" s="163"/>
+      <c r="F15" s="168"/>
+      <c r="G15" s="168"/>
+      <c r="H15" s="155"/>
+      <c r="I15" s="270"/>
+      <c r="J15" s="271"/>
+      <c r="K15" s="163"/>
       <c r="L15" s="135"/>
       <c r="M15" s="129"/>
       <c r="N15" s="134"/>
@@ -3319,152 +3319,152 @@
       <c r="S15" s="129"/>
       <c r="T15" s="129"/>
       <c r="U15" s="130"/>
-      <c r="V15" s="165"/>
+      <c r="V15" s="288"/>
     </row>
     <row r="16" spans="1:22" s="2" customFormat="1" ht="15" customHeight="1">
-      <c r="B16" s="239" t="s">
+      <c r="B16" s="153" t="s">
         <v>15</v>
       </c>
-      <c r="C16" s="146"/>
-      <c r="D16" s="251"/>
-      <c r="E16" s="240" t="s">
+      <c r="C16" s="151"/>
+      <c r="D16" s="236"/>
+      <c r="E16" s="250" t="s">
         <v>16</v>
       </c>
-      <c r="F16" s="145"/>
-      <c r="G16" s="145"/>
-      <c r="H16" s="145"/>
-      <c r="I16" s="146"/>
-      <c r="J16" s="245">
+      <c r="F16" s="150"/>
+      <c r="G16" s="150"/>
+      <c r="H16" s="150"/>
+      <c r="I16" s="151"/>
+      <c r="J16" s="263">
         <v>232323</v>
       </c>
-      <c r="K16" s="235"/>
-      <c r="L16" s="172" t="s">
+      <c r="K16" s="259"/>
+      <c r="L16" s="242" t="s">
         <v>104</v>
       </c>
-      <c r="M16" s="173"/>
-      <c r="N16" s="173"/>
-      <c r="O16" s="173"/>
-      <c r="P16" s="173"/>
-      <c r="Q16" s="173"/>
-      <c r="R16" s="173"/>
-      <c r="S16" s="172" t="s">
+      <c r="M16" s="243"/>
+      <c r="N16" s="243"/>
+      <c r="O16" s="243"/>
+      <c r="P16" s="243"/>
+      <c r="Q16" s="243"/>
+      <c r="R16" s="243"/>
+      <c r="S16" s="242" t="s">
         <v>105</v>
       </c>
-      <c r="T16" s="173"/>
-      <c r="U16" s="174"/>
-      <c r="V16" s="165"/>
+      <c r="T16" s="243"/>
+      <c r="U16" s="295"/>
+      <c r="V16" s="288"/>
     </row>
     <row r="17" spans="2:22" s="2" customFormat="1" ht="15" customHeight="1">
-      <c r="B17" s="226"/>
-      <c r="C17" s="152"/>
-      <c r="D17" s="242"/>
-      <c r="E17" s="147"/>
-      <c r="F17" s="148"/>
-      <c r="G17" s="148"/>
-      <c r="H17" s="148"/>
-      <c r="I17" s="149"/>
-      <c r="J17" s="147"/>
-      <c r="K17" s="246"/>
-      <c r="L17" s="175"/>
-      <c r="M17" s="176"/>
-      <c r="N17" s="176"/>
-      <c r="O17" s="176"/>
-      <c r="P17" s="176"/>
-      <c r="Q17" s="176"/>
-      <c r="R17" s="176"/>
-      <c r="S17" s="175"/>
-      <c r="T17" s="176"/>
-      <c r="U17" s="177"/>
-      <c r="V17" s="165"/>
+      <c r="B17" s="154"/>
+      <c r="C17" s="155"/>
+      <c r="D17" s="235"/>
+      <c r="E17" s="162"/>
+      <c r="F17" s="200"/>
+      <c r="G17" s="200"/>
+      <c r="H17" s="200"/>
+      <c r="I17" s="181"/>
+      <c r="J17" s="162"/>
+      <c r="K17" s="264"/>
+      <c r="L17" s="244"/>
+      <c r="M17" s="245"/>
+      <c r="N17" s="245"/>
+      <c r="O17" s="245"/>
+      <c r="P17" s="245"/>
+      <c r="Q17" s="245"/>
+      <c r="R17" s="245"/>
+      <c r="S17" s="244"/>
+      <c r="T17" s="245"/>
+      <c r="U17" s="296"/>
+      <c r="V17" s="288"/>
     </row>
     <row r="18" spans="2:22" s="2" customFormat="1" ht="15" customHeight="1">
-      <c r="B18" s="276" t="s">
+      <c r="B18" s="203" t="s">
         <v>17</v>
       </c>
-      <c r="C18" s="146"/>
-      <c r="D18" s="310" t="s">
+      <c r="C18" s="151"/>
+      <c r="D18" s="174" t="s">
         <v>110</v>
       </c>
-      <c r="E18" s="147"/>
-      <c r="F18" s="148"/>
-      <c r="G18" s="148"/>
-      <c r="H18" s="148"/>
-      <c r="I18" s="149"/>
-      <c r="J18" s="147"/>
-      <c r="K18" s="246"/>
-      <c r="L18" s="175"/>
-      <c r="M18" s="176"/>
-      <c r="N18" s="176"/>
-      <c r="O18" s="176"/>
-      <c r="P18" s="176"/>
-      <c r="Q18" s="176"/>
-      <c r="R18" s="176"/>
-      <c r="S18" s="175"/>
-      <c r="T18" s="176"/>
-      <c r="U18" s="177"/>
-      <c r="V18" s="165"/>
+      <c r="E18" s="162"/>
+      <c r="F18" s="200"/>
+      <c r="G18" s="200"/>
+      <c r="H18" s="200"/>
+      <c r="I18" s="181"/>
+      <c r="J18" s="162"/>
+      <c r="K18" s="264"/>
+      <c r="L18" s="244"/>
+      <c r="M18" s="245"/>
+      <c r="N18" s="245"/>
+      <c r="O18" s="245"/>
+      <c r="P18" s="245"/>
+      <c r="Q18" s="245"/>
+      <c r="R18" s="245"/>
+      <c r="S18" s="244"/>
+      <c r="T18" s="245"/>
+      <c r="U18" s="296"/>
+      <c r="V18" s="288"/>
     </row>
     <row r="19" spans="2:22" s="2" customFormat="1" ht="15" customHeight="1">
-      <c r="B19" s="226"/>
-      <c r="C19" s="152"/>
-      <c r="D19" s="311"/>
-      <c r="E19" s="150"/>
-      <c r="F19" s="151"/>
-      <c r="G19" s="151"/>
-      <c r="H19" s="151"/>
-      <c r="I19" s="152"/>
-      <c r="J19" s="150"/>
-      <c r="K19" s="237"/>
-      <c r="L19" s="178"/>
-      <c r="M19" s="179"/>
-      <c r="N19" s="179"/>
-      <c r="O19" s="179"/>
-      <c r="P19" s="179"/>
-      <c r="Q19" s="179"/>
-      <c r="R19" s="179"/>
-      <c r="S19" s="178"/>
-      <c r="T19" s="179"/>
-      <c r="U19" s="180"/>
-      <c r="V19" s="165"/>
+      <c r="B19" s="154"/>
+      <c r="C19" s="155"/>
+      <c r="D19" s="175"/>
+      <c r="E19" s="163"/>
+      <c r="F19" s="168"/>
+      <c r="G19" s="168"/>
+      <c r="H19" s="168"/>
+      <c r="I19" s="155"/>
+      <c r="J19" s="163"/>
+      <c r="K19" s="261"/>
+      <c r="L19" s="246"/>
+      <c r="M19" s="247"/>
+      <c r="N19" s="247"/>
+      <c r="O19" s="247"/>
+      <c r="P19" s="247"/>
+      <c r="Q19" s="247"/>
+      <c r="R19" s="247"/>
+      <c r="S19" s="246"/>
+      <c r="T19" s="247"/>
+      <c r="U19" s="297"/>
+      <c r="V19" s="288"/>
     </row>
     <row r="20" spans="2:22" s="2" customFormat="1" ht="15" customHeight="1">
-      <c r="B20" s="239" t="s">
+      <c r="B20" s="153" t="s">
         <v>18</v>
       </c>
-      <c r="C20" s="146"/>
-      <c r="D20" s="249"/>
-      <c r="E20" s="240" t="s">
+      <c r="C20" s="151"/>
+      <c r="D20" s="265"/>
+      <c r="E20" s="250" t="s">
         <v>106</v>
       </c>
-      <c r="F20" s="145"/>
-      <c r="G20" s="145"/>
-      <c r="H20" s="145"/>
-      <c r="I20" s="146"/>
-      <c r="J20" s="234"/>
-      <c r="K20" s="235"/>
-      <c r="L20" s="227"/>
-      <c r="M20" s="228"/>
-      <c r="N20" s="228"/>
-      <c r="O20" s="228"/>
-      <c r="P20" s="228"/>
-      <c r="Q20" s="228"/>
-      <c r="R20" s="228"/>
-      <c r="S20" s="228"/>
-      <c r="T20" s="228"/>
-      <c r="U20" s="228"/>
-      <c r="V20" s="165"/>
+      <c r="F20" s="150"/>
+      <c r="G20" s="150"/>
+      <c r="H20" s="150"/>
+      <c r="I20" s="151"/>
+      <c r="J20" s="258"/>
+      <c r="K20" s="259"/>
+      <c r="L20" s="253"/>
+      <c r="M20" s="254"/>
+      <c r="N20" s="254"/>
+      <c r="O20" s="254"/>
+      <c r="P20" s="254"/>
+      <c r="Q20" s="254"/>
+      <c r="R20" s="254"/>
+      <c r="S20" s="254"/>
+      <c r="T20" s="254"/>
+      <c r="U20" s="254"/>
+      <c r="V20" s="288"/>
     </row>
     <row r="21" spans="2:22" s="2" customFormat="1" ht="62.4" customHeight="1">
-      <c r="B21" s="226"/>
-      <c r="C21" s="152"/>
-      <c r="D21" s="188"/>
-      <c r="E21" s="147"/>
-      <c r="F21" s="148"/>
-      <c r="G21" s="148"/>
-      <c r="H21" s="148"/>
-      <c r="I21" s="149"/>
-      <c r="J21" s="147"/>
-      <c r="K21" s="236"/>
+      <c r="B21" s="154"/>
+      <c r="C21" s="155"/>
+      <c r="D21" s="142"/>
+      <c r="E21" s="162"/>
+      <c r="F21" s="200"/>
+      <c r="G21" s="200"/>
+      <c r="H21" s="200"/>
+      <c r="I21" s="181"/>
+      <c r="J21" s="162"/>
+      <c r="K21" s="260"/>
       <c r="L21" s="120"/>
       <c r="M21" s="121"/>
       <c r="N21" s="121"/>
@@ -3475,85 +3475,85 @@
       <c r="S21" s="123"/>
       <c r="T21" s="121"/>
       <c r="U21" s="122"/>
-      <c r="V21" s="165"/>
+      <c r="V21" s="288"/>
     </row>
     <row r="22" spans="2:22" s="2" customFormat="1" ht="15" customHeight="1">
-      <c r="B22" s="239" t="s">
+      <c r="B22" s="153" t="s">
         <v>19</v>
       </c>
-      <c r="C22" s="146"/>
-      <c r="D22" s="217"/>
-      <c r="E22" s="147"/>
-      <c r="F22" s="148"/>
-      <c r="G22" s="148"/>
-      <c r="H22" s="148"/>
-      <c r="I22" s="149"/>
-      <c r="J22" s="147"/>
-      <c r="K22" s="236"/>
-      <c r="L22" s="153"/>
-      <c r="M22" s="153"/>
-      <c r="N22" s="153"/>
-      <c r="O22" s="153"/>
-      <c r="P22" s="153"/>
-      <c r="Q22" s="153"/>
-      <c r="R22" s="153"/>
-      <c r="S22" s="153"/>
-      <c r="T22" s="153"/>
-      <c r="U22" s="154"/>
-      <c r="V22" s="165"/>
+      <c r="C22" s="151"/>
+      <c r="D22" s="272"/>
+      <c r="E22" s="162"/>
+      <c r="F22" s="200"/>
+      <c r="G22" s="200"/>
+      <c r="H22" s="200"/>
+      <c r="I22" s="181"/>
+      <c r="J22" s="162"/>
+      <c r="K22" s="260"/>
+      <c r="L22" s="281"/>
+      <c r="M22" s="281"/>
+      <c r="N22" s="281"/>
+      <c r="O22" s="281"/>
+      <c r="P22" s="281"/>
+      <c r="Q22" s="281"/>
+      <c r="R22" s="281"/>
+      <c r="S22" s="281"/>
+      <c r="T22" s="281"/>
+      <c r="U22" s="282"/>
+      <c r="V22" s="288"/>
     </row>
     <row r="23" spans="2:22" s="2" customFormat="1" ht="15" customHeight="1">
-      <c r="B23" s="268"/>
-      <c r="C23" s="149"/>
-      <c r="D23" s="187"/>
-      <c r="E23" s="147"/>
-      <c r="F23" s="148"/>
-      <c r="G23" s="148"/>
-      <c r="H23" s="148"/>
-      <c r="I23" s="149"/>
-      <c r="J23" s="147"/>
-      <c r="K23" s="236"/>
-      <c r="L23" s="155"/>
-      <c r="M23" s="155"/>
-      <c r="N23" s="155"/>
-      <c r="O23" s="155"/>
-      <c r="P23" s="155"/>
-      <c r="Q23" s="155"/>
-      <c r="R23" s="155"/>
-      <c r="S23" s="155"/>
-      <c r="T23" s="155"/>
-      <c r="U23" s="156"/>
-      <c r="V23" s="165"/>
+      <c r="B23" s="199"/>
+      <c r="C23" s="181"/>
+      <c r="D23" s="205"/>
+      <c r="E23" s="162"/>
+      <c r="F23" s="200"/>
+      <c r="G23" s="200"/>
+      <c r="H23" s="200"/>
+      <c r="I23" s="181"/>
+      <c r="J23" s="162"/>
+      <c r="K23" s="260"/>
+      <c r="L23" s="283"/>
+      <c r="M23" s="283"/>
+      <c r="N23" s="283"/>
+      <c r="O23" s="283"/>
+      <c r="P23" s="283"/>
+      <c r="Q23" s="283"/>
+      <c r="R23" s="283"/>
+      <c r="S23" s="283"/>
+      <c r="T23" s="283"/>
+      <c r="U23" s="284"/>
+      <c r="V23" s="288"/>
     </row>
     <row r="24" spans="2:22" s="2" customFormat="1" ht="7.5" customHeight="1">
-      <c r="B24" s="226"/>
-      <c r="C24" s="152"/>
-      <c r="D24" s="188"/>
-      <c r="E24" s="150"/>
-      <c r="F24" s="151"/>
-      <c r="G24" s="151"/>
-      <c r="H24" s="151"/>
-      <c r="I24" s="152"/>
-      <c r="J24" s="150"/>
-      <c r="K24" s="237"/>
-      <c r="L24" s="157"/>
-      <c r="M24" s="157"/>
-      <c r="N24" s="157"/>
-      <c r="O24" s="157"/>
-      <c r="P24" s="157"/>
-      <c r="Q24" s="157"/>
-      <c r="R24" s="157"/>
-      <c r="S24" s="157"/>
-      <c r="T24" s="157"/>
-      <c r="U24" s="158"/>
-      <c r="V24" s="165"/>
+      <c r="B24" s="154"/>
+      <c r="C24" s="155"/>
+      <c r="D24" s="142"/>
+      <c r="E24" s="163"/>
+      <c r="F24" s="168"/>
+      <c r="G24" s="168"/>
+      <c r="H24" s="168"/>
+      <c r="I24" s="155"/>
+      <c r="J24" s="163"/>
+      <c r="K24" s="261"/>
+      <c r="L24" s="285"/>
+      <c r="M24" s="285"/>
+      <c r="N24" s="285"/>
+      <c r="O24" s="285"/>
+      <c r="P24" s="285"/>
+      <c r="Q24" s="285"/>
+      <c r="R24" s="285"/>
+      <c r="S24" s="285"/>
+      <c r="T24" s="285"/>
+      <c r="U24" s="286"/>
+      <c r="V24" s="288"/>
     </row>
     <row r="25" spans="2:22" s="2" customFormat="1" ht="30" customHeight="1">
-      <c r="B25" s="244" t="s">
+      <c r="B25" s="262" t="s">
         <v>20</v>
       </c>
-      <c r="C25" s="145"/>
-      <c r="D25" s="146"/>
+      <c r="C25" s="150"/>
+      <c r="D25" s="151"/>
       <c r="E25" s="3" t="s">
         <v>21</v>
       </c>
@@ -3569,21 +3569,21 @@
       <c r="K25" s="102" t="s">
         <v>24</v>
       </c>
-      <c r="L25" s="229" t="s">
+      <c r="L25" s="197" t="s">
         <v>25</v>
       </c>
-      <c r="M25" s="149"/>
-      <c r="N25" s="210" t="s">
+      <c r="M25" s="181"/>
+      <c r="N25" s="233" t="s">
         <v>26</v>
       </c>
-      <c r="O25" s="149"/>
+      <c r="O25" s="181"/>
       <c r="P25" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="Q25" s="210" t="s">
+      <c r="Q25" s="233" t="s">
         <v>28</v>
       </c>
-      <c r="R25" s="149"/>
+      <c r="R25" s="181"/>
       <c r="S25" s="7" t="s">
         <v>29</v>
       </c>
@@ -3593,12 +3593,12 @@
       <c r="U25" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="V25" s="165"/>
+      <c r="V25" s="288"/>
     </row>
     <row r="26" spans="2:22" s="2" customFormat="1" ht="39" customHeight="1">
-      <c r="B26" s="226"/>
-      <c r="C26" s="151"/>
-      <c r="D26" s="152"/>
+      <c r="B26" s="154"/>
+      <c r="C26" s="168"/>
+      <c r="D26" s="155"/>
       <c r="E26" s="10"/>
       <c r="F26" s="11"/>
       <c r="G26" s="12"/>
@@ -3606,19 +3606,19 @@
       <c r="I26" s="12"/>
       <c r="J26" s="11"/>
       <c r="K26" s="13"/>
-      <c r="L26" s="150"/>
-      <c r="M26" s="152"/>
-      <c r="N26" s="229" t="s">
+      <c r="L26" s="163"/>
+      <c r="M26" s="155"/>
+      <c r="N26" s="197" t="s">
         <v>31</v>
       </c>
-      <c r="O26" s="152"/>
+      <c r="O26" s="155"/>
       <c r="P26" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="Q26" s="229" t="s">
+      <c r="Q26" s="197" t="s">
         <v>33</v>
       </c>
-      <c r="R26" s="152"/>
+      <c r="R26" s="155"/>
       <c r="S26" s="14" t="s">
         <v>34</v>
       </c>
@@ -3628,14 +3628,14 @@
       <c r="U26" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="V26" s="165"/>
+      <c r="V26" s="288"/>
     </row>
     <row r="27" spans="2:22" s="2" customFormat="1" ht="46.05" customHeight="1">
-      <c r="B27" s="244" t="s">
+      <c r="B27" s="262" t="s">
         <v>36</v>
       </c>
-      <c r="C27" s="145"/>
-      <c r="D27" s="146"/>
+      <c r="C27" s="150"/>
+      <c r="D27" s="151"/>
       <c r="E27" s="3" t="s">
         <v>21</v>
       </c>
@@ -3649,26 +3649,26 @@
       </c>
       <c r="J27" s="5"/>
       <c r="K27" s="6"/>
-      <c r="L27" s="305" t="s">
+      <c r="L27" s="164" t="s">
         <v>39</v>
       </c>
       <c r="M27" s="118" t="s">
         <v>9</v>
       </c>
-      <c r="N27" s="277"/>
-      <c r="O27" s="278"/>
+      <c r="N27" s="206"/>
+      <c r="O27" s="207"/>
       <c r="P27" s="92"/>
-      <c r="Q27" s="223"/>
-      <c r="R27" s="162"/>
+      <c r="Q27" s="256"/>
+      <c r="R27" s="157"/>
       <c r="S27" s="17"/>
       <c r="T27" s="18"/>
       <c r="U27" s="19"/>
-      <c r="V27" s="165"/>
+      <c r="V27" s="288"/>
     </row>
     <row r="28" spans="2:22" s="2" customFormat="1" ht="46.05" customHeight="1">
-      <c r="B28" s="226"/>
-      <c r="C28" s="151"/>
-      <c r="D28" s="152"/>
+      <c r="B28" s="154"/>
+      <c r="C28" s="168"/>
+      <c r="D28" s="155"/>
       <c r="E28" s="20"/>
       <c r="F28" s="21"/>
       <c r="G28" s="21"/>
@@ -3676,64 +3676,64 @@
       <c r="I28" s="22"/>
       <c r="J28" s="22"/>
       <c r="K28" s="23"/>
-      <c r="L28" s="231"/>
+      <c r="L28" s="165"/>
       <c r="M28" s="118" t="s">
         <v>40</v>
       </c>
-      <c r="N28" s="247"/>
-      <c r="O28" s="248"/>
+      <c r="N28" s="195"/>
+      <c r="O28" s="196"/>
       <c r="P28" s="92"/>
-      <c r="Q28" s="223"/>
-      <c r="R28" s="162"/>
+      <c r="Q28" s="256"/>
+      <c r="R28" s="157"/>
       <c r="S28" s="17"/>
       <c r="T28" s="18"/>
       <c r="U28" s="19"/>
-      <c r="V28" s="165"/>
+      <c r="V28" s="288"/>
     </row>
     <row r="29" spans="2:22" s="2" customFormat="1" ht="46.5" customHeight="1">
-      <c r="B29" s="273" t="s">
+      <c r="B29" s="198" t="s">
         <v>41</v>
       </c>
-      <c r="C29" s="145"/>
-      <c r="D29" s="146"/>
-      <c r="E29" s="238" t="s">
+      <c r="C29" s="150"/>
+      <c r="D29" s="151"/>
+      <c r="E29" s="248" t="s">
         <v>42</v>
       </c>
-      <c r="F29" s="145"/>
-      <c r="G29" s="145"/>
-      <c r="H29" s="145"/>
-      <c r="I29" s="145"/>
-      <c r="J29" s="145"/>
-      <c r="K29" s="146"/>
-      <c r="L29" s="232"/>
+      <c r="F29" s="150"/>
+      <c r="G29" s="150"/>
+      <c r="H29" s="150"/>
+      <c r="I29" s="150"/>
+      <c r="J29" s="150"/>
+      <c r="K29" s="151"/>
+      <c r="L29" s="166"/>
       <c r="M29" s="119" t="s">
         <v>43</v>
       </c>
-      <c r="N29" s="247"/>
-      <c r="O29" s="248"/>
+      <c r="N29" s="195"/>
+      <c r="O29" s="196"/>
       <c r="P29" s="93"/>
-      <c r="Q29" s="223"/>
-      <c r="R29" s="162"/>
+      <c r="Q29" s="256"/>
+      <c r="R29" s="157"/>
       <c r="S29" s="25"/>
       <c r="T29" s="5"/>
       <c r="U29" s="26"/>
-      <c r="V29" s="165"/>
+      <c r="V29" s="288"/>
     </row>
     <row r="30" spans="2:22" s="2" customFormat="1" ht="15" customHeight="1">
-      <c r="B30" s="268"/>
-      <c r="C30" s="148"/>
-      <c r="D30" s="149"/>
-      <c r="E30" s="150"/>
-      <c r="F30" s="151"/>
-      <c r="G30" s="151"/>
-      <c r="H30" s="151"/>
-      <c r="I30" s="151"/>
-      <c r="J30" s="151"/>
-      <c r="K30" s="152"/>
-      <c r="L30" s="230" t="s">
+      <c r="B30" s="199"/>
+      <c r="C30" s="200"/>
+      <c r="D30" s="181"/>
+      <c r="E30" s="163"/>
+      <c r="F30" s="168"/>
+      <c r="G30" s="168"/>
+      <c r="H30" s="168"/>
+      <c r="I30" s="168"/>
+      <c r="J30" s="168"/>
+      <c r="K30" s="155"/>
+      <c r="L30" s="255" t="s">
         <v>44</v>
       </c>
-      <c r="M30" s="243" t="s">
+      <c r="M30" s="232" t="s">
         <v>45</v>
       </c>
       <c r="N30" s="27"/>
@@ -3744,269 +3744,269 @@
       <c r="S30" s="30"/>
       <c r="T30" s="30"/>
       <c r="U30" s="26"/>
-      <c r="V30" s="165"/>
+      <c r="V30" s="288"/>
     </row>
     <row r="31" spans="2:22" s="2" customFormat="1" ht="42" customHeight="1">
-      <c r="B31" s="226"/>
-      <c r="C31" s="151"/>
-      <c r="D31" s="152"/>
-      <c r="E31" s="238" t="s">
+      <c r="B31" s="154"/>
+      <c r="C31" s="168"/>
+      <c r="D31" s="155"/>
+      <c r="E31" s="248" t="s">
         <v>108</v>
       </c>
-      <c r="F31" s="161"/>
-      <c r="G31" s="161"/>
-      <c r="H31" s="161"/>
-      <c r="I31" s="161"/>
-      <c r="J31" s="161"/>
-      <c r="K31" s="162"/>
-      <c r="L31" s="231"/>
-      <c r="M31" s="188"/>
-      <c r="N31" s="233"/>
-      <c r="O31" s="152"/>
+      <c r="F31" s="170"/>
+      <c r="G31" s="170"/>
+      <c r="H31" s="170"/>
+      <c r="I31" s="170"/>
+      <c r="J31" s="170"/>
+      <c r="K31" s="157"/>
+      <c r="L31" s="165"/>
+      <c r="M31" s="142"/>
+      <c r="N31" s="257"/>
+      <c r="O31" s="155"/>
       <c r="P31" s="97"/>
-      <c r="Q31" s="188"/>
-      <c r="R31" s="152"/>
+      <c r="Q31" s="142"/>
+      <c r="R31" s="155"/>
       <c r="S31" s="31"/>
       <c r="T31" s="31"/>
       <c r="U31" s="32"/>
-      <c r="V31" s="165"/>
+      <c r="V31" s="288"/>
     </row>
     <row r="32" spans="2:22" s="2" customFormat="1" ht="21" customHeight="1">
-      <c r="B32" s="252" t="s">
+      <c r="B32" s="237" t="s">
         <v>46</v>
       </c>
-      <c r="C32" s="145"/>
-      <c r="D32" s="145"/>
-      <c r="E32" s="145"/>
-      <c r="F32" s="145"/>
-      <c r="G32" s="145"/>
-      <c r="H32" s="145"/>
-      <c r="I32" s="145"/>
-      <c r="J32" s="145"/>
-      <c r="K32" s="146"/>
-      <c r="L32" s="231"/>
-      <c r="M32" s="243" t="s">
+      <c r="C32" s="150"/>
+      <c r="D32" s="150"/>
+      <c r="E32" s="150"/>
+      <c r="F32" s="150"/>
+      <c r="G32" s="150"/>
+      <c r="H32" s="150"/>
+      <c r="I32" s="150"/>
+      <c r="J32" s="150"/>
+      <c r="K32" s="151"/>
+      <c r="L32" s="165"/>
+      <c r="M32" s="232" t="s">
         <v>47</v>
       </c>
-      <c r="N32" s="209"/>
-      <c r="O32" s="146"/>
+      <c r="N32" s="322"/>
+      <c r="O32" s="151"/>
       <c r="P32" s="96"/>
-      <c r="Q32" s="221"/>
-      <c r="R32" s="146"/>
+      <c r="Q32" s="152"/>
+      <c r="R32" s="151"/>
       <c r="S32" s="33"/>
       <c r="T32" s="33"/>
       <c r="U32" s="34"/>
-      <c r="V32" s="165"/>
+      <c r="V32" s="288"/>
     </row>
     <row r="33" spans="1:22" s="2" customFormat="1" ht="21" customHeight="1">
-      <c r="B33" s="226"/>
-      <c r="C33" s="151"/>
-      <c r="D33" s="151"/>
-      <c r="E33" s="151"/>
-      <c r="F33" s="151"/>
-      <c r="G33" s="151"/>
-      <c r="H33" s="151"/>
-      <c r="I33" s="151"/>
-      <c r="J33" s="151"/>
-      <c r="K33" s="152"/>
-      <c r="L33" s="231"/>
-      <c r="M33" s="188"/>
-      <c r="N33" s="269"/>
-      <c r="O33" s="152"/>
+      <c r="B33" s="154"/>
+      <c r="C33" s="168"/>
+      <c r="D33" s="168"/>
+      <c r="E33" s="168"/>
+      <c r="F33" s="168"/>
+      <c r="G33" s="168"/>
+      <c r="H33" s="168"/>
+      <c r="I33" s="168"/>
+      <c r="J33" s="168"/>
+      <c r="K33" s="155"/>
+      <c r="L33" s="165"/>
+      <c r="M33" s="142"/>
+      <c r="N33" s="251"/>
+      <c r="O33" s="155"/>
       <c r="P33" s="99"/>
-      <c r="Q33" s="267"/>
-      <c r="R33" s="152"/>
+      <c r="Q33" s="249"/>
+      <c r="R33" s="155"/>
       <c r="S33" s="36"/>
       <c r="T33" s="36"/>
       <c r="U33" s="32"/>
-      <c r="V33" s="165"/>
+      <c r="V33" s="288"/>
     </row>
     <row r="34" spans="1:22" s="2" customFormat="1" ht="21" customHeight="1">
-      <c r="B34" s="306" t="s">
+      <c r="B34" s="167" t="s">
         <v>48</v>
       </c>
-      <c r="C34" s="145"/>
-      <c r="D34" s="145"/>
-      <c r="E34" s="145"/>
-      <c r="F34" s="145"/>
-      <c r="G34" s="145"/>
-      <c r="H34" s="145"/>
-      <c r="I34" s="145"/>
-      <c r="J34" s="145"/>
-      <c r="K34" s="146"/>
-      <c r="L34" s="231"/>
-      <c r="M34" s="243" t="s">
+      <c r="C34" s="150"/>
+      <c r="D34" s="150"/>
+      <c r="E34" s="150"/>
+      <c r="F34" s="150"/>
+      <c r="G34" s="150"/>
+      <c r="H34" s="150"/>
+      <c r="I34" s="150"/>
+      <c r="J34" s="150"/>
+      <c r="K34" s="151"/>
+      <c r="L34" s="165"/>
+      <c r="M34" s="232" t="s">
         <v>49</v>
       </c>
-      <c r="N34" s="221"/>
-      <c r="O34" s="146"/>
+      <c r="N34" s="152"/>
+      <c r="O34" s="151"/>
       <c r="P34" s="24"/>
-      <c r="Q34" s="221"/>
-      <c r="R34" s="146"/>
+      <c r="Q34" s="152"/>
+      <c r="R34" s="151"/>
       <c r="S34" s="25"/>
       <c r="T34" s="25"/>
       <c r="U34" s="26"/>
-      <c r="V34" s="165"/>
+      <c r="V34" s="288"/>
     </row>
     <row r="35" spans="1:22" s="2" customFormat="1" ht="21" customHeight="1">
-      <c r="B35" s="226"/>
-      <c r="C35" s="151"/>
-      <c r="D35" s="151"/>
-      <c r="E35" s="151"/>
-      <c r="F35" s="151"/>
-      <c r="G35" s="151"/>
-      <c r="H35" s="151"/>
-      <c r="I35" s="151"/>
-      <c r="J35" s="151"/>
-      <c r="K35" s="152"/>
-      <c r="L35" s="231"/>
-      <c r="M35" s="188"/>
-      <c r="N35" s="188"/>
-      <c r="O35" s="152"/>
+      <c r="B35" s="154"/>
+      <c r="C35" s="168"/>
+      <c r="D35" s="168"/>
+      <c r="E35" s="168"/>
+      <c r="F35" s="168"/>
+      <c r="G35" s="168"/>
+      <c r="H35" s="168"/>
+      <c r="I35" s="168"/>
+      <c r="J35" s="168"/>
+      <c r="K35" s="155"/>
+      <c r="L35" s="165"/>
+      <c r="M35" s="142"/>
+      <c r="N35" s="142"/>
+      <c r="O35" s="155"/>
       <c r="P35" s="35"/>
-      <c r="Q35" s="188"/>
-      <c r="R35" s="152"/>
+      <c r="Q35" s="142"/>
+      <c r="R35" s="155"/>
       <c r="S35" s="36"/>
       <c r="T35" s="36"/>
       <c r="U35" s="32"/>
-      <c r="V35" s="165"/>
+      <c r="V35" s="288"/>
     </row>
     <row r="36" spans="1:22" s="2" customFormat="1" ht="21" customHeight="1">
       <c r="B36" s="37" t="s">
         <v>50</v>
       </c>
       <c r="C36" s="38"/>
-      <c r="D36" s="302"/>
-      <c r="E36" s="145"/>
-      <c r="F36" s="145"/>
-      <c r="G36" s="145"/>
-      <c r="H36" s="145"/>
-      <c r="I36" s="145"/>
-      <c r="J36" s="145"/>
-      <c r="K36" s="146"/>
-      <c r="L36" s="231"/>
-      <c r="M36" s="243" t="s">
+      <c r="D36" s="149"/>
+      <c r="E36" s="150"/>
+      <c r="F36" s="150"/>
+      <c r="G36" s="150"/>
+      <c r="H36" s="150"/>
+      <c r="I36" s="150"/>
+      <c r="J36" s="150"/>
+      <c r="K36" s="151"/>
+      <c r="L36" s="165"/>
+      <c r="M36" s="232" t="s">
         <v>51</v>
       </c>
-      <c r="N36" s="221"/>
-      <c r="O36" s="146"/>
+      <c r="N36" s="152"/>
+      <c r="O36" s="151"/>
       <c r="P36" s="24"/>
-      <c r="Q36" s="221"/>
-      <c r="R36" s="146"/>
+      <c r="Q36" s="152"/>
+      <c r="R36" s="151"/>
       <c r="S36" s="25"/>
       <c r="T36" s="25"/>
       <c r="U36" s="26"/>
-      <c r="V36" s="165"/>
+      <c r="V36" s="288"/>
     </row>
     <row r="37" spans="1:22" s="2" customFormat="1" ht="49.2" customHeight="1">
-      <c r="B37" s="307" t="s">
+      <c r="B37" s="169" t="s">
         <v>52</v>
       </c>
-      <c r="C37" s="161"/>
+      <c r="C37" s="170"/>
       <c r="D37" s="124" t="s">
         <v>53</v>
       </c>
-      <c r="E37" s="265" t="s">
+      <c r="E37" s="241" t="s">
         <v>54</v>
       </c>
-      <c r="F37" s="161"/>
-      <c r="G37" s="266"/>
+      <c r="F37" s="170"/>
+      <c r="G37" s="172"/>
       <c r="H37" s="113" t="s">
         <v>55</v>
       </c>
-      <c r="I37" s="270" t="s">
+      <c r="I37" s="189" t="s">
         <v>56</v>
       </c>
-      <c r="J37" s="271"/>
+      <c r="J37" s="190"/>
       <c r="K37" s="114" t="s">
         <v>57</v>
       </c>
-      <c r="L37" s="231"/>
-      <c r="M37" s="188"/>
-      <c r="N37" s="188"/>
-      <c r="O37" s="152"/>
+      <c r="L37" s="165"/>
+      <c r="M37" s="142"/>
+      <c r="N37" s="142"/>
+      <c r="O37" s="155"/>
       <c r="P37" s="35"/>
-      <c r="Q37" s="188"/>
-      <c r="R37" s="152"/>
+      <c r="Q37" s="142"/>
+      <c r="R37" s="155"/>
       <c r="S37" s="36"/>
       <c r="T37" s="36"/>
       <c r="U37" s="32"/>
-      <c r="V37" s="165"/>
+      <c r="V37" s="288"/>
     </row>
     <row r="38" spans="1:22" s="2" customFormat="1" ht="24.6" customHeight="1">
-      <c r="B38" s="309"/>
-      <c r="C38" s="266"/>
-      <c r="D38" s="259"/>
-      <c r="E38" s="202"/>
-      <c r="F38" s="203"/>
-      <c r="G38" s="204"/>
-      <c r="H38" s="253"/>
-      <c r="I38" s="190"/>
-      <c r="J38" s="191"/>
-      <c r="K38" s="263"/>
-      <c r="L38" s="231"/>
-      <c r="M38" s="243" t="s">
+      <c r="B38" s="173"/>
+      <c r="C38" s="172"/>
+      <c r="D38" s="238"/>
+      <c r="E38" s="315"/>
+      <c r="F38" s="316"/>
+      <c r="G38" s="317"/>
+      <c r="H38" s="227"/>
+      <c r="I38" s="304"/>
+      <c r="J38" s="305"/>
+      <c r="K38" s="230"/>
+      <c r="L38" s="165"/>
+      <c r="M38" s="232" t="s">
         <v>58</v>
       </c>
-      <c r="N38" s="221"/>
-      <c r="O38" s="146"/>
+      <c r="N38" s="152"/>
+      <c r="O38" s="151"/>
       <c r="P38" s="24"/>
-      <c r="Q38" s="221"/>
-      <c r="R38" s="146"/>
+      <c r="Q38" s="152"/>
+      <c r="R38" s="151"/>
       <c r="S38" s="25"/>
       <c r="T38" s="25"/>
       <c r="U38" s="26"/>
-      <c r="V38" s="165"/>
+      <c r="V38" s="288"/>
     </row>
     <row r="39" spans="1:22" s="2" customFormat="1" ht="22.95" customHeight="1">
-      <c r="B39" s="308"/>
-      <c r="C39" s="266"/>
-      <c r="D39" s="260"/>
-      <c r="E39" s="205"/>
-      <c r="F39" s="206"/>
-      <c r="G39" s="207"/>
-      <c r="H39" s="254"/>
-      <c r="I39" s="192"/>
-      <c r="J39" s="193"/>
-      <c r="K39" s="264"/>
-      <c r="L39" s="231"/>
-      <c r="M39" s="188"/>
-      <c r="N39" s="188"/>
-      <c r="O39" s="152"/>
+      <c r="B39" s="171"/>
+      <c r="C39" s="172"/>
+      <c r="D39" s="239"/>
+      <c r="E39" s="318"/>
+      <c r="F39" s="319"/>
+      <c r="G39" s="320"/>
+      <c r="H39" s="228"/>
+      <c r="I39" s="306"/>
+      <c r="J39" s="307"/>
+      <c r="K39" s="231"/>
+      <c r="L39" s="165"/>
+      <c r="M39" s="142"/>
+      <c r="N39" s="142"/>
+      <c r="O39" s="155"/>
       <c r="P39" s="35"/>
-      <c r="Q39" s="188"/>
-      <c r="R39" s="152"/>
+      <c r="Q39" s="142"/>
+      <c r="R39" s="155"/>
       <c r="S39" s="36"/>
       <c r="T39" s="36"/>
       <c r="U39" s="32"/>
-      <c r="V39" s="165"/>
+      <c r="V39" s="288"/>
     </row>
     <row r="40" spans="1:22" s="2" customFormat="1" ht="29.25" customHeight="1">
       <c r="A40" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="B40" s="262"/>
-      <c r="C40" s="161"/>
-      <c r="D40" s="162"/>
-      <c r="E40" s="220"/>
-      <c r="F40" s="161"/>
-      <c r="G40" s="162"/>
-      <c r="H40" s="218"/>
-      <c r="I40" s="152"/>
+      <c r="B40" s="240"/>
+      <c r="C40" s="170"/>
+      <c r="D40" s="157"/>
+      <c r="E40" s="274"/>
+      <c r="F40" s="170"/>
+      <c r="G40" s="157"/>
+      <c r="H40" s="273"/>
+      <c r="I40" s="155"/>
       <c r="K40" s="98"/>
-      <c r="L40" s="231"/>
-      <c r="M40" s="243" t="s">
+      <c r="L40" s="165"/>
+      <c r="M40" s="232" t="s">
         <v>60</v>
       </c>
-      <c r="N40" s="221"/>
-      <c r="O40" s="146"/>
+      <c r="N40" s="152"/>
+      <c r="O40" s="151"/>
       <c r="P40" s="24"/>
-      <c r="Q40" s="221"/>
-      <c r="R40" s="146"/>
+      <c r="Q40" s="152"/>
+      <c r="R40" s="151"/>
       <c r="S40" s="25"/>
       <c r="T40" s="25"/>
       <c r="U40" s="26"/>
-      <c r="V40" s="165"/>
+      <c r="V40" s="288"/>
     </row>
     <row r="41" spans="1:22" s="2" customFormat="1" ht="21" customHeight="1">
       <c r="B41" s="39"/>
@@ -4021,143 +4021,143 @@
       <c r="I41" s="40"/>
       <c r="J41" s="90"/>
       <c r="K41" s="95"/>
-      <c r="L41" s="232"/>
-      <c r="M41" s="188"/>
-      <c r="N41" s="188"/>
-      <c r="O41" s="152"/>
+      <c r="L41" s="166"/>
+      <c r="M41" s="142"/>
+      <c r="N41" s="142"/>
+      <c r="O41" s="155"/>
       <c r="P41" s="35"/>
-      <c r="Q41" s="188"/>
-      <c r="R41" s="152"/>
+      <c r="Q41" s="142"/>
+      <c r="R41" s="155"/>
       <c r="S41" s="36"/>
       <c r="T41" s="36"/>
       <c r="U41" s="32"/>
-      <c r="V41" s="165"/>
+      <c r="V41" s="288"/>
     </row>
     <row r="42" spans="1:22" ht="18" customHeight="1">
-      <c r="B42" s="255" t="s">
+      <c r="B42" s="191" t="s">
         <v>62</v>
       </c>
       <c r="C42" s="41"/>
       <c r="D42" s="41"/>
-      <c r="E42" s="163" t="s">
+      <c r="E42" s="209" t="s">
         <v>63</v>
       </c>
-      <c r="F42" s="146"/>
-      <c r="G42" s="258" t="s">
+      <c r="F42" s="151"/>
+      <c r="G42" s="208" t="s">
         <v>64</v>
       </c>
-      <c r="H42" s="146"/>
-      <c r="I42" s="144" t="s">
+      <c r="H42" s="151"/>
+      <c r="I42" s="204" t="s">
         <v>65</v>
       </c>
       <c r="J42" s="94" t="s">
         <v>66</v>
       </c>
-      <c r="K42" s="258" t="s">
+      <c r="K42" s="208" t="s">
         <v>67</v>
       </c>
-      <c r="L42" s="145"/>
-      <c r="M42" s="146"/>
-      <c r="N42" s="144" t="s">
+      <c r="L42" s="150"/>
+      <c r="M42" s="151"/>
+      <c r="N42" s="204" t="s">
         <v>68</v>
       </c>
       <c r="O42" s="42" t="s">
         <v>66</v>
       </c>
-      <c r="P42" s="144" t="s">
+      <c r="P42" s="204" t="s">
         <v>69</v>
       </c>
       <c r="Q42" s="41"/>
-      <c r="R42" s="144" t="s">
+      <c r="R42" s="204" t="s">
         <v>70</v>
       </c>
-      <c r="S42" s="145"/>
-      <c r="T42" s="146"/>
-      <c r="U42" s="141" t="s">
+      <c r="S42" s="150"/>
+      <c r="T42" s="151"/>
+      <c r="U42" s="278" t="s">
         <v>71</v>
       </c>
-      <c r="V42" s="165"/>
+      <c r="V42" s="288"/>
     </row>
     <row r="43" spans="1:22" ht="50.4" customHeight="1">
-      <c r="B43" s="256"/>
+      <c r="B43" s="192"/>
       <c r="C43" s="94" t="s">
         <v>72</v>
       </c>
       <c r="D43" s="116" t="s">
         <v>73</v>
       </c>
-      <c r="E43" s="147"/>
-      <c r="F43" s="149"/>
-      <c r="G43" s="150"/>
-      <c r="H43" s="152"/>
-      <c r="I43" s="187"/>
-      <c r="J43" s="261" t="s">
+      <c r="E43" s="162"/>
+      <c r="F43" s="181"/>
+      <c r="G43" s="163"/>
+      <c r="H43" s="155"/>
+      <c r="I43" s="205"/>
+      <c r="J43" s="229" t="s">
         <v>74</v>
       </c>
-      <c r="K43" s="150"/>
-      <c r="L43" s="151"/>
-      <c r="M43" s="152"/>
-      <c r="N43" s="187"/>
-      <c r="O43" s="272" t="s">
+      <c r="K43" s="163"/>
+      <c r="L43" s="168"/>
+      <c r="M43" s="155"/>
+      <c r="N43" s="205"/>
+      <c r="O43" s="158" t="s">
         <v>74</v>
       </c>
-      <c r="P43" s="187"/>
+      <c r="P43" s="205"/>
       <c r="Q43" s="43" t="s">
         <v>75</v>
       </c>
-      <c r="R43" s="147"/>
-      <c r="S43" s="148"/>
-      <c r="T43" s="149"/>
-      <c r="U43" s="142"/>
-      <c r="V43" s="165"/>
+      <c r="R43" s="162"/>
+      <c r="S43" s="200"/>
+      <c r="T43" s="181"/>
+      <c r="U43" s="279"/>
+      <c r="V43" s="288"/>
     </row>
     <row r="44" spans="1:22" ht="55.5" customHeight="1">
-      <c r="B44" s="256"/>
+      <c r="B44" s="192"/>
       <c r="C44" s="110" t="s">
         <v>76</v>
       </c>
       <c r="D44" s="109" t="s">
         <v>77</v>
       </c>
-      <c r="E44" s="150"/>
-      <c r="F44" s="152"/>
+      <c r="E44" s="163"/>
+      <c r="F44" s="155"/>
       <c r="G44" s="45" t="s">
         <v>78</v>
       </c>
       <c r="H44" s="72" t="s">
         <v>79</v>
       </c>
-      <c r="I44" s="188"/>
-      <c r="J44" s="188"/>
+      <c r="I44" s="142"/>
+      <c r="J44" s="142"/>
       <c r="K44" s="115" t="s">
         <v>80</v>
       </c>
-      <c r="L44" s="208" t="s">
+      <c r="L44" s="321" t="s">
         <v>79</v>
       </c>
-      <c r="M44" s="162"/>
-      <c r="N44" s="188"/>
-      <c r="O44" s="188"/>
-      <c r="P44" s="188"/>
+      <c r="M44" s="157"/>
+      <c r="N44" s="142"/>
+      <c r="O44" s="142"/>
+      <c r="P44" s="142"/>
       <c r="Q44" s="46" t="s">
         <v>81</v>
       </c>
-      <c r="R44" s="150"/>
-      <c r="S44" s="151"/>
-      <c r="T44" s="152"/>
-      <c r="U44" s="143"/>
-      <c r="V44" s="165"/>
+      <c r="R44" s="163"/>
+      <c r="S44" s="168"/>
+      <c r="T44" s="155"/>
+      <c r="U44" s="280"/>
+      <c r="V44" s="288"/>
     </row>
     <row r="45" spans="1:22" ht="50.1" customHeight="1">
-      <c r="B45" s="256"/>
+      <c r="B45" s="192"/>
       <c r="C45" s="111">
         <v>1</v>
       </c>
       <c r="D45" s="105" t="s">
         <v>82</v>
       </c>
-      <c r="E45" s="189"/>
-      <c r="F45" s="162"/>
+      <c r="E45" s="210"/>
+      <c r="F45" s="157"/>
       <c r="G45" s="49" t="s">
         <v>83</v>
       </c>
@@ -4167,28 +4167,28 @@
       <c r="K45" s="49" t="s">
         <v>83</v>
       </c>
-      <c r="L45" s="219"/>
-      <c r="M45" s="162"/>
+      <c r="L45" s="159"/>
+      <c r="M45" s="157"/>
       <c r="N45" s="52"/>
       <c r="O45" s="52"/>
       <c r="P45" s="53"/>
       <c r="Q45" s="54"/>
-      <c r="R45" s="160"/>
-      <c r="S45" s="161"/>
-      <c r="T45" s="162"/>
+      <c r="R45" s="194"/>
+      <c r="S45" s="170"/>
+      <c r="T45" s="157"/>
       <c r="U45" s="57"/>
-      <c r="V45" s="165"/>
+      <c r="V45" s="288"/>
     </row>
     <row r="46" spans="1:22" ht="50.1" customHeight="1">
-      <c r="B46" s="256"/>
+      <c r="B46" s="192"/>
       <c r="C46" s="112">
         <v>2</v>
       </c>
       <c r="D46" s="106" t="s">
         <v>84</v>
       </c>
-      <c r="E46" s="189"/>
-      <c r="F46" s="162"/>
+      <c r="E46" s="210"/>
+      <c r="F46" s="157"/>
       <c r="G46" s="49" t="s">
         <v>83</v>
       </c>
@@ -4198,28 +4198,28 @@
       <c r="K46" s="49" t="s">
         <v>83</v>
       </c>
-      <c r="L46" s="219"/>
-      <c r="M46" s="162"/>
+      <c r="L46" s="159"/>
+      <c r="M46" s="157"/>
       <c r="N46" s="50"/>
       <c r="O46" s="50"/>
       <c r="P46" s="60"/>
       <c r="Q46" s="61"/>
-      <c r="R46" s="160"/>
-      <c r="S46" s="161"/>
-      <c r="T46" s="162"/>
+      <c r="R46" s="194"/>
+      <c r="S46" s="170"/>
+      <c r="T46" s="157"/>
       <c r="U46" s="57"/>
-      <c r="V46" s="165"/>
+      <c r="V46" s="288"/>
     </row>
     <row r="47" spans="1:22" ht="50.1" customHeight="1">
-      <c r="B47" s="256"/>
+      <c r="B47" s="192"/>
       <c r="C47" s="112">
         <v>3</v>
       </c>
       <c r="D47" s="106" t="s">
         <v>85</v>
       </c>
-      <c r="E47" s="189"/>
-      <c r="F47" s="162"/>
+      <c r="E47" s="210"/>
+      <c r="F47" s="157"/>
       <c r="G47" s="49" t="s">
         <v>83</v>
       </c>
@@ -4229,28 +4229,28 @@
       <c r="K47" s="49" t="s">
         <v>83</v>
       </c>
-      <c r="L47" s="219"/>
-      <c r="M47" s="162"/>
+      <c r="L47" s="159"/>
+      <c r="M47" s="157"/>
       <c r="N47" s="50"/>
       <c r="O47" s="50"/>
       <c r="P47" s="53"/>
       <c r="Q47" s="61"/>
-      <c r="R47" s="160"/>
-      <c r="S47" s="161"/>
-      <c r="T47" s="162"/>
+      <c r="R47" s="194"/>
+      <c r="S47" s="170"/>
+      <c r="T47" s="157"/>
       <c r="U47" s="57"/>
-      <c r="V47" s="165"/>
+      <c r="V47" s="288"/>
     </row>
     <row r="48" spans="1:22" ht="50.1" customHeight="1">
-      <c r="B48" s="256"/>
+      <c r="B48" s="192"/>
       <c r="C48" s="112">
         <v>4</v>
       </c>
       <c r="D48" s="106" t="s">
         <v>86</v>
       </c>
-      <c r="E48" s="189"/>
-      <c r="F48" s="162"/>
+      <c r="E48" s="210"/>
+      <c r="F48" s="157"/>
       <c r="G48" s="49" t="s">
         <v>83</v>
       </c>
@@ -4260,28 +4260,28 @@
       <c r="K48" s="49" t="s">
         <v>83</v>
       </c>
-      <c r="L48" s="219"/>
-      <c r="M48" s="162"/>
+      <c r="L48" s="159"/>
+      <c r="M48" s="157"/>
       <c r="N48" s="50"/>
       <c r="O48" s="50"/>
       <c r="P48" s="53"/>
       <c r="Q48" s="61"/>
-      <c r="R48" s="160"/>
-      <c r="S48" s="161"/>
-      <c r="T48" s="162"/>
+      <c r="R48" s="194"/>
+      <c r="S48" s="170"/>
+      <c r="T48" s="157"/>
       <c r="U48" s="57"/>
-      <c r="V48" s="165"/>
+      <c r="V48" s="288"/>
     </row>
     <row r="49" spans="2:23" ht="50.1" customHeight="1">
-      <c r="B49" s="256"/>
+      <c r="B49" s="192"/>
       <c r="C49" s="112">
         <v>5</v>
       </c>
       <c r="D49" s="107" t="s">
         <v>87</v>
       </c>
-      <c r="E49" s="189"/>
-      <c r="F49" s="162"/>
+      <c r="E49" s="210"/>
+      <c r="F49" s="157"/>
       <c r="G49" s="49" t="s">
         <v>83</v>
       </c>
@@ -4291,28 +4291,28 @@
       <c r="K49" s="49" t="s">
         <v>83</v>
       </c>
-      <c r="L49" s="219"/>
-      <c r="M49" s="162"/>
+      <c r="L49" s="159"/>
+      <c r="M49" s="157"/>
       <c r="N49" s="50"/>
       <c r="O49" s="50"/>
       <c r="P49" s="53"/>
       <c r="Q49" s="61"/>
-      <c r="R49" s="160"/>
-      <c r="S49" s="161"/>
-      <c r="T49" s="162"/>
+      <c r="R49" s="194"/>
+      <c r="S49" s="170"/>
+      <c r="T49" s="157"/>
       <c r="U49" s="57"/>
-      <c r="V49" s="165"/>
+      <c r="V49" s="288"/>
     </row>
     <row r="50" spans="2:23" ht="53.4" customHeight="1">
-      <c r="B50" s="256"/>
+      <c r="B50" s="192"/>
       <c r="C50" s="112">
         <v>6</v>
       </c>
       <c r="D50" s="108" t="s">
         <v>88</v>
       </c>
-      <c r="E50" s="189"/>
-      <c r="F50" s="162"/>
+      <c r="E50" s="210"/>
+      <c r="F50" s="157"/>
       <c r="G50" s="49" t="s">
         <v>83</v>
       </c>
@@ -4322,28 +4322,28 @@
       <c r="K50" s="49" t="s">
         <v>83</v>
       </c>
-      <c r="L50" s="219"/>
-      <c r="M50" s="162"/>
+      <c r="L50" s="159"/>
+      <c r="M50" s="157"/>
       <c r="N50" s="50"/>
       <c r="O50" s="50"/>
       <c r="P50" s="53"/>
       <c r="Q50" s="61"/>
-      <c r="R50" s="160"/>
-      <c r="S50" s="161"/>
-      <c r="T50" s="162"/>
+      <c r="R50" s="194"/>
+      <c r="S50" s="170"/>
+      <c r="T50" s="157"/>
       <c r="U50" s="57"/>
-      <c r="V50" s="165"/>
+      <c r="V50" s="288"/>
     </row>
     <row r="51" spans="2:23" ht="50.1" customHeight="1">
-      <c r="B51" s="257"/>
+      <c r="B51" s="193"/>
       <c r="C51" s="111">
         <v>7</v>
       </c>
       <c r="D51" s="108" t="s">
         <v>89</v>
       </c>
-      <c r="E51" s="189"/>
-      <c r="F51" s="162"/>
+      <c r="E51" s="210"/>
+      <c r="F51" s="157"/>
       <c r="G51" s="49" t="s">
         <v>83</v>
       </c>
@@ -4353,17 +4353,17 @@
       <c r="K51" s="49" t="s">
         <v>83</v>
       </c>
-      <c r="L51" s="219"/>
-      <c r="M51" s="162"/>
+      <c r="L51" s="159"/>
+      <c r="M51" s="157"/>
       <c r="N51" s="52"/>
       <c r="O51" s="52"/>
       <c r="P51" s="60"/>
       <c r="Q51" s="54"/>
-      <c r="R51" s="160"/>
-      <c r="S51" s="161"/>
-      <c r="T51" s="162"/>
+      <c r="R51" s="194"/>
+      <c r="S51" s="170"/>
+      <c r="T51" s="157"/>
       <c r="U51" s="57"/>
-      <c r="V51" s="165"/>
+      <c r="V51" s="288"/>
     </row>
     <row r="52" spans="2:23" ht="3.75" customHeight="1">
       <c r="B52" s="62"/>
@@ -4386,131 +4386,131 @@
       <c r="S52" s="63"/>
       <c r="T52" s="69"/>
       <c r="U52" s="70"/>
-      <c r="V52" s="165"/>
+      <c r="V52" s="288"/>
     </row>
     <row r="53" spans="2:23" ht="18" customHeight="1">
-      <c r="B53" s="255" t="s">
+      <c r="B53" s="191" t="s">
         <v>90</v>
       </c>
       <c r="C53" s="71"/>
       <c r="D53" s="71"/>
-      <c r="E53" s="163" t="s">
+      <c r="E53" s="209" t="s">
         <v>63</v>
       </c>
-      <c r="F53" s="146"/>
-      <c r="G53" s="164" t="s">
+      <c r="F53" s="151"/>
+      <c r="G53" s="156" t="s">
         <v>91</v>
       </c>
-      <c r="H53" s="146"/>
-      <c r="I53" s="144" t="s">
+      <c r="H53" s="151"/>
+      <c r="I53" s="204" t="s">
         <v>92</v>
       </c>
-      <c r="J53" s="222" t="s">
+      <c r="J53" s="275" t="s">
         <v>93</v>
       </c>
-      <c r="K53" s="164" t="s">
+      <c r="K53" s="156" t="s">
         <v>67</v>
       </c>
-      <c r="L53" s="145"/>
-      <c r="M53" s="146"/>
-      <c r="N53" s="144" t="s">
+      <c r="L53" s="150"/>
+      <c r="M53" s="151"/>
+      <c r="N53" s="204" t="s">
         <v>68</v>
       </c>
       <c r="O53" s="42" t="s">
         <v>66</v>
       </c>
-      <c r="P53" s="144" t="s">
+      <c r="P53" s="204" t="s">
         <v>69</v>
       </c>
       <c r="Q53" s="41"/>
-      <c r="R53" s="144" t="s">
+      <c r="R53" s="204" t="s">
         <v>70</v>
       </c>
-      <c r="S53" s="145"/>
-      <c r="T53" s="146"/>
-      <c r="U53" s="159" t="s">
+      <c r="S53" s="150"/>
+      <c r="T53" s="151"/>
+      <c r="U53" s="287" t="s">
         <v>71</v>
       </c>
-      <c r="V53" s="165"/>
+      <c r="V53" s="288"/>
     </row>
     <row r="54" spans="2:23" ht="50.4" customHeight="1">
-      <c r="B54" s="256"/>
+      <c r="B54" s="192"/>
       <c r="C54" s="41" t="s">
         <v>72</v>
       </c>
       <c r="D54" s="41" t="s">
         <v>73</v>
       </c>
-      <c r="E54" s="147"/>
-      <c r="F54" s="149"/>
-      <c r="G54" s="150"/>
-      <c r="H54" s="152"/>
-      <c r="I54" s="187"/>
-      <c r="J54" s="187"/>
-      <c r="K54" s="150"/>
-      <c r="L54" s="151"/>
-      <c r="M54" s="152"/>
-      <c r="N54" s="187"/>
-      <c r="O54" s="272" t="s">
+      <c r="E54" s="162"/>
+      <c r="F54" s="181"/>
+      <c r="G54" s="163"/>
+      <c r="H54" s="155"/>
+      <c r="I54" s="205"/>
+      <c r="J54" s="205"/>
+      <c r="K54" s="163"/>
+      <c r="L54" s="168"/>
+      <c r="M54" s="155"/>
+      <c r="N54" s="205"/>
+      <c r="O54" s="158" t="s">
         <v>74</v>
       </c>
-      <c r="P54" s="187"/>
+      <c r="P54" s="205"/>
       <c r="Q54" s="43" t="s">
         <v>75</v>
       </c>
-      <c r="R54" s="147"/>
-      <c r="S54" s="148"/>
-      <c r="T54" s="149"/>
-      <c r="U54" s="142"/>
-      <c r="V54" s="165"/>
+      <c r="R54" s="162"/>
+      <c r="S54" s="200"/>
+      <c r="T54" s="181"/>
+      <c r="U54" s="279"/>
+      <c r="V54" s="288"/>
     </row>
     <row r="55" spans="2:23" ht="50.4" customHeight="1">
-      <c r="B55" s="256"/>
+      <c r="B55" s="192"/>
       <c r="C55" s="44" t="s">
         <v>76</v>
       </c>
       <c r="D55" s="44" t="s">
         <v>77</v>
       </c>
-      <c r="E55" s="150"/>
-      <c r="F55" s="152"/>
+      <c r="E55" s="163"/>
+      <c r="F55" s="155"/>
       <c r="G55" s="45" t="s">
         <v>80</v>
       </c>
       <c r="H55" s="72" t="s">
         <v>79</v>
       </c>
-      <c r="I55" s="188"/>
-      <c r="J55" s="188"/>
+      <c r="I55" s="142"/>
+      <c r="J55" s="142"/>
       <c r="K55" s="45" t="s">
         <v>80</v>
       </c>
-      <c r="L55" s="164" t="s">
+      <c r="L55" s="156" t="s">
         <v>79</v>
       </c>
-      <c r="M55" s="162"/>
-      <c r="N55" s="188"/>
-      <c r="O55" s="188"/>
-      <c r="P55" s="188"/>
+      <c r="M55" s="157"/>
+      <c r="N55" s="142"/>
+      <c r="O55" s="142"/>
+      <c r="P55" s="142"/>
       <c r="Q55" s="46" t="s">
         <v>81</v>
       </c>
-      <c r="R55" s="150"/>
-      <c r="S55" s="151"/>
-      <c r="T55" s="152"/>
-      <c r="U55" s="143"/>
-      <c r="V55" s="165"/>
+      <c r="R55" s="163"/>
+      <c r="S55" s="168"/>
+      <c r="T55" s="155"/>
+      <c r="U55" s="280"/>
+      <c r="V55" s="288"/>
     </row>
     <row r="56" spans="2:23" ht="30" customHeight="1">
-      <c r="B56" s="256"/>
+      <c r="B56" s="192"/>
       <c r="C56" s="47">
         <v>1</v>
       </c>
       <c r="D56" s="48" t="s">
         <v>82</v>
       </c>
-      <c r="E56" s="189"/>
-      <c r="F56" s="162"/>
+      <c r="E56" s="210"/>
+      <c r="F56" s="157"/>
       <c r="G56" s="49" t="s">
         <v>83</v>
       </c>
@@ -4520,8 +4520,8 @@
       <c r="K56" s="49" t="s">
         <v>83</v>
       </c>
-      <c r="L56" s="219"/>
-      <c r="M56" s="162"/>
+      <c r="L56" s="159"/>
+      <c r="M56" s="157"/>
       <c r="N56" s="52"/>
       <c r="O56" s="52"/>
       <c r="P56" s="60"/>
@@ -4530,18 +4530,18 @@
       <c r="S56" s="56"/>
       <c r="T56" s="18"/>
       <c r="U56" s="57"/>
-      <c r="V56" s="165"/>
+      <c r="V56" s="288"/>
     </row>
     <row r="57" spans="2:23" ht="30" customHeight="1">
-      <c r="B57" s="256"/>
+      <c r="B57" s="192"/>
       <c r="C57" s="55">
         <v>2</v>
       </c>
       <c r="D57" s="74" t="s">
         <v>94</v>
       </c>
-      <c r="E57" s="189"/>
-      <c r="F57" s="162"/>
+      <c r="E57" s="210"/>
+      <c r="F57" s="157"/>
       <c r="G57" s="49" t="s">
         <v>83</v>
       </c>
@@ -4551,8 +4551,8 @@
       <c r="K57" s="49" t="s">
         <v>83</v>
       </c>
-      <c r="L57" s="219"/>
-      <c r="M57" s="162"/>
+      <c r="L57" s="159"/>
+      <c r="M57" s="157"/>
       <c r="N57" s="50"/>
       <c r="O57" s="50"/>
       <c r="P57" s="53"/>
@@ -4561,18 +4561,18 @@
       <c r="S57" s="56"/>
       <c r="T57" s="18"/>
       <c r="U57" s="57"/>
-      <c r="V57" s="165"/>
+      <c r="V57" s="288"/>
     </row>
     <row r="58" spans="2:23" ht="30" customHeight="1">
-      <c r="B58" s="256"/>
+      <c r="B58" s="192"/>
       <c r="C58" s="55">
         <v>3</v>
       </c>
       <c r="D58" s="76" t="s">
         <v>95</v>
       </c>
-      <c r="E58" s="189"/>
-      <c r="F58" s="162"/>
+      <c r="E58" s="210"/>
+      <c r="F58" s="157"/>
       <c r="G58" s="49" t="s">
         <v>83</v>
       </c>
@@ -4582,8 +4582,8 @@
       <c r="K58" s="49" t="s">
         <v>83</v>
       </c>
-      <c r="L58" s="219"/>
-      <c r="M58" s="162"/>
+      <c r="L58" s="159"/>
+      <c r="M58" s="157"/>
       <c r="N58" s="50"/>
       <c r="O58" s="50"/>
       <c r="P58" s="53"/>
@@ -4592,18 +4592,18 @@
       <c r="S58" s="56"/>
       <c r="T58" s="18"/>
       <c r="U58" s="57"/>
-      <c r="V58" s="165"/>
+      <c r="V58" s="288"/>
     </row>
     <row r="59" spans="2:23" ht="30" customHeight="1">
-      <c r="B59" s="256"/>
+      <c r="B59" s="192"/>
       <c r="C59" s="77">
         <v>4</v>
       </c>
       <c r="D59" s="78" t="s">
         <v>96</v>
       </c>
-      <c r="E59" s="189"/>
-      <c r="F59" s="162"/>
+      <c r="E59" s="210"/>
+      <c r="F59" s="157"/>
       <c r="G59" s="49" t="s">
         <v>83</v>
       </c>
@@ -4613,8 +4613,8 @@
       <c r="K59" s="58" t="s">
         <v>83</v>
       </c>
-      <c r="L59" s="219"/>
-      <c r="M59" s="162"/>
+      <c r="L59" s="159"/>
+      <c r="M59" s="157"/>
       <c r="N59" s="50"/>
       <c r="O59" s="50"/>
       <c r="P59" s="53"/>
@@ -4623,18 +4623,18 @@
       <c r="S59" s="56"/>
       <c r="T59" s="18"/>
       <c r="U59" s="57"/>
-      <c r="V59" s="165"/>
+      <c r="V59" s="288"/>
     </row>
     <row r="60" spans="2:23" ht="30" customHeight="1">
-      <c r="B60" s="256"/>
+      <c r="B60" s="192"/>
       <c r="C60" s="77">
         <v>5</v>
       </c>
       <c r="D60" s="78" t="s">
         <v>86</v>
       </c>
-      <c r="E60" s="189"/>
-      <c r="F60" s="162"/>
+      <c r="E60" s="210"/>
+      <c r="F60" s="157"/>
       <c r="G60" s="49" t="s">
         <v>83</v>
       </c>
@@ -4644,8 +4644,8 @@
       <c r="K60" s="58" t="s">
         <v>83</v>
       </c>
-      <c r="L60" s="219"/>
-      <c r="M60" s="162"/>
+      <c r="L60" s="159"/>
+      <c r="M60" s="157"/>
       <c r="N60" s="50"/>
       <c r="O60" s="50"/>
       <c r="P60" s="53"/>
@@ -4654,18 +4654,18 @@
       <c r="S60" s="81"/>
       <c r="T60" s="5"/>
       <c r="U60" s="82"/>
-      <c r="V60" s="165"/>
+      <c r="V60" s="288"/>
     </row>
     <row r="61" spans="2:23" ht="30" customHeight="1">
-      <c r="B61" s="257"/>
+      <c r="B61" s="193"/>
       <c r="C61" s="83">
         <v>6</v>
       </c>
       <c r="D61" s="84" t="s">
         <v>89</v>
       </c>
-      <c r="E61" s="189"/>
-      <c r="F61" s="162"/>
+      <c r="E61" s="210"/>
+      <c r="F61" s="157"/>
       <c r="G61" s="58" t="s">
         <v>83</v>
       </c>
@@ -4675,8 +4675,8 @@
       <c r="K61" s="83" t="s">
         <v>83</v>
       </c>
-      <c r="L61" s="219"/>
-      <c r="M61" s="162"/>
+      <c r="L61" s="159"/>
+      <c r="M61" s="157"/>
       <c r="N61" s="86"/>
       <c r="O61" s="86"/>
       <c r="P61" s="83"/>
@@ -4685,36 +4685,36 @@
       <c r="S61" s="81"/>
       <c r="T61" s="5"/>
       <c r="U61" s="82"/>
-      <c r="V61" s="165"/>
+      <c r="V61" s="288"/>
     </row>
     <row r="62" spans="2:23" ht="30" customHeight="1" thickBot="1">
-      <c r="B62" s="166" t="s">
+      <c r="B62" s="289" t="s">
         <v>97</v>
       </c>
-      <c r="C62" s="167"/>
-      <c r="D62" s="167"/>
-      <c r="E62" s="167"/>
-      <c r="F62" s="168"/>
-      <c r="G62" s="169" t="s">
+      <c r="C62" s="290"/>
+      <c r="D62" s="290"/>
+      <c r="E62" s="290"/>
+      <c r="F62" s="291"/>
+      <c r="G62" s="292" t="s">
         <v>98</v>
       </c>
-      <c r="H62" s="167"/>
-      <c r="I62" s="167"/>
-      <c r="J62" s="167"/>
-      <c r="K62" s="167"/>
-      <c r="L62" s="167"/>
-      <c r="M62" s="168"/>
-      <c r="N62" s="170" t="s">
+      <c r="H62" s="290"/>
+      <c r="I62" s="290"/>
+      <c r="J62" s="290"/>
+      <c r="K62" s="290"/>
+      <c r="L62" s="290"/>
+      <c r="M62" s="291"/>
+      <c r="N62" s="293" t="s">
         <v>99</v>
       </c>
-      <c r="O62" s="167"/>
-      <c r="P62" s="167"/>
-      <c r="Q62" s="167"/>
-      <c r="R62" s="167"/>
-      <c r="S62" s="167"/>
-      <c r="T62" s="167"/>
-      <c r="U62" s="171"/>
-      <c r="V62" s="165"/>
+      <c r="O62" s="290"/>
+      <c r="P62" s="290"/>
+      <c r="Q62" s="290"/>
+      <c r="R62" s="290"/>
+      <c r="S62" s="290"/>
+      <c r="T62" s="290"/>
+      <c r="U62" s="294"/>
+      <c r="V62" s="288"/>
     </row>
     <row r="63" spans="2:23" s="87" customFormat="1" ht="48.6" customHeight="1">
       <c r="B63" s="137"/>
@@ -4737,7 +4737,7 @@
       <c r="S63" s="140"/>
       <c r="T63" s="140"/>
       <c r="U63" s="140"/>
-      <c r="V63" s="165"/>
+      <c r="V63" s="288"/>
       <c r="W63" s="88"/>
     </row>
     <row r="64" spans="2:23" ht="14.4" customHeight="1"/>
@@ -4763,6 +4763,149 @@
     </row>
   </sheetData>
   <mergeCells count="167">
+    <mergeCell ref="U42:U44"/>
+    <mergeCell ref="R42:T44"/>
+    <mergeCell ref="L22:U24"/>
+    <mergeCell ref="U53:U55"/>
+    <mergeCell ref="R49:T49"/>
+    <mergeCell ref="E42:F44"/>
+    <mergeCell ref="K53:M54"/>
+    <mergeCell ref="V1:V63"/>
+    <mergeCell ref="B62:F62"/>
+    <mergeCell ref="G62:M62"/>
+    <mergeCell ref="N62:U62"/>
+    <mergeCell ref="S16:U19"/>
+    <mergeCell ref="E1:N2"/>
+    <mergeCell ref="P42:P44"/>
+    <mergeCell ref="E51:F51"/>
+    <mergeCell ref="R47:T47"/>
+    <mergeCell ref="I38:J39"/>
+    <mergeCell ref="O1:U2"/>
+    <mergeCell ref="E3:K5"/>
+    <mergeCell ref="E38:G39"/>
+    <mergeCell ref="L44:M44"/>
+    <mergeCell ref="N32:O32"/>
+    <mergeCell ref="Q41:R41"/>
+    <mergeCell ref="Q25:R25"/>
+    <mergeCell ref="R50:T50"/>
+    <mergeCell ref="N35:O35"/>
+    <mergeCell ref="I12:J15"/>
+    <mergeCell ref="R53:T55"/>
+    <mergeCell ref="Q35:R35"/>
+    <mergeCell ref="N39:O39"/>
+    <mergeCell ref="R46:T46"/>
+    <mergeCell ref="D22:D24"/>
+    <mergeCell ref="E49:F49"/>
+    <mergeCell ref="N41:O41"/>
+    <mergeCell ref="H40:I40"/>
+    <mergeCell ref="L47:M47"/>
+    <mergeCell ref="E40:G40"/>
+    <mergeCell ref="R45:T45"/>
+    <mergeCell ref="P53:P55"/>
+    <mergeCell ref="E45:F45"/>
+    <mergeCell ref="Q40:R40"/>
+    <mergeCell ref="J53:J55"/>
+    <mergeCell ref="N53:N55"/>
+    <mergeCell ref="L50:M50"/>
+    <mergeCell ref="Q28:R28"/>
+    <mergeCell ref="Q37:R37"/>
+    <mergeCell ref="E12:H15"/>
+    <mergeCell ref="D12:D13"/>
+    <mergeCell ref="B14:C15"/>
+    <mergeCell ref="N37:O37"/>
+    <mergeCell ref="L20:U20"/>
+    <mergeCell ref="Q26:R26"/>
+    <mergeCell ref="Q34:R34"/>
+    <mergeCell ref="L30:L41"/>
+    <mergeCell ref="R48:T48"/>
+    <mergeCell ref="Q27:R27"/>
+    <mergeCell ref="N31:O31"/>
+    <mergeCell ref="N40:O40"/>
+    <mergeCell ref="J20:K24"/>
+    <mergeCell ref="E31:K31"/>
+    <mergeCell ref="B20:C21"/>
+    <mergeCell ref="E20:I24"/>
+    <mergeCell ref="M40:M41"/>
+    <mergeCell ref="Q39:R39"/>
+    <mergeCell ref="B25:D26"/>
+    <mergeCell ref="J16:K19"/>
+    <mergeCell ref="Q29:R29"/>
+    <mergeCell ref="B27:D28"/>
+    <mergeCell ref="Q32:R32"/>
+    <mergeCell ref="N29:O29"/>
+    <mergeCell ref="N38:O38"/>
+    <mergeCell ref="D20:D21"/>
+    <mergeCell ref="N25:O25"/>
+    <mergeCell ref="L25:M26"/>
+    <mergeCell ref="D14:D15"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="Q31:R31"/>
+    <mergeCell ref="E60:F60"/>
+    <mergeCell ref="L59:M59"/>
+    <mergeCell ref="B32:K33"/>
+    <mergeCell ref="L46:M46"/>
+    <mergeCell ref="B53:B61"/>
+    <mergeCell ref="D38:D39"/>
+    <mergeCell ref="M34:M35"/>
+    <mergeCell ref="M32:M33"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="M36:M37"/>
+    <mergeCell ref="M30:M31"/>
+    <mergeCell ref="B16:C17"/>
+    <mergeCell ref="E37:G37"/>
+    <mergeCell ref="L16:R19"/>
+    <mergeCell ref="E29:K30"/>
+    <mergeCell ref="Q33:R33"/>
+    <mergeCell ref="B22:C24"/>
+    <mergeCell ref="E16:I19"/>
+    <mergeCell ref="N33:O33"/>
+    <mergeCell ref="L61:M61"/>
+    <mergeCell ref="E58:F58"/>
+    <mergeCell ref="I42:I44"/>
+    <mergeCell ref="L48:M48"/>
+    <mergeCell ref="E50:F50"/>
+    <mergeCell ref="H38:H39"/>
+    <mergeCell ref="E61:F61"/>
+    <mergeCell ref="E59:F59"/>
+    <mergeCell ref="L58:M58"/>
+    <mergeCell ref="E56:F56"/>
+    <mergeCell ref="L60:M60"/>
+    <mergeCell ref="L45:M45"/>
+    <mergeCell ref="G42:H43"/>
+    <mergeCell ref="I53:I55"/>
+    <mergeCell ref="K42:M43"/>
+    <mergeCell ref="E46:F46"/>
+    <mergeCell ref="L57:M57"/>
+    <mergeCell ref="J43:J44"/>
+    <mergeCell ref="E57:F57"/>
+    <mergeCell ref="E48:F48"/>
+    <mergeCell ref="K38:K39"/>
+    <mergeCell ref="M38:M39"/>
+    <mergeCell ref="L56:M56"/>
+    <mergeCell ref="I37:J37"/>
+    <mergeCell ref="B42:B51"/>
+    <mergeCell ref="R51:T51"/>
+    <mergeCell ref="N28:O28"/>
+    <mergeCell ref="N26:O26"/>
+    <mergeCell ref="O54:O55"/>
+    <mergeCell ref="B29:D31"/>
+    <mergeCell ref="B1:C5"/>
+    <mergeCell ref="Q36:R36"/>
+    <mergeCell ref="B18:C19"/>
+    <mergeCell ref="B8:C9"/>
+    <mergeCell ref="N34:O34"/>
+    <mergeCell ref="L49:M49"/>
+    <mergeCell ref="G53:H54"/>
+    <mergeCell ref="N42:N44"/>
+    <mergeCell ref="N27:O27"/>
+    <mergeCell ref="D3:D5"/>
+    <mergeCell ref="E53:F55"/>
+    <mergeCell ref="N36:O36"/>
+    <mergeCell ref="E47:F47"/>
+    <mergeCell ref="E8:F10"/>
+    <mergeCell ref="G8:H10"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="G11:H11"/>
     <mergeCell ref="D6:D7"/>
     <mergeCell ref="K8:K11"/>
     <mergeCell ref="D10:D11"/>
@@ -4787,149 +4930,6 @@
     <mergeCell ref="E6:H7"/>
     <mergeCell ref="B10:C11"/>
     <mergeCell ref="I8:J11"/>
-    <mergeCell ref="I37:J37"/>
-    <mergeCell ref="B42:B51"/>
-    <mergeCell ref="R51:T51"/>
-    <mergeCell ref="N28:O28"/>
-    <mergeCell ref="N26:O26"/>
-    <mergeCell ref="O54:O55"/>
-    <mergeCell ref="B29:D31"/>
-    <mergeCell ref="B1:C5"/>
-    <mergeCell ref="Q36:R36"/>
-    <mergeCell ref="B18:C19"/>
-    <mergeCell ref="B8:C9"/>
-    <mergeCell ref="N34:O34"/>
-    <mergeCell ref="L49:M49"/>
-    <mergeCell ref="G53:H54"/>
-    <mergeCell ref="N42:N44"/>
-    <mergeCell ref="N27:O27"/>
-    <mergeCell ref="D3:D5"/>
-    <mergeCell ref="E53:F55"/>
-    <mergeCell ref="N36:O36"/>
-    <mergeCell ref="E47:F47"/>
-    <mergeCell ref="E8:F10"/>
-    <mergeCell ref="G8:H10"/>
-    <mergeCell ref="E11:F11"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="L61:M61"/>
-    <mergeCell ref="E58:F58"/>
-    <mergeCell ref="I42:I44"/>
-    <mergeCell ref="L48:M48"/>
-    <mergeCell ref="E50:F50"/>
-    <mergeCell ref="H38:H39"/>
-    <mergeCell ref="E61:F61"/>
-    <mergeCell ref="E59:F59"/>
-    <mergeCell ref="L58:M58"/>
-    <mergeCell ref="E56:F56"/>
-    <mergeCell ref="L60:M60"/>
-    <mergeCell ref="L45:M45"/>
-    <mergeCell ref="G42:H43"/>
-    <mergeCell ref="I53:I55"/>
-    <mergeCell ref="K42:M43"/>
-    <mergeCell ref="E46:F46"/>
-    <mergeCell ref="L57:M57"/>
-    <mergeCell ref="J43:J44"/>
-    <mergeCell ref="E57:F57"/>
-    <mergeCell ref="E48:F48"/>
-    <mergeCell ref="K38:K39"/>
-    <mergeCell ref="M38:M39"/>
-    <mergeCell ref="L56:M56"/>
-    <mergeCell ref="N25:O25"/>
-    <mergeCell ref="L25:M26"/>
-    <mergeCell ref="D14:D15"/>
-    <mergeCell ref="D16:D17"/>
-    <mergeCell ref="Q31:R31"/>
-    <mergeCell ref="E60:F60"/>
-    <mergeCell ref="L59:M59"/>
-    <mergeCell ref="B32:K33"/>
-    <mergeCell ref="L46:M46"/>
-    <mergeCell ref="B53:B61"/>
-    <mergeCell ref="D38:D39"/>
-    <mergeCell ref="M34:M35"/>
-    <mergeCell ref="M32:M33"/>
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="M36:M37"/>
-    <mergeCell ref="M30:M31"/>
-    <mergeCell ref="B16:C17"/>
-    <mergeCell ref="E37:G37"/>
-    <mergeCell ref="L16:R19"/>
-    <mergeCell ref="E29:K30"/>
-    <mergeCell ref="Q33:R33"/>
-    <mergeCell ref="B22:C24"/>
-    <mergeCell ref="E16:I19"/>
-    <mergeCell ref="N33:O33"/>
-    <mergeCell ref="B14:C15"/>
-    <mergeCell ref="N37:O37"/>
-    <mergeCell ref="L20:U20"/>
-    <mergeCell ref="Q26:R26"/>
-    <mergeCell ref="Q34:R34"/>
-    <mergeCell ref="L30:L41"/>
-    <mergeCell ref="R48:T48"/>
-    <mergeCell ref="Q27:R27"/>
-    <mergeCell ref="N31:O31"/>
-    <mergeCell ref="N40:O40"/>
-    <mergeCell ref="J20:K24"/>
-    <mergeCell ref="E31:K31"/>
-    <mergeCell ref="B20:C21"/>
-    <mergeCell ref="E20:I24"/>
-    <mergeCell ref="M40:M41"/>
-    <mergeCell ref="Q39:R39"/>
-    <mergeCell ref="B25:D26"/>
-    <mergeCell ref="J16:K19"/>
-    <mergeCell ref="Q29:R29"/>
-    <mergeCell ref="B27:D28"/>
-    <mergeCell ref="Q32:R32"/>
-    <mergeCell ref="N29:O29"/>
-    <mergeCell ref="N38:O38"/>
-    <mergeCell ref="D20:D21"/>
-    <mergeCell ref="R50:T50"/>
-    <mergeCell ref="N35:O35"/>
-    <mergeCell ref="I12:J15"/>
-    <mergeCell ref="R53:T55"/>
-    <mergeCell ref="Q35:R35"/>
-    <mergeCell ref="N39:O39"/>
-    <mergeCell ref="R46:T46"/>
-    <mergeCell ref="D22:D24"/>
-    <mergeCell ref="E49:F49"/>
-    <mergeCell ref="N41:O41"/>
-    <mergeCell ref="H40:I40"/>
-    <mergeCell ref="L47:M47"/>
-    <mergeCell ref="E40:G40"/>
-    <mergeCell ref="R45:T45"/>
-    <mergeCell ref="P53:P55"/>
-    <mergeCell ref="E45:F45"/>
-    <mergeCell ref="Q40:R40"/>
-    <mergeCell ref="J53:J55"/>
-    <mergeCell ref="N53:N55"/>
-    <mergeCell ref="L50:M50"/>
-    <mergeCell ref="Q28:R28"/>
-    <mergeCell ref="Q37:R37"/>
-    <mergeCell ref="E12:H15"/>
-    <mergeCell ref="D12:D13"/>
-    <mergeCell ref="U42:U44"/>
-    <mergeCell ref="R42:T44"/>
-    <mergeCell ref="L22:U24"/>
-    <mergeCell ref="U53:U55"/>
-    <mergeCell ref="R49:T49"/>
-    <mergeCell ref="E42:F44"/>
-    <mergeCell ref="K53:M54"/>
-    <mergeCell ref="V1:V63"/>
-    <mergeCell ref="B62:F62"/>
-    <mergeCell ref="G62:M62"/>
-    <mergeCell ref="N62:U62"/>
-    <mergeCell ref="S16:U19"/>
-    <mergeCell ref="E1:N2"/>
-    <mergeCell ref="P42:P44"/>
-    <mergeCell ref="E51:F51"/>
-    <mergeCell ref="R47:T47"/>
-    <mergeCell ref="I38:J39"/>
-    <mergeCell ref="O1:U2"/>
-    <mergeCell ref="E3:K5"/>
-    <mergeCell ref="E38:G39"/>
-    <mergeCell ref="L44:M44"/>
-    <mergeCell ref="N32:O32"/>
-    <mergeCell ref="Q41:R41"/>
-    <mergeCell ref="Q25:R25"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="3.9370078740157501E-2" right="3.9370078740157501E-2" top="0.35433070866141703" bottom="0.35433070866141703" header="0.118110236220472" footer="0.118110236220472"/>

--- a/jo.xlsx
+++ b/jo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\production_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AD6FAC3-B365-4BD8-ABBD-7CBAED4CB922}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D570C3DE-D46E-47E5-9414-EF13E4FABA96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Job_order" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="110">
   <si>
     <t>ПУК 8.5</t>
   </si>
@@ -394,10 +394,7 @@
     </r>
   </si>
   <si>
-    <t>I10111-I10121</t>
-  </si>
-  <si>
-    <t>H248 MAIN LHD</t>
+    <t>H248 MAIN RHD</t>
   </si>
 </sst>
 </file>
@@ -3223,9 +3220,7 @@
       <c r="D11" s="147"/>
       <c r="E11" s="223"/>
       <c r="F11" s="224"/>
-      <c r="G11" s="225" t="s">
-        <v>109</v>
-      </c>
+      <c r="G11" s="225"/>
       <c r="H11" s="226"/>
       <c r="I11" s="187"/>
       <c r="J11" s="188"/>
@@ -3383,7 +3378,7 @@
       </c>
       <c r="C18" s="151"/>
       <c r="D18" s="174" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E18" s="162"/>
       <c r="F18" s="200"/>

--- a/jo.xlsx
+++ b/jo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\production_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D570C3DE-D46E-47E5-9414-EF13E4FABA96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A83697A5-ED97-4BC9-9D27-8C826F9A4402}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="109">
   <si>
     <t>ПУК 8.5</t>
   </si>
@@ -392,9 +392,6 @@
       </rPr>
       <t>Пламен Димитров</t>
     </r>
-  </si>
-  <si>
-    <t>H248 MAIN RHD</t>
   </si>
 </sst>
 </file>
@@ -2253,302 +2250,141 @@
     </xf>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="62" xfId="0" applyBorder="1"/>
-    <xf numFmtId="14" fontId="44" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="33" fillId="0" borderId="65" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="71" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="72" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="68" fillId="0" borderId="20" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="64" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="64" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="42" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="55" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="24" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="55" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="41" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="17" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="24" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="51" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="52" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="53" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="61" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="34" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="35" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="40" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="57" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="36" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="37" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="50" fillId="0" borderId="34" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="50" fillId="0" borderId="35" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="50" fillId="0" borderId="40" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="50" fillId="0" borderId="57" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="50" fillId="0" borderId="36" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="50" fillId="0" borderId="37" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="59" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="59" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="45" fillId="0" borderId="31" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="60" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="62" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="48" fillId="0" borderId="54" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="27" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="58" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="59" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="60" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="41" fillId="0" borderId="34" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="41" fillId="0" borderId="42" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="43" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="41" fillId="0" borderId="40" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="41" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="41" fillId="0" borderId="36" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="41" fillId="0" borderId="44" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="45" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="50" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="64" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="64" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="64" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="64" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="64" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="64" fillId="0" borderId="64" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="164" fontId="63" fillId="7" borderId="65" xfId="26" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="68" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="38" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="57" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="20" xfId="26" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2564,105 +2400,268 @@
     <xf numFmtId="0" fontId="29" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="40" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="45" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="43" fontId="60" fillId="0" borderId="5" xfId="26" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="50" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="68" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="27" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="58" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="59" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="60" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="43" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="55" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="38" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="57" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="20" xfId="26" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="60" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="62" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="52" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="53" xfId="0" applyBorder="1"/>
+    <xf numFmtId="3" fontId="48" fillId="0" borderId="54" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="41" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="45" fillId="0" borderId="31" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="45" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="51" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="61" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="34" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="35" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="40" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="57" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="36" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="37" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="50" fillId="0" borderId="34" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="50" fillId="0" borderId="35" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="50" fillId="0" borderId="40" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="50" fillId="0" borderId="57" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="50" fillId="0" borderId="36" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="50" fillId="0" borderId="37" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="59" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="64" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="64" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="64" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="64" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="64" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="64" fillId="0" borderId="64" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="63" fillId="7" borderId="65" xfId="26" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="44" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="33" fillId="0" borderId="65" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="71" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="72" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="68" fillId="0" borderId="20" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="64" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="64" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="42" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="24" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="55" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="17" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="24" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="41" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="29">
     <cellStyle name="Comma" xfId="26" builtinId="3"/>
@@ -3006,72 +3005,72 @@
       <c r="A1" s="1">
         <v>24</v>
       </c>
-      <c r="B1" s="201"/>
-      <c r="C1" s="202"/>
-      <c r="D1" s="148" t="s">
+      <c r="B1" s="274"/>
+      <c r="C1" s="275"/>
+      <c r="D1" s="301" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="298" t="s">
+      <c r="E1" s="181" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="299"/>
-      <c r="G1" s="299"/>
-      <c r="H1" s="299"/>
-      <c r="I1" s="299"/>
-      <c r="J1" s="299"/>
-      <c r="K1" s="299"/>
-      <c r="L1" s="299"/>
-      <c r="M1" s="299"/>
-      <c r="N1" s="300"/>
-      <c r="O1" s="308" t="s">
+      <c r="F1" s="182"/>
+      <c r="G1" s="182"/>
+      <c r="H1" s="182"/>
+      <c r="I1" s="182"/>
+      <c r="J1" s="182"/>
+      <c r="K1" s="182"/>
+      <c r="L1" s="182"/>
+      <c r="M1" s="182"/>
+      <c r="N1" s="183"/>
+      <c r="O1" s="194" t="s">
         <v>2</v>
       </c>
-      <c r="P1" s="309"/>
-      <c r="Q1" s="309"/>
-      <c r="R1" s="309"/>
-      <c r="S1" s="309"/>
-      <c r="T1" s="309"/>
-      <c r="U1" s="310"/>
-      <c r="V1" s="288"/>
+      <c r="P1" s="195"/>
+      <c r="Q1" s="195"/>
+      <c r="R1" s="195"/>
+      <c r="S1" s="195"/>
+      <c r="T1" s="195"/>
+      <c r="U1" s="196"/>
+      <c r="V1" s="165"/>
     </row>
     <row r="2" spans="1:22" s="1" customFormat="1" ht="18.75" customHeight="1">
-      <c r="B2" s="199"/>
-      <c r="C2" s="181"/>
-      <c r="D2" s="147"/>
-      <c r="E2" s="301"/>
-      <c r="F2" s="302"/>
-      <c r="G2" s="302"/>
-      <c r="H2" s="302"/>
-      <c r="I2" s="302"/>
-      <c r="J2" s="302"/>
-      <c r="K2" s="302"/>
-      <c r="L2" s="302"/>
-      <c r="M2" s="302"/>
-      <c r="N2" s="303"/>
-      <c r="O2" s="311"/>
-      <c r="P2" s="312"/>
-      <c r="Q2" s="312"/>
-      <c r="R2" s="312"/>
-      <c r="S2" s="312"/>
-      <c r="T2" s="312"/>
-      <c r="U2" s="313"/>
-      <c r="V2" s="288"/>
+      <c r="B2" s="262"/>
+      <c r="C2" s="149"/>
+      <c r="D2" s="300"/>
+      <c r="E2" s="184"/>
+      <c r="F2" s="185"/>
+      <c r="G2" s="185"/>
+      <c r="H2" s="185"/>
+      <c r="I2" s="185"/>
+      <c r="J2" s="185"/>
+      <c r="K2" s="185"/>
+      <c r="L2" s="185"/>
+      <c r="M2" s="185"/>
+      <c r="N2" s="186"/>
+      <c r="O2" s="197"/>
+      <c r="P2" s="198"/>
+      <c r="Q2" s="198"/>
+      <c r="R2" s="198"/>
+      <c r="S2" s="198"/>
+      <c r="T2" s="198"/>
+      <c r="U2" s="199"/>
+      <c r="V2" s="165"/>
     </row>
     <row r="3" spans="1:22" ht="12.45" customHeight="1">
-      <c r="B3" s="199"/>
-      <c r="C3" s="181"/>
-      <c r="D3" s="208" t="s">
+      <c r="B3" s="262"/>
+      <c r="C3" s="149"/>
+      <c r="D3" s="266" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="314" t="s">
+      <c r="E3" s="200" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="150"/>
-      <c r="G3" s="150"/>
-      <c r="H3" s="150"/>
-      <c r="I3" s="150"/>
-      <c r="J3" s="150"/>
-      <c r="K3" s="150"/>
+      <c r="F3" s="145"/>
+      <c r="G3" s="145"/>
+      <c r="H3" s="145"/>
+      <c r="I3" s="145"/>
+      <c r="J3" s="145"/>
+      <c r="K3" s="145"/>
       <c r="L3" s="125"/>
       <c r="M3" s="5"/>
       <c r="N3" s="5"/>
@@ -3082,149 +3081,149 @@
       <c r="S3" s="5"/>
       <c r="T3" s="5"/>
       <c r="U3" s="126"/>
-      <c r="V3" s="288"/>
+      <c r="V3" s="165"/>
     </row>
     <row r="4" spans="1:22" ht="14.85" customHeight="1">
-      <c r="B4" s="199"/>
-      <c r="C4" s="181"/>
-      <c r="D4" s="205"/>
-      <c r="E4" s="162"/>
-      <c r="F4" s="200"/>
-      <c r="G4" s="200"/>
-      <c r="H4" s="200"/>
-      <c r="I4" s="200"/>
-      <c r="J4" s="200"/>
-      <c r="K4" s="180"/>
+      <c r="B4" s="262"/>
+      <c r="C4" s="149"/>
+      <c r="D4" s="187"/>
+      <c r="E4" s="147"/>
+      <c r="F4" s="148"/>
+      <c r="G4" s="148"/>
+      <c r="H4" s="148"/>
+      <c r="I4" s="148"/>
+      <c r="J4" s="148"/>
+      <c r="K4" s="201"/>
       <c r="L4" s="127"/>
       <c r="U4" s="128"/>
-      <c r="V4" s="288"/>
+      <c r="V4" s="165"/>
     </row>
     <row r="5" spans="1:22" ht="14.85" customHeight="1">
-      <c r="B5" s="154"/>
-      <c r="C5" s="155"/>
-      <c r="D5" s="142"/>
-      <c r="E5" s="163"/>
-      <c r="F5" s="168"/>
-      <c r="G5" s="168"/>
-      <c r="H5" s="168"/>
-      <c r="I5" s="168"/>
-      <c r="J5" s="168"/>
-      <c r="K5" s="168"/>
+      <c r="B5" s="228"/>
+      <c r="C5" s="152"/>
+      <c r="D5" s="188"/>
+      <c r="E5" s="150"/>
+      <c r="F5" s="151"/>
+      <c r="G5" s="151"/>
+      <c r="H5" s="151"/>
+      <c r="I5" s="151"/>
+      <c r="J5" s="151"/>
+      <c r="K5" s="151"/>
       <c r="L5" s="127"/>
       <c r="U5" s="128"/>
-      <c r="V5" s="288"/>
+      <c r="V5" s="165"/>
     </row>
     <row r="6" spans="1:22" s="2" customFormat="1" ht="27.75" customHeight="1">
-      <c r="B6" s="153" t="s">
+      <c r="B6" s="241" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="151"/>
-      <c r="D6" s="141"/>
-      <c r="E6" s="179" t="s">
+      <c r="C6" s="146"/>
+      <c r="D6" s="295"/>
+      <c r="E6" s="313" t="s">
         <v>6</v>
       </c>
-      <c r="F6" s="150"/>
-      <c r="G6" s="150"/>
-      <c r="H6" s="151"/>
-      <c r="I6" s="177" t="s">
+      <c r="F6" s="145"/>
+      <c r="G6" s="145"/>
+      <c r="H6" s="146"/>
+      <c r="I6" s="311" t="s">
         <v>7</v>
       </c>
-      <c r="J6" s="157"/>
+      <c r="J6" s="162"/>
       <c r="K6" s="100" t="s">
         <v>8</v>
       </c>
       <c r="L6" s="127"/>
       <c r="U6" s="128"/>
-      <c r="V6" s="288"/>
+      <c r="V6" s="165"/>
     </row>
     <row r="7" spans="1:22" s="2" customFormat="1" ht="28.5" customHeight="1">
-      <c r="B7" s="154"/>
-      <c r="C7" s="155"/>
-      <c r="D7" s="142"/>
-      <c r="E7" s="162"/>
-      <c r="F7" s="180"/>
-      <c r="G7" s="180"/>
-      <c r="H7" s="181"/>
-      <c r="I7" s="178"/>
-      <c r="J7" s="157"/>
+      <c r="B7" s="228"/>
+      <c r="C7" s="152"/>
+      <c r="D7" s="188"/>
+      <c r="E7" s="147"/>
+      <c r="F7" s="201"/>
+      <c r="G7" s="201"/>
+      <c r="H7" s="149"/>
+      <c r="I7" s="312"/>
+      <c r="J7" s="162"/>
       <c r="K7" s="101"/>
       <c r="L7" s="127"/>
       <c r="P7" s="131"/>
       <c r="U7" s="128"/>
-      <c r="V7" s="288"/>
+      <c r="V7" s="165"/>
     </row>
     <row r="8" spans="1:22" s="2" customFormat="1" ht="31.95" customHeight="1">
-      <c r="B8" s="153" t="s">
+      <c r="B8" s="241" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="151"/>
-      <c r="D8" s="176"/>
-      <c r="E8" s="211" t="s">
+      <c r="C8" s="146"/>
+      <c r="D8" s="310"/>
+      <c r="E8" s="279" t="s">
         <v>101</v>
       </c>
-      <c r="F8" s="212"/>
-      <c r="G8" s="217" t="s">
+      <c r="F8" s="280"/>
+      <c r="G8" s="285" t="s">
         <v>100</v>
       </c>
-      <c r="H8" s="218"/>
-      <c r="I8" s="183" t="s">
+      <c r="H8" s="286"/>
+      <c r="I8" s="315" t="s">
         <v>103</v>
       </c>
-      <c r="J8" s="184"/>
-      <c r="K8" s="143"/>
+      <c r="J8" s="316"/>
+      <c r="K8" s="296"/>
       <c r="L8" s="127"/>
       <c r="P8" s="131"/>
       <c r="U8" s="128"/>
-      <c r="V8" s="288"/>
+      <c r="V8" s="165"/>
     </row>
     <row r="9" spans="1:22" s="2" customFormat="1" ht="3.75" hidden="1" customHeight="1">
-      <c r="B9" s="154"/>
-      <c r="C9" s="155"/>
-      <c r="D9" s="163"/>
-      <c r="E9" s="213"/>
-      <c r="F9" s="214"/>
-      <c r="G9" s="219"/>
-      <c r="H9" s="220"/>
-      <c r="I9" s="185"/>
-      <c r="J9" s="186"/>
-      <c r="K9" s="144"/>
+      <c r="B9" s="228"/>
+      <c r="C9" s="152"/>
+      <c r="D9" s="150"/>
+      <c r="E9" s="281"/>
+      <c r="F9" s="282"/>
+      <c r="G9" s="287"/>
+      <c r="H9" s="288"/>
+      <c r="I9" s="317"/>
+      <c r="J9" s="318"/>
+      <c r="K9" s="297"/>
       <c r="L9" s="127"/>
       <c r="P9" s="131" t="str">
         <f t="shared" ref="P9" si="0">"*"&amp;J18&amp;"*"</f>
         <v>**</v>
       </c>
       <c r="U9" s="128"/>
-      <c r="V9" s="288"/>
+      <c r="V9" s="165"/>
     </row>
     <row r="10" spans="1:22" s="2" customFormat="1" ht="15" customHeight="1">
-      <c r="B10" s="182" t="s">
+      <c r="B10" s="314" t="s">
         <v>11</v>
       </c>
-      <c r="C10" s="151"/>
-      <c r="D10" s="146"/>
-      <c r="E10" s="215"/>
-      <c r="F10" s="216"/>
-      <c r="G10" s="221"/>
-      <c r="H10" s="222"/>
-      <c r="I10" s="185"/>
-      <c r="J10" s="186"/>
-      <c r="K10" s="144"/>
+      <c r="C10" s="146"/>
+      <c r="D10" s="299"/>
+      <c r="E10" s="283"/>
+      <c r="F10" s="284"/>
+      <c r="G10" s="289"/>
+      <c r="H10" s="290"/>
+      <c r="I10" s="317"/>
+      <c r="J10" s="318"/>
+      <c r="K10" s="297"/>
       <c r="L10" s="127"/>
       <c r="P10" s="131"/>
       <c r="U10" s="128"/>
-      <c r="V10" s="288"/>
+      <c r="V10" s="165"/>
     </row>
     <row r="11" spans="1:22" s="2" customFormat="1" ht="78.599999999999994" customHeight="1">
-      <c r="B11" s="154"/>
-      <c r="C11" s="155"/>
-      <c r="D11" s="147"/>
-      <c r="E11" s="223"/>
-      <c r="F11" s="224"/>
-      <c r="G11" s="225"/>
-      <c r="H11" s="226"/>
-      <c r="I11" s="187"/>
-      <c r="J11" s="188"/>
-      <c r="K11" s="145"/>
+      <c r="B11" s="228"/>
+      <c r="C11" s="152"/>
+      <c r="D11" s="300"/>
+      <c r="E11" s="291"/>
+      <c r="F11" s="292"/>
+      <c r="G11" s="293"/>
+      <c r="H11" s="294"/>
+      <c r="I11" s="319"/>
+      <c r="J11" s="320"/>
+      <c r="K11" s="298"/>
       <c r="L11" s="127"/>
       <c r="M11" s="132" t="str">
         <f>"*"&amp;J16&amp;"*"</f>
@@ -3236,74 +3235,74 @@
       <c r="Q11" s="132"/>
       <c r="S11" s="133"/>
       <c r="U11" s="128"/>
-      <c r="V11" s="288"/>
+      <c r="V11" s="165"/>
     </row>
     <row r="12" spans="1:22" s="2" customFormat="1" ht="28.5" customHeight="1">
-      <c r="B12" s="160" t="s">
+      <c r="B12" s="303" t="s">
         <v>12</v>
       </c>
-      <c r="C12" s="151"/>
-      <c r="D12" s="277" t="s">
+      <c r="C12" s="146"/>
+      <c r="D12" s="225" t="s">
         <v>102</v>
       </c>
-      <c r="E12" s="276"/>
-      <c r="F12" s="150"/>
-      <c r="G12" s="150"/>
-      <c r="H12" s="151"/>
-      <c r="I12" s="266" t="s">
+      <c r="E12" s="224"/>
+      <c r="F12" s="145"/>
+      <c r="G12" s="145"/>
+      <c r="H12" s="146"/>
+      <c r="I12" s="211" t="s">
         <v>13</v>
       </c>
-      <c r="J12" s="267"/>
-      <c r="K12" s="161"/>
+      <c r="J12" s="212"/>
+      <c r="K12" s="304"/>
       <c r="L12" s="127"/>
       <c r="U12" s="128"/>
-      <c r="V12" s="288"/>
+      <c r="V12" s="165"/>
     </row>
     <row r="13" spans="1:22" s="2" customFormat="1" ht="13.5" customHeight="1">
-      <c r="B13" s="154"/>
-      <c r="C13" s="155"/>
-      <c r="D13" s="235"/>
-      <c r="E13" s="162"/>
-      <c r="F13" s="200"/>
-      <c r="G13" s="200"/>
-      <c r="H13" s="181"/>
-      <c r="I13" s="268"/>
-      <c r="J13" s="269"/>
-      <c r="K13" s="162"/>
+      <c r="B13" s="228"/>
+      <c r="C13" s="152"/>
+      <c r="D13" s="226"/>
+      <c r="E13" s="147"/>
+      <c r="F13" s="148"/>
+      <c r="G13" s="148"/>
+      <c r="H13" s="149"/>
+      <c r="I13" s="213"/>
+      <c r="J13" s="214"/>
+      <c r="K13" s="147"/>
       <c r="L13" s="127"/>
       <c r="U13" s="128"/>
-      <c r="V13" s="288"/>
+      <c r="V13" s="165"/>
     </row>
     <row r="14" spans="1:22" s="2" customFormat="1" ht="15" customHeight="1">
-      <c r="B14" s="252" t="s">
+      <c r="B14" s="227" t="s">
         <v>14</v>
       </c>
-      <c r="C14" s="151"/>
-      <c r="D14" s="234" t="s">
+      <c r="C14" s="146"/>
+      <c r="D14" s="250" t="s">
         <v>107</v>
       </c>
-      <c r="E14" s="162"/>
-      <c r="F14" s="200"/>
-      <c r="G14" s="200"/>
-      <c r="H14" s="181"/>
-      <c r="I14" s="268"/>
-      <c r="J14" s="269"/>
-      <c r="K14" s="162"/>
+      <c r="E14" s="147"/>
+      <c r="F14" s="148"/>
+      <c r="G14" s="148"/>
+      <c r="H14" s="149"/>
+      <c r="I14" s="213"/>
+      <c r="J14" s="214"/>
+      <c r="K14" s="147"/>
       <c r="L14" s="127"/>
       <c r="U14" s="128"/>
-      <c r="V14" s="288"/>
+      <c r="V14" s="165"/>
     </row>
     <row r="15" spans="1:22" s="2" customFormat="1" ht="48" customHeight="1">
-      <c r="B15" s="154"/>
-      <c r="C15" s="155"/>
-      <c r="D15" s="235"/>
-      <c r="E15" s="163"/>
-      <c r="F15" s="168"/>
-      <c r="G15" s="168"/>
-      <c r="H15" s="155"/>
-      <c r="I15" s="270"/>
-      <c r="J15" s="271"/>
-      <c r="K15" s="163"/>
+      <c r="B15" s="228"/>
+      <c r="C15" s="152"/>
+      <c r="D15" s="226"/>
+      <c r="E15" s="150"/>
+      <c r="F15" s="151"/>
+      <c r="G15" s="151"/>
+      <c r="H15" s="152"/>
+      <c r="I15" s="215"/>
+      <c r="J15" s="216"/>
+      <c r="K15" s="150"/>
       <c r="L15" s="135"/>
       <c r="M15" s="129"/>
       <c r="N15" s="134"/>
@@ -3314,152 +3313,150 @@
       <c r="S15" s="129"/>
       <c r="T15" s="129"/>
       <c r="U15" s="130"/>
-      <c r="V15" s="288"/>
+      <c r="V15" s="165"/>
     </row>
     <row r="16" spans="1:22" s="2" customFormat="1" ht="15" customHeight="1">
-      <c r="B16" s="153" t="s">
+      <c r="B16" s="241" t="s">
         <v>15</v>
       </c>
-      <c r="C16" s="151"/>
-      <c r="D16" s="236"/>
-      <c r="E16" s="250" t="s">
+      <c r="C16" s="146"/>
+      <c r="D16" s="251"/>
+      <c r="E16" s="242" t="s">
         <v>16</v>
       </c>
-      <c r="F16" s="150"/>
-      <c r="G16" s="150"/>
-      <c r="H16" s="150"/>
-      <c r="I16" s="151"/>
-      <c r="J16" s="263">
+      <c r="F16" s="145"/>
+      <c r="G16" s="145"/>
+      <c r="H16" s="145"/>
+      <c r="I16" s="146"/>
+      <c r="J16" s="245">
         <v>232323</v>
       </c>
-      <c r="K16" s="259"/>
-      <c r="L16" s="242" t="s">
+      <c r="K16" s="237"/>
+      <c r="L16" s="172" t="s">
         <v>104</v>
       </c>
-      <c r="M16" s="243"/>
-      <c r="N16" s="243"/>
-      <c r="O16" s="243"/>
-      <c r="P16" s="243"/>
-      <c r="Q16" s="243"/>
-      <c r="R16" s="243"/>
-      <c r="S16" s="242" t="s">
+      <c r="M16" s="173"/>
+      <c r="N16" s="173"/>
+      <c r="O16" s="173"/>
+      <c r="P16" s="173"/>
+      <c r="Q16" s="173"/>
+      <c r="R16" s="173"/>
+      <c r="S16" s="172" t="s">
         <v>105</v>
       </c>
-      <c r="T16" s="243"/>
-      <c r="U16" s="295"/>
-      <c r="V16" s="288"/>
+      <c r="T16" s="173"/>
+      <c r="U16" s="174"/>
+      <c r="V16" s="165"/>
     </row>
     <row r="17" spans="2:22" s="2" customFormat="1" ht="15" customHeight="1">
-      <c r="B17" s="154"/>
-      <c r="C17" s="155"/>
-      <c r="D17" s="235"/>
-      <c r="E17" s="162"/>
-      <c r="F17" s="200"/>
-      <c r="G17" s="200"/>
-      <c r="H17" s="200"/>
-      <c r="I17" s="181"/>
-      <c r="J17" s="162"/>
-      <c r="K17" s="264"/>
-      <c r="L17" s="244"/>
-      <c r="M17" s="245"/>
-      <c r="N17" s="245"/>
-      <c r="O17" s="245"/>
-      <c r="P17" s="245"/>
-      <c r="Q17" s="245"/>
-      <c r="R17" s="245"/>
-      <c r="S17" s="244"/>
-      <c r="T17" s="245"/>
-      <c r="U17" s="296"/>
-      <c r="V17" s="288"/>
+      <c r="B17" s="228"/>
+      <c r="C17" s="152"/>
+      <c r="D17" s="226"/>
+      <c r="E17" s="147"/>
+      <c r="F17" s="148"/>
+      <c r="G17" s="148"/>
+      <c r="H17" s="148"/>
+      <c r="I17" s="149"/>
+      <c r="J17" s="147"/>
+      <c r="K17" s="246"/>
+      <c r="L17" s="175"/>
+      <c r="M17" s="176"/>
+      <c r="N17" s="176"/>
+      <c r="O17" s="176"/>
+      <c r="P17" s="176"/>
+      <c r="Q17" s="176"/>
+      <c r="R17" s="176"/>
+      <c r="S17" s="175"/>
+      <c r="T17" s="176"/>
+      <c r="U17" s="177"/>
+      <c r="V17" s="165"/>
     </row>
     <row r="18" spans="2:22" s="2" customFormat="1" ht="15" customHeight="1">
-      <c r="B18" s="203" t="s">
+      <c r="B18" s="276" t="s">
         <v>17</v>
       </c>
-      <c r="C18" s="151"/>
-      <c r="D18" s="174" t="s">
-        <v>109</v>
-      </c>
-      <c r="E18" s="162"/>
-      <c r="F18" s="200"/>
-      <c r="G18" s="200"/>
-      <c r="H18" s="200"/>
-      <c r="I18" s="181"/>
-      <c r="J18" s="162"/>
-      <c r="K18" s="264"/>
-      <c r="L18" s="244"/>
-      <c r="M18" s="245"/>
-      <c r="N18" s="245"/>
-      <c r="O18" s="245"/>
-      <c r="P18" s="245"/>
-      <c r="Q18" s="245"/>
-      <c r="R18" s="245"/>
-      <c r="S18" s="244"/>
-      <c r="T18" s="245"/>
-      <c r="U18" s="296"/>
-      <c r="V18" s="288"/>
+      <c r="C18" s="146"/>
+      <c r="D18" s="321"/>
+      <c r="E18" s="147"/>
+      <c r="F18" s="148"/>
+      <c r="G18" s="148"/>
+      <c r="H18" s="148"/>
+      <c r="I18" s="149"/>
+      <c r="J18" s="147"/>
+      <c r="K18" s="246"/>
+      <c r="L18" s="175"/>
+      <c r="M18" s="176"/>
+      <c r="N18" s="176"/>
+      <c r="O18" s="176"/>
+      <c r="P18" s="176"/>
+      <c r="Q18" s="176"/>
+      <c r="R18" s="176"/>
+      <c r="S18" s="175"/>
+      <c r="T18" s="176"/>
+      <c r="U18" s="177"/>
+      <c r="V18" s="165"/>
     </row>
     <row r="19" spans="2:22" s="2" customFormat="1" ht="15" customHeight="1">
-      <c r="B19" s="154"/>
-      <c r="C19" s="155"/>
-      <c r="D19" s="175"/>
-      <c r="E19" s="163"/>
-      <c r="F19" s="168"/>
-      <c r="G19" s="168"/>
-      <c r="H19" s="168"/>
-      <c r="I19" s="155"/>
-      <c r="J19" s="163"/>
-      <c r="K19" s="261"/>
-      <c r="L19" s="246"/>
-      <c r="M19" s="247"/>
-      <c r="N19" s="247"/>
-      <c r="O19" s="247"/>
-      <c r="P19" s="247"/>
-      <c r="Q19" s="247"/>
-      <c r="R19" s="247"/>
-      <c r="S19" s="246"/>
-      <c r="T19" s="247"/>
-      <c r="U19" s="297"/>
-      <c r="V19" s="288"/>
+      <c r="B19" s="228"/>
+      <c r="C19" s="152"/>
+      <c r="D19" s="322"/>
+      <c r="E19" s="150"/>
+      <c r="F19" s="151"/>
+      <c r="G19" s="151"/>
+      <c r="H19" s="151"/>
+      <c r="I19" s="152"/>
+      <c r="J19" s="150"/>
+      <c r="K19" s="239"/>
+      <c r="L19" s="178"/>
+      <c r="M19" s="179"/>
+      <c r="N19" s="179"/>
+      <c r="O19" s="179"/>
+      <c r="P19" s="179"/>
+      <c r="Q19" s="179"/>
+      <c r="R19" s="179"/>
+      <c r="S19" s="178"/>
+      <c r="T19" s="179"/>
+      <c r="U19" s="180"/>
+      <c r="V19" s="165"/>
     </row>
     <row r="20" spans="2:22" s="2" customFormat="1" ht="15" customHeight="1">
-      <c r="B20" s="153" t="s">
+      <c r="B20" s="241" t="s">
         <v>18</v>
       </c>
-      <c r="C20" s="151"/>
-      <c r="D20" s="265"/>
-      <c r="E20" s="250" t="s">
+      <c r="C20" s="146"/>
+      <c r="D20" s="249"/>
+      <c r="E20" s="242" t="s">
         <v>106</v>
       </c>
-      <c r="F20" s="150"/>
-      <c r="G20" s="150"/>
-      <c r="H20" s="150"/>
-      <c r="I20" s="151"/>
-      <c r="J20" s="258"/>
-      <c r="K20" s="259"/>
-      <c r="L20" s="253"/>
-      <c r="M20" s="254"/>
-      <c r="N20" s="254"/>
-      <c r="O20" s="254"/>
-      <c r="P20" s="254"/>
-      <c r="Q20" s="254"/>
-      <c r="R20" s="254"/>
-      <c r="S20" s="254"/>
-      <c r="T20" s="254"/>
-      <c r="U20" s="254"/>
-      <c r="V20" s="288"/>
+      <c r="F20" s="145"/>
+      <c r="G20" s="145"/>
+      <c r="H20" s="145"/>
+      <c r="I20" s="146"/>
+      <c r="J20" s="236"/>
+      <c r="K20" s="237"/>
+      <c r="L20" s="229"/>
+      <c r="M20" s="230"/>
+      <c r="N20" s="230"/>
+      <c r="O20" s="230"/>
+      <c r="P20" s="230"/>
+      <c r="Q20" s="230"/>
+      <c r="R20" s="230"/>
+      <c r="S20" s="230"/>
+      <c r="T20" s="230"/>
+      <c r="U20" s="230"/>
+      <c r="V20" s="165"/>
     </row>
     <row r="21" spans="2:22" s="2" customFormat="1" ht="62.4" customHeight="1">
-      <c r="B21" s="154"/>
-      <c r="C21" s="155"/>
-      <c r="D21" s="142"/>
-      <c r="E21" s="162"/>
-      <c r="F21" s="200"/>
-      <c r="G21" s="200"/>
-      <c r="H21" s="200"/>
-      <c r="I21" s="181"/>
-      <c r="J21" s="162"/>
-      <c r="K21" s="260"/>
+      <c r="B21" s="228"/>
+      <c r="C21" s="152"/>
+      <c r="D21" s="188"/>
+      <c r="E21" s="147"/>
+      <c r="F21" s="148"/>
+      <c r="G21" s="148"/>
+      <c r="H21" s="148"/>
+      <c r="I21" s="149"/>
+      <c r="J21" s="147"/>
+      <c r="K21" s="238"/>
       <c r="L21" s="120"/>
       <c r="M21" s="121"/>
       <c r="N21" s="121"/>
@@ -3470,85 +3467,85 @@
       <c r="S21" s="123"/>
       <c r="T21" s="121"/>
       <c r="U21" s="122"/>
-      <c r="V21" s="288"/>
+      <c r="V21" s="165"/>
     </row>
     <row r="22" spans="2:22" s="2" customFormat="1" ht="15" customHeight="1">
-      <c r="B22" s="153" t="s">
+      <c r="B22" s="241" t="s">
         <v>19</v>
       </c>
-      <c r="C22" s="151"/>
-      <c r="D22" s="272"/>
-      <c r="E22" s="162"/>
-      <c r="F22" s="200"/>
-      <c r="G22" s="200"/>
-      <c r="H22" s="200"/>
-      <c r="I22" s="181"/>
-      <c r="J22" s="162"/>
-      <c r="K22" s="260"/>
-      <c r="L22" s="281"/>
-      <c r="M22" s="281"/>
-      <c r="N22" s="281"/>
-      <c r="O22" s="281"/>
-      <c r="P22" s="281"/>
-      <c r="Q22" s="281"/>
-      <c r="R22" s="281"/>
-      <c r="S22" s="281"/>
-      <c r="T22" s="281"/>
-      <c r="U22" s="282"/>
-      <c r="V22" s="288"/>
+      <c r="C22" s="146"/>
+      <c r="D22" s="217"/>
+      <c r="E22" s="147"/>
+      <c r="F22" s="148"/>
+      <c r="G22" s="148"/>
+      <c r="H22" s="148"/>
+      <c r="I22" s="149"/>
+      <c r="J22" s="147"/>
+      <c r="K22" s="238"/>
+      <c r="L22" s="153"/>
+      <c r="M22" s="153"/>
+      <c r="N22" s="153"/>
+      <c r="O22" s="153"/>
+      <c r="P22" s="153"/>
+      <c r="Q22" s="153"/>
+      <c r="R22" s="153"/>
+      <c r="S22" s="153"/>
+      <c r="T22" s="153"/>
+      <c r="U22" s="154"/>
+      <c r="V22" s="165"/>
     </row>
     <row r="23" spans="2:22" s="2" customFormat="1" ht="15" customHeight="1">
-      <c r="B23" s="199"/>
-      <c r="C23" s="181"/>
-      <c r="D23" s="205"/>
-      <c r="E23" s="162"/>
-      <c r="F23" s="200"/>
-      <c r="G23" s="200"/>
-      <c r="H23" s="200"/>
-      <c r="I23" s="181"/>
-      <c r="J23" s="162"/>
-      <c r="K23" s="260"/>
-      <c r="L23" s="283"/>
-      <c r="M23" s="283"/>
-      <c r="N23" s="283"/>
-      <c r="O23" s="283"/>
-      <c r="P23" s="283"/>
-      <c r="Q23" s="283"/>
-      <c r="R23" s="283"/>
-      <c r="S23" s="283"/>
-      <c r="T23" s="283"/>
-      <c r="U23" s="284"/>
-      <c r="V23" s="288"/>
+      <c r="B23" s="262"/>
+      <c r="C23" s="149"/>
+      <c r="D23" s="187"/>
+      <c r="E23" s="147"/>
+      <c r="F23" s="148"/>
+      <c r="G23" s="148"/>
+      <c r="H23" s="148"/>
+      <c r="I23" s="149"/>
+      <c r="J23" s="147"/>
+      <c r="K23" s="238"/>
+      <c r="L23" s="155"/>
+      <c r="M23" s="155"/>
+      <c r="N23" s="155"/>
+      <c r="O23" s="155"/>
+      <c r="P23" s="155"/>
+      <c r="Q23" s="155"/>
+      <c r="R23" s="155"/>
+      <c r="S23" s="155"/>
+      <c r="T23" s="155"/>
+      <c r="U23" s="156"/>
+      <c r="V23" s="165"/>
     </row>
     <row r="24" spans="2:22" s="2" customFormat="1" ht="7.5" customHeight="1">
-      <c r="B24" s="154"/>
-      <c r="C24" s="155"/>
-      <c r="D24" s="142"/>
-      <c r="E24" s="163"/>
-      <c r="F24" s="168"/>
-      <c r="G24" s="168"/>
-      <c r="H24" s="168"/>
-      <c r="I24" s="155"/>
-      <c r="J24" s="163"/>
-      <c r="K24" s="261"/>
-      <c r="L24" s="285"/>
-      <c r="M24" s="285"/>
-      <c r="N24" s="285"/>
-      <c r="O24" s="285"/>
-      <c r="P24" s="285"/>
-      <c r="Q24" s="285"/>
-      <c r="R24" s="285"/>
-      <c r="S24" s="285"/>
-      <c r="T24" s="285"/>
-      <c r="U24" s="286"/>
-      <c r="V24" s="288"/>
+      <c r="B24" s="228"/>
+      <c r="C24" s="152"/>
+      <c r="D24" s="188"/>
+      <c r="E24" s="150"/>
+      <c r="F24" s="151"/>
+      <c r="G24" s="151"/>
+      <c r="H24" s="151"/>
+      <c r="I24" s="152"/>
+      <c r="J24" s="150"/>
+      <c r="K24" s="239"/>
+      <c r="L24" s="157"/>
+      <c r="M24" s="157"/>
+      <c r="N24" s="157"/>
+      <c r="O24" s="157"/>
+      <c r="P24" s="157"/>
+      <c r="Q24" s="157"/>
+      <c r="R24" s="157"/>
+      <c r="S24" s="157"/>
+      <c r="T24" s="157"/>
+      <c r="U24" s="158"/>
+      <c r="V24" s="165"/>
     </row>
     <row r="25" spans="2:22" s="2" customFormat="1" ht="30" customHeight="1">
-      <c r="B25" s="262" t="s">
+      <c r="B25" s="244" t="s">
         <v>20</v>
       </c>
-      <c r="C25" s="150"/>
-      <c r="D25" s="151"/>
+      <c r="C25" s="145"/>
+      <c r="D25" s="146"/>
       <c r="E25" s="3" t="s">
         <v>21</v>
       </c>
@@ -3564,21 +3561,21 @@
       <c r="K25" s="102" t="s">
         <v>24</v>
       </c>
-      <c r="L25" s="197" t="s">
+      <c r="L25" s="231" t="s">
         <v>25</v>
       </c>
-      <c r="M25" s="181"/>
-      <c r="N25" s="233" t="s">
+      <c r="M25" s="149"/>
+      <c r="N25" s="210" t="s">
         <v>26</v>
       </c>
-      <c r="O25" s="181"/>
+      <c r="O25" s="149"/>
       <c r="P25" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="Q25" s="233" t="s">
+      <c r="Q25" s="210" t="s">
         <v>28</v>
       </c>
-      <c r="R25" s="181"/>
+      <c r="R25" s="149"/>
       <c r="S25" s="7" t="s">
         <v>29</v>
       </c>
@@ -3588,12 +3585,12 @@
       <c r="U25" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="V25" s="288"/>
+      <c r="V25" s="165"/>
     </row>
     <row r="26" spans="2:22" s="2" customFormat="1" ht="39" customHeight="1">
-      <c r="B26" s="154"/>
-      <c r="C26" s="168"/>
-      <c r="D26" s="155"/>
+      <c r="B26" s="228"/>
+      <c r="C26" s="151"/>
+      <c r="D26" s="152"/>
       <c r="E26" s="10"/>
       <c r="F26" s="11"/>
       <c r="G26" s="12"/>
@@ -3601,19 +3598,19 @@
       <c r="I26" s="12"/>
       <c r="J26" s="11"/>
       <c r="K26" s="13"/>
-      <c r="L26" s="163"/>
-      <c r="M26" s="155"/>
-      <c r="N26" s="197" t="s">
+      <c r="L26" s="150"/>
+      <c r="M26" s="152"/>
+      <c r="N26" s="231" t="s">
         <v>31</v>
       </c>
-      <c r="O26" s="155"/>
+      <c r="O26" s="152"/>
       <c r="P26" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="Q26" s="197" t="s">
+      <c r="Q26" s="231" t="s">
         <v>33</v>
       </c>
-      <c r="R26" s="155"/>
+      <c r="R26" s="152"/>
       <c r="S26" s="14" t="s">
         <v>34</v>
       </c>
@@ -3623,14 +3620,14 @@
       <c r="U26" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="V26" s="288"/>
+      <c r="V26" s="165"/>
     </row>
     <row r="27" spans="2:22" s="2" customFormat="1" ht="46.05" customHeight="1">
-      <c r="B27" s="262" t="s">
+      <c r="B27" s="244" t="s">
         <v>36</v>
       </c>
-      <c r="C27" s="150"/>
-      <c r="D27" s="151"/>
+      <c r="C27" s="145"/>
+      <c r="D27" s="146"/>
       <c r="E27" s="3" t="s">
         <v>21</v>
       </c>
@@ -3644,26 +3641,26 @@
       </c>
       <c r="J27" s="5"/>
       <c r="K27" s="6"/>
-      <c r="L27" s="164" t="s">
+      <c r="L27" s="305" t="s">
         <v>39</v>
       </c>
       <c r="M27" s="118" t="s">
         <v>9</v>
       </c>
-      <c r="N27" s="206"/>
-      <c r="O27" s="207"/>
+      <c r="N27" s="277"/>
+      <c r="O27" s="278"/>
       <c r="P27" s="92"/>
-      <c r="Q27" s="256"/>
-      <c r="R27" s="157"/>
+      <c r="Q27" s="223"/>
+      <c r="R27" s="162"/>
       <c r="S27" s="17"/>
       <c r="T27" s="18"/>
       <c r="U27" s="19"/>
-      <c r="V27" s="288"/>
+      <c r="V27" s="165"/>
     </row>
     <row r="28" spans="2:22" s="2" customFormat="1" ht="46.05" customHeight="1">
-      <c r="B28" s="154"/>
-      <c r="C28" s="168"/>
-      <c r="D28" s="155"/>
+      <c r="B28" s="228"/>
+      <c r="C28" s="151"/>
+      <c r="D28" s="152"/>
       <c r="E28" s="20"/>
       <c r="F28" s="21"/>
       <c r="G28" s="21"/>
@@ -3671,64 +3668,64 @@
       <c r="I28" s="22"/>
       <c r="J28" s="22"/>
       <c r="K28" s="23"/>
-      <c r="L28" s="165"/>
+      <c r="L28" s="233"/>
       <c r="M28" s="118" t="s">
         <v>40</v>
       </c>
-      <c r="N28" s="195"/>
-      <c r="O28" s="196"/>
+      <c r="N28" s="247"/>
+      <c r="O28" s="248"/>
       <c r="P28" s="92"/>
-      <c r="Q28" s="256"/>
-      <c r="R28" s="157"/>
+      <c r="Q28" s="223"/>
+      <c r="R28" s="162"/>
       <c r="S28" s="17"/>
       <c r="T28" s="18"/>
       <c r="U28" s="19"/>
-      <c r="V28" s="288"/>
+      <c r="V28" s="165"/>
     </row>
     <row r="29" spans="2:22" s="2" customFormat="1" ht="46.5" customHeight="1">
-      <c r="B29" s="198" t="s">
+      <c r="B29" s="273" t="s">
         <v>41</v>
       </c>
-      <c r="C29" s="150"/>
-      <c r="D29" s="151"/>
-      <c r="E29" s="248" t="s">
+      <c r="C29" s="145"/>
+      <c r="D29" s="146"/>
+      <c r="E29" s="240" t="s">
         <v>42</v>
       </c>
-      <c r="F29" s="150"/>
-      <c r="G29" s="150"/>
-      <c r="H29" s="150"/>
-      <c r="I29" s="150"/>
-      <c r="J29" s="150"/>
-      <c r="K29" s="151"/>
-      <c r="L29" s="166"/>
+      <c r="F29" s="145"/>
+      <c r="G29" s="145"/>
+      <c r="H29" s="145"/>
+      <c r="I29" s="145"/>
+      <c r="J29" s="145"/>
+      <c r="K29" s="146"/>
+      <c r="L29" s="234"/>
       <c r="M29" s="119" t="s">
         <v>43</v>
       </c>
-      <c r="N29" s="195"/>
-      <c r="O29" s="196"/>
+      <c r="N29" s="247"/>
+      <c r="O29" s="248"/>
       <c r="P29" s="93"/>
-      <c r="Q29" s="256"/>
-      <c r="R29" s="157"/>
+      <c r="Q29" s="223"/>
+      <c r="R29" s="162"/>
       <c r="S29" s="25"/>
       <c r="T29" s="5"/>
       <c r="U29" s="26"/>
-      <c r="V29" s="288"/>
+      <c r="V29" s="165"/>
     </row>
     <row r="30" spans="2:22" s="2" customFormat="1" ht="15" customHeight="1">
-      <c r="B30" s="199"/>
-      <c r="C30" s="200"/>
-      <c r="D30" s="181"/>
-      <c r="E30" s="163"/>
-      <c r="F30" s="168"/>
-      <c r="G30" s="168"/>
-      <c r="H30" s="168"/>
-      <c r="I30" s="168"/>
-      <c r="J30" s="168"/>
-      <c r="K30" s="155"/>
-      <c r="L30" s="255" t="s">
+      <c r="B30" s="262"/>
+      <c r="C30" s="148"/>
+      <c r="D30" s="149"/>
+      <c r="E30" s="150"/>
+      <c r="F30" s="151"/>
+      <c r="G30" s="151"/>
+      <c r="H30" s="151"/>
+      <c r="I30" s="151"/>
+      <c r="J30" s="151"/>
+      <c r="K30" s="152"/>
+      <c r="L30" s="232" t="s">
         <v>44</v>
       </c>
-      <c r="M30" s="232" t="s">
+      <c r="M30" s="243" t="s">
         <v>45</v>
       </c>
       <c r="N30" s="27"/>
@@ -3739,269 +3736,269 @@
       <c r="S30" s="30"/>
       <c r="T30" s="30"/>
       <c r="U30" s="26"/>
-      <c r="V30" s="288"/>
+      <c r="V30" s="165"/>
     </row>
     <row r="31" spans="2:22" s="2" customFormat="1" ht="42" customHeight="1">
-      <c r="B31" s="154"/>
-      <c r="C31" s="168"/>
-      <c r="D31" s="155"/>
-      <c r="E31" s="248" t="s">
+      <c r="B31" s="228"/>
+      <c r="C31" s="151"/>
+      <c r="D31" s="152"/>
+      <c r="E31" s="240" t="s">
         <v>108</v>
       </c>
-      <c r="F31" s="170"/>
-      <c r="G31" s="170"/>
-      <c r="H31" s="170"/>
-      <c r="I31" s="170"/>
-      <c r="J31" s="170"/>
-      <c r="K31" s="157"/>
-      <c r="L31" s="165"/>
-      <c r="M31" s="142"/>
-      <c r="N31" s="257"/>
-      <c r="O31" s="155"/>
+      <c r="F31" s="161"/>
+      <c r="G31" s="161"/>
+      <c r="H31" s="161"/>
+      <c r="I31" s="161"/>
+      <c r="J31" s="161"/>
+      <c r="K31" s="162"/>
+      <c r="L31" s="233"/>
+      <c r="M31" s="188"/>
+      <c r="N31" s="235"/>
+      <c r="O31" s="152"/>
       <c r="P31" s="97"/>
-      <c r="Q31" s="142"/>
-      <c r="R31" s="155"/>
+      <c r="Q31" s="188"/>
+      <c r="R31" s="152"/>
       <c r="S31" s="31"/>
       <c r="T31" s="31"/>
       <c r="U31" s="32"/>
-      <c r="V31" s="288"/>
+      <c r="V31" s="165"/>
     </row>
     <row r="32" spans="2:22" s="2" customFormat="1" ht="21" customHeight="1">
-      <c r="B32" s="237" t="s">
+      <c r="B32" s="252" t="s">
         <v>46</v>
       </c>
-      <c r="C32" s="150"/>
-      <c r="D32" s="150"/>
-      <c r="E32" s="150"/>
-      <c r="F32" s="150"/>
-      <c r="G32" s="150"/>
-      <c r="H32" s="150"/>
-      <c r="I32" s="150"/>
-      <c r="J32" s="150"/>
-      <c r="K32" s="151"/>
-      <c r="L32" s="165"/>
-      <c r="M32" s="232" t="s">
+      <c r="C32" s="145"/>
+      <c r="D32" s="145"/>
+      <c r="E32" s="145"/>
+      <c r="F32" s="145"/>
+      <c r="G32" s="145"/>
+      <c r="H32" s="145"/>
+      <c r="I32" s="145"/>
+      <c r="J32" s="145"/>
+      <c r="K32" s="146"/>
+      <c r="L32" s="233"/>
+      <c r="M32" s="243" t="s">
         <v>47</v>
       </c>
-      <c r="N32" s="322"/>
-      <c r="O32" s="151"/>
+      <c r="N32" s="209"/>
+      <c r="O32" s="146"/>
       <c r="P32" s="96"/>
-      <c r="Q32" s="152"/>
-      <c r="R32" s="151"/>
+      <c r="Q32" s="221"/>
+      <c r="R32" s="146"/>
       <c r="S32" s="33"/>
       <c r="T32" s="33"/>
       <c r="U32" s="34"/>
-      <c r="V32" s="288"/>
+      <c r="V32" s="165"/>
     </row>
     <row r="33" spans="1:22" s="2" customFormat="1" ht="21" customHeight="1">
-      <c r="B33" s="154"/>
-      <c r="C33" s="168"/>
-      <c r="D33" s="168"/>
-      <c r="E33" s="168"/>
-      <c r="F33" s="168"/>
-      <c r="G33" s="168"/>
-      <c r="H33" s="168"/>
-      <c r="I33" s="168"/>
-      <c r="J33" s="168"/>
-      <c r="K33" s="155"/>
-      <c r="L33" s="165"/>
-      <c r="M33" s="142"/>
-      <c r="N33" s="251"/>
-      <c r="O33" s="155"/>
+      <c r="B33" s="228"/>
+      <c r="C33" s="151"/>
+      <c r="D33" s="151"/>
+      <c r="E33" s="151"/>
+      <c r="F33" s="151"/>
+      <c r="G33" s="151"/>
+      <c r="H33" s="151"/>
+      <c r="I33" s="151"/>
+      <c r="J33" s="151"/>
+      <c r="K33" s="152"/>
+      <c r="L33" s="233"/>
+      <c r="M33" s="188"/>
+      <c r="N33" s="263"/>
+      <c r="O33" s="152"/>
       <c r="P33" s="99"/>
-      <c r="Q33" s="249"/>
-      <c r="R33" s="155"/>
+      <c r="Q33" s="261"/>
+      <c r="R33" s="152"/>
       <c r="S33" s="36"/>
       <c r="T33" s="36"/>
       <c r="U33" s="32"/>
-      <c r="V33" s="288"/>
+      <c r="V33" s="165"/>
     </row>
     <row r="34" spans="1:22" s="2" customFormat="1" ht="21" customHeight="1">
-      <c r="B34" s="167" t="s">
+      <c r="B34" s="306" t="s">
         <v>48</v>
       </c>
-      <c r="C34" s="150"/>
-      <c r="D34" s="150"/>
-      <c r="E34" s="150"/>
-      <c r="F34" s="150"/>
-      <c r="G34" s="150"/>
-      <c r="H34" s="150"/>
-      <c r="I34" s="150"/>
-      <c r="J34" s="150"/>
-      <c r="K34" s="151"/>
-      <c r="L34" s="165"/>
-      <c r="M34" s="232" t="s">
+      <c r="C34" s="145"/>
+      <c r="D34" s="145"/>
+      <c r="E34" s="145"/>
+      <c r="F34" s="145"/>
+      <c r="G34" s="145"/>
+      <c r="H34" s="145"/>
+      <c r="I34" s="145"/>
+      <c r="J34" s="145"/>
+      <c r="K34" s="146"/>
+      <c r="L34" s="233"/>
+      <c r="M34" s="243" t="s">
         <v>49</v>
       </c>
-      <c r="N34" s="152"/>
-      <c r="O34" s="151"/>
+      <c r="N34" s="221"/>
+      <c r="O34" s="146"/>
       <c r="P34" s="24"/>
-      <c r="Q34" s="152"/>
-      <c r="R34" s="151"/>
+      <c r="Q34" s="221"/>
+      <c r="R34" s="146"/>
       <c r="S34" s="25"/>
       <c r="T34" s="25"/>
       <c r="U34" s="26"/>
-      <c r="V34" s="288"/>
+      <c r="V34" s="165"/>
     </row>
     <row r="35" spans="1:22" s="2" customFormat="1" ht="21" customHeight="1">
-      <c r="B35" s="154"/>
-      <c r="C35" s="168"/>
-      <c r="D35" s="168"/>
-      <c r="E35" s="168"/>
-      <c r="F35" s="168"/>
-      <c r="G35" s="168"/>
-      <c r="H35" s="168"/>
-      <c r="I35" s="168"/>
-      <c r="J35" s="168"/>
-      <c r="K35" s="155"/>
-      <c r="L35" s="165"/>
-      <c r="M35" s="142"/>
-      <c r="N35" s="142"/>
-      <c r="O35" s="155"/>
+      <c r="B35" s="228"/>
+      <c r="C35" s="151"/>
+      <c r="D35" s="151"/>
+      <c r="E35" s="151"/>
+      <c r="F35" s="151"/>
+      <c r="G35" s="151"/>
+      <c r="H35" s="151"/>
+      <c r="I35" s="151"/>
+      <c r="J35" s="151"/>
+      <c r="K35" s="152"/>
+      <c r="L35" s="233"/>
+      <c r="M35" s="188"/>
+      <c r="N35" s="188"/>
+      <c r="O35" s="152"/>
       <c r="P35" s="35"/>
-      <c r="Q35" s="142"/>
-      <c r="R35" s="155"/>
+      <c r="Q35" s="188"/>
+      <c r="R35" s="152"/>
       <c r="S35" s="36"/>
       <c r="T35" s="36"/>
       <c r="U35" s="32"/>
-      <c r="V35" s="288"/>
+      <c r="V35" s="165"/>
     </row>
     <row r="36" spans="1:22" s="2" customFormat="1" ht="21" customHeight="1">
       <c r="B36" s="37" t="s">
         <v>50</v>
       </c>
       <c r="C36" s="38"/>
-      <c r="D36" s="149"/>
-      <c r="E36" s="150"/>
-      <c r="F36" s="150"/>
-      <c r="G36" s="150"/>
-      <c r="H36" s="150"/>
-      <c r="I36" s="150"/>
-      <c r="J36" s="150"/>
-      <c r="K36" s="151"/>
-      <c r="L36" s="165"/>
-      <c r="M36" s="232" t="s">
+      <c r="D36" s="302"/>
+      <c r="E36" s="145"/>
+      <c r="F36" s="145"/>
+      <c r="G36" s="145"/>
+      <c r="H36" s="145"/>
+      <c r="I36" s="145"/>
+      <c r="J36" s="145"/>
+      <c r="K36" s="146"/>
+      <c r="L36" s="233"/>
+      <c r="M36" s="243" t="s">
         <v>51</v>
       </c>
-      <c r="N36" s="152"/>
-      <c r="O36" s="151"/>
+      <c r="N36" s="221"/>
+      <c r="O36" s="146"/>
       <c r="P36" s="24"/>
-      <c r="Q36" s="152"/>
-      <c r="R36" s="151"/>
+      <c r="Q36" s="221"/>
+      <c r="R36" s="146"/>
       <c r="S36" s="25"/>
       <c r="T36" s="25"/>
       <c r="U36" s="26"/>
-      <c r="V36" s="288"/>
+      <c r="V36" s="165"/>
     </row>
     <row r="37" spans="1:22" s="2" customFormat="1" ht="49.2" customHeight="1">
-      <c r="B37" s="169" t="s">
+      <c r="B37" s="307" t="s">
         <v>52</v>
       </c>
-      <c r="C37" s="170"/>
+      <c r="C37" s="161"/>
       <c r="D37" s="124" t="s">
         <v>53</v>
       </c>
-      <c r="E37" s="241" t="s">
+      <c r="E37" s="259" t="s">
         <v>54</v>
       </c>
-      <c r="F37" s="170"/>
-      <c r="G37" s="172"/>
+      <c r="F37" s="161"/>
+      <c r="G37" s="260"/>
       <c r="H37" s="113" t="s">
         <v>55</v>
       </c>
-      <c r="I37" s="189" t="s">
+      <c r="I37" s="270" t="s">
         <v>56</v>
       </c>
-      <c r="J37" s="190"/>
+      <c r="J37" s="271"/>
       <c r="K37" s="114" t="s">
         <v>57</v>
       </c>
-      <c r="L37" s="165"/>
-      <c r="M37" s="142"/>
-      <c r="N37" s="142"/>
-      <c r="O37" s="155"/>
+      <c r="L37" s="233"/>
+      <c r="M37" s="188"/>
+      <c r="N37" s="188"/>
+      <c r="O37" s="152"/>
       <c r="P37" s="35"/>
-      <c r="Q37" s="142"/>
-      <c r="R37" s="155"/>
+      <c r="Q37" s="188"/>
+      <c r="R37" s="152"/>
       <c r="S37" s="36"/>
       <c r="T37" s="36"/>
       <c r="U37" s="32"/>
-      <c r="V37" s="288"/>
+      <c r="V37" s="165"/>
     </row>
     <row r="38" spans="1:22" s="2" customFormat="1" ht="24.6" customHeight="1">
-      <c r="B38" s="173"/>
-      <c r="C38" s="172"/>
-      <c r="D38" s="238"/>
-      <c r="E38" s="315"/>
-      <c r="F38" s="316"/>
-      <c r="G38" s="317"/>
-      <c r="H38" s="227"/>
-      <c r="I38" s="304"/>
-      <c r="J38" s="305"/>
-      <c r="K38" s="230"/>
-      <c r="L38" s="165"/>
-      <c r="M38" s="232" t="s">
+      <c r="B38" s="309"/>
+      <c r="C38" s="260"/>
+      <c r="D38" s="256"/>
+      <c r="E38" s="202"/>
+      <c r="F38" s="203"/>
+      <c r="G38" s="204"/>
+      <c r="H38" s="264"/>
+      <c r="I38" s="190"/>
+      <c r="J38" s="191"/>
+      <c r="K38" s="268"/>
+      <c r="L38" s="233"/>
+      <c r="M38" s="243" t="s">
         <v>58</v>
       </c>
-      <c r="N38" s="152"/>
-      <c r="O38" s="151"/>
+      <c r="N38" s="221"/>
+      <c r="O38" s="146"/>
       <c r="P38" s="24"/>
-      <c r="Q38" s="152"/>
-      <c r="R38" s="151"/>
+      <c r="Q38" s="221"/>
+      <c r="R38" s="146"/>
       <c r="S38" s="25"/>
       <c r="T38" s="25"/>
       <c r="U38" s="26"/>
-      <c r="V38" s="288"/>
+      <c r="V38" s="165"/>
     </row>
     <row r="39" spans="1:22" s="2" customFormat="1" ht="22.95" customHeight="1">
-      <c r="B39" s="171"/>
-      <c r="C39" s="172"/>
-      <c r="D39" s="239"/>
-      <c r="E39" s="318"/>
-      <c r="F39" s="319"/>
-      <c r="G39" s="320"/>
-      <c r="H39" s="228"/>
-      <c r="I39" s="306"/>
-      <c r="J39" s="307"/>
-      <c r="K39" s="231"/>
-      <c r="L39" s="165"/>
-      <c r="M39" s="142"/>
-      <c r="N39" s="142"/>
-      <c r="O39" s="155"/>
+      <c r="B39" s="308"/>
+      <c r="C39" s="260"/>
+      <c r="D39" s="257"/>
+      <c r="E39" s="205"/>
+      <c r="F39" s="206"/>
+      <c r="G39" s="207"/>
+      <c r="H39" s="265"/>
+      <c r="I39" s="192"/>
+      <c r="J39" s="193"/>
+      <c r="K39" s="269"/>
+      <c r="L39" s="233"/>
+      <c r="M39" s="188"/>
+      <c r="N39" s="188"/>
+      <c r="O39" s="152"/>
       <c r="P39" s="35"/>
-      <c r="Q39" s="142"/>
-      <c r="R39" s="155"/>
+      <c r="Q39" s="188"/>
+      <c r="R39" s="152"/>
       <c r="S39" s="36"/>
       <c r="T39" s="36"/>
       <c r="U39" s="32"/>
-      <c r="V39" s="288"/>
+      <c r="V39" s="165"/>
     </row>
     <row r="40" spans="1:22" s="2" customFormat="1" ht="29.25" customHeight="1">
       <c r="A40" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="B40" s="240"/>
-      <c r="C40" s="170"/>
-      <c r="D40" s="157"/>
-      <c r="E40" s="274"/>
-      <c r="F40" s="170"/>
-      <c r="G40" s="157"/>
-      <c r="H40" s="273"/>
-      <c r="I40" s="155"/>
+      <c r="B40" s="258"/>
+      <c r="C40" s="161"/>
+      <c r="D40" s="162"/>
+      <c r="E40" s="220"/>
+      <c r="F40" s="161"/>
+      <c r="G40" s="162"/>
+      <c r="H40" s="218"/>
+      <c r="I40" s="152"/>
       <c r="K40" s="98"/>
-      <c r="L40" s="165"/>
-      <c r="M40" s="232" t="s">
+      <c r="L40" s="233"/>
+      <c r="M40" s="243" t="s">
         <v>60</v>
       </c>
-      <c r="N40" s="152"/>
-      <c r="O40" s="151"/>
+      <c r="N40" s="221"/>
+      <c r="O40" s="146"/>
       <c r="P40" s="24"/>
-      <c r="Q40" s="152"/>
-      <c r="R40" s="151"/>
+      <c r="Q40" s="221"/>
+      <c r="R40" s="146"/>
       <c r="S40" s="25"/>
       <c r="T40" s="25"/>
       <c r="U40" s="26"/>
-      <c r="V40" s="288"/>
+      <c r="V40" s="165"/>
     </row>
     <row r="41" spans="1:22" s="2" customFormat="1" ht="21" customHeight="1">
       <c r="B41" s="39"/>
@@ -4016,143 +4013,143 @@
       <c r="I41" s="40"/>
       <c r="J41" s="90"/>
       <c r="K41" s="95"/>
-      <c r="L41" s="166"/>
-      <c r="M41" s="142"/>
-      <c r="N41" s="142"/>
-      <c r="O41" s="155"/>
+      <c r="L41" s="234"/>
+      <c r="M41" s="188"/>
+      <c r="N41" s="188"/>
+      <c r="O41" s="152"/>
       <c r="P41" s="35"/>
-      <c r="Q41" s="142"/>
-      <c r="R41" s="155"/>
+      <c r="Q41" s="188"/>
+      <c r="R41" s="152"/>
       <c r="S41" s="36"/>
       <c r="T41" s="36"/>
       <c r="U41" s="32"/>
-      <c r="V41" s="288"/>
+      <c r="V41" s="165"/>
     </row>
     <row r="42" spans="1:22" ht="18" customHeight="1">
-      <c r="B42" s="191" t="s">
+      <c r="B42" s="253" t="s">
         <v>62</v>
       </c>
       <c r="C42" s="41"/>
       <c r="D42" s="41"/>
-      <c r="E42" s="209" t="s">
+      <c r="E42" s="163" t="s">
         <v>63</v>
       </c>
-      <c r="F42" s="151"/>
-      <c r="G42" s="208" t="s">
+      <c r="F42" s="146"/>
+      <c r="G42" s="266" t="s">
         <v>64</v>
       </c>
-      <c r="H42" s="151"/>
-      <c r="I42" s="204" t="s">
+      <c r="H42" s="146"/>
+      <c r="I42" s="144" t="s">
         <v>65</v>
       </c>
       <c r="J42" s="94" t="s">
         <v>66</v>
       </c>
-      <c r="K42" s="208" t="s">
+      <c r="K42" s="266" t="s">
         <v>67</v>
       </c>
-      <c r="L42" s="150"/>
-      <c r="M42" s="151"/>
-      <c r="N42" s="204" t="s">
+      <c r="L42" s="145"/>
+      <c r="M42" s="146"/>
+      <c r="N42" s="144" t="s">
         <v>68</v>
       </c>
       <c r="O42" s="42" t="s">
         <v>66</v>
       </c>
-      <c r="P42" s="204" t="s">
+      <c r="P42" s="144" t="s">
         <v>69</v>
       </c>
       <c r="Q42" s="41"/>
-      <c r="R42" s="204" t="s">
+      <c r="R42" s="144" t="s">
         <v>70</v>
       </c>
-      <c r="S42" s="150"/>
-      <c r="T42" s="151"/>
-      <c r="U42" s="278" t="s">
+      <c r="S42" s="145"/>
+      <c r="T42" s="146"/>
+      <c r="U42" s="141" t="s">
         <v>71</v>
       </c>
-      <c r="V42" s="288"/>
+      <c r="V42" s="165"/>
     </row>
     <row r="43" spans="1:22" ht="50.4" customHeight="1">
-      <c r="B43" s="192"/>
+      <c r="B43" s="254"/>
       <c r="C43" s="94" t="s">
         <v>72</v>
       </c>
       <c r="D43" s="116" t="s">
         <v>73</v>
       </c>
-      <c r="E43" s="162"/>
-      <c r="F43" s="181"/>
-      <c r="G43" s="163"/>
-      <c r="H43" s="155"/>
-      <c r="I43" s="205"/>
-      <c r="J43" s="229" t="s">
+      <c r="E43" s="147"/>
+      <c r="F43" s="149"/>
+      <c r="G43" s="150"/>
+      <c r="H43" s="152"/>
+      <c r="I43" s="187"/>
+      <c r="J43" s="267" t="s">
         <v>74</v>
       </c>
-      <c r="K43" s="163"/>
-      <c r="L43" s="168"/>
-      <c r="M43" s="155"/>
-      <c r="N43" s="205"/>
-      <c r="O43" s="158" t="s">
+      <c r="K43" s="150"/>
+      <c r="L43" s="151"/>
+      <c r="M43" s="152"/>
+      <c r="N43" s="187"/>
+      <c r="O43" s="272" t="s">
         <v>74</v>
       </c>
-      <c r="P43" s="205"/>
+      <c r="P43" s="187"/>
       <c r="Q43" s="43" t="s">
         <v>75</v>
       </c>
-      <c r="R43" s="162"/>
-      <c r="S43" s="200"/>
-      <c r="T43" s="181"/>
-      <c r="U43" s="279"/>
-      <c r="V43" s="288"/>
+      <c r="R43" s="147"/>
+      <c r="S43" s="148"/>
+      <c r="T43" s="149"/>
+      <c r="U43" s="142"/>
+      <c r="V43" s="165"/>
     </row>
     <row r="44" spans="1:22" ht="55.5" customHeight="1">
-      <c r="B44" s="192"/>
+      <c r="B44" s="254"/>
       <c r="C44" s="110" t="s">
         <v>76</v>
       </c>
       <c r="D44" s="109" t="s">
         <v>77</v>
       </c>
-      <c r="E44" s="163"/>
-      <c r="F44" s="155"/>
+      <c r="E44" s="150"/>
+      <c r="F44" s="152"/>
       <c r="G44" s="45" t="s">
         <v>78</v>
       </c>
       <c r="H44" s="72" t="s">
         <v>79</v>
       </c>
-      <c r="I44" s="142"/>
-      <c r="J44" s="142"/>
+      <c r="I44" s="188"/>
+      <c r="J44" s="188"/>
       <c r="K44" s="115" t="s">
         <v>80</v>
       </c>
-      <c r="L44" s="321" t="s">
+      <c r="L44" s="208" t="s">
         <v>79</v>
       </c>
-      <c r="M44" s="157"/>
-      <c r="N44" s="142"/>
-      <c r="O44" s="142"/>
-      <c r="P44" s="142"/>
+      <c r="M44" s="162"/>
+      <c r="N44" s="188"/>
+      <c r="O44" s="188"/>
+      <c r="P44" s="188"/>
       <c r="Q44" s="46" t="s">
         <v>81</v>
       </c>
-      <c r="R44" s="163"/>
-      <c r="S44" s="168"/>
-      <c r="T44" s="155"/>
-      <c r="U44" s="280"/>
-      <c r="V44" s="288"/>
+      <c r="R44" s="150"/>
+      <c r="S44" s="151"/>
+      <c r="T44" s="152"/>
+      <c r="U44" s="143"/>
+      <c r="V44" s="165"/>
     </row>
     <row r="45" spans="1:22" ht="50.1" customHeight="1">
-      <c r="B45" s="192"/>
+      <c r="B45" s="254"/>
       <c r="C45" s="111">
         <v>1</v>
       </c>
       <c r="D45" s="105" t="s">
         <v>82</v>
       </c>
-      <c r="E45" s="210"/>
-      <c r="F45" s="157"/>
+      <c r="E45" s="189"/>
+      <c r="F45" s="162"/>
       <c r="G45" s="49" t="s">
         <v>83</v>
       </c>
@@ -4162,28 +4159,28 @@
       <c r="K45" s="49" t="s">
         <v>83</v>
       </c>
-      <c r="L45" s="159"/>
-      <c r="M45" s="157"/>
+      <c r="L45" s="219"/>
+      <c r="M45" s="162"/>
       <c r="N45" s="52"/>
       <c r="O45" s="52"/>
       <c r="P45" s="53"/>
       <c r="Q45" s="54"/>
-      <c r="R45" s="194"/>
-      <c r="S45" s="170"/>
-      <c r="T45" s="157"/>
+      <c r="R45" s="160"/>
+      <c r="S45" s="161"/>
+      <c r="T45" s="162"/>
       <c r="U45" s="57"/>
-      <c r="V45" s="288"/>
+      <c r="V45" s="165"/>
     </row>
     <row r="46" spans="1:22" ht="50.1" customHeight="1">
-      <c r="B46" s="192"/>
+      <c r="B46" s="254"/>
       <c r="C46" s="112">
         <v>2</v>
       </c>
       <c r="D46" s="106" t="s">
         <v>84</v>
       </c>
-      <c r="E46" s="210"/>
-      <c r="F46" s="157"/>
+      <c r="E46" s="189"/>
+      <c r="F46" s="162"/>
       <c r="G46" s="49" t="s">
         <v>83</v>
       </c>
@@ -4193,28 +4190,28 @@
       <c r="K46" s="49" t="s">
         <v>83</v>
       </c>
-      <c r="L46" s="159"/>
-      <c r="M46" s="157"/>
+      <c r="L46" s="219"/>
+      <c r="M46" s="162"/>
       <c r="N46" s="50"/>
       <c r="O46" s="50"/>
       <c r="P46" s="60"/>
       <c r="Q46" s="61"/>
-      <c r="R46" s="194"/>
-      <c r="S46" s="170"/>
-      <c r="T46" s="157"/>
+      <c r="R46" s="160"/>
+      <c r="S46" s="161"/>
+      <c r="T46" s="162"/>
       <c r="U46" s="57"/>
-      <c r="V46" s="288"/>
+      <c r="V46" s="165"/>
     </row>
     <row r="47" spans="1:22" ht="50.1" customHeight="1">
-      <c r="B47" s="192"/>
+      <c r="B47" s="254"/>
       <c r="C47" s="112">
         <v>3</v>
       </c>
       <c r="D47" s="106" t="s">
         <v>85</v>
       </c>
-      <c r="E47" s="210"/>
-      <c r="F47" s="157"/>
+      <c r="E47" s="189"/>
+      <c r="F47" s="162"/>
       <c r="G47" s="49" t="s">
         <v>83</v>
       </c>
@@ -4224,28 +4221,28 @@
       <c r="K47" s="49" t="s">
         <v>83</v>
       </c>
-      <c r="L47" s="159"/>
-      <c r="M47" s="157"/>
+      <c r="L47" s="219"/>
+      <c r="M47" s="162"/>
       <c r="N47" s="50"/>
       <c r="O47" s="50"/>
       <c r="P47" s="53"/>
       <c r="Q47" s="61"/>
-      <c r="R47" s="194"/>
-      <c r="S47" s="170"/>
-      <c r="T47" s="157"/>
+      <c r="R47" s="160"/>
+      <c r="S47" s="161"/>
+      <c r="T47" s="162"/>
       <c r="U47" s="57"/>
-      <c r="V47" s="288"/>
+      <c r="V47" s="165"/>
     </row>
     <row r="48" spans="1:22" ht="50.1" customHeight="1">
-      <c r="B48" s="192"/>
+      <c r="B48" s="254"/>
       <c r="C48" s="112">
         <v>4</v>
       </c>
       <c r="D48" s="106" t="s">
         <v>86</v>
       </c>
-      <c r="E48" s="210"/>
-      <c r="F48" s="157"/>
+      <c r="E48" s="189"/>
+      <c r="F48" s="162"/>
       <c r="G48" s="49" t="s">
         <v>83</v>
       </c>
@@ -4255,28 +4252,28 @@
       <c r="K48" s="49" t="s">
         <v>83</v>
       </c>
-      <c r="L48" s="159"/>
-      <c r="M48" s="157"/>
+      <c r="L48" s="219"/>
+      <c r="M48" s="162"/>
       <c r="N48" s="50"/>
       <c r="O48" s="50"/>
       <c r="P48" s="53"/>
       <c r="Q48" s="61"/>
-      <c r="R48" s="194"/>
-      <c r="S48" s="170"/>
-      <c r="T48" s="157"/>
+      <c r="R48" s="160"/>
+      <c r="S48" s="161"/>
+      <c r="T48" s="162"/>
       <c r="U48" s="57"/>
-      <c r="V48" s="288"/>
+      <c r="V48" s="165"/>
     </row>
     <row r="49" spans="2:23" ht="50.1" customHeight="1">
-      <c r="B49" s="192"/>
+      <c r="B49" s="254"/>
       <c r="C49" s="112">
         <v>5</v>
       </c>
       <c r="D49" s="107" t="s">
         <v>87</v>
       </c>
-      <c r="E49" s="210"/>
-      <c r="F49" s="157"/>
+      <c r="E49" s="189"/>
+      <c r="F49" s="162"/>
       <c r="G49" s="49" t="s">
         <v>83</v>
       </c>
@@ -4286,28 +4283,28 @@
       <c r="K49" s="49" t="s">
         <v>83</v>
       </c>
-      <c r="L49" s="159"/>
-      <c r="M49" s="157"/>
+      <c r="L49" s="219"/>
+      <c r="M49" s="162"/>
       <c r="N49" s="50"/>
       <c r="O49" s="50"/>
       <c r="P49" s="53"/>
       <c r="Q49" s="61"/>
-      <c r="R49" s="194"/>
-      <c r="S49" s="170"/>
-      <c r="T49" s="157"/>
+      <c r="R49" s="160"/>
+      <c r="S49" s="161"/>
+      <c r="T49" s="162"/>
       <c r="U49" s="57"/>
-      <c r="V49" s="288"/>
+      <c r="V49" s="165"/>
     </row>
     <row r="50" spans="2:23" ht="53.4" customHeight="1">
-      <c r="B50" s="192"/>
+      <c r="B50" s="254"/>
       <c r="C50" s="112">
         <v>6</v>
       </c>
       <c r="D50" s="108" t="s">
         <v>88</v>
       </c>
-      <c r="E50" s="210"/>
-      <c r="F50" s="157"/>
+      <c r="E50" s="189"/>
+      <c r="F50" s="162"/>
       <c r="G50" s="49" t="s">
         <v>83</v>
       </c>
@@ -4317,28 +4314,28 @@
       <c r="K50" s="49" t="s">
         <v>83</v>
       </c>
-      <c r="L50" s="159"/>
-      <c r="M50" s="157"/>
+      <c r="L50" s="219"/>
+      <c r="M50" s="162"/>
       <c r="N50" s="50"/>
       <c r="O50" s="50"/>
       <c r="P50" s="53"/>
       <c r="Q50" s="61"/>
-      <c r="R50" s="194"/>
-      <c r="S50" s="170"/>
-      <c r="T50" s="157"/>
+      <c r="R50" s="160"/>
+      <c r="S50" s="161"/>
+      <c r="T50" s="162"/>
       <c r="U50" s="57"/>
-      <c r="V50" s="288"/>
+      <c r="V50" s="165"/>
     </row>
     <row r="51" spans="2:23" ht="50.1" customHeight="1">
-      <c r="B51" s="193"/>
+      <c r="B51" s="255"/>
       <c r="C51" s="111">
         <v>7</v>
       </c>
       <c r="D51" s="108" t="s">
         <v>89</v>
       </c>
-      <c r="E51" s="210"/>
-      <c r="F51" s="157"/>
+      <c r="E51" s="189"/>
+      <c r="F51" s="162"/>
       <c r="G51" s="49" t="s">
         <v>83</v>
       </c>
@@ -4348,17 +4345,17 @@
       <c r="K51" s="49" t="s">
         <v>83</v>
       </c>
-      <c r="L51" s="159"/>
-      <c r="M51" s="157"/>
+      <c r="L51" s="219"/>
+      <c r="M51" s="162"/>
       <c r="N51" s="52"/>
       <c r="O51" s="52"/>
       <c r="P51" s="60"/>
       <c r="Q51" s="54"/>
-      <c r="R51" s="194"/>
-      <c r="S51" s="170"/>
-      <c r="T51" s="157"/>
+      <c r="R51" s="160"/>
+      <c r="S51" s="161"/>
+      <c r="T51" s="162"/>
       <c r="U51" s="57"/>
-      <c r="V51" s="288"/>
+      <c r="V51" s="165"/>
     </row>
     <row r="52" spans="2:23" ht="3.75" customHeight="1">
       <c r="B52" s="62"/>
@@ -4381,131 +4378,131 @@
       <c r="S52" s="63"/>
       <c r="T52" s="69"/>
       <c r="U52" s="70"/>
-      <c r="V52" s="288"/>
+      <c r="V52" s="165"/>
     </row>
     <row r="53" spans="2:23" ht="18" customHeight="1">
-      <c r="B53" s="191" t="s">
+      <c r="B53" s="253" t="s">
         <v>90</v>
       </c>
       <c r="C53" s="71"/>
       <c r="D53" s="71"/>
-      <c r="E53" s="209" t="s">
+      <c r="E53" s="163" t="s">
         <v>63</v>
       </c>
-      <c r="F53" s="151"/>
-      <c r="G53" s="156" t="s">
+      <c r="F53" s="146"/>
+      <c r="G53" s="164" t="s">
         <v>91</v>
       </c>
-      <c r="H53" s="151"/>
-      <c r="I53" s="204" t="s">
+      <c r="H53" s="146"/>
+      <c r="I53" s="144" t="s">
         <v>92</v>
       </c>
-      <c r="J53" s="275" t="s">
+      <c r="J53" s="222" t="s">
         <v>93</v>
       </c>
-      <c r="K53" s="156" t="s">
+      <c r="K53" s="164" t="s">
         <v>67</v>
       </c>
-      <c r="L53" s="150"/>
-      <c r="M53" s="151"/>
-      <c r="N53" s="204" t="s">
+      <c r="L53" s="145"/>
+      <c r="M53" s="146"/>
+      <c r="N53" s="144" t="s">
         <v>68</v>
       </c>
       <c r="O53" s="42" t="s">
         <v>66</v>
       </c>
-      <c r="P53" s="204" t="s">
+      <c r="P53" s="144" t="s">
         <v>69</v>
       </c>
       <c r="Q53" s="41"/>
-      <c r="R53" s="204" t="s">
+      <c r="R53" s="144" t="s">
         <v>70</v>
       </c>
-      <c r="S53" s="150"/>
-      <c r="T53" s="151"/>
-      <c r="U53" s="287" t="s">
+      <c r="S53" s="145"/>
+      <c r="T53" s="146"/>
+      <c r="U53" s="159" t="s">
         <v>71</v>
       </c>
-      <c r="V53" s="288"/>
+      <c r="V53" s="165"/>
     </row>
     <row r="54" spans="2:23" ht="50.4" customHeight="1">
-      <c r="B54" s="192"/>
+      <c r="B54" s="254"/>
       <c r="C54" s="41" t="s">
         <v>72</v>
       </c>
       <c r="D54" s="41" t="s">
         <v>73</v>
       </c>
-      <c r="E54" s="162"/>
-      <c r="F54" s="181"/>
-      <c r="G54" s="163"/>
-      <c r="H54" s="155"/>
-      <c r="I54" s="205"/>
-      <c r="J54" s="205"/>
-      <c r="K54" s="163"/>
-      <c r="L54" s="168"/>
-      <c r="M54" s="155"/>
-      <c r="N54" s="205"/>
-      <c r="O54" s="158" t="s">
+      <c r="E54" s="147"/>
+      <c r="F54" s="149"/>
+      <c r="G54" s="150"/>
+      <c r="H54" s="152"/>
+      <c r="I54" s="187"/>
+      <c r="J54" s="187"/>
+      <c r="K54" s="150"/>
+      <c r="L54" s="151"/>
+      <c r="M54" s="152"/>
+      <c r="N54" s="187"/>
+      <c r="O54" s="272" t="s">
         <v>74</v>
       </c>
-      <c r="P54" s="205"/>
+      <c r="P54" s="187"/>
       <c r="Q54" s="43" t="s">
         <v>75</v>
       </c>
-      <c r="R54" s="162"/>
-      <c r="S54" s="200"/>
-      <c r="T54" s="181"/>
-      <c r="U54" s="279"/>
-      <c r="V54" s="288"/>
+      <c r="R54" s="147"/>
+      <c r="S54" s="148"/>
+      <c r="T54" s="149"/>
+      <c r="U54" s="142"/>
+      <c r="V54" s="165"/>
     </row>
     <row r="55" spans="2:23" ht="50.4" customHeight="1">
-      <c r="B55" s="192"/>
+      <c r="B55" s="254"/>
       <c r="C55" s="44" t="s">
         <v>76</v>
       </c>
       <c r="D55" s="44" t="s">
         <v>77</v>
       </c>
-      <c r="E55" s="163"/>
-      <c r="F55" s="155"/>
+      <c r="E55" s="150"/>
+      <c r="F55" s="152"/>
       <c r="G55" s="45" t="s">
         <v>80</v>
       </c>
       <c r="H55" s="72" t="s">
         <v>79</v>
       </c>
-      <c r="I55" s="142"/>
-      <c r="J55" s="142"/>
+      <c r="I55" s="188"/>
+      <c r="J55" s="188"/>
       <c r="K55" s="45" t="s">
         <v>80</v>
       </c>
-      <c r="L55" s="156" t="s">
+      <c r="L55" s="164" t="s">
         <v>79</v>
       </c>
-      <c r="M55" s="157"/>
-      <c r="N55" s="142"/>
-      <c r="O55" s="142"/>
-      <c r="P55" s="142"/>
+      <c r="M55" s="162"/>
+      <c r="N55" s="188"/>
+      <c r="O55" s="188"/>
+      <c r="P55" s="188"/>
       <c r="Q55" s="46" t="s">
         <v>81</v>
       </c>
-      <c r="R55" s="163"/>
-      <c r="S55" s="168"/>
-      <c r="T55" s="155"/>
-      <c r="U55" s="280"/>
-      <c r="V55" s="288"/>
+      <c r="R55" s="150"/>
+      <c r="S55" s="151"/>
+      <c r="T55" s="152"/>
+      <c r="U55" s="143"/>
+      <c r="V55" s="165"/>
     </row>
     <row r="56" spans="2:23" ht="30" customHeight="1">
-      <c r="B56" s="192"/>
+      <c r="B56" s="254"/>
       <c r="C56" s="47">
         <v>1</v>
       </c>
       <c r="D56" s="48" t="s">
         <v>82</v>
       </c>
-      <c r="E56" s="210"/>
-      <c r="F56" s="157"/>
+      <c r="E56" s="189"/>
+      <c r="F56" s="162"/>
       <c r="G56" s="49" t="s">
         <v>83</v>
       </c>
@@ -4515,8 +4512,8 @@
       <c r="K56" s="49" t="s">
         <v>83</v>
       </c>
-      <c r="L56" s="159"/>
-      <c r="M56" s="157"/>
+      <c r="L56" s="219"/>
+      <c r="M56" s="162"/>
       <c r="N56" s="52"/>
       <c r="O56" s="52"/>
       <c r="P56" s="60"/>
@@ -4525,18 +4522,18 @@
       <c r="S56" s="56"/>
       <c r="T56" s="18"/>
       <c r="U56" s="57"/>
-      <c r="V56" s="288"/>
+      <c r="V56" s="165"/>
     </row>
     <row r="57" spans="2:23" ht="30" customHeight="1">
-      <c r="B57" s="192"/>
+      <c r="B57" s="254"/>
       <c r="C57" s="55">
         <v>2</v>
       </c>
       <c r="D57" s="74" t="s">
         <v>94</v>
       </c>
-      <c r="E57" s="210"/>
-      <c r="F57" s="157"/>
+      <c r="E57" s="189"/>
+      <c r="F57" s="162"/>
       <c r="G57" s="49" t="s">
         <v>83</v>
       </c>
@@ -4546,8 +4543,8 @@
       <c r="K57" s="49" t="s">
         <v>83</v>
       </c>
-      <c r="L57" s="159"/>
-      <c r="M57" s="157"/>
+      <c r="L57" s="219"/>
+      <c r="M57" s="162"/>
       <c r="N57" s="50"/>
       <c r="O57" s="50"/>
       <c r="P57" s="53"/>
@@ -4556,18 +4553,18 @@
       <c r="S57" s="56"/>
       <c r="T57" s="18"/>
       <c r="U57" s="57"/>
-      <c r="V57" s="288"/>
+      <c r="V57" s="165"/>
     </row>
     <row r="58" spans="2:23" ht="30" customHeight="1">
-      <c r="B58" s="192"/>
+      <c r="B58" s="254"/>
       <c r="C58" s="55">
         <v>3</v>
       </c>
       <c r="D58" s="76" t="s">
         <v>95</v>
       </c>
-      <c r="E58" s="210"/>
-      <c r="F58" s="157"/>
+      <c r="E58" s="189"/>
+      <c r="F58" s="162"/>
       <c r="G58" s="49" t="s">
         <v>83</v>
       </c>
@@ -4577,8 +4574,8 @@
       <c r="K58" s="49" t="s">
         <v>83</v>
       </c>
-      <c r="L58" s="159"/>
-      <c r="M58" s="157"/>
+      <c r="L58" s="219"/>
+      <c r="M58" s="162"/>
       <c r="N58" s="50"/>
       <c r="O58" s="50"/>
       <c r="P58" s="53"/>
@@ -4587,18 +4584,18 @@
       <c r="S58" s="56"/>
       <c r="T58" s="18"/>
       <c r="U58" s="57"/>
-      <c r="V58" s="288"/>
+      <c r="V58" s="165"/>
     </row>
     <row r="59" spans="2:23" ht="30" customHeight="1">
-      <c r="B59" s="192"/>
+      <c r="B59" s="254"/>
       <c r="C59" s="77">
         <v>4</v>
       </c>
       <c r="D59" s="78" t="s">
         <v>96</v>
       </c>
-      <c r="E59" s="210"/>
-      <c r="F59" s="157"/>
+      <c r="E59" s="189"/>
+      <c r="F59" s="162"/>
       <c r="G59" s="49" t="s">
         <v>83</v>
       </c>
@@ -4608,8 +4605,8 @@
       <c r="K59" s="58" t="s">
         <v>83</v>
       </c>
-      <c r="L59" s="159"/>
-      <c r="M59" s="157"/>
+      <c r="L59" s="219"/>
+      <c r="M59" s="162"/>
       <c r="N59" s="50"/>
       <c r="O59" s="50"/>
       <c r="P59" s="53"/>
@@ -4618,18 +4615,18 @@
       <c r="S59" s="56"/>
       <c r="T59" s="18"/>
       <c r="U59" s="57"/>
-      <c r="V59" s="288"/>
+      <c r="V59" s="165"/>
     </row>
     <row r="60" spans="2:23" ht="30" customHeight="1">
-      <c r="B60" s="192"/>
+      <c r="B60" s="254"/>
       <c r="C60" s="77">
         <v>5</v>
       </c>
       <c r="D60" s="78" t="s">
         <v>86</v>
       </c>
-      <c r="E60" s="210"/>
-      <c r="F60" s="157"/>
+      <c r="E60" s="189"/>
+      <c r="F60" s="162"/>
       <c r="G60" s="49" t="s">
         <v>83</v>
       </c>
@@ -4639,8 +4636,8 @@
       <c r="K60" s="58" t="s">
         <v>83</v>
       </c>
-      <c r="L60" s="159"/>
-      <c r="M60" s="157"/>
+      <c r="L60" s="219"/>
+      <c r="M60" s="162"/>
       <c r="N60" s="50"/>
       <c r="O60" s="50"/>
       <c r="P60" s="53"/>
@@ -4649,18 +4646,18 @@
       <c r="S60" s="81"/>
       <c r="T60" s="5"/>
       <c r="U60" s="82"/>
-      <c r="V60" s="288"/>
+      <c r="V60" s="165"/>
     </row>
     <row r="61" spans="2:23" ht="30" customHeight="1">
-      <c r="B61" s="193"/>
+      <c r="B61" s="255"/>
       <c r="C61" s="83">
         <v>6</v>
       </c>
       <c r="D61" s="84" t="s">
         <v>89</v>
       </c>
-      <c r="E61" s="210"/>
-      <c r="F61" s="157"/>
+      <c r="E61" s="189"/>
+      <c r="F61" s="162"/>
       <c r="G61" s="58" t="s">
         <v>83</v>
       </c>
@@ -4670,8 +4667,8 @@
       <c r="K61" s="83" t="s">
         <v>83</v>
       </c>
-      <c r="L61" s="159"/>
-      <c r="M61" s="157"/>
+      <c r="L61" s="219"/>
+      <c r="M61" s="162"/>
       <c r="N61" s="86"/>
       <c r="O61" s="86"/>
       <c r="P61" s="83"/>
@@ -4680,36 +4677,36 @@
       <c r="S61" s="81"/>
       <c r="T61" s="5"/>
       <c r="U61" s="82"/>
-      <c r="V61" s="288"/>
+      <c r="V61" s="165"/>
     </row>
     <row r="62" spans="2:23" ht="30" customHeight="1" thickBot="1">
-      <c r="B62" s="289" t="s">
+      <c r="B62" s="166" t="s">
         <v>97</v>
       </c>
-      <c r="C62" s="290"/>
-      <c r="D62" s="290"/>
-      <c r="E62" s="290"/>
-      <c r="F62" s="291"/>
-      <c r="G62" s="292" t="s">
+      <c r="C62" s="167"/>
+      <c r="D62" s="167"/>
+      <c r="E62" s="167"/>
+      <c r="F62" s="168"/>
+      <c r="G62" s="169" t="s">
         <v>98</v>
       </c>
-      <c r="H62" s="290"/>
-      <c r="I62" s="290"/>
-      <c r="J62" s="290"/>
-      <c r="K62" s="290"/>
-      <c r="L62" s="290"/>
-      <c r="M62" s="291"/>
-      <c r="N62" s="293" t="s">
+      <c r="H62" s="167"/>
+      <c r="I62" s="167"/>
+      <c r="J62" s="167"/>
+      <c r="K62" s="167"/>
+      <c r="L62" s="167"/>
+      <c r="M62" s="168"/>
+      <c r="N62" s="170" t="s">
         <v>99</v>
       </c>
-      <c r="O62" s="290"/>
-      <c r="P62" s="290"/>
-      <c r="Q62" s="290"/>
-      <c r="R62" s="290"/>
-      <c r="S62" s="290"/>
-      <c r="T62" s="290"/>
-      <c r="U62" s="294"/>
-      <c r="V62" s="288"/>
+      <c r="O62" s="167"/>
+      <c r="P62" s="167"/>
+      <c r="Q62" s="167"/>
+      <c r="R62" s="167"/>
+      <c r="S62" s="167"/>
+      <c r="T62" s="167"/>
+      <c r="U62" s="171"/>
+      <c r="V62" s="165"/>
     </row>
     <row r="63" spans="2:23" s="87" customFormat="1" ht="48.6" customHeight="1">
       <c r="B63" s="137"/>
@@ -4732,7 +4729,7 @@
       <c r="S63" s="140"/>
       <c r="T63" s="140"/>
       <c r="U63" s="140"/>
-      <c r="V63" s="288"/>
+      <c r="V63" s="165"/>
       <c r="W63" s="88"/>
     </row>
     <row r="64" spans="2:23" ht="14.4" customHeight="1"/>
@@ -4758,6 +4755,149 @@
     </row>
   </sheetData>
   <mergeCells count="167">
+    <mergeCell ref="D6:D7"/>
+    <mergeCell ref="K8:K11"/>
+    <mergeCell ref="D10:D11"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="D36:K36"/>
+    <mergeCell ref="Q38:R38"/>
+    <mergeCell ref="B6:C7"/>
+    <mergeCell ref="L55:M55"/>
+    <mergeCell ref="O43:O44"/>
+    <mergeCell ref="L51:M51"/>
+    <mergeCell ref="B12:C13"/>
+    <mergeCell ref="K12:K15"/>
+    <mergeCell ref="L27:L29"/>
+    <mergeCell ref="B34:K35"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="D18:D19"/>
+    <mergeCell ref="D8:D9"/>
+    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="I7:J7"/>
+    <mergeCell ref="E6:H7"/>
+    <mergeCell ref="B10:C11"/>
+    <mergeCell ref="I8:J11"/>
+    <mergeCell ref="I37:J37"/>
+    <mergeCell ref="B42:B51"/>
+    <mergeCell ref="R51:T51"/>
+    <mergeCell ref="N28:O28"/>
+    <mergeCell ref="N26:O26"/>
+    <mergeCell ref="O54:O55"/>
+    <mergeCell ref="B29:D31"/>
+    <mergeCell ref="B1:C5"/>
+    <mergeCell ref="Q36:R36"/>
+    <mergeCell ref="B18:C19"/>
+    <mergeCell ref="B8:C9"/>
+    <mergeCell ref="N34:O34"/>
+    <mergeCell ref="L49:M49"/>
+    <mergeCell ref="G53:H54"/>
+    <mergeCell ref="N42:N44"/>
+    <mergeCell ref="N27:O27"/>
+    <mergeCell ref="D3:D5"/>
+    <mergeCell ref="E53:F55"/>
+    <mergeCell ref="N36:O36"/>
+    <mergeCell ref="E47:F47"/>
+    <mergeCell ref="E8:F10"/>
+    <mergeCell ref="G8:H10"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="L61:M61"/>
+    <mergeCell ref="E58:F58"/>
+    <mergeCell ref="I42:I44"/>
+    <mergeCell ref="L48:M48"/>
+    <mergeCell ref="E50:F50"/>
+    <mergeCell ref="H38:H39"/>
+    <mergeCell ref="E61:F61"/>
+    <mergeCell ref="E59:F59"/>
+    <mergeCell ref="L58:M58"/>
+    <mergeCell ref="E56:F56"/>
+    <mergeCell ref="L60:M60"/>
+    <mergeCell ref="L45:M45"/>
+    <mergeCell ref="G42:H43"/>
+    <mergeCell ref="I53:I55"/>
+    <mergeCell ref="K42:M43"/>
+    <mergeCell ref="E46:F46"/>
+    <mergeCell ref="L57:M57"/>
+    <mergeCell ref="J43:J44"/>
+    <mergeCell ref="E57:F57"/>
+    <mergeCell ref="E48:F48"/>
+    <mergeCell ref="K38:K39"/>
+    <mergeCell ref="M38:M39"/>
+    <mergeCell ref="L56:M56"/>
+    <mergeCell ref="N25:O25"/>
+    <mergeCell ref="L25:M26"/>
+    <mergeCell ref="D14:D15"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="Q31:R31"/>
+    <mergeCell ref="E60:F60"/>
+    <mergeCell ref="L59:M59"/>
+    <mergeCell ref="B32:K33"/>
+    <mergeCell ref="L46:M46"/>
+    <mergeCell ref="B53:B61"/>
+    <mergeCell ref="D38:D39"/>
+    <mergeCell ref="M34:M35"/>
+    <mergeCell ref="M32:M33"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="M36:M37"/>
+    <mergeCell ref="M30:M31"/>
+    <mergeCell ref="B16:C17"/>
+    <mergeCell ref="E37:G37"/>
+    <mergeCell ref="L16:R19"/>
+    <mergeCell ref="E29:K30"/>
+    <mergeCell ref="Q33:R33"/>
+    <mergeCell ref="B22:C24"/>
+    <mergeCell ref="E16:I19"/>
+    <mergeCell ref="N33:O33"/>
+    <mergeCell ref="B14:C15"/>
+    <mergeCell ref="N37:O37"/>
+    <mergeCell ref="L20:U20"/>
+    <mergeCell ref="Q26:R26"/>
+    <mergeCell ref="Q34:R34"/>
+    <mergeCell ref="L30:L41"/>
+    <mergeCell ref="R48:T48"/>
+    <mergeCell ref="Q27:R27"/>
+    <mergeCell ref="N31:O31"/>
+    <mergeCell ref="N40:O40"/>
+    <mergeCell ref="J20:K24"/>
+    <mergeCell ref="E31:K31"/>
+    <mergeCell ref="B20:C21"/>
+    <mergeCell ref="E20:I24"/>
+    <mergeCell ref="M40:M41"/>
+    <mergeCell ref="Q39:R39"/>
+    <mergeCell ref="B25:D26"/>
+    <mergeCell ref="J16:K19"/>
+    <mergeCell ref="Q29:R29"/>
+    <mergeCell ref="B27:D28"/>
+    <mergeCell ref="Q32:R32"/>
+    <mergeCell ref="N29:O29"/>
+    <mergeCell ref="N38:O38"/>
+    <mergeCell ref="D20:D21"/>
+    <mergeCell ref="R50:T50"/>
+    <mergeCell ref="N35:O35"/>
+    <mergeCell ref="I12:J15"/>
+    <mergeCell ref="R53:T55"/>
+    <mergeCell ref="Q35:R35"/>
+    <mergeCell ref="N39:O39"/>
+    <mergeCell ref="R46:T46"/>
+    <mergeCell ref="D22:D24"/>
+    <mergeCell ref="E49:F49"/>
+    <mergeCell ref="N41:O41"/>
+    <mergeCell ref="H40:I40"/>
+    <mergeCell ref="L47:M47"/>
+    <mergeCell ref="E40:G40"/>
+    <mergeCell ref="R45:T45"/>
+    <mergeCell ref="P53:P55"/>
+    <mergeCell ref="E45:F45"/>
+    <mergeCell ref="Q40:R40"/>
+    <mergeCell ref="J53:J55"/>
+    <mergeCell ref="N53:N55"/>
+    <mergeCell ref="L50:M50"/>
+    <mergeCell ref="Q28:R28"/>
+    <mergeCell ref="Q37:R37"/>
+    <mergeCell ref="E12:H15"/>
+    <mergeCell ref="D12:D13"/>
     <mergeCell ref="U42:U44"/>
     <mergeCell ref="R42:T44"/>
     <mergeCell ref="L22:U24"/>
@@ -4782,149 +4922,6 @@
     <mergeCell ref="N32:O32"/>
     <mergeCell ref="Q41:R41"/>
     <mergeCell ref="Q25:R25"/>
-    <mergeCell ref="R50:T50"/>
-    <mergeCell ref="N35:O35"/>
-    <mergeCell ref="I12:J15"/>
-    <mergeCell ref="R53:T55"/>
-    <mergeCell ref="Q35:R35"/>
-    <mergeCell ref="N39:O39"/>
-    <mergeCell ref="R46:T46"/>
-    <mergeCell ref="D22:D24"/>
-    <mergeCell ref="E49:F49"/>
-    <mergeCell ref="N41:O41"/>
-    <mergeCell ref="H40:I40"/>
-    <mergeCell ref="L47:M47"/>
-    <mergeCell ref="E40:G40"/>
-    <mergeCell ref="R45:T45"/>
-    <mergeCell ref="P53:P55"/>
-    <mergeCell ref="E45:F45"/>
-    <mergeCell ref="Q40:R40"/>
-    <mergeCell ref="J53:J55"/>
-    <mergeCell ref="N53:N55"/>
-    <mergeCell ref="L50:M50"/>
-    <mergeCell ref="Q28:R28"/>
-    <mergeCell ref="Q37:R37"/>
-    <mergeCell ref="E12:H15"/>
-    <mergeCell ref="D12:D13"/>
-    <mergeCell ref="B14:C15"/>
-    <mergeCell ref="N37:O37"/>
-    <mergeCell ref="L20:U20"/>
-    <mergeCell ref="Q26:R26"/>
-    <mergeCell ref="Q34:R34"/>
-    <mergeCell ref="L30:L41"/>
-    <mergeCell ref="R48:T48"/>
-    <mergeCell ref="Q27:R27"/>
-    <mergeCell ref="N31:O31"/>
-    <mergeCell ref="N40:O40"/>
-    <mergeCell ref="J20:K24"/>
-    <mergeCell ref="E31:K31"/>
-    <mergeCell ref="B20:C21"/>
-    <mergeCell ref="E20:I24"/>
-    <mergeCell ref="M40:M41"/>
-    <mergeCell ref="Q39:R39"/>
-    <mergeCell ref="B25:D26"/>
-    <mergeCell ref="J16:K19"/>
-    <mergeCell ref="Q29:R29"/>
-    <mergeCell ref="B27:D28"/>
-    <mergeCell ref="Q32:R32"/>
-    <mergeCell ref="N29:O29"/>
-    <mergeCell ref="N38:O38"/>
-    <mergeCell ref="D20:D21"/>
-    <mergeCell ref="N25:O25"/>
-    <mergeCell ref="L25:M26"/>
-    <mergeCell ref="D14:D15"/>
-    <mergeCell ref="D16:D17"/>
-    <mergeCell ref="Q31:R31"/>
-    <mergeCell ref="E60:F60"/>
-    <mergeCell ref="L59:M59"/>
-    <mergeCell ref="B32:K33"/>
-    <mergeCell ref="L46:M46"/>
-    <mergeCell ref="B53:B61"/>
-    <mergeCell ref="D38:D39"/>
-    <mergeCell ref="M34:M35"/>
-    <mergeCell ref="M32:M33"/>
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="M36:M37"/>
-    <mergeCell ref="M30:M31"/>
-    <mergeCell ref="B16:C17"/>
-    <mergeCell ref="E37:G37"/>
-    <mergeCell ref="L16:R19"/>
-    <mergeCell ref="E29:K30"/>
-    <mergeCell ref="Q33:R33"/>
-    <mergeCell ref="B22:C24"/>
-    <mergeCell ref="E16:I19"/>
-    <mergeCell ref="N33:O33"/>
-    <mergeCell ref="L61:M61"/>
-    <mergeCell ref="E58:F58"/>
-    <mergeCell ref="I42:I44"/>
-    <mergeCell ref="L48:M48"/>
-    <mergeCell ref="E50:F50"/>
-    <mergeCell ref="H38:H39"/>
-    <mergeCell ref="E61:F61"/>
-    <mergeCell ref="E59:F59"/>
-    <mergeCell ref="L58:M58"/>
-    <mergeCell ref="E56:F56"/>
-    <mergeCell ref="L60:M60"/>
-    <mergeCell ref="L45:M45"/>
-    <mergeCell ref="G42:H43"/>
-    <mergeCell ref="I53:I55"/>
-    <mergeCell ref="K42:M43"/>
-    <mergeCell ref="E46:F46"/>
-    <mergeCell ref="L57:M57"/>
-    <mergeCell ref="J43:J44"/>
-    <mergeCell ref="E57:F57"/>
-    <mergeCell ref="E48:F48"/>
-    <mergeCell ref="K38:K39"/>
-    <mergeCell ref="M38:M39"/>
-    <mergeCell ref="L56:M56"/>
-    <mergeCell ref="I37:J37"/>
-    <mergeCell ref="B42:B51"/>
-    <mergeCell ref="R51:T51"/>
-    <mergeCell ref="N28:O28"/>
-    <mergeCell ref="N26:O26"/>
-    <mergeCell ref="O54:O55"/>
-    <mergeCell ref="B29:D31"/>
-    <mergeCell ref="B1:C5"/>
-    <mergeCell ref="Q36:R36"/>
-    <mergeCell ref="B18:C19"/>
-    <mergeCell ref="B8:C9"/>
-    <mergeCell ref="N34:O34"/>
-    <mergeCell ref="L49:M49"/>
-    <mergeCell ref="G53:H54"/>
-    <mergeCell ref="N42:N44"/>
-    <mergeCell ref="N27:O27"/>
-    <mergeCell ref="D3:D5"/>
-    <mergeCell ref="E53:F55"/>
-    <mergeCell ref="N36:O36"/>
-    <mergeCell ref="E47:F47"/>
-    <mergeCell ref="E8:F10"/>
-    <mergeCell ref="G8:H10"/>
-    <mergeCell ref="E11:F11"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="D6:D7"/>
-    <mergeCell ref="K8:K11"/>
-    <mergeCell ref="D10:D11"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="D36:K36"/>
-    <mergeCell ref="Q38:R38"/>
-    <mergeCell ref="B6:C7"/>
-    <mergeCell ref="L55:M55"/>
-    <mergeCell ref="O43:O44"/>
-    <mergeCell ref="L51:M51"/>
-    <mergeCell ref="B12:C13"/>
-    <mergeCell ref="K12:K15"/>
-    <mergeCell ref="L27:L29"/>
-    <mergeCell ref="B34:K35"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="D18:D19"/>
-    <mergeCell ref="D8:D9"/>
-    <mergeCell ref="I6:J6"/>
-    <mergeCell ref="I7:J7"/>
-    <mergeCell ref="E6:H7"/>
-    <mergeCell ref="B10:C11"/>
-    <mergeCell ref="I8:J11"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="3.9370078740157501E-2" right="3.9370078740157501E-2" top="0.35433070866141703" bottom="0.35433070866141703" header="0.118110236220472" footer="0.118110236220472"/>

--- a/jo.xlsx
+++ b/jo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\production_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A83697A5-ED97-4BC9-9D27-8C826F9A4402}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FF455FB-0E91-4303-A212-CA524C2AACE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -406,7 +406,7 @@
     <numFmt numFmtId="167" formatCode="&quot; &quot;#,##0&quot; &quot;;&quot; (&quot;#,##0&quot;)&quot;;&quot; - &quot;;@&quot; &quot;"/>
     <numFmt numFmtId="168" formatCode="[$-402]0%"/>
   </numFmts>
-  <fonts count="72">
+  <fonts count="74">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -919,6 +919,19 @@
     </font>
     <font>
       <sz val="28"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="16"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
@@ -2623,6 +2636,12 @@
     <xf numFmtId="0" fontId="34" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="3" fontId="72" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="73" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="14" fontId="17" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2655,12 +2674,6 @@
     </xf>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="41" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="29">
@@ -3119,13 +3132,13 @@
       </c>
       <c r="C6" s="146"/>
       <c r="D6" s="295"/>
-      <c r="E6" s="313" t="s">
+      <c r="E6" s="315" t="s">
         <v>6</v>
       </c>
       <c r="F6" s="145"/>
       <c r="G6" s="145"/>
       <c r="H6" s="146"/>
-      <c r="I6" s="311" t="s">
+      <c r="I6" s="313" t="s">
         <v>7</v>
       </c>
       <c r="J6" s="162"/>
@@ -3144,7 +3157,7 @@
       <c r="F7" s="201"/>
       <c r="G7" s="201"/>
       <c r="H7" s="149"/>
-      <c r="I7" s="312"/>
+      <c r="I7" s="314"/>
       <c r="J7" s="162"/>
       <c r="K7" s="101"/>
       <c r="L7" s="127"/>
@@ -3157,7 +3170,7 @@
         <v>10</v>
       </c>
       <c r="C8" s="146"/>
-      <c r="D8" s="310"/>
+      <c r="D8" s="312"/>
       <c r="E8" s="279" t="s">
         <v>101</v>
       </c>
@@ -3166,10 +3179,10 @@
         <v>100</v>
       </c>
       <c r="H8" s="286"/>
-      <c r="I8" s="315" t="s">
+      <c r="I8" s="317" t="s">
         <v>103</v>
       </c>
-      <c r="J8" s="316"/>
+      <c r="J8" s="318"/>
       <c r="K8" s="296"/>
       <c r="L8" s="127"/>
       <c r="P8" s="131"/>
@@ -3184,8 +3197,8 @@
       <c r="F9" s="282"/>
       <c r="G9" s="287"/>
       <c r="H9" s="288"/>
-      <c r="I9" s="317"/>
-      <c r="J9" s="318"/>
+      <c r="I9" s="319"/>
+      <c r="J9" s="320"/>
       <c r="K9" s="297"/>
       <c r="L9" s="127"/>
       <c r="P9" s="131" t="str">
@@ -3196,7 +3209,7 @@
       <c r="V9" s="165"/>
     </row>
     <row r="10" spans="1:22" s="2" customFormat="1" ht="15" customHeight="1">
-      <c r="B10" s="314" t="s">
+      <c r="B10" s="316" t="s">
         <v>11</v>
       </c>
       <c r="C10" s="146"/>
@@ -3205,8 +3218,8 @@
       <c r="F10" s="284"/>
       <c r="G10" s="289"/>
       <c r="H10" s="290"/>
-      <c r="I10" s="317"/>
-      <c r="J10" s="318"/>
+      <c r="I10" s="319"/>
+      <c r="J10" s="320"/>
       <c r="K10" s="297"/>
       <c r="L10" s="127"/>
       <c r="P10" s="131"/>
@@ -3221,8 +3234,8 @@
       <c r="F11" s="292"/>
       <c r="G11" s="293"/>
       <c r="H11" s="294"/>
-      <c r="I11" s="319"/>
-      <c r="J11" s="320"/>
+      <c r="I11" s="321"/>
+      <c r="J11" s="322"/>
       <c r="K11" s="298"/>
       <c r="L11" s="127"/>
       <c r="M11" s="132" t="str">
@@ -3376,7 +3389,7 @@
         <v>17</v>
       </c>
       <c r="C18" s="146"/>
-      <c r="D18" s="321"/>
+      <c r="D18" s="310"/>
       <c r="E18" s="147"/>
       <c r="F18" s="148"/>
       <c r="G18" s="148"/>
@@ -3399,7 +3412,7 @@
     <row r="19" spans="2:22" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="B19" s="228"/>
       <c r="C19" s="152"/>
-      <c r="D19" s="322"/>
+      <c r="D19" s="311"/>
       <c r="E19" s="150"/>
       <c r="F19" s="151"/>
       <c r="G19" s="151"/>
